--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU12"/>
+  <dimension ref="A1:AU64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,12 +751,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G3">
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-10-28 13:00:00</t>
+          <t>2026-10-28 11:00:00</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G4">
@@ -957,7 +957,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N4">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-10-28 13:00:00</t>
+          <t>2026-10-28 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-10-28 13:00:00</t>
+          <t>2026-10-28 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G6">
@@ -1283,68 +1283,68 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -1566,27 +1566,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.28</v>
+        <v>2.35</v>
       </c>
       <c r="O8">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="P8">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-10-28 14:30:00</t>
+          <t>2026-10-28 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>6.07</v>
+        <v>0</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-10-28 14:30:00</t>
+          <t>2026-10-28 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1984,10 +1984,10 @@
         <v>0</v>
       </c>
       <c r="AC10">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-10-28 14:30:00</t>
+          <t>2026-10-28 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-10-28 16:45:00</t>
+          <t>2026-10-28 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2218,158 +2218,8634 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Montenegro Montenegrin First League</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sutjeska</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>FK Jezero Plav</t>
+        </is>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>-1</v>
+      </c>
+      <c r="AN12">
+        <v>-1</v>
+      </c>
+      <c r="AO12">
+        <v>-1</v>
+      </c>
+      <c r="AP12">
+        <v>-1</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2026-10-28 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Montenegro Montenegrin First League</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Petrovac</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mladost DG</t>
+        </is>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>-1</v>
+      </c>
+      <c r="AN13">
+        <v>-1</v>
+      </c>
+      <c r="AO13">
+        <v>-1</v>
+      </c>
+      <c r="AP13">
+        <v>-1</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2026-10-28 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Atalanta II</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vis Pesaro</t>
+        </is>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>-1</v>
+      </c>
+      <c r="AN14">
+        <v>-1</v>
+      </c>
+      <c r="AO14">
+        <v>-1</v>
+      </c>
+      <c r="AP14">
+        <v>-1</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Zamalek</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Al Mokawloon</t>
+        </is>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>-1</v>
+      </c>
+      <c r="AN15">
+        <v>-1</v>
+      </c>
+      <c r="AO15">
+        <v>-1</v>
+      </c>
+      <c r="AP15">
+        <v>-1</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Estonia Meistriliiga</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Paide</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nõmme Kalju</t>
+        </is>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N16">
+        <v>2.29</v>
+      </c>
+      <c r="O16">
+        <v>3.5</v>
+      </c>
+      <c r="P16">
+        <v>2.73</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>-1</v>
+      </c>
+      <c r="AN16">
+        <v>-1</v>
+      </c>
+      <c r="AO16">
+        <v>-1</v>
+      </c>
+      <c r="AP16">
+        <v>-1</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N17">
+        <v>3.28</v>
+      </c>
+      <c r="O17">
+        <v>3.45</v>
+      </c>
+      <c r="P17">
+        <v>2.38</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>-1</v>
+      </c>
+      <c r="AN17">
+        <v>-1</v>
+      </c>
+      <c r="AO17">
+        <v>-1</v>
+      </c>
+      <c r="AP17">
+        <v>-1</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Inter Milan</t>
+        </is>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N18">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="O18">
+        <v>6.33</v>
+      </c>
+      <c r="P18">
+        <v>1.35</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>1.85</v>
+      </c>
+      <c r="AD18">
+        <v>2</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>-1</v>
+      </c>
+      <c r="AN18">
+        <v>-1</v>
+      </c>
+      <c r="AO18">
+        <v>-1</v>
+      </c>
+      <c r="AP18">
+        <v>-1</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N19">
+        <v>1.61</v>
+      </c>
+      <c r="O19">
+        <v>4.38</v>
+      </c>
+      <c r="P19">
+        <v>6.07</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>1.81</v>
+      </c>
+      <c r="AB19">
+        <v>2</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>-1</v>
+      </c>
+      <c r="AN19">
+        <v>-1</v>
+      </c>
+      <c r="AO19">
+        <v>-1</v>
+      </c>
+      <c r="AP19">
+        <v>-1</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-1</v>
+      </c>
+      <c r="AN20">
+        <v>-1</v>
+      </c>
+      <c r="AO20">
+        <v>-1</v>
+      </c>
+      <c r="AP20">
+        <v>-1</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sweden Allsvenskan</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Häcken</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>-1</v>
+      </c>
+      <c r="AN21">
+        <v>-1</v>
+      </c>
+      <c r="AO21">
+        <v>-1</v>
+      </c>
+      <c r="AP21">
+        <v>-1</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Sweden Allsvenskan</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Malmö FF</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>-1</v>
+      </c>
+      <c r="AN22">
+        <v>-1</v>
+      </c>
+      <c r="AO22">
+        <v>-1</v>
+      </c>
+      <c r="AP22">
+        <v>-1</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Sweden Allsvenskan</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Västerås SK</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>-1</v>
+      </c>
+      <c r="AN23">
+        <v>-1</v>
+      </c>
+      <c r="AO23">
+        <v>-1</v>
+      </c>
+      <c r="AP23">
+        <v>-1</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Sweden Allsvenskan</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Djurgården</t>
+        </is>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>-1</v>
+      </c>
+      <c r="AN24">
+        <v>-1</v>
+      </c>
+      <c r="AO24">
+        <v>-1</v>
+      </c>
+      <c r="AP24">
+        <v>-1</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Slovenia PrvaLiga</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Olimpija</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Celje</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N25">
+        <v>2.63</v>
+      </c>
+      <c r="O25">
+        <v>3.25</v>
+      </c>
+      <c r="P25">
+        <v>2.3</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>-1</v>
+      </c>
+      <c r="AN25">
+        <v>-1</v>
+      </c>
+      <c r="AO25">
+        <v>-1</v>
+      </c>
+      <c r="AP25">
+        <v>-1</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Carrarese</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Arezzo</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>-1</v>
+      </c>
+      <c r="AN26">
+        <v>-1</v>
+      </c>
+      <c r="AO26">
+        <v>-1</v>
+      </c>
+      <c r="AP26">
+        <v>-1</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Juve Stabia</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Hellas Verona</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-1</v>
+      </c>
+      <c r="AN27">
+        <v>-1</v>
+      </c>
+      <c r="AO27">
+        <v>-1</v>
+      </c>
+      <c r="AP27">
+        <v>-1</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Neftchi</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bunyodkor</t>
+        </is>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>-1</v>
+      </c>
+      <c r="AN28">
+        <v>-1</v>
+      </c>
+      <c r="AO28">
+        <v>-1</v>
+      </c>
+      <c r="AP28">
+        <v>-1</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>16:45</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Dundee</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kilmarnock</t>
+        </is>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N29">
+        <v>1.92</v>
+      </c>
+      <c r="O29">
+        <v>3.66</v>
+      </c>
+      <c r="P29">
+        <v>3.62</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>-1</v>
+      </c>
+      <c r="AN29">
+        <v>-1</v>
+      </c>
+      <c r="AO29">
+        <v>-1</v>
+      </c>
+      <c r="AP29">
+        <v>-1</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N30">
+        <v>1.28</v>
+      </c>
+      <c r="O30">
+        <v>5.7</v>
+      </c>
+      <c r="P30">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>-1</v>
+      </c>
+      <c r="AN30">
+        <v>-1</v>
+      </c>
+      <c r="AO30">
+        <v>-1</v>
+      </c>
+      <c r="AP30">
+        <v>-1</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>St. Johnstone</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Motherwell</t>
+        </is>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N31">
+        <v>2.25</v>
+      </c>
+      <c r="O31">
+        <v>3.42</v>
+      </c>
+      <c r="P31">
+        <v>3</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>1.88</v>
+      </c>
+      <c r="AB31">
+        <v>1.98</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>0</v>
+      </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>-1</v>
+      </c>
+      <c r="AN31">
+        <v>-1</v>
+      </c>
+      <c r="AO31">
+        <v>-1</v>
+      </c>
+      <c r="AP31">
+        <v>-1</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Falkirk</t>
+        </is>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N32">
+        <v>1.95</v>
+      </c>
+      <c r="O32">
+        <v>3.55</v>
+      </c>
+      <c r="P32">
+        <v>3.64</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>1.88</v>
+      </c>
+      <c r="AB32">
+        <v>1.98</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>-1</v>
+      </c>
+      <c r="AN32">
+        <v>-1</v>
+      </c>
+      <c r="AO32">
+        <v>-1</v>
+      </c>
+      <c r="AP32">
+        <v>-1</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>St. Mirren</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N33">
+        <v>3.44</v>
+      </c>
+      <c r="O33">
+        <v>3.62</v>
+      </c>
+      <c r="P33">
+        <v>1.99</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
+        <v>0</v>
+      </c>
+      <c r="AK33">
+        <v>0</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>-1</v>
+      </c>
+      <c r="AN33">
+        <v>-1</v>
+      </c>
+      <c r="AO33">
+        <v>-1</v>
+      </c>
+      <c r="AP33">
+        <v>-1</v>
+      </c>
+      <c r="AQ33">
+        <v>0</v>
+      </c>
+      <c r="AR33">
+        <v>0</v>
+      </c>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Italy Serie A</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N34">
+        <v>4.22</v>
+      </c>
+      <c r="O34">
+        <v>3.95</v>
+      </c>
+      <c r="P34">
+        <v>1.9</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>-1</v>
+      </c>
+      <c r="AN34">
+        <v>-1</v>
+      </c>
+      <c r="AO34">
+        <v>-1</v>
+      </c>
+      <c r="AP34">
+        <v>-1</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>Genoa</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Juventus</t>
         </is>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N12">
+      <c r="N35">
         <v>5.61</v>
       </c>
-      <c r="O12">
+      <c r="O35">
         <v>4.02</v>
       </c>
-      <c r="P12">
+      <c r="P35">
         <v>1.7</v>
       </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>0</v>
-      </c>
-      <c r="Y12">
-        <v>0</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
         <v>1.84</v>
       </c>
-      <c r="AB12">
+      <c r="AB35">
         <v>1.97</v>
       </c>
-      <c r="AC12">
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>0</v>
-      </c>
-      <c r="AG12">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>0</v>
-      </c>
-      <c r="AK12">
-        <v>0</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>-1</v>
-      </c>
-      <c r="AN12">
-        <v>-1</v>
-      </c>
-      <c r="AO12">
-        <v>-1</v>
-      </c>
-      <c r="AP12">
-        <v>-1</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0</v>
+      </c>
+      <c r="AG35">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>0</v>
+      </c>
+      <c r="AK35">
+        <v>0</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>-1</v>
+      </c>
+      <c r="AN35">
+        <v>-1</v>
+      </c>
+      <c r="AO35">
+        <v>-1</v>
+      </c>
+      <c r="AP35">
+        <v>-1</v>
+      </c>
+      <c r="AQ35">
+        <v>0</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
         <is>
           <t>2026-10-28 16:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Hearts</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N36">
+        <v>3.13</v>
+      </c>
+      <c r="O36">
+        <v>3.58</v>
+      </c>
+      <c r="P36">
+        <v>2.12</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+      <c r="AG36">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>0</v>
+      </c>
+      <c r="AK36">
+        <v>0</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>-1</v>
+      </c>
+      <c r="AN36">
+        <v>-1</v>
+      </c>
+      <c r="AO36">
+        <v>-1</v>
+      </c>
+      <c r="AP36">
+        <v>-1</v>
+      </c>
+      <c r="AQ36">
+        <v>0</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>0</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>2026-10-28 17:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N37">
+        <v>1.98</v>
+      </c>
+      <c r="O37">
+        <v>3.51</v>
+      </c>
+      <c r="P37">
+        <v>3.96</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>0</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
+        <v>0</v>
+      </c>
+      <c r="AK37">
+        <v>0</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>-1</v>
+      </c>
+      <c r="AN37">
+        <v>-1</v>
+      </c>
+      <c r="AO37">
+        <v>-1</v>
+      </c>
+      <c r="AP37">
+        <v>-1</v>
+      </c>
+      <c r="AQ37">
+        <v>0</v>
+      </c>
+      <c r="AR37">
+        <v>0</v>
+      </c>
+      <c r="AS37">
+        <v>0</v>
+      </c>
+      <c r="AT37">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>2026-10-28 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N38">
+        <v>1.31</v>
+      </c>
+      <c r="O38">
+        <v>5.56</v>
+      </c>
+      <c r="P38">
+        <v>10.2</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
+      </c>
+      <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
+        <v>0</v>
+      </c>
+      <c r="AK38">
+        <v>0</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>-1</v>
+      </c>
+      <c r="AN38">
+        <v>-1</v>
+      </c>
+      <c r="AO38">
+        <v>-1</v>
+      </c>
+      <c r="AP38">
+        <v>-1</v>
+      </c>
+      <c r="AQ38">
+        <v>0</v>
+      </c>
+      <c r="AR38">
+        <v>0</v>
+      </c>
+      <c r="AS38">
+        <v>0</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>2026-10-28 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N39">
+        <v>2.99</v>
+      </c>
+      <c r="O39">
+        <v>3.43</v>
+      </c>
+      <c r="P39">
+        <v>2.41</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <v>0</v>
+      </c>
+      <c r="AD39">
+        <v>0</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>0</v>
+      </c>
+      <c r="AG39">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>0</v>
+      </c>
+      <c r="AK39">
+        <v>0</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39">
+        <v>-1</v>
+      </c>
+      <c r="AN39">
+        <v>-1</v>
+      </c>
+      <c r="AO39">
+        <v>-1</v>
+      </c>
+      <c r="AP39">
+        <v>-1</v>
+      </c>
+      <c r="AQ39">
+        <v>0</v>
+      </c>
+      <c r="AR39">
+        <v>0</v>
+      </c>
+      <c r="AS39">
+        <v>0</v>
+      </c>
+      <c r="AT39">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>2026-10-28 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Universidad Católica</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N40">
+        <v>1.53</v>
+      </c>
+      <c r="O40">
+        <v>3.95</v>
+      </c>
+      <c r="P40">
+        <v>5.56</v>
+      </c>
+      <c r="Q40">
+        <v>2.04</v>
+      </c>
+      <c r="R40">
+        <v>2.4</v>
+      </c>
+      <c r="S40">
+        <v>1.29</v>
+      </c>
+      <c r="T40">
+        <v>3.3</v>
+      </c>
+      <c r="U40">
+        <v>2.38</v>
+      </c>
+      <c r="V40">
+        <v>1.53</v>
+      </c>
+      <c r="W40">
+        <v>1.11</v>
+      </c>
+      <c r="X40">
+        <v>1.02</v>
+      </c>
+      <c r="Y40">
+        <v>1.24</v>
+      </c>
+      <c r="Z40">
+        <v>3.85</v>
+      </c>
+      <c r="AA40">
+        <v>1.78</v>
+      </c>
+      <c r="AB40">
+        <v>2</v>
+      </c>
+      <c r="AC40">
+        <v>2.66</v>
+      </c>
+      <c r="AD40">
+        <v>1.37</v>
+      </c>
+      <c r="AE40">
+        <v>1.15</v>
+      </c>
+      <c r="AF40">
+        <v>1.8</v>
+      </c>
+      <c r="AG40">
+        <v>1.92</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
+        <v>1.17</v>
+      </c>
+      <c r="AK40">
+        <v>2.38</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>-1</v>
+      </c>
+      <c r="AN40">
+        <v>-1</v>
+      </c>
+      <c r="AO40">
+        <v>-1</v>
+      </c>
+      <c r="AP40">
+        <v>-1</v>
+      </c>
+      <c r="AQ40">
+        <v>0</v>
+      </c>
+      <c r="AR40">
+        <v>0</v>
+      </c>
+      <c r="AS40">
+        <v>0</v>
+      </c>
+      <c r="AT40">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>2026-10-28 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+      <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41">
+        <v>0</v>
+      </c>
+      <c r="AC41">
+        <v>0</v>
+      </c>
+      <c r="AD41">
+        <v>0</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>0</v>
+      </c>
+      <c r="AG41">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>0</v>
+      </c>
+      <c r="AK41">
+        <v>0</v>
+      </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
+      <c r="AM41">
+        <v>-1</v>
+      </c>
+      <c r="AN41">
+        <v>-1</v>
+      </c>
+      <c r="AO41">
+        <v>-1</v>
+      </c>
+      <c r="AP41">
+        <v>-1</v>
+      </c>
+      <c r="AQ41">
+        <v>0</v>
+      </c>
+      <c r="AR41">
+        <v>0</v>
+      </c>
+      <c r="AS41">
+        <v>0</v>
+      </c>
+      <c r="AT41">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>2026-10-28 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Montreal Impact</t>
+        </is>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+      <c r="AD42">
+        <v>0</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>0</v>
+      </c>
+      <c r="AG42">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <v>0</v>
+      </c>
+      <c r="AK42">
+        <v>0</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>-1</v>
+      </c>
+      <c r="AN42">
+        <v>-1</v>
+      </c>
+      <c r="AO42">
+        <v>-1</v>
+      </c>
+      <c r="AP42">
+        <v>-1</v>
+      </c>
+      <c r="AQ42">
+        <v>0</v>
+      </c>
+      <c r="AR42">
+        <v>0</v>
+      </c>
+      <c r="AS42">
+        <v>0</v>
+      </c>
+      <c r="AT42">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>2026-10-28 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Atlanta United FC</t>
+        </is>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
+      <c r="AB43">
+        <v>0</v>
+      </c>
+      <c r="AC43">
+        <v>0</v>
+      </c>
+      <c r="AD43">
+        <v>0</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>0</v>
+      </c>
+      <c r="AG43">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <v>0</v>
+      </c>
+      <c r="AK43">
+        <v>0</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>-1</v>
+      </c>
+      <c r="AN43">
+        <v>-1</v>
+      </c>
+      <c r="AO43">
+        <v>-1</v>
+      </c>
+      <c r="AP43">
+        <v>-1</v>
+      </c>
+      <c r="AQ43">
+        <v>0</v>
+      </c>
+      <c r="AR43">
+        <v>0</v>
+      </c>
+      <c r="AS43">
+        <v>0</v>
+      </c>
+      <c r="AT43">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>2026-10-28 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <v>0</v>
+      </c>
+      <c r="AB44">
+        <v>0</v>
+      </c>
+      <c r="AC44">
+        <v>0</v>
+      </c>
+      <c r="AD44">
+        <v>0</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>0</v>
+      </c>
+      <c r="AG44">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
+        <v>0</v>
+      </c>
+      <c r="AK44">
+        <v>0</v>
+      </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
+      <c r="AM44">
+        <v>-1</v>
+      </c>
+      <c r="AN44">
+        <v>-1</v>
+      </c>
+      <c r="AO44">
+        <v>-1</v>
+      </c>
+      <c r="AP44">
+        <v>-1</v>
+      </c>
+      <c r="AQ44">
+        <v>0</v>
+      </c>
+      <c r="AR44">
+        <v>0</v>
+      </c>
+      <c r="AS44">
+        <v>0</v>
+      </c>
+      <c r="AT44">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>2026-10-28 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>New York RB</t>
+        </is>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <v>0</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+      <c r="AA45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
+        <v>0</v>
+      </c>
+      <c r="AC45">
+        <v>0</v>
+      </c>
+      <c r="AD45">
+        <v>0</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>0</v>
+      </c>
+      <c r="AG45">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
+        <v>0</v>
+      </c>
+      <c r="AK45">
+        <v>0</v>
+      </c>
+      <c r="AL45">
+        <v>0</v>
+      </c>
+      <c r="AM45">
+        <v>-1</v>
+      </c>
+      <c r="AN45">
+        <v>-1</v>
+      </c>
+      <c r="AO45">
+        <v>-1</v>
+      </c>
+      <c r="AP45">
+        <v>-1</v>
+      </c>
+      <c r="AQ45">
+        <v>0</v>
+      </c>
+      <c r="AR45">
+        <v>0</v>
+      </c>
+      <c r="AS45">
+        <v>0</v>
+      </c>
+      <c r="AT45">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>2026-10-28 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>CS Constantine</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ben Aknoun</t>
+        </is>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+      <c r="AA46">
+        <v>0</v>
+      </c>
+      <c r="AB46">
+        <v>0</v>
+      </c>
+      <c r="AC46">
+        <v>0</v>
+      </c>
+      <c r="AD46">
+        <v>0</v>
+      </c>
+      <c r="AE46">
+        <v>0</v>
+      </c>
+      <c r="AF46">
+        <v>0</v>
+      </c>
+      <c r="AG46">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
+        <v>0</v>
+      </c>
+      <c r="AK46">
+        <v>0</v>
+      </c>
+      <c r="AL46">
+        <v>0</v>
+      </c>
+      <c r="AM46">
+        <v>-1</v>
+      </c>
+      <c r="AN46">
+        <v>-1</v>
+      </c>
+      <c r="AO46">
+        <v>-1</v>
+      </c>
+      <c r="AP46">
+        <v>-1</v>
+      </c>
+      <c r="AQ46">
+        <v>0</v>
+      </c>
+      <c r="AR46">
+        <v>0</v>
+      </c>
+      <c r="AS46">
+        <v>0</v>
+      </c>
+      <c r="AT46">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Temouchent</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>JS El Biar</t>
+        </is>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+      <c r="AA47">
+        <v>0</v>
+      </c>
+      <c r="AB47">
+        <v>0</v>
+      </c>
+      <c r="AC47">
+        <v>0</v>
+      </c>
+      <c r="AD47">
+        <v>0</v>
+      </c>
+      <c r="AE47">
+        <v>0</v>
+      </c>
+      <c r="AF47">
+        <v>0</v>
+      </c>
+      <c r="AG47">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
+        <v>0</v>
+      </c>
+      <c r="AK47">
+        <v>0</v>
+      </c>
+      <c r="AL47">
+        <v>0</v>
+      </c>
+      <c r="AM47">
+        <v>-1</v>
+      </c>
+      <c r="AN47">
+        <v>-1</v>
+      </c>
+      <c r="AO47">
+        <v>-1</v>
+      </c>
+      <c r="AP47">
+        <v>-1</v>
+      </c>
+      <c r="AQ47">
+        <v>0</v>
+      </c>
+      <c r="AR47">
+        <v>0</v>
+      </c>
+      <c r="AS47">
+        <v>0</v>
+      </c>
+      <c r="AT47">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>JS Kabylie</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>USM Alger</t>
+        </is>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <v>0</v>
+      </c>
+      <c r="AC48">
+        <v>0</v>
+      </c>
+      <c r="AD48">
+        <v>0</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>0</v>
+      </c>
+      <c r="AG48">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>0</v>
+      </c>
+      <c r="AK48">
+        <v>0</v>
+      </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
+        <v>-1</v>
+      </c>
+      <c r="AN48">
+        <v>-1</v>
+      </c>
+      <c r="AO48">
+        <v>-1</v>
+      </c>
+      <c r="AP48">
+        <v>-1</v>
+      </c>
+      <c r="AQ48">
+        <v>0</v>
+      </c>
+      <c r="AR48">
+        <v>0</v>
+      </c>
+      <c r="AS48">
+        <v>0</v>
+      </c>
+      <c r="AT48">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ASO Chlef</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>USM Khenchela</t>
+        </is>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>0</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>0</v>
+      </c>
+      <c r="AK49">
+        <v>0</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>-1</v>
+      </c>
+      <c r="AN49">
+        <v>-1</v>
+      </c>
+      <c r="AO49">
+        <v>-1</v>
+      </c>
+      <c r="AP49">
+        <v>-1</v>
+      </c>
+      <c r="AQ49">
+        <v>0</v>
+      </c>
+      <c r="AR49">
+        <v>0</v>
+      </c>
+      <c r="AS49">
+        <v>0</v>
+      </c>
+      <c r="AT49">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>MC Alger</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Oued Akbou</t>
+        </is>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+      <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>0</v>
+      </c>
+      <c r="AC50">
+        <v>0</v>
+      </c>
+      <c r="AD50">
+        <v>0</v>
+      </c>
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>0</v>
+      </c>
+      <c r="AG50">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>0</v>
+      </c>
+      <c r="AK50">
+        <v>0</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>-1</v>
+      </c>
+      <c r="AN50">
+        <v>-1</v>
+      </c>
+      <c r="AO50">
+        <v>-1</v>
+      </c>
+      <c r="AP50">
+        <v>-1</v>
+      </c>
+      <c r="AQ50">
+        <v>0</v>
+      </c>
+      <c r="AR50">
+        <v>0</v>
+      </c>
+      <c r="AS50">
+        <v>0</v>
+      </c>
+      <c r="AT50">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ES Sétif</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>US Biskra</t>
+        </is>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <v>0</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+      <c r="AA51">
+        <v>0</v>
+      </c>
+      <c r="AB51">
+        <v>0</v>
+      </c>
+      <c r="AC51">
+        <v>0</v>
+      </c>
+      <c r="AD51">
+        <v>0</v>
+      </c>
+      <c r="AE51">
+        <v>0</v>
+      </c>
+      <c r="AF51">
+        <v>0</v>
+      </c>
+      <c r="AG51">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>0</v>
+      </c>
+      <c r="AK51">
+        <v>0</v>
+      </c>
+      <c r="AL51">
+        <v>0</v>
+      </c>
+      <c r="AM51">
+        <v>-1</v>
+      </c>
+      <c r="AN51">
+        <v>-1</v>
+      </c>
+      <c r="AO51">
+        <v>-1</v>
+      </c>
+      <c r="AP51">
+        <v>-1</v>
+      </c>
+      <c r="AQ51">
+        <v>0</v>
+      </c>
+      <c r="AR51">
+        <v>0</v>
+      </c>
+      <c r="AS51">
+        <v>0</v>
+      </c>
+      <c r="AT51">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>MB Rouisset</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>CR Belouizdad</t>
+        </is>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0</v>
+      </c>
+      <c r="X52">
+        <v>0</v>
+      </c>
+      <c r="Y52">
+        <v>0</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+      <c r="AA52">
+        <v>0</v>
+      </c>
+      <c r="AB52">
+        <v>0</v>
+      </c>
+      <c r="AC52">
+        <v>0</v>
+      </c>
+      <c r="AD52">
+        <v>0</v>
+      </c>
+      <c r="AE52">
+        <v>0</v>
+      </c>
+      <c r="AF52">
+        <v>0</v>
+      </c>
+      <c r="AG52">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
+        <v>0</v>
+      </c>
+      <c r="AK52">
+        <v>0</v>
+      </c>
+      <c r="AL52">
+        <v>0</v>
+      </c>
+      <c r="AM52">
+        <v>-1</v>
+      </c>
+      <c r="AN52">
+        <v>-1</v>
+      </c>
+      <c r="AO52">
+        <v>-1</v>
+      </c>
+      <c r="AP52">
+        <v>-1</v>
+      </c>
+      <c r="AQ52">
+        <v>0</v>
+      </c>
+      <c r="AR52">
+        <v>0</v>
+      </c>
+      <c r="AS52">
+        <v>0</v>
+      </c>
+      <c r="AT52">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>MC Oran</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>JS Saoura</t>
+        </is>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0</v>
+      </c>
+      <c r="X53">
+        <v>0</v>
+      </c>
+      <c r="Y53">
+        <v>0</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+      <c r="AA53">
+        <v>0</v>
+      </c>
+      <c r="AB53">
+        <v>0</v>
+      </c>
+      <c r="AC53">
+        <v>0</v>
+      </c>
+      <c r="AD53">
+        <v>0</v>
+      </c>
+      <c r="AE53">
+        <v>0</v>
+      </c>
+      <c r="AF53">
+        <v>0</v>
+      </c>
+      <c r="AG53">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
+        <v>0</v>
+      </c>
+      <c r="AK53">
+        <v>0</v>
+      </c>
+      <c r="AL53">
+        <v>0</v>
+      </c>
+      <c r="AM53">
+        <v>-1</v>
+      </c>
+      <c r="AN53">
+        <v>-1</v>
+      </c>
+      <c r="AO53">
+        <v>-1</v>
+      </c>
+      <c r="AP53">
+        <v>-1</v>
+      </c>
+      <c r="AQ53">
+        <v>0</v>
+      </c>
+      <c r="AR53">
+        <v>0</v>
+      </c>
+      <c r="AS53">
+        <v>0</v>
+      </c>
+      <c r="AT53">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N54">
+        <v>2.6</v>
+      </c>
+      <c r="O54">
+        <v>3.61</v>
+      </c>
+      <c r="P54">
+        <v>2.63</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54">
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0</v>
+      </c>
+      <c r="X54">
+        <v>0</v>
+      </c>
+      <c r="Y54">
+        <v>0</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+      <c r="AA54">
+        <v>0</v>
+      </c>
+      <c r="AB54">
+        <v>0</v>
+      </c>
+      <c r="AC54">
+        <v>0</v>
+      </c>
+      <c r="AD54">
+        <v>0</v>
+      </c>
+      <c r="AE54">
+        <v>0</v>
+      </c>
+      <c r="AF54">
+        <v>0</v>
+      </c>
+      <c r="AG54">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ54">
+        <v>0</v>
+      </c>
+      <c r="AK54">
+        <v>0</v>
+      </c>
+      <c r="AL54">
+        <v>0</v>
+      </c>
+      <c r="AM54">
+        <v>-1</v>
+      </c>
+      <c r="AN54">
+        <v>-1</v>
+      </c>
+      <c r="AO54">
+        <v>-1</v>
+      </c>
+      <c r="AP54">
+        <v>-1</v>
+      </c>
+      <c r="AQ54">
+        <v>0</v>
+      </c>
+      <c r="AR54">
+        <v>0</v>
+      </c>
+      <c r="AS54">
+        <v>0</v>
+      </c>
+      <c r="AT54">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N55">
+        <v>2.01</v>
+      </c>
+      <c r="O55">
+        <v>3.53</v>
+      </c>
+      <c r="P55">
+        <v>3.82</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55">
+        <v>0</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0</v>
+      </c>
+      <c r="X55">
+        <v>0</v>
+      </c>
+      <c r="Y55">
+        <v>0</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+      <c r="AA55">
+        <v>2.03</v>
+      </c>
+      <c r="AB55">
+        <v>1.83</v>
+      </c>
+      <c r="AC55">
+        <v>0</v>
+      </c>
+      <c r="AD55">
+        <v>0</v>
+      </c>
+      <c r="AE55">
+        <v>0</v>
+      </c>
+      <c r="AF55">
+        <v>0</v>
+      </c>
+      <c r="AG55">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ55">
+        <v>0</v>
+      </c>
+      <c r="AK55">
+        <v>0</v>
+      </c>
+      <c r="AL55">
+        <v>0</v>
+      </c>
+      <c r="AM55">
+        <v>-1</v>
+      </c>
+      <c r="AN55">
+        <v>-1</v>
+      </c>
+      <c r="AO55">
+        <v>-1</v>
+      </c>
+      <c r="AP55">
+        <v>-1</v>
+      </c>
+      <c r="AQ55">
+        <v>0</v>
+      </c>
+      <c r="AR55">
+        <v>0</v>
+      </c>
+      <c r="AS55">
+        <v>0</v>
+      </c>
+      <c r="AT55">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56">
+        <v>0</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0</v>
+      </c>
+      <c r="X56">
+        <v>0</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+      <c r="AA56">
+        <v>0</v>
+      </c>
+      <c r="AB56">
+        <v>0</v>
+      </c>
+      <c r="AC56">
+        <v>0</v>
+      </c>
+      <c r="AD56">
+        <v>0</v>
+      </c>
+      <c r="AE56">
+        <v>0</v>
+      </c>
+      <c r="AF56">
+        <v>0</v>
+      </c>
+      <c r="AG56">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
+        <v>0</v>
+      </c>
+      <c r="AK56">
+        <v>0</v>
+      </c>
+      <c r="AL56">
+        <v>0</v>
+      </c>
+      <c r="AM56">
+        <v>-1</v>
+      </c>
+      <c r="AN56">
+        <v>-1</v>
+      </c>
+      <c r="AO56">
+        <v>-1</v>
+      </c>
+      <c r="AP56">
+        <v>-1</v>
+      </c>
+      <c r="AQ56">
+        <v>0</v>
+      </c>
+      <c r="AR56">
+        <v>0</v>
+      </c>
+      <c r="AS56">
+        <v>0</v>
+      </c>
+      <c r="AT56">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>0</v>
+      </c>
+      <c r="U57">
+        <v>0</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0</v>
+      </c>
+      <c r="X57">
+        <v>0</v>
+      </c>
+      <c r="Y57">
+        <v>0</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+      <c r="AA57">
+        <v>0</v>
+      </c>
+      <c r="AB57">
+        <v>0</v>
+      </c>
+      <c r="AC57">
+        <v>0</v>
+      </c>
+      <c r="AD57">
+        <v>0</v>
+      </c>
+      <c r="AE57">
+        <v>0</v>
+      </c>
+      <c r="AF57">
+        <v>0</v>
+      </c>
+      <c r="AG57">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
+        <v>0</v>
+      </c>
+      <c r="AK57">
+        <v>0</v>
+      </c>
+      <c r="AL57">
+        <v>0</v>
+      </c>
+      <c r="AM57">
+        <v>-1</v>
+      </c>
+      <c r="AN57">
+        <v>-1</v>
+      </c>
+      <c r="AO57">
+        <v>-1</v>
+      </c>
+      <c r="AP57">
+        <v>-1</v>
+      </c>
+      <c r="AQ57">
+        <v>0</v>
+      </c>
+      <c r="AR57">
+        <v>0</v>
+      </c>
+      <c r="AS57">
+        <v>0</v>
+      </c>
+      <c r="AT57">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0</v>
+      </c>
+      <c r="X58">
+        <v>0</v>
+      </c>
+      <c r="Y58">
+        <v>0</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+      <c r="AA58">
+        <v>0</v>
+      </c>
+      <c r="AB58">
+        <v>0</v>
+      </c>
+      <c r="AC58">
+        <v>0</v>
+      </c>
+      <c r="AD58">
+        <v>0</v>
+      </c>
+      <c r="AE58">
+        <v>0</v>
+      </c>
+      <c r="AF58">
+        <v>0</v>
+      </c>
+      <c r="AG58">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
+        <v>0</v>
+      </c>
+      <c r="AK58">
+        <v>0</v>
+      </c>
+      <c r="AL58">
+        <v>0</v>
+      </c>
+      <c r="AM58">
+        <v>-1</v>
+      </c>
+      <c r="AN58">
+        <v>-1</v>
+      </c>
+      <c r="AO58">
+        <v>-1</v>
+      </c>
+      <c r="AP58">
+        <v>-1</v>
+      </c>
+      <c r="AQ58">
+        <v>0</v>
+      </c>
+      <c r="AR58">
+        <v>0</v>
+      </c>
+      <c r="AS58">
+        <v>0</v>
+      </c>
+      <c r="AT58">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Sporting KC</t>
+        </is>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <v>0</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0</v>
+      </c>
+      <c r="X59">
+        <v>0</v>
+      </c>
+      <c r="Y59">
+        <v>0</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+      <c r="AA59">
+        <v>0</v>
+      </c>
+      <c r="AB59">
+        <v>0</v>
+      </c>
+      <c r="AC59">
+        <v>0</v>
+      </c>
+      <c r="AD59">
+        <v>0</v>
+      </c>
+      <c r="AE59">
+        <v>0</v>
+      </c>
+      <c r="AF59">
+        <v>0</v>
+      </c>
+      <c r="AG59">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ59">
+        <v>0</v>
+      </c>
+      <c r="AK59">
+        <v>0</v>
+      </c>
+      <c r="AL59">
+        <v>0</v>
+      </c>
+      <c r="AM59">
+        <v>-1</v>
+      </c>
+      <c r="AN59">
+        <v>-1</v>
+      </c>
+      <c r="AO59">
+        <v>-1</v>
+      </c>
+      <c r="AP59">
+        <v>-1</v>
+      </c>
+      <c r="AQ59">
+        <v>0</v>
+      </c>
+      <c r="AR59">
+        <v>0</v>
+      </c>
+      <c r="AS59">
+        <v>0</v>
+      </c>
+      <c r="AT59">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>0</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="T60">
+        <v>0</v>
+      </c>
+      <c r="U60">
+        <v>0</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>0</v>
+      </c>
+      <c r="X60">
+        <v>0</v>
+      </c>
+      <c r="Y60">
+        <v>0</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+      <c r="AA60">
+        <v>0</v>
+      </c>
+      <c r="AB60">
+        <v>0</v>
+      </c>
+      <c r="AC60">
+        <v>0</v>
+      </c>
+      <c r="AD60">
+        <v>0</v>
+      </c>
+      <c r="AE60">
+        <v>0</v>
+      </c>
+      <c r="AF60">
+        <v>0</v>
+      </c>
+      <c r="AG60">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ60">
+        <v>0</v>
+      </c>
+      <c r="AK60">
+        <v>0</v>
+      </c>
+      <c r="AL60">
+        <v>0</v>
+      </c>
+      <c r="AM60">
+        <v>-1</v>
+      </c>
+      <c r="AN60">
+        <v>-1</v>
+      </c>
+      <c r="AO60">
+        <v>-1</v>
+      </c>
+      <c r="AP60">
+        <v>-1</v>
+      </c>
+      <c r="AQ60">
+        <v>0</v>
+      </c>
+      <c r="AR60">
+        <v>0</v>
+      </c>
+      <c r="AS60">
+        <v>0</v>
+      </c>
+      <c r="AT60">
+        <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>0</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>0</v>
+      </c>
+      <c r="T61">
+        <v>0</v>
+      </c>
+      <c r="U61">
+        <v>0</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <v>0</v>
+      </c>
+      <c r="X61">
+        <v>0</v>
+      </c>
+      <c r="Y61">
+        <v>0</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+      <c r="AA61">
+        <v>0</v>
+      </c>
+      <c r="AB61">
+        <v>0</v>
+      </c>
+      <c r="AC61">
+        <v>0</v>
+      </c>
+      <c r="AD61">
+        <v>0</v>
+      </c>
+      <c r="AE61">
+        <v>0</v>
+      </c>
+      <c r="AF61">
+        <v>0</v>
+      </c>
+      <c r="AG61">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ61">
+        <v>0</v>
+      </c>
+      <c r="AK61">
+        <v>0</v>
+      </c>
+      <c r="AL61">
+        <v>0</v>
+      </c>
+      <c r="AM61">
+        <v>-1</v>
+      </c>
+      <c r="AN61">
+        <v>-1</v>
+      </c>
+      <c r="AO61">
+        <v>-1</v>
+      </c>
+      <c r="AP61">
+        <v>-1</v>
+      </c>
+      <c r="AQ61">
+        <v>0</v>
+      </c>
+      <c r="AR61">
+        <v>0</v>
+      </c>
+      <c r="AS61">
+        <v>0</v>
+      </c>
+      <c r="AT61">
+        <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
+        <v>0</v>
+      </c>
+      <c r="T62">
+        <v>0</v>
+      </c>
+      <c r="U62">
+        <v>0</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>0</v>
+      </c>
+      <c r="X62">
+        <v>0</v>
+      </c>
+      <c r="Y62">
+        <v>0</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+      <c r="AA62">
+        <v>0</v>
+      </c>
+      <c r="AB62">
+        <v>0</v>
+      </c>
+      <c r="AC62">
+        <v>0</v>
+      </c>
+      <c r="AD62">
+        <v>0</v>
+      </c>
+      <c r="AE62">
+        <v>0</v>
+      </c>
+      <c r="AF62">
+        <v>0</v>
+      </c>
+      <c r="AG62">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
+        <v>0</v>
+      </c>
+      <c r="AK62">
+        <v>0</v>
+      </c>
+      <c r="AL62">
+        <v>0</v>
+      </c>
+      <c r="AM62">
+        <v>-1</v>
+      </c>
+      <c r="AN62">
+        <v>-1</v>
+      </c>
+      <c r="AO62">
+        <v>-1</v>
+      </c>
+      <c r="AP62">
+        <v>-1</v>
+      </c>
+      <c r="AQ62">
+        <v>0</v>
+      </c>
+      <c r="AR62">
+        <v>0</v>
+      </c>
+      <c r="AS62">
+        <v>0</v>
+      </c>
+      <c r="AT62">
+        <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>2026-10-28 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+      <c r="U63">
+        <v>0</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0</v>
+      </c>
+      <c r="X63">
+        <v>0</v>
+      </c>
+      <c r="Y63">
+        <v>0</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+      <c r="AA63">
+        <v>0</v>
+      </c>
+      <c r="AB63">
+        <v>0</v>
+      </c>
+      <c r="AC63">
+        <v>0</v>
+      </c>
+      <c r="AD63">
+        <v>0</v>
+      </c>
+      <c r="AE63">
+        <v>0</v>
+      </c>
+      <c r="AF63">
+        <v>0</v>
+      </c>
+      <c r="AG63">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
+        <v>0</v>
+      </c>
+      <c r="AK63">
+        <v>0</v>
+      </c>
+      <c r="AL63">
+        <v>0</v>
+      </c>
+      <c r="AM63">
+        <v>-1</v>
+      </c>
+      <c r="AN63">
+        <v>-1</v>
+      </c>
+      <c r="AO63">
+        <v>-1</v>
+      </c>
+      <c r="AP63">
+        <v>-1</v>
+      </c>
+      <c r="AQ63">
+        <v>0</v>
+      </c>
+      <c r="AR63">
+        <v>0</v>
+      </c>
+      <c r="AS63">
+        <v>0</v>
+      </c>
+      <c r="AT63">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>2026-10-28 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>SJ Earthquakes</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0</v>
+      </c>
+      <c r="X64">
+        <v>0</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+      <c r="AA64">
+        <v>0</v>
+      </c>
+      <c r="AB64">
+        <v>0</v>
+      </c>
+      <c r="AC64">
+        <v>0</v>
+      </c>
+      <c r="AD64">
+        <v>0</v>
+      </c>
+      <c r="AE64">
+        <v>0</v>
+      </c>
+      <c r="AF64">
+        <v>0</v>
+      </c>
+      <c r="AG64">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64">
+        <v>0</v>
+      </c>
+      <c r="AK64">
+        <v>0</v>
+      </c>
+      <c r="AL64">
+        <v>0</v>
+      </c>
+      <c r="AM64">
+        <v>-1</v>
+      </c>
+      <c r="AN64">
+        <v>-1</v>
+      </c>
+      <c r="AO64">
+        <v>-1</v>
+      </c>
+      <c r="AP64">
+        <v>-1</v>
+      </c>
+      <c r="AQ64">
+        <v>0</v>
+      </c>
+      <c r="AR64">
+        <v>0</v>
+      </c>
+      <c r="AS64">
+        <v>0</v>
+      </c>
+      <c r="AT64">
+        <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>2026-10-28 23:30:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G45">

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU64"/>
+  <dimension ref="A1:AU66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G13">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-10-28 15:30:00</t>
+          <t>2026-10-28 15:00:00</t>
         </is>
       </c>
     </row>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-10-28 16:00:00</t>
+          <t>2026-10-28 15:30:00</t>
         </is>
       </c>
     </row>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G27">
@@ -4831,22 +4831,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G28">
@@ -4989,27 +4989,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-10-28 16:45:00</t>
+          <t>2026-10-28 16:00:00</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>4.22</v>
+        <v>1.92</v>
       </c>
       <c r="O34">
-        <v>3.95</v>
+        <v>3.66</v>
       </c>
       <c r="P34">
-        <v>1.9</v>
+        <v>3.62</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>5.61</v>
+        <v>4.22</v>
       </c>
       <c r="O35">
-        <v>4.02</v>
+        <v>3.95</v>
       </c>
       <c r="P35">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB35">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.13</v>
+        <v>5.61</v>
       </c>
       <c r="O36">
-        <v>3.58</v>
+        <v>4.02</v>
       </c>
       <c r="P36">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-10-28 17:00:00</t>
+          <t>2026-10-28 16:45:00</t>
         </is>
       </c>
     </row>
@@ -6293,27 +6293,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-10-28 19:30:00</t>
+          <t>2026-10-28 17:00:00</t>
         </is>
       </c>
     </row>
@@ -6456,27 +6456,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.31</v>
+        <v>3.13</v>
       </c>
       <c r="O38">
-        <v>5.56</v>
+        <v>3.58</v>
       </c>
       <c r="P38">
-        <v>10.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-10-28 19:30:00</t>
+          <t>2026-10-28 17:00:00</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.99</v>
+        <v>1.98</v>
       </c>
       <c r="O39">
-        <v>3.43</v>
+        <v>3.51</v>
       </c>
       <c r="P39">
-        <v>2.41</v>
+        <v>3.96</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G40">
@@ -6825,68 +6825,68 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N40">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="O40">
-        <v>3.95</v>
+        <v>5.56</v>
       </c>
       <c r="P40">
-        <v>5.56</v>
+        <v>10.2</v>
       </c>
       <c r="Q40">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK40">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-10-28 20:30:00</t>
+          <t>2026-10-28 19:30:00</t>
         </is>
       </c>
     </row>
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-10-28 20:30:00</t>
+          <t>2026-10-28 19:30:00</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G42">
@@ -7151,68 +7151,68 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G44">
@@ -7760,27 +7760,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G46">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-10-28 21:00:00</t>
+          <t>2026-10-28 20:30:00</t>
         </is>
       </c>
     </row>
@@ -7923,27 +7923,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G47">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-10-28 21:00:00</t>
+          <t>2026-10-28 20:30:00</t>
         </is>
       </c>
     </row>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G53">
@@ -9064,27 +9064,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-10-28 21:30:00</t>
+          <t>2026-10-28 21:00:00</t>
         </is>
       </c>
     </row>
@@ -9227,27 +9227,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O55">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="P55">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9313,10 +9313,10 @@
         <v>0</v>
       </c>
       <c r="AA55">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB55">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC55">
         <v>0</v>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-10-28 21:30:00</t>
+          <t>2026-10-28 21:00:00</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9639,10 +9639,10 @@
         <v>0</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G61">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G62">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-10-28 23:30:00</t>
+          <t>2026-10-28 21:30:00</t>
         </is>
       </c>
     </row>
@@ -10531,7 +10531,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G63">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-10-28 23:30:00</t>
+          <t>2026-10-28 21:30:00</t>
         </is>
       </c>
     </row>
@@ -10709,141 +10709,467 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0</v>
+      </c>
+      <c r="X64">
+        <v>0</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+      <c r="AA64">
+        <v>0</v>
+      </c>
+      <c r="AB64">
+        <v>0</v>
+      </c>
+      <c r="AC64">
+        <v>0</v>
+      </c>
+      <c r="AD64">
+        <v>0</v>
+      </c>
+      <c r="AE64">
+        <v>0</v>
+      </c>
+      <c r="AF64">
+        <v>0</v>
+      </c>
+      <c r="AG64">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64">
+        <v>0</v>
+      </c>
+      <c r="AK64">
+        <v>0</v>
+      </c>
+      <c r="AL64">
+        <v>0</v>
+      </c>
+      <c r="AM64">
+        <v>-1</v>
+      </c>
+      <c r="AN64">
+        <v>-1</v>
+      </c>
+      <c r="AO64">
+        <v>-1</v>
+      </c>
+      <c r="AP64">
+        <v>-1</v>
+      </c>
+      <c r="AQ64">
+        <v>0</v>
+      </c>
+      <c r="AR64">
+        <v>0</v>
+      </c>
+      <c r="AS64">
+        <v>0</v>
+      </c>
+      <c r="AT64">
+        <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>2026-10-28 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>0</v>
+      </c>
+      <c r="Y65">
+        <v>0</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+      <c r="AA65">
+        <v>0</v>
+      </c>
+      <c r="AB65">
+        <v>0</v>
+      </c>
+      <c r="AC65">
+        <v>0</v>
+      </c>
+      <c r="AD65">
+        <v>0</v>
+      </c>
+      <c r="AE65">
+        <v>0</v>
+      </c>
+      <c r="AF65">
+        <v>0</v>
+      </c>
+      <c r="AG65">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
+        <v>0</v>
+      </c>
+      <c r="AK65">
+        <v>0</v>
+      </c>
+      <c r="AL65">
+        <v>0</v>
+      </c>
+      <c r="AM65">
+        <v>-1</v>
+      </c>
+      <c r="AN65">
+        <v>-1</v>
+      </c>
+      <c r="AO65">
+        <v>-1</v>
+      </c>
+      <c r="AP65">
+        <v>-1</v>
+      </c>
+      <c r="AQ65">
+        <v>0</v>
+      </c>
+      <c r="AR65">
+        <v>0</v>
+      </c>
+      <c r="AS65">
+        <v>0</v>
+      </c>
+      <c r="AT65">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>2026-10-28 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>SJ Earthquakes</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Colorado Rapids</t>
         </is>
       </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
-      <c r="H64">
-        <v>0</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="K64">
-        <v>0</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64" t="inlineStr">
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N64">
-        <v>0</v>
-      </c>
-      <c r="O64">
-        <v>0</v>
-      </c>
-      <c r="P64">
-        <v>0</v>
-      </c>
-      <c r="Q64">
-        <v>0</v>
-      </c>
-      <c r="R64">
-        <v>0</v>
-      </c>
-      <c r="S64">
-        <v>0</v>
-      </c>
-      <c r="T64">
-        <v>0</v>
-      </c>
-      <c r="U64">
-        <v>0</v>
-      </c>
-      <c r="V64">
-        <v>0</v>
-      </c>
-      <c r="W64">
-        <v>0</v>
-      </c>
-      <c r="X64">
-        <v>0</v>
-      </c>
-      <c r="Y64">
-        <v>0</v>
-      </c>
-      <c r="Z64">
-        <v>0</v>
-      </c>
-      <c r="AA64">
-        <v>0</v>
-      </c>
-      <c r="AB64">
-        <v>0</v>
-      </c>
-      <c r="AC64">
-        <v>0</v>
-      </c>
-      <c r="AD64">
-        <v>0</v>
-      </c>
-      <c r="AE64">
-        <v>0</v>
-      </c>
-      <c r="AF64">
-        <v>0</v>
-      </c>
-      <c r="AG64">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64">
-        <v>0</v>
-      </c>
-      <c r="AK64">
-        <v>0</v>
-      </c>
-      <c r="AL64">
-        <v>0</v>
-      </c>
-      <c r="AM64">
-        <v>-1</v>
-      </c>
-      <c r="AN64">
-        <v>-1</v>
-      </c>
-      <c r="AO64">
-        <v>-1</v>
-      </c>
-      <c r="AP64">
-        <v>-1</v>
-      </c>
-      <c r="AQ64">
-        <v>0</v>
-      </c>
-      <c r="AR64">
-        <v>0</v>
-      </c>
-      <c r="AS64">
-        <v>0</v>
-      </c>
-      <c r="AT64">
-        <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66">
+        <v>0</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0</v>
+      </c>
+      <c r="X66">
+        <v>0</v>
+      </c>
+      <c r="Y66">
+        <v>0</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+      <c r="AA66">
+        <v>0</v>
+      </c>
+      <c r="AB66">
+        <v>0</v>
+      </c>
+      <c r="AC66">
+        <v>0</v>
+      </c>
+      <c r="AD66">
+        <v>0</v>
+      </c>
+      <c r="AE66">
+        <v>0</v>
+      </c>
+      <c r="AF66">
+        <v>0</v>
+      </c>
+      <c r="AG66">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
+        <v>0</v>
+      </c>
+      <c r="AK66">
+        <v>0</v>
+      </c>
+      <c r="AL66">
+        <v>0</v>
+      </c>
+      <c r="AM66">
+        <v>-1</v>
+      </c>
+      <c r="AN66">
+        <v>-1</v>
+      </c>
+      <c r="AO66">
+        <v>-1</v>
+      </c>
+      <c r="AP66">
+        <v>-1</v>
+      </c>
+      <c r="AQ66">
+        <v>0</v>
+      </c>
+      <c r="AR66">
+        <v>0</v>
+      </c>
+      <c r="AS66">
+        <v>0</v>
+      </c>
+      <c r="AT66">
+        <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
         <is>
           <t>2026-10-28 23:30:00</t>
         </is>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="O31">
-        <v>3.42</v>
+        <v>3.66</v>
       </c>
       <c r="P31">
-        <v>3</v>
+        <v>3.62</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O32">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="P32">
-        <v>3.64</v>
+        <v>3</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O34">
-        <v>3.66</v>
+        <v>3.55</v>
       </c>
       <c r="P34">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G55">

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G47">

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q24">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q28">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G13">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.31</v>
+        <v>2.99</v>
       </c>
       <c r="O40">
-        <v>5.56</v>
+        <v>3.43</v>
       </c>
       <c r="P40">
-        <v>10.2</v>
+        <v>2.41</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.99</v>
+        <v>1.31</v>
       </c>
       <c r="O41">
-        <v>3.43</v>
+        <v>5.56</v>
       </c>
       <c r="P41">
-        <v>2.41</v>
+        <v>10.2</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G47">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G55">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G64">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G66">

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="O22">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="P22">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.65</v>
+        <v>3.75</v>
       </c>
       <c r="O23">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="P23">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G63">

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.6</v>
+        <v>2.01</v>
       </c>
       <c r="O56">
-        <v>3.61</v>
+        <v>3.53</v>
       </c>
       <c r="P56">
-        <v>2.63</v>
+        <v>3.82</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9476,10 +9476,10 @@
         <v>0</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.01</v>
+        <v>2.6</v>
       </c>
       <c r="O57">
-        <v>3.53</v>
+        <v>3.61</v>
       </c>
       <c r="P57">
-        <v>3.82</v>
+        <v>2.63</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9639,10 +9639,10 @@
         <v>0</v>
       </c>
       <c r="AA57">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB57">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC57">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL2">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G66">

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -1133,34 +1133,34 @@
         <v>5.1</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA5">
         <v>1.87</v>
@@ -1169,19 +1169,19 @@
         <v>1.88</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -807,55 +807,55 @@
         <v>2.61</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1459,34 +1459,34 @@
         <v>2.6</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA7">
         <v>1.83</v>
@@ -1495,19 +1495,19 @@
         <v>1.98</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,55 +1622,55 @@
         <v>2.49</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>4.17</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2926,55 +2926,55 @@
         <v>2.73</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3089,55 +3089,55 @@
         <v>2.38</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>8.449999999999999</v>
+        <v>1.61</v>
       </c>
       <c r="O18">
-        <v>6.33</v>
+        <v>4.38</v>
       </c>
       <c r="P18">
-        <v>1.35</v>
+        <v>6.07</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC18">
+        <v>3.06</v>
+      </c>
+      <c r="AD18">
+        <v>1.37</v>
+      </c>
+      <c r="AE18">
+        <v>1.08</v>
+      </c>
+      <c r="AF18">
         <v>1.85</v>
       </c>
-      <c r="AD18">
-        <v>2</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
-        <v>0</v>
-      </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.61</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O19">
-        <v>4.38</v>
+        <v>6.33</v>
       </c>
       <c r="P19">
-        <v>6.07</v>
+        <v>1.35</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>7.21</v>
       </c>
       <c r="AA19">
-        <v>1.81</v>
+        <v>1.32</v>
       </c>
       <c r="AB19">
+        <v>3.34</v>
+      </c>
+      <c r="AC19">
+        <v>1.85</v>
+      </c>
+      <c r="AD19">
         <v>2</v>
       </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4556,55 +4556,55 @@
         <v>2.3</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5208,55 +5208,55 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5371,55 +5371,55 @@
         <v>3.62</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.25</v>
+        <v>3.44</v>
       </c>
       <c r="O32">
-        <v>3.42</v>
+        <v>3.62</v>
       </c>
       <c r="P32">
-        <v>3</v>
+        <v>1.99</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA32">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="AB32">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.44</v>
+        <v>1.95</v>
       </c>
       <c r="O33">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="P33">
-        <v>1.99</v>
+        <v>3.64</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,43 +5851,43 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O34">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="P34">
-        <v>3.64</v>
+        <v>3</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA34">
         <v>1.88</v>
@@ -5896,19 +5896,19 @@
         <v>1.98</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>4.22</v>
+        <v>5.61</v>
       </c>
       <c r="O35">
-        <v>3.95</v>
+        <v>4.02</v>
       </c>
       <c r="P35">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>5.61</v>
+        <v>4.22</v>
       </c>
       <c r="O36">
-        <v>4.02</v>
+        <v>3.95</v>
       </c>
       <c r="P36">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="AA36">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="AB36">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6512,55 +6512,55 @@
         <v>2.12</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G55">

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -4067,55 +4067,55 @@
         <v>1.87</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.28</v>
+        <v>1.92</v>
       </c>
       <c r="O30">
-        <v>5.7</v>
+        <v>3.66</v>
       </c>
       <c r="P30">
-        <v>8.800000000000001</v>
+        <v>3.62</v>
       </c>
       <c r="Q30">
-        <v>1.67</v>
+        <v>2.44</v>
       </c>
       <c r="R30">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="S30">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="T30">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="U30">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="V30">
+        <v>1.53</v>
+      </c>
+      <c r="W30">
+        <v>1.14</v>
+      </c>
+      <c r="X30">
+        <v>1.03</v>
+      </c>
+      <c r="Y30">
+        <v>1.15</v>
+      </c>
+      <c r="Z30">
+        <v>4.2</v>
+      </c>
+      <c r="AA30">
+        <v>1.63</v>
+      </c>
+      <c r="AB30">
+        <v>2.2</v>
+      </c>
+      <c r="AC30">
+        <v>2.46</v>
+      </c>
+      <c r="AD30">
+        <v>1.43</v>
+      </c>
+      <c r="AE30">
+        <v>1.14</v>
+      </c>
+      <c r="AF30">
+        <v>1.55</v>
+      </c>
+      <c r="AG30">
+        <v>2.25</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>1.25</v>
+      </c>
+      <c r="AK30">
         <v>1.83</v>
-      </c>
-      <c r="W30">
-        <v>1.22</v>
-      </c>
-      <c r="X30">
-        <v>1.01</v>
-      </c>
-      <c r="Y30">
-        <v>1.08</v>
-      </c>
-      <c r="Z30">
-        <v>5.65</v>
-      </c>
-      <c r="AA30">
-        <v>1.4</v>
-      </c>
-      <c r="AB30">
-        <v>3</v>
-      </c>
-      <c r="AC30">
-        <v>1.9</v>
-      </c>
-      <c r="AD30">
-        <v>1.77</v>
-      </c>
-      <c r="AE30">
-        <v>1.31</v>
-      </c>
-      <c r="AF30">
-        <v>1.7</v>
-      </c>
-      <c r="AG30">
-        <v>1.98</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.11</v>
-      </c>
-      <c r="AK30">
-        <v>3.65</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O31">
-        <v>3.66</v>
+        <v>3.55</v>
       </c>
       <c r="P31">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="Q31">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="R31">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="S31">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T31">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U31">
-        <v>2.3</v>
+        <v>2.74</v>
       </c>
       <c r="V31">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="W31">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X31">
         <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z31">
-        <v>4.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA31">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="AB31">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AC31">
-        <v>2.46</v>
+        <v>3.08</v>
       </c>
       <c r="AD31">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AE31">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF31">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG31">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK31">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,65 +5525,65 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.44</v>
+        <v>2.25</v>
       </c>
       <c r="O32">
-        <v>3.62</v>
+        <v>3.42</v>
       </c>
       <c r="P32">
-        <v>1.99</v>
+        <v>3</v>
       </c>
       <c r="Q32">
-        <v>4.03</v>
+        <v>2.81</v>
       </c>
       <c r="R32">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="S32">
+        <v>1.35</v>
+      </c>
+      <c r="T32">
+        <v>2.97</v>
+      </c>
+      <c r="U32">
+        <v>2.62</v>
+      </c>
+      <c r="V32">
+        <v>1.44</v>
+      </c>
+      <c r="W32">
+        <v>1.1</v>
+      </c>
+      <c r="X32">
+        <v>1.03</v>
+      </c>
+      <c r="Y32">
+        <v>1.23</v>
+      </c>
+      <c r="Z32">
+        <v>3.42</v>
+      </c>
+      <c r="AA32">
+        <v>1.88</v>
+      </c>
+      <c r="AB32">
+        <v>1.98</v>
+      </c>
+      <c r="AC32">
+        <v>3.25</v>
+      </c>
+      <c r="AD32">
         <v>1.3</v>
       </c>
-      <c r="T32">
-        <v>3.12</v>
-      </c>
-      <c r="U32">
-        <v>2.47</v>
-      </c>
-      <c r="V32">
-        <v>1.46</v>
-      </c>
-      <c r="W32">
-        <v>1.07</v>
-      </c>
-      <c r="X32">
-        <v>1.04</v>
-      </c>
-      <c r="Y32">
-        <v>1.18</v>
-      </c>
-      <c r="Z32">
-        <v>3.88</v>
-      </c>
-      <c r="AA32">
-        <v>1.71</v>
-      </c>
-      <c r="AB32">
+      <c r="AE32">
+        <v>1.06</v>
+      </c>
+      <c r="AF32">
+        <v>1.68</v>
+      </c>
+      <c r="AG32">
         <v>2.06</v>
       </c>
-      <c r="AC32">
-        <v>2.66</v>
-      </c>
-      <c r="AD32">
-        <v>1.37</v>
-      </c>
-      <c r="AE32">
-        <v>1.11</v>
-      </c>
-      <c r="AF32">
-        <v>1.65</v>
-      </c>
-      <c r="AG32">
-        <v>2.15</v>
-      </c>
       <c r="AH32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK32">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.95</v>
+        <v>3.44</v>
       </c>
       <c r="O33">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="P33">
-        <v>3.64</v>
+        <v>1.99</v>
       </c>
       <c r="Q33">
-        <v>2.52</v>
+        <v>4.03</v>
       </c>
       <c r="R33">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="S33">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="U33">
-        <v>2.74</v>
+        <v>2.47</v>
       </c>
       <c r="V33">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W33">
+        <v>1.07</v>
+      </c>
+      <c r="X33">
         <v>1.04</v>
       </c>
-      <c r="X33">
-        <v>1.03</v>
-      </c>
       <c r="Y33">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z33">
-        <v>3.42</v>
+        <v>3.88</v>
       </c>
       <c r="AA33">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="AB33">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AC33">
-        <v>3.08</v>
+        <v>2.66</v>
       </c>
       <c r="AD33">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF33">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
+        <v>1.29</v>
+      </c>
+      <c r="AK33">
         <v>1.3</v>
-      </c>
-      <c r="AK33">
-        <v>1.8</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,65 +5851,65 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.25</v>
+        <v>1.28</v>
       </c>
       <c r="O34">
-        <v>3.42</v>
+        <v>5.7</v>
       </c>
       <c r="P34">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q34">
+        <v>1.67</v>
+      </c>
+      <c r="R34">
+        <v>2.8</v>
+      </c>
+      <c r="S34">
+        <v>1.18</v>
+      </c>
+      <c r="T34">
+        <v>3.78</v>
+      </c>
+      <c r="U34">
+        <v>2.02</v>
+      </c>
+      <c r="V34">
+        <v>1.83</v>
+      </c>
+      <c r="W34">
+        <v>1.22</v>
+      </c>
+      <c r="X34">
+        <v>1.01</v>
+      </c>
+      <c r="Y34">
+        <v>1.08</v>
+      </c>
+      <c r="Z34">
+        <v>5.65</v>
+      </c>
+      <c r="AA34">
+        <v>1.4</v>
+      </c>
+      <c r="AB34">
         <v>3</v>
       </c>
-      <c r="Q34">
-        <v>2.81</v>
-      </c>
-      <c r="R34">
-        <v>2.12</v>
-      </c>
-      <c r="S34">
-        <v>1.35</v>
-      </c>
-      <c r="T34">
-        <v>2.97</v>
-      </c>
-      <c r="U34">
-        <v>2.62</v>
-      </c>
-      <c r="V34">
-        <v>1.44</v>
-      </c>
-      <c r="W34">
-        <v>1.1</v>
-      </c>
-      <c r="X34">
-        <v>1.03</v>
-      </c>
-      <c r="Y34">
-        <v>1.23</v>
-      </c>
-      <c r="Z34">
-        <v>3.42</v>
-      </c>
-      <c r="AA34">
-        <v>1.88</v>
-      </c>
-      <c r="AB34">
+      <c r="AC34">
+        <v>1.9</v>
+      </c>
+      <c r="AD34">
+        <v>1.77</v>
+      </c>
+      <c r="AE34">
+        <v>1.31</v>
+      </c>
+      <c r="AF34">
+        <v>1.7</v>
+      </c>
+      <c r="AG34">
         <v>1.98</v>
       </c>
-      <c r="AC34">
-        <v>3.25</v>
-      </c>
-      <c r="AD34">
-        <v>1.3</v>
-      </c>
-      <c r="AE34">
-        <v>1.06</v>
-      </c>
-      <c r="AF34">
-        <v>1.68</v>
-      </c>
-      <c r="AG34">
-        <v>2.06</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AK34">
-        <v>1.57</v>
+        <v>3.65</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6675,55 +6675,55 @@
         <v>3.96</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6838,55 +6838,55 @@
         <v>2.41</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,55 +7001,55 @@
         <v>10.2</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G55">
@@ -9446,34 +9446,34 @@
         <v>3.82</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA56">
         <v>2.03</v>
@@ -9482,19 +9482,19 @@
         <v>1.83</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9609,55 +9609,55 @@
         <v>2.63</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G63">

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU66"/>
+  <dimension ref="A1:AU62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,12 +588,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSS Sleman</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC2">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AK2">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-10-28 05:30:00</t>
+          <t>2026-10-28 09:00:00</t>
         </is>
       </c>
     </row>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G9">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-10-28 13:00:00</t>
+          <t>2026-10-28 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-10-28 13:00:00</t>
+          <t>2026-10-28 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2218,27 +2218,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-10-28 13:00:00</t>
+          <t>2026-10-28 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>6.07</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-10-28 13:00:00</t>
+          <t>2026-10-28 14:30:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>6.33</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>7.21</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-10-28 14:00:00</t>
+          <t>2026-10-28 14:30:00</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.89</v>
+        <v>3.28</v>
       </c>
       <c r="O15">
-        <v>2.97</v>
+        <v>3.45</v>
       </c>
       <c r="P15">
-        <v>4.17</v>
+        <v>2.38</v>
       </c>
       <c r="Q15">
-        <v>2.62</v>
+        <v>3.69</v>
       </c>
       <c r="R15">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="S15">
         <v>1.44</v>
       </c>
       <c r="T15">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U15">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="V15">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
+        <v>1.02</v>
+      </c>
+      <c r="Y15">
+        <v>1.38</v>
+      </c>
+      <c r="Z15">
+        <v>3.04</v>
+      </c>
+      <c r="AA15">
+        <v>2.22</v>
+      </c>
+      <c r="AB15">
+        <v>1.66</v>
+      </c>
+      <c r="AC15">
+        <v>3.82</v>
+      </c>
+      <c r="AD15">
+        <v>1.26</v>
+      </c>
+      <c r="AE15">
         <v>1.06</v>
       </c>
-      <c r="Y15">
-        <v>1.42</v>
-      </c>
-      <c r="Z15">
-        <v>2.69</v>
-      </c>
-      <c r="AA15">
-        <v>2.29</v>
-      </c>
-      <c r="AB15">
+      <c r="AF15">
+        <v>1.83</v>
+      </c>
+      <c r="AG15">
+        <v>1.91</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
         <v>1.55</v>
       </c>
-      <c r="AC15">
-        <v>4.38</v>
-      </c>
-      <c r="AD15">
-        <v>1.15</v>
-      </c>
-      <c r="AE15">
-        <v>1.01</v>
-      </c>
-      <c r="AF15">
-        <v>2.1</v>
-      </c>
-      <c r="AG15">
-        <v>1.64</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.29</v>
-      </c>
       <c r="AK15">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-10-28 14:00:00</t>
+          <t>2026-10-28 14:30:00</t>
         </is>
       </c>
     </row>
@@ -2870,27 +2870,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G16">
@@ -2920,61 +2920,61 @@
         <v>2.29</v>
       </c>
       <c r="O16">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
-        <v>2.73</v>
+        <v>2.92</v>
       </c>
       <c r="Q16">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-10-28 14:00:00</t>
+          <t>2026-10-28 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3033,27 +3033,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="O17">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="P17">
-        <v>2.38</v>
+        <v>1.89</v>
       </c>
       <c r="Q17">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-10-28 14:30:00</t>
+          <t>2026-10-28 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3196,27 +3196,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.61</v>
+        <v>2.65</v>
       </c>
       <c r="O18">
-        <v>4.38</v>
+        <v>3.25</v>
       </c>
       <c r="P18">
-        <v>6.07</v>
+        <v>2.5</v>
       </c>
       <c r="Q18">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z18">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC18">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK18">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-10-28 14:30:00</t>
+          <t>2026-10-28 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3359,27 +3359,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>8.449999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="O19">
-        <v>6.33</v>
+        <v>3.65</v>
       </c>
       <c r="P19">
-        <v>1.35</v>
+        <v>1.87</v>
       </c>
       <c r="Q19">
-        <v>7</v>
+        <v>4.78</v>
       </c>
       <c r="R19">
-        <v>3.11</v>
+        <v>2.38</v>
       </c>
       <c r="S19">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>3.46</v>
       </c>
       <c r="U19">
-        <v>1.86</v>
+        <v>2.21</v>
       </c>
       <c r="V19">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="W19">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z19">
-        <v>7.21</v>
+        <v>4.3</v>
       </c>
       <c r="AA19">
-        <v>1.32</v>
+        <v>1.59</v>
       </c>
       <c r="AB19">
-        <v>3.34</v>
+        <v>2.2</v>
       </c>
       <c r="AC19">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AD19">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AE19">
-        <v>1.41</v>
+        <v>1.16</v>
       </c>
       <c r="AF19">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AG19">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AK19">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-10-28 14:30:00</t>
+          <t>2026-10-28 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3527,22 +3527,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.29</v>
+        <v>3.8</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="P20">
-        <v>2.92</v>
+        <v>1.81</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3690,22 +3690,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3848,27 +3848,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="O22">
         <v>3.25</v>
       </c>
       <c r="P22">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-10-28 15:00:00</t>
+          <t>2026-10-28 15:30:00</t>
         </is>
       </c>
     </row>
@@ -4011,27 +4011,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.75</v>
+        <v>2.41</v>
       </c>
       <c r="O23">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="P23">
-        <v>1.87</v>
+        <v>2.92</v>
       </c>
       <c r="Q23">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z23">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK23">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-10-28 15:00:00</t>
+          <t>2026-10-28 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4174,27 +4174,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.8</v>
+        <v>2.87</v>
       </c>
       <c r="O24">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="P24">
-        <v>1.81</v>
+        <v>2.39</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-10-28 15:00:00</t>
+          <t>2026-10-28 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4337,27 +4337,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G25">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-10-28 15:00:00</t>
+          <t>2026-10-28 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.63</v>
+        <v>1.92</v>
       </c>
       <c r="O26">
-        <v>3.25</v>
+        <v>3.66</v>
       </c>
       <c r="P26">
+        <v>3.62</v>
+      </c>
+      <c r="Q26">
+        <v>2.44</v>
+      </c>
+      <c r="R26">
+        <v>2.25</v>
+      </c>
+      <c r="S26">
+        <v>1.29</v>
+      </c>
+      <c r="T26">
+        <v>3.5</v>
+      </c>
+      <c r="U26">
         <v>2.3</v>
       </c>
-      <c r="Q26">
-        <v>3.1</v>
-      </c>
-      <c r="R26">
+      <c r="V26">
+        <v>1.53</v>
+      </c>
+      <c r="W26">
+        <v>1.14</v>
+      </c>
+      <c r="X26">
+        <v>1.03</v>
+      </c>
+      <c r="Y26">
+        <v>1.15</v>
+      </c>
+      <c r="Z26">
+        <v>4.2</v>
+      </c>
+      <c r="AA26">
+        <v>1.63</v>
+      </c>
+      <c r="AB26">
         <v>2.2</v>
       </c>
-      <c r="S26">
-        <v>1.33</v>
-      </c>
-      <c r="T26">
-        <v>3.2</v>
-      </c>
-      <c r="U26">
-        <v>2.63</v>
-      </c>
-      <c r="V26">
-        <v>1.44</v>
-      </c>
-      <c r="W26">
-        <v>1.1</v>
-      </c>
-      <c r="X26">
-        <v>1.02</v>
-      </c>
-      <c r="Y26">
-        <v>1.25</v>
-      </c>
-      <c r="Z26">
-        <v>3.6</v>
-      </c>
-      <c r="AA26">
-        <v>1.85</v>
-      </c>
-      <c r="AB26">
-        <v>1.98</v>
-      </c>
       <c r="AC26">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="AD26">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AE26">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF26">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AG26">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-10-28 15:30:00</t>
+          <t>2026-10-28 16:45:00</t>
         </is>
       </c>
     </row>
@@ -4663,12 +4663,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="O27">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="P27">
-        <v>2.92</v>
+        <v>3.64</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-10-28 16:00:00</t>
+          <t>2026-10-28 16:45:00</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.87</v>
+        <v>2.25</v>
       </c>
       <c r="O28">
+        <v>3.42</v>
+      </c>
+      <c r="P28">
+        <v>3</v>
+      </c>
+      <c r="Q28">
+        <v>2.81</v>
+      </c>
+      <c r="R28">
+        <v>2.12</v>
+      </c>
+      <c r="S28">
+        <v>1.35</v>
+      </c>
+      <c r="T28">
+        <v>2.97</v>
+      </c>
+      <c r="U28">
+        <v>2.62</v>
+      </c>
+      <c r="V28">
+        <v>1.44</v>
+      </c>
+      <c r="W28">
+        <v>1.1</v>
+      </c>
+      <c r="X28">
+        <v>1.03</v>
+      </c>
+      <c r="Y28">
+        <v>1.23</v>
+      </c>
+      <c r="Z28">
+        <v>3.42</v>
+      </c>
+      <c r="AA28">
+        <v>1.88</v>
+      </c>
+      <c r="AB28">
+        <v>1.98</v>
+      </c>
+      <c r="AC28">
         <v>3.25</v>
       </c>
-      <c r="P28">
-        <v>2.39</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0</v>
-      </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
-        <v>0</v>
-      </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>0</v>
-      </c>
-      <c r="AB28">
-        <v>0</v>
-      </c>
-      <c r="AC28">
-        <v>0</v>
-      </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-10-28 16:00:00</t>
+          <t>2026-10-28 16:45:00</t>
         </is>
       </c>
     </row>
@@ -4989,27 +4989,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-10-28 16:00:00</t>
+          <t>2026-10-28 16:45:00</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.92</v>
+        <v>1.28</v>
       </c>
       <c r="O30">
-        <v>3.66</v>
+        <v>5.7</v>
       </c>
       <c r="P30">
-        <v>3.62</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q30">
-        <v>2.44</v>
+        <v>1.67</v>
       </c>
       <c r="R30">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="S30">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="T30">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="U30">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="V30">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="W30">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="Z30">
-        <v>4.2</v>
+        <v>5.65</v>
       </c>
       <c r="AA30">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="AB30">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="AC30">
-        <v>2.46</v>
+        <v>1.9</v>
       </c>
       <c r="AD30">
-        <v>1.43</v>
+        <v>1.77</v>
       </c>
       <c r="AE30">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AF30">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG30">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK30">
-        <v>1.83</v>
+        <v>3.65</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.95</v>
+        <v>5.61</v>
       </c>
       <c r="O31">
-        <v>3.55</v>
+        <v>4.02</v>
       </c>
       <c r="P31">
+        <v>1.7</v>
+      </c>
+      <c r="Q31">
+        <v>5.5</v>
+      </c>
+      <c r="R31">
+        <v>2.2</v>
+      </c>
+      <c r="S31">
+        <v>1.42</v>
+      </c>
+      <c r="T31">
+        <v>2.8</v>
+      </c>
+      <c r="U31">
+        <v>3.11</v>
+      </c>
+      <c r="V31">
+        <v>1.35</v>
+      </c>
+      <c r="W31">
+        <v>1.05</v>
+      </c>
+      <c r="X31">
+        <v>1.04</v>
+      </c>
+      <c r="Y31">
+        <v>1.34</v>
+      </c>
+      <c r="Z31">
+        <v>3.15</v>
+      </c>
+      <c r="AA31">
+        <v>1.84</v>
+      </c>
+      <c r="AB31">
+        <v>1.97</v>
+      </c>
+      <c r="AC31">
         <v>3.64</v>
-      </c>
-      <c r="Q31">
-        <v>2.52</v>
-      </c>
-      <c r="R31">
-        <v>2.14</v>
-      </c>
-      <c r="S31">
-        <v>1.38</v>
-      </c>
-      <c r="T31">
-        <v>3.1</v>
-      </c>
-      <c r="U31">
-        <v>2.74</v>
-      </c>
-      <c r="V31">
-        <v>1.38</v>
-      </c>
-      <c r="W31">
-        <v>1.04</v>
-      </c>
-      <c r="X31">
-        <v>1.03</v>
-      </c>
-      <c r="Y31">
-        <v>1.23</v>
-      </c>
-      <c r="Z31">
-        <v>3.42</v>
-      </c>
-      <c r="AA31">
-        <v>1.88</v>
-      </c>
-      <c r="AB31">
-        <v>1.98</v>
-      </c>
-      <c r="AC31">
-        <v>3.08</v>
       </c>
       <c r="AD31">
         <v>1.28</v>
       </c>
       <c r="AE31">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF31">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AG31">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK31">
-        <v>1.8</v>
+        <v>1.16</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.25</v>
+        <v>4.22</v>
       </c>
       <c r="O32">
-        <v>3.42</v>
+        <v>3.95</v>
       </c>
       <c r="P32">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="Q32">
-        <v>2.81</v>
+        <v>4.47</v>
       </c>
       <c r="R32">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="S32">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="U32">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="V32">
+        <v>1.46</v>
+      </c>
+      <c r="W32">
+        <v>1.08</v>
+      </c>
+      <c r="X32">
+        <v>1</v>
+      </c>
+      <c r="Y32">
+        <v>1.22</v>
+      </c>
+      <c r="Z32">
+        <v>4.08</v>
+      </c>
+      <c r="AA32">
+        <v>1.74</v>
+      </c>
+      <c r="AB32">
+        <v>2.11</v>
+      </c>
+      <c r="AC32">
+        <v>2.8</v>
+      </c>
+      <c r="AD32">
         <v>1.44</v>
       </c>
-      <c r="W32">
-        <v>1.1</v>
-      </c>
-      <c r="X32">
-        <v>1.03</v>
-      </c>
-      <c r="Y32">
-        <v>1.23</v>
-      </c>
-      <c r="Z32">
-        <v>3.42</v>
-      </c>
-      <c r="AA32">
-        <v>1.88</v>
-      </c>
-      <c r="AB32">
-        <v>1.98</v>
-      </c>
-      <c r="AC32">
-        <v>3.25</v>
-      </c>
-      <c r="AD32">
-        <v>1.3</v>
-      </c>
       <c r="AE32">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF32">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG32">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="AK32">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y33">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z33">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK33">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-10-28 16:45:00</t>
+          <t>2026-10-28 17:00:00</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.28</v>
+        <v>3.13</v>
       </c>
       <c r="O34">
-        <v>5.7</v>
+        <v>3.58</v>
       </c>
       <c r="P34">
-        <v>8.800000000000001</v>
+        <v>2.12</v>
       </c>
       <c r="Q34">
-        <v>1.67</v>
+        <v>3.74</v>
       </c>
       <c r="R34">
-        <v>2.8</v>
+        <v>2.22</v>
       </c>
       <c r="S34">
+        <v>1.3</v>
+      </c>
+      <c r="T34">
+        <v>3.25</v>
+      </c>
+      <c r="U34">
+        <v>2.38</v>
+      </c>
+      <c r="V34">
+        <v>1.5</v>
+      </c>
+      <c r="W34">
+        <v>1.1</v>
+      </c>
+      <c r="X34">
+        <v>1.04</v>
+      </c>
+      <c r="Y34">
         <v>1.18</v>
       </c>
-      <c r="T34">
-        <v>3.78</v>
-      </c>
-      <c r="U34">
-        <v>2.02</v>
-      </c>
-      <c r="V34">
-        <v>1.83</v>
-      </c>
-      <c r="W34">
-        <v>1.22</v>
-      </c>
-      <c r="X34">
-        <v>1.01</v>
-      </c>
-      <c r="Y34">
-        <v>1.08</v>
-      </c>
       <c r="Z34">
-        <v>5.65</v>
+        <v>3.92</v>
       </c>
       <c r="AA34">
+        <v>1.72</v>
+      </c>
+      <c r="AB34">
+        <v>2.1</v>
+      </c>
+      <c r="AC34">
+        <v>2.75</v>
+      </c>
+      <c r="AD34">
         <v>1.4</v>
       </c>
-      <c r="AB34">
-        <v>3</v>
-      </c>
-      <c r="AC34">
-        <v>1.9</v>
-      </c>
-      <c r="AD34">
-        <v>1.77</v>
-      </c>
       <c r="AE34">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AF34">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AG34">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>3.65</v>
+        <v>1.35</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-10-28 16:45:00</t>
+          <t>2026-10-28 17:00:00</t>
         </is>
       </c>
     </row>
@@ -5967,27 +5967,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,61 +6014,61 @@
         </is>
       </c>
       <c r="N35">
-        <v>5.61</v>
+        <v>1.31</v>
       </c>
       <c r="O35">
-        <v>4.02</v>
+        <v>5.56</v>
       </c>
       <c r="P35">
-        <v>1.7</v>
+        <v>10.2</v>
       </c>
       <c r="Q35">
-        <v>5.5</v>
+        <v>1.71</v>
       </c>
       <c r="R35">
+        <v>2.63</v>
+      </c>
+      <c r="S35">
+        <v>1.24</v>
+      </c>
+      <c r="T35">
+        <v>3.6</v>
+      </c>
+      <c r="U35">
         <v>2.2</v>
       </c>
-      <c r="S35">
-        <v>1.42</v>
-      </c>
-      <c r="T35">
-        <v>2.8</v>
-      </c>
-      <c r="U35">
-        <v>3.11</v>
-      </c>
       <c r="V35">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="W35">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y35">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="Z35">
-        <v>3.15</v>
+        <v>4.85</v>
       </c>
       <c r="AA35">
-        <v>1.84</v>
+        <v>1.57</v>
       </c>
       <c r="AB35">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="AC35">
-        <v>3.64</v>
+        <v>2.37</v>
       </c>
       <c r="AD35">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="AE35">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AF35">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AG35">
         <v>1.8</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AK35">
-        <v>1.16</v>
+        <v>3.6</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-10-28 16:45:00</t>
+          <t>2026-10-28 19:30:00</t>
         </is>
       </c>
     </row>
@@ -6130,27 +6130,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>4.22</v>
+        <v>2.99</v>
       </c>
       <c r="O36">
-        <v>3.95</v>
+        <v>3.43</v>
       </c>
       <c r="P36">
-        <v>1.9</v>
+        <v>2.41</v>
       </c>
       <c r="Q36">
-        <v>4.47</v>
+        <v>3.5</v>
       </c>
       <c r="R36">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="S36">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T36">
-        <v>3.23</v>
+        <v>2.88</v>
       </c>
       <c r="U36">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="V36">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
         <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z36">
-        <v>4.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA36">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="AB36">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="AC36">
-        <v>2.8</v>
+        <v>3.32</v>
       </c>
       <c r="AD36">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AE36">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-10-28 16:45:00</t>
+          <t>2026-10-28 19:30:00</t>
         </is>
       </c>
     </row>
@@ -6293,27 +6293,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-10-28 17:00:00</t>
+          <t>2026-10-28 19:30:00</t>
         </is>
       </c>
     </row>
@@ -6456,27 +6456,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G38">
@@ -6499,68 +6499,68 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N38">
-        <v>3.13</v>
+        <v>1.53</v>
       </c>
       <c r="O38">
-        <v>3.58</v>
+        <v>3.95</v>
       </c>
       <c r="P38">
-        <v>2.12</v>
+        <v>5.56</v>
       </c>
       <c r="Q38">
-        <v>3.74</v>
+        <v>2.04</v>
       </c>
       <c r="R38">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T38">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U38">
         <v>2.38</v>
       </c>
       <c r="V38">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W38">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z38">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="AA38">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AB38">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC38">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AD38">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE38">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF38">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AG38">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK38">
-        <v>1.35</v>
+        <v>2.38</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-10-28 17:00:00</t>
+          <t>2026-10-28 20:30:00</t>
         </is>
       </c>
     </row>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK39">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-10-28 19:30:00</t>
+          <t>2026-10-28 20:30:00</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK40">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-10-28 19:30:00</t>
+          <t>2026-10-28 20:30:00</t>
         </is>
       </c>
     </row>
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S41">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T41">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U41">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V41">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W41">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y41">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z41">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AA41">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC41">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AD41">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE41">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF41">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG41">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK41">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-10-28 19:30:00</t>
+          <t>2026-10-28 20:30:00</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G42">
@@ -7151,68 +7151,68 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N42">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S42">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T42">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U42">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V42">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W42">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y42">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z42">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA42">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC42">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD42">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE42">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF42">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG42">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK42">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G43">
@@ -7434,27 +7434,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G44">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-10-28 20:30:00</t>
+          <t>2026-10-28 21:00:00</t>
         </is>
       </c>
     </row>
@@ -7597,27 +7597,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G45">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-10-28 20:30:00</t>
+          <t>2026-10-28 21:00:00</t>
         </is>
       </c>
     </row>
@@ -7760,27 +7760,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G46">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-10-28 20:30:00</t>
+          <t>2026-10-28 21:00:00</t>
         </is>
       </c>
     </row>
@@ -7923,27 +7923,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G47">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-10-28 20:30:00</t>
+          <t>2026-10-28 21:00:00</t>
         </is>
       </c>
     </row>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G51">
@@ -8738,27 +8738,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-10-28 21:00:00</t>
+          <t>2026-10-28 21:30:00</t>
         </is>
       </c>
     </row>
@@ -8901,27 +8901,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-10-28 21:00:00</t>
+          <t>2026-10-28 21:30:00</t>
         </is>
       </c>
     </row>
@@ -9064,27 +9064,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G54">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-10-28 21:00:00</t>
+          <t>2026-10-28 21:30:00</t>
         </is>
       </c>
     </row>
@@ -9227,27 +9227,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G55">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-10-28 21:00:00</t>
+          <t>2026-10-28 21:30:00</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O56">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="P56">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="Q56">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R56">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S56">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T56">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="U56">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="V56">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W56">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X56">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y56">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z56">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA56">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB56">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC56">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD56">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE56">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF56">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG56">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK56">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O57">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P57">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q57">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R57">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S57">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T57">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U57">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V57">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W57">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y57">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z57">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA57">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB57">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC57">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD57">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE57">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF57">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG57">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK57">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G59">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G60">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-10-28 21:30:00</t>
+          <t>2026-10-28 23:30:00</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G61">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-10-28 21:30:00</t>
+          <t>2026-10-28 23:30:00</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G62">
@@ -10518,658 +10518,6 @@
         <v>0</v>
       </c>
       <c r="AU62" t="inlineStr">
-        <is>
-          <t>2026-10-28 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Philadelphia Union</t>
-        </is>
-      </c>
-      <c r="G63">
-        <v>0</v>
-      </c>
-      <c r="H63">
-        <v>0</v>
-      </c>
-      <c r="I63">
-        <v>0</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-      <c r="K63">
-        <v>0</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63">
-        <v>0</v>
-      </c>
-      <c r="P63">
-        <v>0</v>
-      </c>
-      <c r="Q63">
-        <v>0</v>
-      </c>
-      <c r="R63">
-        <v>0</v>
-      </c>
-      <c r="S63">
-        <v>0</v>
-      </c>
-      <c r="T63">
-        <v>0</v>
-      </c>
-      <c r="U63">
-        <v>0</v>
-      </c>
-      <c r="V63">
-        <v>0</v>
-      </c>
-      <c r="W63">
-        <v>0</v>
-      </c>
-      <c r="X63">
-        <v>0</v>
-      </c>
-      <c r="Y63">
-        <v>0</v>
-      </c>
-      <c r="Z63">
-        <v>0</v>
-      </c>
-      <c r="AA63">
-        <v>0</v>
-      </c>
-      <c r="AB63">
-        <v>0</v>
-      </c>
-      <c r="AC63">
-        <v>0</v>
-      </c>
-      <c r="AD63">
-        <v>0</v>
-      </c>
-      <c r="AE63">
-        <v>0</v>
-      </c>
-      <c r="AF63">
-        <v>0</v>
-      </c>
-      <c r="AG63">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63">
-        <v>0</v>
-      </c>
-      <c r="AK63">
-        <v>0</v>
-      </c>
-      <c r="AL63">
-        <v>0</v>
-      </c>
-      <c r="AM63">
-        <v>-1</v>
-      </c>
-      <c r="AN63">
-        <v>-1</v>
-      </c>
-      <c r="AO63">
-        <v>-1</v>
-      </c>
-      <c r="AP63">
-        <v>-1</v>
-      </c>
-      <c r="AQ63">
-        <v>0</v>
-      </c>
-      <c r="AR63">
-        <v>0</v>
-      </c>
-      <c r="AS63">
-        <v>0</v>
-      </c>
-      <c r="AT63">
-        <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>2026-10-28 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>SJ Earthquakes</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Colorado Rapids</t>
-        </is>
-      </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
-      <c r="H64">
-        <v>0</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="K64">
-        <v>0</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N64">
-        <v>0</v>
-      </c>
-      <c r="O64">
-        <v>0</v>
-      </c>
-      <c r="P64">
-        <v>0</v>
-      </c>
-      <c r="Q64">
-        <v>0</v>
-      </c>
-      <c r="R64">
-        <v>0</v>
-      </c>
-      <c r="S64">
-        <v>0</v>
-      </c>
-      <c r="T64">
-        <v>0</v>
-      </c>
-      <c r="U64">
-        <v>0</v>
-      </c>
-      <c r="V64">
-        <v>0</v>
-      </c>
-      <c r="W64">
-        <v>0</v>
-      </c>
-      <c r="X64">
-        <v>0</v>
-      </c>
-      <c r="Y64">
-        <v>0</v>
-      </c>
-      <c r="Z64">
-        <v>0</v>
-      </c>
-      <c r="AA64">
-        <v>0</v>
-      </c>
-      <c r="AB64">
-        <v>0</v>
-      </c>
-      <c r="AC64">
-        <v>0</v>
-      </c>
-      <c r="AD64">
-        <v>0</v>
-      </c>
-      <c r="AE64">
-        <v>0</v>
-      </c>
-      <c r="AF64">
-        <v>0</v>
-      </c>
-      <c r="AG64">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64">
-        <v>0</v>
-      </c>
-      <c r="AK64">
-        <v>0</v>
-      </c>
-      <c r="AL64">
-        <v>0</v>
-      </c>
-      <c r="AM64">
-        <v>-1</v>
-      </c>
-      <c r="AN64">
-        <v>-1</v>
-      </c>
-      <c r="AO64">
-        <v>-1</v>
-      </c>
-      <c r="AP64">
-        <v>-1</v>
-      </c>
-      <c r="AQ64">
-        <v>0</v>
-      </c>
-      <c r="AR64">
-        <v>0</v>
-      </c>
-      <c r="AS64">
-        <v>0</v>
-      </c>
-      <c r="AT64">
-        <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>2026-10-28 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Seattle Sounders</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Houston Dynamo</t>
-        </is>
-      </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
-      <c r="K65">
-        <v>0</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
-      <c r="O65">
-        <v>0</v>
-      </c>
-      <c r="P65">
-        <v>0</v>
-      </c>
-      <c r="Q65">
-        <v>0</v>
-      </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65">
-        <v>0</v>
-      </c>
-      <c r="T65">
-        <v>0</v>
-      </c>
-      <c r="U65">
-        <v>0</v>
-      </c>
-      <c r="V65">
-        <v>0</v>
-      </c>
-      <c r="W65">
-        <v>0</v>
-      </c>
-      <c r="X65">
-        <v>0</v>
-      </c>
-      <c r="Y65">
-        <v>0</v>
-      </c>
-      <c r="Z65">
-        <v>0</v>
-      </c>
-      <c r="AA65">
-        <v>0</v>
-      </c>
-      <c r="AB65">
-        <v>0</v>
-      </c>
-      <c r="AC65">
-        <v>0</v>
-      </c>
-      <c r="AD65">
-        <v>0</v>
-      </c>
-      <c r="AE65">
-        <v>0</v>
-      </c>
-      <c r="AF65">
-        <v>0</v>
-      </c>
-      <c r="AG65">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>0</v>
-      </c>
-      <c r="AK65">
-        <v>0</v>
-      </c>
-      <c r="AL65">
-        <v>0</v>
-      </c>
-      <c r="AM65">
-        <v>-1</v>
-      </c>
-      <c r="AN65">
-        <v>-1</v>
-      </c>
-      <c r="AO65">
-        <v>-1</v>
-      </c>
-      <c r="AP65">
-        <v>-1</v>
-      </c>
-      <c r="AQ65">
-        <v>0</v>
-      </c>
-      <c r="AR65">
-        <v>0</v>
-      </c>
-      <c r="AS65">
-        <v>0</v>
-      </c>
-      <c r="AT65">
-        <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>2026-10-28 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>San Diego</t>
-        </is>
-      </c>
-      <c r="G66">
-        <v>0</v>
-      </c>
-      <c r="H66">
-        <v>0</v>
-      </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-      <c r="J66">
-        <v>0</v>
-      </c>
-      <c r="K66">
-        <v>0</v>
-      </c>
-      <c r="L66">
-        <v>0</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N66">
-        <v>0</v>
-      </c>
-      <c r="O66">
-        <v>0</v>
-      </c>
-      <c r="P66">
-        <v>0</v>
-      </c>
-      <c r="Q66">
-        <v>0</v>
-      </c>
-      <c r="R66">
-        <v>0</v>
-      </c>
-      <c r="S66">
-        <v>0</v>
-      </c>
-      <c r="T66">
-        <v>0</v>
-      </c>
-      <c r="U66">
-        <v>0</v>
-      </c>
-      <c r="V66">
-        <v>0</v>
-      </c>
-      <c r="W66">
-        <v>0</v>
-      </c>
-      <c r="X66">
-        <v>0</v>
-      </c>
-      <c r="Y66">
-        <v>0</v>
-      </c>
-      <c r="Z66">
-        <v>0</v>
-      </c>
-      <c r="AA66">
-        <v>0</v>
-      </c>
-      <c r="AB66">
-        <v>0</v>
-      </c>
-      <c r="AC66">
-        <v>0</v>
-      </c>
-      <c r="AD66">
-        <v>0</v>
-      </c>
-      <c r="AE66">
-        <v>0</v>
-      </c>
-      <c r="AF66">
-        <v>0</v>
-      </c>
-      <c r="AG66">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>0</v>
-      </c>
-      <c r="AK66">
-        <v>0</v>
-      </c>
-      <c r="AL66">
-        <v>0</v>
-      </c>
-      <c r="AM66">
-        <v>-1</v>
-      </c>
-      <c r="AN66">
-        <v>-1</v>
-      </c>
-      <c r="AO66">
-        <v>-1</v>
-      </c>
-      <c r="AP66">
-        <v>-1</v>
-      </c>
-      <c r="AQ66">
-        <v>0</v>
-      </c>
-      <c r="AR66">
-        <v>0</v>
-      </c>
-      <c r="AS66">
-        <v>0</v>
-      </c>
-      <c r="AT66">
-        <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
         <is>
           <t>2026-10-28 23:30:00</t>
         </is>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.31</v>
+        <v>2.99</v>
       </c>
       <c r="O35">
-        <v>5.56</v>
+        <v>3.43</v>
       </c>
       <c r="P35">
-        <v>10.2</v>
+        <v>2.41</v>
       </c>
       <c r="Q35">
-        <v>1.71</v>
+        <v>3.5</v>
       </c>
       <c r="R35">
-        <v>2.63</v>
+        <v>2.09</v>
       </c>
       <c r="S35">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="T35">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="U35">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="V35">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
         <v>1</v>
       </c>
       <c r="Y35">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="Z35">
-        <v>4.85</v>
+        <v>3.25</v>
       </c>
       <c r="AA35">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AB35">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AC35">
-        <v>2.37</v>
+        <v>3.32</v>
       </c>
       <c r="AD35">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="AE35">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AG35">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>3.6</v>
+        <v>1.36</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.99</v>
+        <v>1.31</v>
       </c>
       <c r="O36">
-        <v>3.43</v>
+        <v>5.56</v>
       </c>
       <c r="P36">
-        <v>2.41</v>
+        <v>10.2</v>
       </c>
       <c r="Q36">
-        <v>3.5</v>
+        <v>1.71</v>
       </c>
       <c r="R36">
-        <v>2.09</v>
+        <v>2.63</v>
       </c>
       <c r="S36">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="T36">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="U36">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="W36">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X36">
         <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z36">
-        <v>3.25</v>
+        <v>4.85</v>
       </c>
       <c r="AA36">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AB36">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AC36">
-        <v>3.32</v>
+        <v>2.37</v>
       </c>
       <c r="AD36">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="AE36">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AF36">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AG36">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK36">
-        <v>1.36</v>
+        <v>3.6</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G62">

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,61 +6177,61 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.31</v>
+        <v>1.98</v>
       </c>
       <c r="O36">
-        <v>5.56</v>
+        <v>3.51</v>
       </c>
       <c r="P36">
-        <v>10.2</v>
+        <v>3.96</v>
       </c>
       <c r="Q36">
-        <v>1.71</v>
+        <v>2.62</v>
       </c>
       <c r="R36">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="S36">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="T36">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="U36">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="V36">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="W36">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X36">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="Z36">
-        <v>4.85</v>
+        <v>2.78</v>
       </c>
       <c r="AA36">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AB36">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AC36">
-        <v>2.37</v>
+        <v>3.76</v>
       </c>
       <c r="AD36">
-        <v>1.56</v>
+        <v>1.19</v>
       </c>
       <c r="AE36">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AG36">
         <v>1.8</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,61 +6340,61 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.98</v>
+        <v>1.31</v>
       </c>
       <c r="O37">
-        <v>3.51</v>
+        <v>5.56</v>
       </c>
       <c r="P37">
-        <v>3.96</v>
+        <v>10.2</v>
       </c>
       <c r="Q37">
-        <v>2.62</v>
+        <v>1.71</v>
       </c>
       <c r="R37">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="S37">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="T37">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="U37">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="V37">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="W37">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y37">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="Z37">
-        <v>2.78</v>
+        <v>4.85</v>
       </c>
       <c r="AA37">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AB37">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AC37">
-        <v>3.76</v>
+        <v>2.37</v>
       </c>
       <c r="AD37">
-        <v>1.19</v>
+        <v>1.56</v>
       </c>
       <c r="AE37">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF37">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AG37">
         <v>1.8</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK37">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="AL37">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="O5">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="P5">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="Q5">
         <v>2.02</v>
@@ -1139,16 +1139,16 @@
         <v>2.24</v>
       </c>
       <c r="S5">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>2.94</v>
+        <v>3.19</v>
       </c>
       <c r="U5">
-        <v>2.51</v>
+        <v>2.67</v>
       </c>
       <c r="V5">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
         <v>1.11</v>
@@ -1163,10 +1163,10 @@
         <v>3.82</v>
       </c>
       <c r="AA5">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AB5">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AC5">
         <v>2.94</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK5">
         <v>2.16</v>
@@ -1287,25 +1287,25 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.87</v>
+        <v>4.12</v>
       </c>
       <c r="O6">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P6">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="Q6">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="R6">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S6">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="U6">
         <v>2.33</v>
@@ -1335,16 +1335,16 @@
         <v>2.75</v>
       </c>
       <c r="AD6">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AE6">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF6">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AG6">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>2</v>
+        <v>1.08</v>
       </c>
       <c r="AK6">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1462,25 +1462,25 @@
         <v>2.75</v>
       </c>
       <c r="R7">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T7">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="U7">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W7">
         <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
         <v>1.25</v>
@@ -1489,25 +1489,25 @@
         <v>3.6</v>
       </c>
       <c r="AA7">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB7">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AC7">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="AD7">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE7">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
         <v>1.62</v>
       </c>
       <c r="AG7">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AK7">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1652,7 +1652,7 @@
         <v>4.15</v>
       </c>
       <c r="AA8">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB8">
         <v>2.2</v>
@@ -3252,55 +3252,55 @@
         <v>2.5</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL18">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -1139,10 +1139,10 @@
         <v>2.24</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T5">
-        <v>3.19</v>
+        <v>2.94</v>
       </c>
       <c r="U5">
         <v>2.67</v>
@@ -1462,13 +1462,13 @@
         <v>2.75</v>
       </c>
       <c r="R7">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="S7">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="U7">
         <v>2.38</v>
@@ -1480,34 +1480,34 @@
         <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA7">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AB7">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AC7">
-        <v>2.83</v>
+        <v>2.66</v>
       </c>
       <c r="AD7">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE7">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF7">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG7">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AK7">
         <v>1.5</v>
@@ -1625,7 +1625,7 @@
         <v>2.88</v>
       </c>
       <c r="R8">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S8">
         <v>1.27</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="P12">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="Q12">
         <v>2.83</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="O13">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="P13">
-        <v>6.07</v>
+        <v>5.5</v>
       </c>
       <c r="Q13">
         <v>2.15</v>
@@ -2443,7 +2443,7 @@
         <v>2.22</v>
       </c>
       <c r="S13">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
         <v>3.1</v>
@@ -2467,7 +2467,7 @@
         <v>3.79</v>
       </c>
       <c r="AA13">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AB13">
         <v>2</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>8.449999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="O14">
-        <v>6.33</v>
+        <v>6.05</v>
       </c>
       <c r="P14">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Q14">
         <v>7</v>
@@ -2609,13 +2609,13 @@
         <v>1.17</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="U14">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V14">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="W14">
         <v>1.26</v>
@@ -2636,19 +2636,19 @@
         <v>3.34</v>
       </c>
       <c r="AC14">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AD14">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AE14">
         <v>1.41</v>
       </c>
       <c r="AF14">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG14">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="O15">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="P15">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q15">
         <v>3.69</v>
@@ -2784,7 +2784,7 @@
         <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
         <v>1.38</v>
@@ -2802,13 +2802,13 @@
         <v>3.82</v>
       </c>
       <c r="AD15">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE15">
         <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG15">
         <v>1.91</v>
@@ -2923,7 +2923,7 @@
         <v>3.4</v>
       </c>
       <c r="P16">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.6</v>
+        <v>4.16</v>
       </c>
       <c r="O17">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P17">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="O18">
         <v>3.25</v>
       </c>
       <c r="P18">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -3258,7 +3258,7 @@
         <v>2.1</v>
       </c>
       <c r="S18">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T18">
         <v>2.82</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK18">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="O19">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="P19">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="Q19">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="R19">
         <v>2.38</v>
@@ -3427,25 +3427,25 @@
         <v>3.46</v>
       </c>
       <c r="U19">
-        <v>2.21</v>
+        <v>2.39</v>
       </c>
       <c r="V19">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z19">
-        <v>4.3</v>
+        <v>4.58</v>
       </c>
       <c r="AA19">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AB19">
         <v>2.2</v>
@@ -3457,13 +3457,13 @@
         <v>1.46</v>
       </c>
       <c r="AE19">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
         <v>1.61</v>
       </c>
       <c r="AG19">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.21</v>
       </c>
       <c r="AK19">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="O22">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="P22">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="Q22">
         <v>3.1</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O26">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="Q26">
         <v>2.44</v>
@@ -4562,22 +4562,22 @@
         <v>2.25</v>
       </c>
       <c r="S26">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T26">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U26">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="V26">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W26">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
         <v>1.15</v>
@@ -4598,13 +4598,13 @@
         <v>1.43</v>
       </c>
       <c r="AE26">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AF26">
         <v>1.55</v>
       </c>
       <c r="AG26">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="O27">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="Q27">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="R27">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S27">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T27">
         <v>3.1</v>
       </c>
       <c r="U27">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="V27">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z27">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA27">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AB27">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AC27">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AD27">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG27">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O28">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
         <v>3</v>
@@ -4885,7 +4885,7 @@
         <v>2.81</v>
       </c>
       <c r="R28">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S28">
         <v>1.35</v>
@@ -4912,10 +4912,10 @@
         <v>3.42</v>
       </c>
       <c r="AA28">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB28">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AC28">
         <v>3.25</v>
@@ -4927,7 +4927,7 @@
         <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG28">
         <v>2.06</v>
@@ -5039,16 +5039,16 @@
         <v>3.44</v>
       </c>
       <c r="O29">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q29">
         <v>4.03</v>
       </c>
       <c r="R29">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S29">
         <v>1.3</v>
@@ -5063,7 +5063,7 @@
         <v>1.46</v>
       </c>
       <c r="W29">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
         <v>1.04</v>
@@ -5075,10 +5075,10 @@
         <v>3.88</v>
       </c>
       <c r="AA29">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AB29">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AC29">
         <v>2.66</v>
@@ -5202,10 +5202,10 @@
         <v>1.28</v>
       </c>
       <c r="O30">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="P30">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="Q30">
         <v>1.67</v>
@@ -5241,7 +5241,7 @@
         <v>1.4</v>
       </c>
       <c r="AB30">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AC30">
         <v>1.9</v>
@@ -5253,10 +5253,10 @@
         <v>1.31</v>
       </c>
       <c r="AF30">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG30">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>5.61</v>
+        <v>5.25</v>
       </c>
       <c r="O31">
-        <v>4.02</v>
+        <v>3.86</v>
       </c>
       <c r="P31">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -5377,13 +5377,13 @@
         <v>2.2</v>
       </c>
       <c r="S31">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T31">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="U31">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="V31">
         <v>1.35</v>
@@ -5398,13 +5398,13 @@
         <v>1.34</v>
       </c>
       <c r="Z31">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="AA31">
-        <v>1.84</v>
+        <v>2.11</v>
       </c>
       <c r="AB31">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AC31">
         <v>3.64</v>
@@ -5419,7 +5419,7 @@
         <v>1.95</v>
       </c>
       <c r="AG31">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.27</v>
       </c>
       <c r="AK31">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.22</v>
+        <v>3.7</v>
       </c>
       <c r="O32">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="P32">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q32">
         <v>4.47</v>
@@ -5546,7 +5546,7 @@
         <v>3.23</v>
       </c>
       <c r="U32">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="V32">
         <v>1.46</v>
@@ -5576,7 +5576,7 @@
         <v>1.44</v>
       </c>
       <c r="AE32">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF32">
         <v>1.65</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AK32">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="O34">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="Q34">
         <v>3.74</v>
@@ -5893,7 +5893,7 @@
         <v>1.72</v>
       </c>
       <c r="AB34">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC34">
         <v>2.75</v>
@@ -5905,7 +5905,7 @@
         <v>1.13</v>
       </c>
       <c r="AF34">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG34">
         <v>2.2</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="O3">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
         <v>2.61</v>
@@ -825,28 +825,28 @@
         <v>1.36</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z3">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AA3">
         <v>2.12</v>
       </c>
       <c r="AB3">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC3">
-        <v>3.71</v>
+        <v>3.58</v>
       </c>
       <c r="AD3">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AE3">
         <v>1.03</v>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK3">
         <v>1.44</v>
@@ -1139,7 +1139,7 @@
         <v>2.24</v>
       </c>
       <c r="S5">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
         <v>2.94</v>
@@ -1465,10 +1465,10 @@
         <v>2.19</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T7">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="U7">
         <v>2.38</v>
@@ -1486,13 +1486,13 @@
         <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA7">
         <v>1.69</v>
       </c>
       <c r="AB7">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AC7">
         <v>2.66</v>
@@ -1504,7 +1504,7 @@
         <v>1.12</v>
       </c>
       <c r="AF7">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG7">
         <v>2.19</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="O11">
         <v>2.97</v>
       </c>
       <c r="P11">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="Q11">
         <v>2.62</v>
@@ -2138,16 +2138,16 @@
         <v>1.42</v>
       </c>
       <c r="Z11">
-        <v>2.69</v>
+        <v>2.49</v>
       </c>
       <c r="AA11">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AB11">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AC11">
-        <v>4.38</v>
+        <v>4.3</v>
       </c>
       <c r="AD11">
         <v>1.15</v>
@@ -2159,7 +2159,7 @@
         <v>2.1</v>
       </c>
       <c r="AG11">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK11">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2485,7 +2485,7 @@
         <v>1.85</v>
       </c>
       <c r="AG13">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>4.16</v>
+        <v>2.39</v>
       </c>
       <c r="O17">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P17">
-        <v>1.67</v>
+        <v>2.62</v>
       </c>
       <c r="Q17">
-        <v>4.41</v>
+        <v>3</v>
       </c>
       <c r="R17">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="S17">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="T17">
-        <v>3.8</v>
+        <v>2.82</v>
       </c>
       <c r="U17">
-        <v>2.11</v>
+        <v>2.62</v>
       </c>
       <c r="V17">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="Z17">
-        <v>5.05</v>
+        <v>3.61</v>
       </c>
       <c r="AA17">
+        <v>1.88</v>
+      </c>
+      <c r="AB17">
+        <v>1.86</v>
+      </c>
+      <c r="AC17">
+        <v>3.08</v>
+      </c>
+      <c r="AD17">
+        <v>1.28</v>
+      </c>
+      <c r="AE17">
+        <v>1.07</v>
+      </c>
+      <c r="AF17">
+        <v>1.69</v>
+      </c>
+      <c r="AG17">
+        <v>2.05</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>1.33</v>
+      </c>
+      <c r="AK17">
         <v>1.44</v>
-      </c>
-      <c r="AB17">
-        <v>2.36</v>
-      </c>
-      <c r="AC17">
-        <v>2.19</v>
-      </c>
-      <c r="AD17">
-        <v>1.58</v>
-      </c>
-      <c r="AE17">
-        <v>1.2</v>
-      </c>
-      <c r="AF17">
-        <v>1.5</v>
-      </c>
-      <c r="AG17">
-        <v>2.4</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.22</v>
-      </c>
-      <c r="AK17">
-        <v>1.22</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
+        <v>4.6</v>
+      </c>
+      <c r="O18">
+        <v>4</v>
+      </c>
+      <c r="P18">
+        <v>1.64</v>
+      </c>
+      <c r="Q18">
+        <v>4.8</v>
+      </c>
+      <c r="R18">
+        <v>2.38</v>
+      </c>
+      <c r="S18">
+        <v>1.25</v>
+      </c>
+      <c r="T18">
+        <v>3.46</v>
+      </c>
+      <c r="U18">
         <v>2.39</v>
       </c>
-      <c r="O18">
-        <v>3.25</v>
-      </c>
-      <c r="P18">
-        <v>2.75</v>
-      </c>
-      <c r="Q18">
-        <v>3</v>
-      </c>
-      <c r="R18">
-        <v>2.1</v>
-      </c>
-      <c r="S18">
-        <v>1.33</v>
-      </c>
-      <c r="T18">
-        <v>2.82</v>
-      </c>
-      <c r="U18">
-        <v>2.74</v>
-      </c>
       <c r="V18">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="W18">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z18">
-        <v>3.61</v>
+        <v>4.58</v>
       </c>
       <c r="AA18">
-        <v>1.88</v>
+        <v>1.61</v>
       </c>
       <c r="AB18">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AC18">
-        <v>3.08</v>
+        <v>2.38</v>
       </c>
       <c r="AD18">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AE18">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AF18">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AG18">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AK18">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="O19">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P19">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="Q19">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z19">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC19">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD19">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG19">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK19">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
+        <v>4.2</v>
+      </c>
+      <c r="O20">
         <v>3.8</v>
       </c>
-      <c r="O20">
-        <v>3.85</v>
-      </c>
       <c r="P20">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4577,7 +4577,7 @@
         <v>1.15</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
         <v>1.15</v>
@@ -4586,7 +4586,7 @@
         <v>4.2</v>
       </c>
       <c r="AA26">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB26">
         <v>2.2</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O27">
         <v>3.4</v>
@@ -5066,7 +5066,7 @@
         <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
         <v>1.18</v>
@@ -5401,7 +5401,7 @@
         <v>3.17</v>
       </c>
       <c r="AA31">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB31">
         <v>1.85</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.7</v>
+        <v>4.36</v>
       </c>
       <c r="O32">
         <v>3.7</v>
@@ -5534,22 +5534,22 @@
         <v>1.89</v>
       </c>
       <c r="Q32">
-        <v>4.47</v>
+        <v>4.94</v>
       </c>
       <c r="R32">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="S32">
         <v>1.3</v>
       </c>
       <c r="T32">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="U32">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="V32">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W32">
         <v>1.08</v>
@@ -5561,19 +5561,19 @@
         <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>4.08</v>
+        <v>4.14</v>
       </c>
       <c r="AA32">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB32">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AC32">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AD32">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE32">
         <v>1.13</v>
@@ -5582,7 +5582,7 @@
         <v>1.65</v>
       </c>
       <c r="AG32">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AK32">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5881,7 +5881,7 @@
         <v>1.1</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
         <v>1.18</v>
@@ -5893,7 +5893,7 @@
         <v>1.72</v>
       </c>
       <c r="AB34">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC34">
         <v>2.75</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="O35">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
         <v>2.41</v>
@@ -6026,52 +6026,52 @@
         <v>3.5</v>
       </c>
       <c r="R35">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S35">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T35">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="U35">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V35">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X35">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
         <v>1.3</v>
       </c>
       <c r="Z35">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AA35">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB35">
         <v>1.75</v>
       </c>
       <c r="AC35">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="AD35">
         <v>1.31</v>
       </c>
       <c r="AE35">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF35">
         <v>1.75</v>
       </c>
       <c r="AG35">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK35">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,61 +6177,61 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O36">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="Q36">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="R36">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="S36">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="U36">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="V36">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W36">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y36">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z36">
-        <v>2.78</v>
+        <v>3.14</v>
       </c>
       <c r="AA36">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AB36">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AC36">
-        <v>3.76</v>
+        <v>3.52</v>
       </c>
       <c r="AD36">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AE36">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AG36">
         <v>1.8</v>
@@ -6250,7 +6250,7 @@
         <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="O37">
-        <v>5.56</v>
+        <v>5.5</v>
       </c>
       <c r="P37">
-        <v>10.2</v>
+        <v>9</v>
       </c>
       <c r="Q37">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="R37">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="S37">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U37">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V37">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W37">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X37">
         <v>1</v>
       </c>
       <c r="Y37">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z37">
-        <v>4.85</v>
+        <v>5.12</v>
       </c>
       <c r="AA37">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AB37">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC37">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="AD37">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AE37">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AF37">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AG37">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AK37">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>1.53</v>
       </c>
       <c r="O38">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P38">
-        <v>5.56</v>
+        <v>5.28</v>
       </c>
       <c r="Q38">
         <v>2.04</v>
@@ -6539,13 +6539,13 @@
         <v>1.24</v>
       </c>
       <c r="Z38">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AA38">
         <v>1.78</v>
       </c>
       <c r="AB38">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC38">
         <v>2.66</v>
@@ -6554,13 +6554,13 @@
         <v>1.37</v>
       </c>
       <c r="AE38">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF38">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG38">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6711,10 +6711,10 @@
         <v>0</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7037,10 +7037,10 @@
         <v>0</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7200,10 +7200,10 @@
         <v>0</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7357,10 +7357,10 @@
         <v>0</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC43">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9150,10 +9150,10 @@
         <v>0</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC54">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9319,10 +9319,10 @@
         <v>0</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9645,10 +9645,10 @@
         <v>0</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9808,10 +9808,10 @@
         <v>0</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10134,10 +10134,10 @@
         <v>0</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE60">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -2470,7 +2470,7 @@
         <v>1.84</v>
       </c>
       <c r="AB13">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC13">
         <v>3.06</v>
@@ -2633,7 +2633,7 @@
         <v>1.32</v>
       </c>
       <c r="AB14">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AC14">
         <v>1.82</v>
@@ -5528,10 +5528,10 @@
         <v>4.36</v>
       </c>
       <c r="O32">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P32">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="Q32">
         <v>4.94</v>
@@ -5564,10 +5564,10 @@
         <v>4.14</v>
       </c>
       <c r="AA32">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB32">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AC32">
         <v>2.76</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -1652,7 +1652,7 @@
         <v>4.15</v>
       </c>
       <c r="AA8">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB8">
         <v>2.2</v>
@@ -3249,7 +3249,7 @@
         <v>4</v>
       </c>
       <c r="P18">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q18">
         <v>4.8</v>
@@ -3261,7 +3261,7 @@
         <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="U18">
         <v>2.39</v>
@@ -3572,7 +3572,7 @@
         <v>4.2</v>
       </c>
       <c r="O20">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="P20">
         <v>1.67</v>
@@ -3934,7 +3934,7 @@
         <v>3.6</v>
       </c>
       <c r="AA22">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AB22">
         <v>1.98</v>
@@ -4550,10 +4550,10 @@
         <v>1.95</v>
       </c>
       <c r="O26">
+        <v>3.7</v>
+      </c>
+      <c r="P26">
         <v>3.6</v>
-      </c>
-      <c r="P26">
-        <v>3.75</v>
       </c>
       <c r="Q26">
         <v>2.44</v>
@@ -4601,7 +4601,7 @@
         <v>1.21</v>
       </c>
       <c r="AF26">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG26">
         <v>2.4</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O27">
         <v>3.4</v>
       </c>
       <c r="P27">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q27">
         <v>2.53</v>
@@ -5202,10 +5202,10 @@
         <v>1.28</v>
       </c>
       <c r="O30">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="P30">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Q30">
         <v>1.67</v>
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="N35">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="O35">
+        <v>3.3</v>
+      </c>
+      <c r="P35">
+        <v>2.5</v>
+      </c>
+      <c r="Q35">
         <v>3.4</v>
       </c>
-      <c r="P35">
-        <v>2.41</v>
-      </c>
-      <c r="Q35">
-        <v>3.5</v>
-      </c>
       <c r="R35">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="S35">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="U35">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V35">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W35">
         <v>1.05</v>
@@ -6047,31 +6047,31 @@
         <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z35">
-        <v>3.45</v>
+        <v>3.63</v>
       </c>
       <c r="AA35">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AB35">
         <v>1.75</v>
       </c>
       <c r="AC35">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD35">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE35">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF35">
         <v>1.75</v>
       </c>
       <c r="AG35">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.34</v>
       </c>
       <c r="AK35">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6183,7 +6183,7 @@
         <v>3.5</v>
       </c>
       <c r="P36">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q36">
         <v>2.52</v>
@@ -6343,10 +6343,10 @@
         <v>1.33</v>
       </c>
       <c r="O37">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="P37">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Q37">
         <v>1.65</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="O39">
-        <v>3.6</v>
+        <v>4.74</v>
       </c>
       <c r="P39">
-        <v>3.2</v>
+        <v>5.05</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6711,10 +6711,10 @@
         <v>0</v>
       </c>
       <c r="AC39">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6874,10 +6874,10 @@
         <v>0</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="O41">
-        <v>4.6</v>
+        <v>4.21</v>
       </c>
       <c r="P41">
-        <v>4.6</v>
+        <v>3.53</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7037,10 +7037,10 @@
         <v>0</v>
       </c>
       <c r="AC41">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AD41">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AE41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="O42">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P42">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7200,10 +7200,10 @@
         <v>0</v>
       </c>
       <c r="AC42">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AD42">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AE42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="O43">
+        <v>3.96</v>
+      </c>
+      <c r="P43">
         <v>3.75</v>
-      </c>
-      <c r="P43">
-        <v>3.6</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O52">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="P52">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="Q52">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R52">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S52">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U52">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V52">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W52">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X52">
         <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z52">
-        <v>3.75</v>
+        <v>4.18</v>
       </c>
       <c r="AA52">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB52">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC52">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD52">
         <v>1.4</v>
       </c>
       <c r="AE52">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF52">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AG52">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AK52">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="O53">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="P53">
-        <v>3.82</v>
+        <v>3.54</v>
       </c>
       <c r="Q53">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="R53">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S53">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T53">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="U53">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="V53">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W53">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X53">
         <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z53">
-        <v>3.24</v>
+        <v>3.53</v>
       </c>
       <c r="AA53">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="AB53">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC53">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AD53">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE53">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF53">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG53">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.3</v>
       </c>
       <c r="AK53">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="O55">
-        <v>4.6</v>
+        <v>4.79</v>
       </c>
       <c r="P55">
-        <v>4.33</v>
+        <v>4.58</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9482,10 +9482,10 @@
         <v>0</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="O57">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="P57">
-        <v>5.75</v>
+        <v>4.51</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9645,10 +9645,10 @@
         <v>0</v>
       </c>
       <c r="AC57">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD57">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE57">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O58">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P58">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="O59">
-        <v>3.77</v>
+        <v>3.8</v>
       </c>
       <c r="P59">
-        <v>3.16</v>
+        <v>2.98</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10092,10 +10092,10 @@
         <v>2.1</v>
       </c>
       <c r="O60">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="P60">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>5.31</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q62">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -1290,10 +1290,10 @@
         <v>4.12</v>
       </c>
       <c r="O6">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P6">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -1471,10 +1471,10 @@
         <v>2.87</v>
       </c>
       <c r="U7">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V7">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
         <v>1.1</v>
@@ -2304,7 +2304,7 @@
         <v>4.2</v>
       </c>
       <c r="AA12">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB12">
         <v>2.15</v>
@@ -2485,7 +2485,7 @@
         <v>1.85</v>
       </c>
       <c r="AG13">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="O14">
         <v>6.05</v>
@@ -2606,16 +2606,16 @@
         <v>3.11</v>
       </c>
       <c r="S14">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T14">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="U14">
         <v>1.85</v>
       </c>
       <c r="V14">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W14">
         <v>1.26</v>
@@ -2793,7 +2793,7 @@
         <v>3.04</v>
       </c>
       <c r="AA15">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AB15">
         <v>1.66</v>
@@ -3246,13 +3246,13 @@
         <v>4.6</v>
       </c>
       <c r="O18">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P18">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q18">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="R18">
         <v>2.38</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O20">
         <v>4.15</v>
       </c>
       <c r="P20">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q20">
         <v>4.41</v>
@@ -3904,7 +3904,7 @@
         <v>2.29</v>
       </c>
       <c r="Q22">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R22">
         <v>2.2</v>
@@ -4725,7 +4725,7 @@
         <v>2.15</v>
       </c>
       <c r="S27">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T27">
         <v>3.1</v>
@@ -4758,7 +4758,7 @@
         <v>2.92</v>
       </c>
       <c r="AD27">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE27">
         <v>1.08</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="O29">
         <v>3.6</v>
@@ -5528,13 +5528,13 @@
         <v>4.36</v>
       </c>
       <c r="O32">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P32">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q32">
-        <v>4.94</v>
+        <v>4.99</v>
       </c>
       <c r="R32">
         <v>2.42</v>
@@ -5893,7 +5893,7 @@
         <v>1.72</v>
       </c>
       <c r="AB34">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC34">
         <v>2.75</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O35">
         <v>3.3</v>
@@ -6186,10 +6186,10 @@
         <v>3.9</v>
       </c>
       <c r="Q36">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="R36">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="S36">
         <v>1.36</v>
@@ -6198,7 +6198,7 @@
         <v>2.9</v>
       </c>
       <c r="U36">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="V36">
         <v>1.39</v>
@@ -6222,7 +6222,7 @@
         <v>1.8</v>
       </c>
       <c r="AC36">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="AD36">
         <v>1.29</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="O37">
         <v>5.75</v>
@@ -6382,7 +6382,7 @@
         <v>1.52</v>
       </c>
       <c r="AB37">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AC37">
         <v>2.27</v>
@@ -6397,7 +6397,7 @@
         <v>1.85</v>
       </c>
       <c r="AG37">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="O39">
-        <v>4.74</v>
+        <v>4.64</v>
       </c>
       <c r="P39">
-        <v>5.05</v>
+        <v>4.94</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="O40">
-        <v>5.05</v>
+        <v>4.85</v>
       </c>
       <c r="P40">
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6995,10 +6995,10 @@
         <v>1.95</v>
       </c>
       <c r="O41">
-        <v>4.21</v>
+        <v>3.75</v>
       </c>
       <c r="P41">
-        <v>3.53</v>
+        <v>3.1</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="O43">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="P43">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="N53">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O53">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
         <v>3.54</v>
@@ -8990,7 +8990,7 @@
         <v>1.86</v>
       </c>
       <c r="AB53">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AC53">
         <v>3.25</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="O54">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P54">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="O56">
         <v>5</v>
       </c>
       <c r="P56">
-        <v>5.25</v>
+        <v>5.8</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="O57">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P57">
-        <v>4.51</v>
+        <v>4</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="O59">
         <v>3.8</v>
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="O61">
-        <v>5.31</v>
+        <v>5.2</v>
       </c>
       <c r="P61">
         <v>6.15</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="O62">
-        <v>3.94</v>
+        <v>3.78</v>
       </c>
       <c r="P62">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="Q62">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -816,7 +816,7 @@
         <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.76</v>
+        <v>2.51</v>
       </c>
       <c r="U3">
         <v>2.9</v>
@@ -1163,10 +1163,10 @@
         <v>3.82</v>
       </c>
       <c r="AA5">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AB5">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AC5">
         <v>2.94</v>
@@ -1293,7 +1293,7 @@
         <v>3.7</v>
       </c>
       <c r="P6">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="O11">
         <v>2.97</v>
@@ -2114,7 +2114,7 @@
         <v>2.62</v>
       </c>
       <c r="R11">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="S11">
         <v>1.44</v>
@@ -2141,10 +2141,10 @@
         <v>2.49</v>
       </c>
       <c r="AA11">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AB11">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AC11">
         <v>4.3</v>
@@ -2283,7 +2283,7 @@
         <v>1.27</v>
       </c>
       <c r="T12">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U12">
         <v>2.5</v>
@@ -2428,49 +2428,49 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="O13">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P13">
         <v>5.5</v>
       </c>
       <c r="Q13">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R13">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
         <v>1.3</v>
       </c>
       <c r="T13">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U13">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V13">
         <v>1.44</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
         <v>1.25</v>
       </c>
       <c r="Z13">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="AA13">
         <v>1.84</v>
       </c>
       <c r="AB13">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="AC13">
         <v>3.06</v>
@@ -2482,10 +2482,10 @@
         <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG13">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="O14">
         <v>6.05</v>
@@ -2600,25 +2600,25 @@
         <v>1.3</v>
       </c>
       <c r="Q14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>3.11</v>
+        <v>2.88</v>
       </c>
       <c r="S14">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="U14">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="V14">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="W14">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="X14">
         <v>1</v>
@@ -2630,25 +2630,25 @@
         <v>7.21</v>
       </c>
       <c r="AA14">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AB14">
         <v>3.4</v>
       </c>
       <c r="AC14">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AD14">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AE14">
         <v>1.41</v>
       </c>
       <c r="AF14">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG14">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK14">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,37 +2754,37 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="O15">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="P15">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q15">
-        <v>3.69</v>
+        <v>3.5</v>
       </c>
       <c r="R15">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S15">
         <v>1.44</v>
       </c>
       <c r="T15">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U15">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="V15">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W15">
+        <v>1.05</v>
+      </c>
+      <c r="X15">
         <v>1.03</v>
-      </c>
-      <c r="X15">
-        <v>1.05</v>
       </c>
       <c r="Y15">
         <v>1.38</v>
@@ -2793,10 +2793,10 @@
         <v>3.04</v>
       </c>
       <c r="AA15">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB15">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC15">
         <v>3.82</v>
@@ -2808,10 +2808,10 @@
         <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG15">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AK15">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3098,7 +3098,7 @@
         <v>1.33</v>
       </c>
       <c r="T17">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="U17">
         <v>2.62</v>
@@ -3267,7 +3267,7 @@
         <v>2.39</v>
       </c>
       <c r="V18">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W18">
         <v>1.11</v>
@@ -3572,7 +3572,7 @@
         <v>4.1</v>
       </c>
       <c r="O20">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="P20">
         <v>1.7</v>
@@ -3584,19 +3584,19 @@
         <v>2.44</v>
       </c>
       <c r="S20">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T20">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="U20">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="V20">
         <v>1.62</v>
       </c>
       <c r="W20">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3898,7 +3898,7 @@
         <v>2.65</v>
       </c>
       <c r="O22">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="P22">
         <v>2.29</v>
@@ -3968,7 +3968,7 @@
         <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4556,46 +4556,46 @@
         <v>3.6</v>
       </c>
       <c r="Q26">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="R26">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S26">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T26">
         <v>3.6</v>
       </c>
       <c r="U26">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="V26">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W26">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z26">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA26">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB26">
         <v>2.2</v>
       </c>
       <c r="AC26">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="AD26">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AE26">
         <v>1.21</v>
@@ -4620,7 +4620,7 @@
         <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4740,7 +4740,7 @@
         <v>1.11</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
         <v>1.21</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="O28">
         <v>3.4</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O29">
         <v>3.6</v>
@@ -5048,7 +5048,7 @@
         <v>4.03</v>
       </c>
       <c r="R29">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S29">
         <v>1.3</v>
@@ -5066,7 +5066,7 @@
         <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
         <v>1.18</v>
@@ -5075,10 +5075,10 @@
         <v>3.88</v>
       </c>
       <c r="AA29">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AB29">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AC29">
         <v>2.66</v>
@@ -5202,10 +5202,10 @@
         <v>1.28</v>
       </c>
       <c r="O30">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="P30">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q30">
         <v>1.67</v>
@@ -5244,10 +5244,10 @@
         <v>2.74</v>
       </c>
       <c r="AC30">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AD30">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AE30">
         <v>1.31</v>
@@ -5371,10 +5371,10 @@
         <v>1.64</v>
       </c>
       <c r="Q31">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R31">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S31">
         <v>1.41</v>
@@ -5392,7 +5392,7 @@
         <v>1.05</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
         <v>1.34</v>
@@ -5401,10 +5401,10 @@
         <v>3.17</v>
       </c>
       <c r="AA31">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB31">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AC31">
         <v>3.64</v>
@@ -5416,10 +5416,10 @@
         <v>1.04</v>
       </c>
       <c r="AF31">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG31">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5531,31 +5531,31 @@
         <v>3.9</v>
       </c>
       <c r="P32">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q32">
-        <v>4.99</v>
+        <v>4.89</v>
       </c>
       <c r="R32">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="S32">
         <v>1.3</v>
       </c>
       <c r="T32">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U32">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="V32">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W32">
         <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
         <v>1.22</v>
@@ -5567,7 +5567,7 @@
         <v>1.73</v>
       </c>
       <c r="AB32">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AC32">
         <v>2.76</v>
@@ -5579,10 +5579,10 @@
         <v>1.13</v>
       </c>
       <c r="AF32">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG32">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>2</v>
       </c>
       <c r="AK32">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5881,7 +5881,7 @@
         <v>1.1</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
         <v>1.18</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="O57">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P57">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9645,10 +9645,10 @@
         <v>0</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="O58">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P58">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9808,10 +9808,10 @@
         <v>0</v>
       </c>
       <c r="AC58">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD58">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="O59">
         <v>3.8</v>
       </c>
       <c r="P59">
-        <v>2.98</v>
+        <v>4</v>
       </c>
       <c r="Q59">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -1133,10 +1133,10 @@
         <v>4.5</v>
       </c>
       <c r="Q5">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="R5">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="S5">
         <v>1.33</v>
@@ -1151,7 +1151,7 @@
         <v>1.44</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK5">
         <v>2.16</v>
@@ -1465,7 +1465,7 @@
         <v>2.19</v>
       </c>
       <c r="S7">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
         <v>2.87</v>
@@ -2289,7 +2289,7 @@
         <v>2.5</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W12">
         <v>1.07</v>
@@ -2304,7 +2304,7 @@
         <v>4.2</v>
       </c>
       <c r="AA12">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB12">
         <v>2.15</v>
@@ -2431,7 +2431,7 @@
         <v>1.61</v>
       </c>
       <c r="O13">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P13">
         <v>5.5</v>
@@ -2805,7 +2805,7 @@
         <v>1.22</v>
       </c>
       <c r="AE15">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF15">
         <v>1.73</v>
@@ -3083,10 +3083,10 @@
         <v>2.39</v>
       </c>
       <c r="O17">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P17">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="N18">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="O18">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P18">
         <v>1.66</v>
@@ -3264,7 +3264,7 @@
         <v>3.4</v>
       </c>
       <c r="U18">
-        <v>2.39</v>
+        <v>2.21</v>
       </c>
       <c r="V18">
         <v>1.57</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="O19">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="P19">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,61 +3569,61 @@
         </is>
       </c>
       <c r="N20">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="O20">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P20">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="Q20">
-        <v>4.41</v>
+        <v>3.69</v>
       </c>
       <c r="R20">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="S20">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T20">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="U20">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="V20">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W20">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z20">
-        <v>5.05</v>
+        <v>4.45</v>
       </c>
       <c r="AA20">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AB20">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="AC20">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="AD20">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AE20">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF20">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG20">
         <v>2.4</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3910,7 +3910,7 @@
         <v>2.2</v>
       </c>
       <c r="S22">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T22">
         <v>3.2</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.41</v>
+        <v>2.21</v>
       </c>
       <c r="O23">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="P23">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>1.95</v>
       </c>
       <c r="O26">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P26">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -4713,10 +4713,10 @@
         <v>2</v>
       </c>
       <c r="O27">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q27">
         <v>2.53</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.24</v>
+        <v>2.47</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="Q28">
-        <v>2.81</v>
+        <v>3.11</v>
       </c>
       <c r="R28">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="S28">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="U28">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="V28">
         <v>1.44</v>
       </c>
       <c r="W28">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z28">
-        <v>3.42</v>
+        <v>4.03</v>
       </c>
       <c r="AA28">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB28">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AC28">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="AD28">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE28">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF28">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG28">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK28">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5039,61 +5039,61 @@
         <v>3.4</v>
       </c>
       <c r="O29">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P29">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q29">
-        <v>4.03</v>
+        <v>3.94</v>
       </c>
       <c r="R29">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S29">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T29">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="U29">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="V29">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W29">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z29">
-        <v>3.88</v>
+        <v>4.25</v>
       </c>
       <c r="AA29">
         <v>1.63</v>
       </c>
       <c r="AB29">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="AC29">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="AD29">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AE29">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF29">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG29">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.29</v>
       </c>
       <c r="AK29">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5202,7 +5202,7 @@
         <v>1.28</v>
       </c>
       <c r="O30">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="P30">
         <v>9.199999999999999</v>
@@ -5211,16 +5211,16 @@
         <v>1.67</v>
       </c>
       <c r="R30">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="S30">
         <v>1.18</v>
       </c>
       <c r="T30">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="U30">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="V30">
         <v>1.83</v>
@@ -5232,31 +5232,31 @@
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z30">
-        <v>5.65</v>
+        <v>5.95</v>
       </c>
       <c r="AA30">
         <v>1.4</v>
       </c>
       <c r="AB30">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="AC30">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AD30">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AE30">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AF30">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AG30">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.11</v>
       </c>
       <c r="AK30">
-        <v>3.65</v>
+        <v>3.58</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="O32">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P32">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="Q32">
         <v>4.89</v>
@@ -5540,19 +5540,19 @@
         <v>2.43</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U32">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V32">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
         <v>1.01</v>
@@ -5579,10 +5579,10 @@
         <v>1.13</v>
       </c>
       <c r="AF32">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG32">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AK32">
         <v>1.17</v>
@@ -5854,16 +5854,16 @@
         <v>3.1</v>
       </c>
       <c r="O34">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P34">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q34">
-        <v>3.74</v>
+        <v>3.69</v>
       </c>
       <c r="R34">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="S34">
         <v>1.3</v>
@@ -5872,43 +5872,43 @@
         <v>3.25</v>
       </c>
       <c r="U34">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="V34">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W34">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
         <v>1.18</v>
       </c>
       <c r="Z34">
-        <v>3.92</v>
+        <v>4.81</v>
       </c>
       <c r="AA34">
         <v>1.72</v>
       </c>
       <c r="AB34">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AC34">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AD34">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE34">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF34">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG34">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O36">
         <v>3.5</v>
       </c>
       <c r="P36">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q36">
         <v>2.51</v>
@@ -6201,7 +6201,7 @@
         <v>2.96</v>
       </c>
       <c r="V36">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W36">
         <v>1.07</v>
@@ -6367,7 +6367,7 @@
         <v>1.67</v>
       </c>
       <c r="W37">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X37">
         <v>1</v>
@@ -6397,7 +6397,7 @@
         <v>1.85</v>
       </c>
       <c r="AG37">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.05</v>
       </c>
       <c r="AK37">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6506,16 +6506,16 @@
         <v>1.53</v>
       </c>
       <c r="O38">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P38">
-        <v>5.28</v>
+        <v>5.25</v>
       </c>
       <c r="Q38">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="R38">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S38">
         <v>1.29</v>
@@ -6524,43 +6524,43 @@
         <v>3.3</v>
       </c>
       <c r="U38">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="V38">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X38">
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="AA38">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AB38">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AC38">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="AD38">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE38">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF38">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG38">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK38">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="O39">
-        <v>4.64</v>
+        <v>4.9</v>
       </c>
       <c r="P39">
-        <v>4.94</v>
+        <v>4.9</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X39">
         <v>0</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.51</v>
+        <v>1.91</v>
       </c>
       <c r="O40">
-        <v>4.85</v>
+        <v>3.75</v>
       </c>
       <c r="P40">
-        <v>4.5</v>
+        <v>3.53</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X40">
         <v>0</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>6.07</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC40">
-        <v>1.57</v>
+        <v>2.06</v>
       </c>
       <c r="AD40">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="O41">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P41">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AC41">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="AD41">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.09</v>
+        <v>1.83</v>
       </c>
       <c r="O42">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P42">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC42">
-        <v>2.15</v>
+        <v>2.52</v>
       </c>
       <c r="AD42">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,80 +7318,80 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="O43">
-        <v>3.8</v>
+        <v>4.64</v>
       </c>
       <c r="P43">
-        <v>3.6</v>
+        <v>4.94</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X43">
         <v>0</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="AA43">
+        <v>1.44</v>
+      </c>
+      <c r="AB43">
+        <v>2.77</v>
+      </c>
+      <c r="AC43">
+        <v>2.14</v>
+      </c>
+      <c r="AD43">
+        <v>1.72</v>
+      </c>
+      <c r="AE43">
+        <v>1.29</v>
+      </c>
+      <c r="AF43">
         <v>1.53</v>
       </c>
-      <c r="AB43">
+      <c r="AG43">
+        <v>2.4</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <v>1.2</v>
+      </c>
+      <c r="AK43">
         <v>2.3</v>
-      </c>
-      <c r="AC43">
-        <v>0</v>
-      </c>
-      <c r="AD43">
-        <v>0</v>
-      </c>
-      <c r="AE43">
-        <v>0</v>
-      </c>
-      <c r="AF43">
-        <v>0</v>
-      </c>
-      <c r="AG43">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>0</v>
-      </c>
-      <c r="AK43">
-        <v>0</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O52">
         <v>3.6</v>
       </c>
       <c r="P52">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -8824,10 +8824,10 @@
         <v>4.18</v>
       </c>
       <c r="AA52">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB52">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC52">
         <v>2.7</v>
@@ -8839,7 +8839,7 @@
         <v>1.13</v>
       </c>
       <c r="AF52">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG52">
         <v>2.3</v>
@@ -8948,28 +8948,28 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O53">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P53">
         <v>3.54</v>
       </c>
       <c r="Q53">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="R53">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="S53">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T53">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="U53">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="V53">
         <v>1.43</v>
@@ -9002,10 +9002,10 @@
         <v>1.14</v>
       </c>
       <c r="AF53">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG53">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O54">
         <v>3.4</v>
       </c>
       <c r="P54">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X54">
         <v>0</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="AA54">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AB54">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O55">
-        <v>4.79</v>
+        <v>4</v>
       </c>
       <c r="P55">
-        <v>4.58</v>
+        <v>4</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X55">
         <v>0</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AC55">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AD55">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="O56">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="P56">
-        <v>5.8</v>
+        <v>3.58</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC56">
-        <v>1.82</v>
+        <v>2.34</v>
       </c>
       <c r="AD56">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O57">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P57">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X57">
         <v>0</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AC57">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD57">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="O58">
-        <v>3.8</v>
+        <v>4.32</v>
       </c>
       <c r="P58">
-        <v>2.98</v>
+        <v>4</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X58">
         <v>0</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="O59">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="P59">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X59">
         <v>0</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>6.99</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10092,61 +10092,61 @@
         <v>2.1</v>
       </c>
       <c r="O60">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="P60">
-        <v>3.17</v>
+        <v>2.93</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X60">
         <v>0</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC60">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="AD60">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10255,61 +10255,61 @@
         <v>1.44</v>
       </c>
       <c r="O61">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="P61">
-        <v>6.15</v>
+        <v>6</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X61">
         <v>0</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10418,61 +10418,61 @@
         <v>1.87</v>
       </c>
       <c r="O62">
-        <v>3.78</v>
+        <v>3.86</v>
       </c>
       <c r="P62">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X62">
         <v>0</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL62">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -2434,10 +2434,10 @@
         <v>4</v>
       </c>
       <c r="P13">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="Q13">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R13">
         <v>2.25</v>
@@ -2449,37 +2449,37 @@
         <v>3.2</v>
       </c>
       <c r="U13">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V13">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
         <v>1.07</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
         <v>1.25</v>
       </c>
       <c r="Z13">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AA13">
         <v>1.84</v>
       </c>
       <c r="AB13">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC13">
-        <v>3.06</v>
+        <v>2.79</v>
       </c>
       <c r="AD13">
         <v>1.37</v>
       </c>
       <c r="AE13">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF13">
         <v>1.8</v>
@@ -2501,7 +2501,7 @@
         <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2594,7 +2594,7 @@
         <v>7.75</v>
       </c>
       <c r="O14">
-        <v>6.05</v>
+        <v>5.75</v>
       </c>
       <c r="P14">
         <v>1.3</v>
@@ -2612,10 +2612,10 @@
         <v>4.8</v>
       </c>
       <c r="U14">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="V14">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="W14">
         <v>1.2</v>
@@ -2627,28 +2627,28 @@
         <v>1.07</v>
       </c>
       <c r="Z14">
-        <v>7.21</v>
+        <v>8</v>
       </c>
       <c r="AA14">
         <v>1.33</v>
       </c>
       <c r="AB14">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AC14">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AD14">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AE14">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AF14">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG14">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.67</v>
+        <v>2.95</v>
       </c>
       <c r="O15">
         <v>3.23</v>
       </c>
       <c r="P15">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q15">
         <v>3.5</v>
@@ -2784,7 +2784,7 @@
         <v>1.05</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y15">
         <v>1.38</v>
@@ -2793,19 +2793,19 @@
         <v>3.04</v>
       </c>
       <c r="AA15">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB15">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC15">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="AD15">
         <v>1.22</v>
       </c>
       <c r="AE15">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF15">
         <v>1.73</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="O31">
         <v>3.86</v>
       </c>
       <c r="P31">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q31">
         <v>5</v>
@@ -5392,7 +5392,7 @@
         <v>1.05</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y31">
         <v>1.34</v>
@@ -5401,10 +5401,10 @@
         <v>3.17</v>
       </c>
       <c r="AA31">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB31">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC31">
         <v>3.64</v>
@@ -5416,7 +5416,7 @@
         <v>1.04</v>
       </c>
       <c r="AF31">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG31">
         <v>1.83</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="AK31">
         <v>1.14</v>
@@ -5525,19 +5525,19 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="O32">
-        <v>3.85</v>
+        <v>3.71</v>
       </c>
       <c r="P32">
         <v>1.72</v>
       </c>
       <c r="Q32">
-        <v>4.89</v>
+        <v>4.61</v>
       </c>
       <c r="R32">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="S32">
         <v>1.29</v>
@@ -5546,16 +5546,16 @@
         <v>3.3</v>
       </c>
       <c r="U32">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
         <v>1.22</v>
@@ -5564,10 +5564,10 @@
         <v>4.14</v>
       </c>
       <c r="AA32">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB32">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC32">
         <v>2.76</v>
@@ -5598,7 +5598,7 @@
         <v>1.91</v>
       </c>
       <c r="AK32">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6186,7 +6186,7 @@
         <v>3.8</v>
       </c>
       <c r="Q36">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="R36">
         <v>2.1</v>
@@ -6198,7 +6198,7 @@
         <v>2.9</v>
       </c>
       <c r="U36">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="V36">
         <v>1.4</v>
@@ -6213,28 +6213,28 @@
         <v>1.33</v>
       </c>
       <c r="Z36">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AA36">
         <v>2.06</v>
       </c>
       <c r="AB36">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC36">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="AD36">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE36">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF36">
         <v>1.84</v>
       </c>
       <c r="AG36">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>1.3</v>
       </c>
       <c r="O37">
-        <v>5.75</v>
+        <v>5.65</v>
       </c>
       <c r="P37">
         <v>8.5</v>
@@ -6358,7 +6358,7 @@
         <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="U37">
         <v>2.18</v>
@@ -6382,7 +6382,7 @@
         <v>1.52</v>
       </c>
       <c r="AB37">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AC37">
         <v>2.27</v>
@@ -6829,16 +6829,16 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O40">
-        <v>3.75</v>
+        <v>4.21</v>
       </c>
       <c r="P40">
-        <v>3.53</v>
+        <v>3.1</v>
       </c>
       <c r="Q40">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="R40">
         <v>2.65</v>
@@ -6995,7 +6995,7 @@
         <v>2.09</v>
       </c>
       <c r="O41">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P41">
         <v>3.35</v>
@@ -7321,19 +7321,19 @@
         <v>1.5</v>
       </c>
       <c r="O43">
-        <v>4.64</v>
+        <v>4.9</v>
       </c>
       <c r="P43">
-        <v>4.94</v>
+        <v>4.8</v>
       </c>
       <c r="Q43">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R43">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="S43">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T43">
         <v>4</v>
@@ -7345,31 +7345,31 @@
         <v>1.7</v>
       </c>
       <c r="W43">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X43">
         <v>0</v>
       </c>
       <c r="Y43">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z43">
-        <v>5.78</v>
+        <v>6</v>
       </c>
       <c r="AA43">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB43">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AC43">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AD43">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AE43">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF43">
         <v>1.53</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK43">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8791,7 +8791,7 @@
         <v>3.6</v>
       </c>
       <c r="P52">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
         <v>1.44</v>
@@ -8972,7 +8972,7 @@
         <v>2.69</v>
       </c>
       <c r="V53">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W53">
         <v>1.08</v>
@@ -8990,16 +8990,16 @@
         <v>1.86</v>
       </c>
       <c r="AB53">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC53">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD53">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE53">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF53">
         <v>1.67</v>
@@ -9114,10 +9114,10 @@
         <v>2.6</v>
       </c>
       <c r="O54">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P54">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="Q54">
         <v>3.09</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="O56">
         <v>3.9</v>
@@ -9449,7 +9449,7 @@
         <v>2.4</v>
       </c>
       <c r="R56">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="S56">
         <v>1.25</v>
@@ -9603,10 +9603,10 @@
         <v>1.91</v>
       </c>
       <c r="O57">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P57">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q57">
         <v>2.4</v>
@@ -9645,7 +9645,7 @@
         <v>2.57</v>
       </c>
       <c r="AC57">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AD57">
         <v>1.66</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="O59">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P59">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q59">
         <v>1.73</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="O60">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="P60">
-        <v>2.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q60">
-        <v>2.64</v>
+        <v>1.85</v>
       </c>
       <c r="R60">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="S60">
+        <v>1.18</v>
+      </c>
+      <c r="T60">
+        <v>4.5</v>
+      </c>
+      <c r="U60">
+        <v>1.85</v>
+      </c>
+      <c r="V60">
+        <v>1.85</v>
+      </c>
+      <c r="W60">
         <v>1.25</v>
       </c>
-      <c r="T60">
-        <v>3.7</v>
-      </c>
-      <c r="U60">
-        <v>2.2</v>
-      </c>
-      <c r="V60">
-        <v>1.62</v>
-      </c>
-      <c r="W60">
-        <v>1.17</v>
-      </c>
       <c r="X60">
         <v>0</v>
       </c>
       <c r="Y60">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="Z60">
-        <v>4.99</v>
+        <v>8</v>
       </c>
       <c r="AA60">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AB60">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="AC60">
-        <v>2.41</v>
+        <v>1.85</v>
       </c>
       <c r="AD60">
-        <v>1.58</v>
+        <v>1.99</v>
       </c>
       <c r="AE60">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AF60">
         <v>1.44</v>
       </c>
       <c r="AG60">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK60">
-        <v>1.73</v>
+        <v>2.62</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,80 +10252,80 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="O61">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="P61">
-        <v>6</v>
+        <v>3.55</v>
       </c>
       <c r="Q61">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="R61">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="S61">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="T61">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="U61">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="V61">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="W61">
+        <v>1.14</v>
+      </c>
+      <c r="X61">
+        <v>0</v>
+      </c>
+      <c r="Y61">
+        <v>1.2</v>
+      </c>
+      <c r="Z61">
+        <v>4.52</v>
+      </c>
+      <c r="AA61">
+        <v>1.64</v>
+      </c>
+      <c r="AB61">
+        <v>2.28</v>
+      </c>
+      <c r="AC61">
+        <v>2.58</v>
+      </c>
+      <c r="AD61">
+        <v>1.51</v>
+      </c>
+      <c r="AE61">
+        <v>1.2</v>
+      </c>
+      <c r="AF61">
+        <v>1.6</v>
+      </c>
+      <c r="AG61">
+        <v>2.25</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ61">
         <v>1.25</v>
       </c>
-      <c r="X61">
-        <v>0</v>
-      </c>
-      <c r="Y61">
-        <v>1.03</v>
-      </c>
-      <c r="Z61">
-        <v>8</v>
-      </c>
-      <c r="AA61">
-        <v>1.3</v>
-      </c>
-      <c r="AB61">
-        <v>3.3</v>
-      </c>
-      <c r="AC61">
-        <v>1.85</v>
-      </c>
-      <c r="AD61">
-        <v>1.99</v>
-      </c>
-      <c r="AE61">
-        <v>1.4</v>
-      </c>
-      <c r="AF61">
-        <v>1.44</v>
-      </c>
-      <c r="AG61">
-        <v>2.62</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ61">
-        <v>1.17</v>
-      </c>
       <c r="AK61">
-        <v>2.62</v>
+        <v>1.83</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="O62">
-        <v>3.86</v>
+        <v>3.65</v>
       </c>
       <c r="P62">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q62">
-        <v>2.38</v>
+        <v>2.68</v>
       </c>
       <c r="R62">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="S62">
+        <v>1.25</v>
+      </c>
+      <c r="T62">
+        <v>3.7</v>
+      </c>
+      <c r="U62">
+        <v>2.2</v>
+      </c>
+      <c r="V62">
+        <v>1.62</v>
+      </c>
+      <c r="W62">
+        <v>1.17</v>
+      </c>
+      <c r="X62">
+        <v>0</v>
+      </c>
+      <c r="Y62">
+        <v>1.17</v>
+      </c>
+      <c r="Z62">
+        <v>4.98</v>
+      </c>
+      <c r="AA62">
+        <v>1.58</v>
+      </c>
+      <c r="AB62">
+        <v>2.4</v>
+      </c>
+      <c r="AC62">
+        <v>2.41</v>
+      </c>
+      <c r="AD62">
+        <v>1.58</v>
+      </c>
+      <c r="AE62">
+        <v>1.23</v>
+      </c>
+      <c r="AF62">
+        <v>1.44</v>
+      </c>
+      <c r="AG62">
+        <v>2.5</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
         <v>1.29</v>
       </c>
-      <c r="T62">
-        <v>3.5</v>
-      </c>
-      <c r="U62">
-        <v>2.3</v>
-      </c>
-      <c r="V62">
-        <v>1.55</v>
-      </c>
-      <c r="W62">
-        <v>1.14</v>
-      </c>
-      <c r="X62">
-        <v>0</v>
-      </c>
-      <c r="Y62">
-        <v>1.2</v>
-      </c>
-      <c r="Z62">
-        <v>4.52</v>
-      </c>
-      <c r="AA62">
-        <v>1.64</v>
-      </c>
-      <c r="AB62">
-        <v>2.28</v>
-      </c>
-      <c r="AC62">
-        <v>2.58</v>
-      </c>
-      <c r="AD62">
-        <v>1.51</v>
-      </c>
-      <c r="AE62">
-        <v>1.2</v>
-      </c>
-      <c r="AF62">
-        <v>1.6</v>
-      </c>
-      <c r="AG62">
-        <v>2.25</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.25</v>
-      </c>
       <c r="AK62">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL62">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -1483,10 +1483,10 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z7">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA7">
         <v>1.69</v>
@@ -1504,7 +1504,7 @@
         <v>1.12</v>
       </c>
       <c r="AF7">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG7">
         <v>2.19</v>
@@ -1652,7 +1652,7 @@
         <v>4.15</v>
       </c>
       <c r="AA8">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB8">
         <v>2.2</v>
@@ -2304,7 +2304,7 @@
         <v>4.2</v>
       </c>
       <c r="AA12">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB12">
         <v>2.15</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="O13">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P13">
-        <v>4.75</v>
+        <v>4.95</v>
       </c>
       <c r="Q13">
         <v>2.1</v>
@@ -2446,13 +2446,13 @@
         <v>1.3</v>
       </c>
       <c r="T13">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="U13">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W13">
         <v>1.07</v>
@@ -2467,16 +2467,16 @@
         <v>3.8</v>
       </c>
       <c r="AA13">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AB13">
         <v>1.9</v>
       </c>
       <c r="AC13">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="AD13">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE13">
         <v>1.1</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="O14">
         <v>5.75</v>
       </c>
       <c r="P14">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Q14">
         <v>6</v>
@@ -2648,7 +2648,7 @@
         <v>1.5</v>
       </c>
       <c r="AG14">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK14">
         <v>1.06</v>
@@ -2769,7 +2769,7 @@
         <v>2</v>
       </c>
       <c r="S15">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T15">
         <v>2.75</v>
@@ -2787,10 +2787,10 @@
         <v>1.06</v>
       </c>
       <c r="Y15">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z15">
-        <v>3.04</v>
+        <v>3.09</v>
       </c>
       <c r="AA15">
         <v>2.2</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="O16">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3083,19 +3083,19 @@
         <v>2.39</v>
       </c>
       <c r="O17">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="Q17">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="R17">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="S17">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T17">
         <v>3</v>
@@ -3107,7 +3107,7 @@
         <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
         <v>1.01</v>
@@ -3119,10 +3119,10 @@
         <v>3.61</v>
       </c>
       <c r="AA17">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB17">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC17">
         <v>3.08</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK17">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="O18">
         <v>3.85</v>
@@ -3252,10 +3252,10 @@
         <v>1.66</v>
       </c>
       <c r="Q18">
-        <v>4.5</v>
+        <v>4.16</v>
       </c>
       <c r="R18">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="S18">
         <v>1.25</v>
@@ -3279,13 +3279,13 @@
         <v>1.19</v>
       </c>
       <c r="Z18">
-        <v>4.58</v>
+        <v>4.56</v>
       </c>
       <c r="AA18">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB18">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC18">
         <v>2.38</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK18">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,25 +3415,25 @@
         <v>1.7</v>
       </c>
       <c r="Q19">
-        <v>4.41</v>
+        <v>3.77</v>
       </c>
       <c r="R19">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="S19">
         <v>1.22</v>
       </c>
       <c r="T19">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="U19">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="V19">
         <v>1.62</v>
       </c>
       <c r="W19">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3445,13 +3445,13 @@
         <v>5.05</v>
       </c>
       <c r="AA19">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB19">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AC19">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AD19">
         <v>1.62</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK19">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,22 +3569,22 @@
         </is>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O20">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q20">
-        <v>3.69</v>
+        <v>3.26</v>
       </c>
       <c r="R20">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S20">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T20">
         <v>3.5</v>
@@ -3599,7 +3599,7 @@
         <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
         <v>1.14</v>
@@ -3608,10 +3608,10 @@
         <v>4.45</v>
       </c>
       <c r="AA20">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB20">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AC20">
         <v>2.38</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK20">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3901,10 +3901,10 @@
         <v>3.25</v>
       </c>
       <c r="P22">
-        <v>2.29</v>
+        <v>2.6</v>
       </c>
       <c r="Q22">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="R22">
         <v>2.2</v>
@@ -3934,7 +3934,7 @@
         <v>3.6</v>
       </c>
       <c r="AA22">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB22">
         <v>1.98</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="O23">
         <v>3.32</v>
@@ -4073,49 +4073,49 @@
         <v>2.1</v>
       </c>
       <c r="S23">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T23">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U23">
         <v>2.8</v>
       </c>
       <c r="V23">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z23">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="AA23">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB23">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC23">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD23">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE23">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF23">
         <v>1.75</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AK23">
         <v>1.57</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="O24">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P24">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4556,7 +4556,7 @@
         <v>3.5</v>
       </c>
       <c r="Q26">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="R26">
         <v>2.3</v>
@@ -4568,7 +4568,7 @@
         <v>3.6</v>
       </c>
       <c r="U26">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="V26">
         <v>1.55</v>
@@ -4577,7 +4577,7 @@
         <v>1.11</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
         <v>1.13</v>
@@ -4598,7 +4598,7 @@
         <v>1.48</v>
       </c>
       <c r="AE26">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF26">
         <v>1.53</v>
@@ -4740,7 +4740,7 @@
         <v>1.11</v>
       </c>
       <c r="X27">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
         <v>1.21</v>
@@ -4876,13 +4876,13 @@
         <v>2.47</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P28">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q28">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="R28">
         <v>2.32</v>
@@ -4915,7 +4915,7 @@
         <v>1.8</v>
       </c>
       <c r="AB28">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AC28">
         <v>2.92</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK28">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5039,10 +5039,10 @@
         <v>3.4</v>
       </c>
       <c r="O29">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P29">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q29">
         <v>3.94</v>
@@ -5075,7 +5075,7 @@
         <v>4.25</v>
       </c>
       <c r="AA29">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB29">
         <v>2.21</v>
@@ -5087,7 +5087,7 @@
         <v>1.43</v>
       </c>
       <c r="AE29">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF29">
         <v>1.57</v>
@@ -5109,7 +5109,7 @@
         <v>1.29</v>
       </c>
       <c r="AK29">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O30">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="P30">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="Q30">
         <v>1.67</v>
@@ -5244,7 +5244,7 @@
         <v>3</v>
       </c>
       <c r="AC30">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AD30">
         <v>1.87</v>
@@ -5256,7 +5256,7 @@
         <v>1.65</v>
       </c>
       <c r="AG30">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK30">
         <v>3.58</v>
@@ -5374,19 +5374,19 @@
         <v>5</v>
       </c>
       <c r="R31">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S31">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T31">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="U31">
-        <v>3.09</v>
+        <v>3.18</v>
       </c>
       <c r="V31">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W31">
         <v>1.05</v>
@@ -5398,7 +5398,7 @@
         <v>1.34</v>
       </c>
       <c r="Z31">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="AA31">
         <v>2.05</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AK31">
         <v>1.14</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O32">
         <v>3.71</v>
@@ -5534,10 +5534,10 @@
         <v>1.72</v>
       </c>
       <c r="Q32">
-        <v>4.61</v>
+        <v>4.72</v>
       </c>
       <c r="R32">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="S32">
         <v>1.29</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O35">
         <v>3.3</v>
@@ -6026,7 +6026,7 @@
         <v>3.4</v>
       </c>
       <c r="R35">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
         <v>1.36</v>
@@ -6035,7 +6035,7 @@
         <v>2.66</v>
       </c>
       <c r="U35">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="V35">
         <v>1.4</v>
@@ -6047,13 +6047,13 @@
         <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z35">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
       <c r="AA35">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB35">
         <v>1.75</v>
@@ -6087,7 +6087,7 @@
         <v>1.34</v>
       </c>
       <c r="AK35">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O38">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P38">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q38">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="R38">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="S38">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
         <v>3.3</v>
       </c>
       <c r="U38">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="V38">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W38">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X38">
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z38">
-        <v>3.86</v>
+        <v>4.05</v>
       </c>
       <c r="AA38">
+        <v>1.68</v>
+      </c>
+      <c r="AB38">
+        <v>2.22</v>
+      </c>
+      <c r="AC38">
+        <v>2.62</v>
+      </c>
+      <c r="AD38">
+        <v>1.48</v>
+      </c>
+      <c r="AE38">
+        <v>1.11</v>
+      </c>
+      <c r="AF38">
         <v>1.72</v>
       </c>
-      <c r="AB38">
-        <v>2.03</v>
-      </c>
-      <c r="AC38">
-        <v>2.74</v>
-      </c>
-      <c r="AD38">
-        <v>1.35</v>
-      </c>
-      <c r="AE38">
-        <v>1.1</v>
-      </c>
-      <c r="AF38">
-        <v>1.8</v>
-      </c>
       <c r="AG38">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6678,7 +6678,7 @@
         <v>1.95</v>
       </c>
       <c r="R39">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="S39">
         <v>1.15</v>
@@ -6717,7 +6717,7 @@
         <v>2.25</v>
       </c>
       <c r="AE39">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AF39">
         <v>1.3</v>
@@ -6835,7 +6835,7 @@
         <v>4.21</v>
       </c>
       <c r="P40">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q40">
         <v>2.44</v>
@@ -6865,13 +6865,13 @@
         <v>1.13</v>
       </c>
       <c r="Z40">
-        <v>6.07</v>
+        <v>6.09</v>
       </c>
       <c r="AA40">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AB40">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="AC40">
         <v>2.06</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="O41">
         <v>3.6</v>
@@ -7158,10 +7158,10 @@
         <v>1.83</v>
       </c>
       <c r="O42">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P42">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -7197,7 +7197,7 @@
         <v>1.62</v>
       </c>
       <c r="AB42">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="AC42">
         <v>2.52</v>
@@ -7321,7 +7321,7 @@
         <v>1.5</v>
       </c>
       <c r="O43">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="P43">
         <v>4.8</v>
@@ -7357,7 +7357,7 @@
         <v>6</v>
       </c>
       <c r="AA43">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AB43">
         <v>2.75</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="O54">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P54">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="Q54">
         <v>3.09</v>
@@ -9277,10 +9277,10 @@
         <v>1.7</v>
       </c>
       <c r="O55">
-        <v>4</v>
+        <v>4.58</v>
       </c>
       <c r="P55">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="Q55">
         <v>2.04</v>
@@ -9479,7 +9479,7 @@
         <v>1.55</v>
       </c>
       <c r="AB56">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AC56">
         <v>2.34</v>
@@ -9766,7 +9766,7 @@
         <v>1.76</v>
       </c>
       <c r="O58">
-        <v>4.32</v>
+        <v>3.8</v>
       </c>
       <c r="P58">
         <v>4</v>
@@ -9805,7 +9805,7 @@
         <v>1.41</v>
       </c>
       <c r="AB58">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AC58">
         <v>2.04</v>
@@ -9932,7 +9932,7 @@
         <v>5</v>
       </c>
       <c r="P59">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Q59">
         <v>1.73</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="O60">
         <v>4.5</v>
       </c>
       <c r="P60">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="Q60">
         <v>1.85</v>
@@ -10258,13 +10258,13 @@
         <v>3.75</v>
       </c>
       <c r="P61">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
       </c>
       <c r="R61">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S61">
         <v>1.29</v>
@@ -10297,16 +10297,16 @@
         <v>2.28</v>
       </c>
       <c r="AC61">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AD61">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AE61">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF61">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG61">
         <v>2.25</v>
@@ -10325,7 +10325,7 @@
         <v>1.25</v>
       </c>
       <c r="AK61">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL62">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -804,7 +804,7 @@
         <v>3.1</v>
       </c>
       <c r="P3">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -816,7 +816,7 @@
         <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="U3">
         <v>2.9</v>
@@ -1468,13 +1468,13 @@
         <v>1.3</v>
       </c>
       <c r="T7">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="U7">
         <v>2.45</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W7">
         <v>1.1</v>
@@ -1492,7 +1492,7 @@
         <v>1.69</v>
       </c>
       <c r="AB7">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC7">
         <v>2.66</v>
@@ -1652,7 +1652,7 @@
         <v>4.15</v>
       </c>
       <c r="AA8">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB8">
         <v>2.2</v>
@@ -2141,7 +2141,7 @@
         <v>2.49</v>
       </c>
       <c r="AA11">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AB11">
         <v>1.53</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,80 +2428,80 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.51</v>
+        <v>7.5</v>
       </c>
       <c r="O13">
-        <v>4.05</v>
+        <v>5.75</v>
       </c>
       <c r="P13">
-        <v>4.95</v>
+        <v>1.33</v>
       </c>
       <c r="Q13">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="S13">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="T13">
-        <v>3.18</v>
+        <v>4.8</v>
       </c>
       <c r="U13">
-        <v>2.79</v>
+        <v>1.85</v>
       </c>
       <c r="V13">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="W13">
+        <v>1.2</v>
+      </c>
+      <c r="X13">
+        <v>1</v>
+      </c>
+      <c r="Y13">
         <v>1.07</v>
       </c>
-      <c r="X13">
-        <v>1.04</v>
-      </c>
-      <c r="Y13">
-        <v>1.25</v>
-      </c>
       <c r="Z13">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="AA13">
-        <v>1.88</v>
+        <v>1.33</v>
       </c>
       <c r="AB13">
+        <v>3.25</v>
+      </c>
+      <c r="AC13">
+        <v>1.87</v>
+      </c>
+      <c r="AD13">
         <v>1.9</v>
       </c>
-      <c r="AC13">
-        <v>2.82</v>
-      </c>
-      <c r="AD13">
-        <v>1.38</v>
-      </c>
       <c r="AE13">
+        <v>1.4</v>
+      </c>
+      <c r="AF13">
+        <v>1.5</v>
+      </c>
+      <c r="AG13">
+        <v>2.3</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
         <v>1.1</v>
       </c>
-      <c r="AF13">
-        <v>1.8</v>
-      </c>
-      <c r="AG13">
-        <v>1.95</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.22</v>
-      </c>
       <c r="AK13">
-        <v>2.2</v>
+        <v>1.06</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>7.5</v>
+        <v>2.95</v>
       </c>
       <c r="O14">
-        <v>5.75</v>
+        <v>3.23</v>
       </c>
       <c r="P14">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="Q14">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="R14">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="S14">
-        <v>1.14</v>
+        <v>1.46</v>
       </c>
       <c r="T14">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="U14">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="V14">
-        <v>1.85</v>
+        <v>1.29</v>
       </c>
       <c r="W14">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y14">
+        <v>1.39</v>
+      </c>
+      <c r="Z14">
+        <v>3.09</v>
+      </c>
+      <c r="AA14">
+        <v>2.2</v>
+      </c>
+      <c r="AB14">
+        <v>1.67</v>
+      </c>
+      <c r="AC14">
+        <v>4.1</v>
+      </c>
+      <c r="AD14">
+        <v>1.22</v>
+      </c>
+      <c r="AE14">
         <v>1.07</v>
       </c>
-      <c r="Z14">
-        <v>8</v>
-      </c>
-      <c r="AA14">
-        <v>1.33</v>
-      </c>
-      <c r="AB14">
-        <v>3.25</v>
-      </c>
-      <c r="AC14">
-        <v>1.87</v>
-      </c>
-      <c r="AD14">
-        <v>1.9</v>
-      </c>
-      <c r="AE14">
-        <v>1.4</v>
-      </c>
       <c r="AF14">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AG14">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="AK14">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.95</v>
+        <v>1.51</v>
       </c>
       <c r="O15">
-        <v>3.23</v>
+        <v>4.05</v>
       </c>
       <c r="P15">
-        <v>2.5</v>
+        <v>4.95</v>
       </c>
       <c r="Q15">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="R15">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S15">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>2.75</v>
+        <v>3.18</v>
       </c>
       <c r="U15">
-        <v>3.3</v>
+        <v>2.79</v>
       </c>
       <c r="V15">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="Z15">
-        <v>3.09</v>
+        <v>3.8</v>
       </c>
       <c r="AA15">
+        <v>1.88</v>
+      </c>
+      <c r="AB15">
+        <v>1.9</v>
+      </c>
+      <c r="AC15">
+        <v>2.82</v>
+      </c>
+      <c r="AD15">
+        <v>1.38</v>
+      </c>
+      <c r="AE15">
+        <v>1.1</v>
+      </c>
+      <c r="AF15">
+        <v>1.8</v>
+      </c>
+      <c r="AG15">
+        <v>1.95</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <v>1.22</v>
+      </c>
+      <c r="AK15">
         <v>2.2</v>
-      </c>
-      <c r="AB15">
-        <v>1.67</v>
-      </c>
-      <c r="AC15">
-        <v>4.1</v>
-      </c>
-      <c r="AD15">
-        <v>1.22</v>
-      </c>
-      <c r="AE15">
-        <v>1.07</v>
-      </c>
-      <c r="AF15">
-        <v>1.73</v>
-      </c>
-      <c r="AG15">
-        <v>2.05</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.35</v>
-      </c>
-      <c r="AK15">
-        <v>1.3</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.39</v>
+        <v>4.3</v>
       </c>
       <c r="O17">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="P17">
-        <v>2.62</v>
+        <v>1.66</v>
       </c>
       <c r="Q17">
-        <v>2.82</v>
+        <v>4.16</v>
       </c>
       <c r="R17">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="S17">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U17">
-        <v>2.62</v>
+        <v>2.21</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z17">
-        <v>3.61</v>
+        <v>4.56</v>
       </c>
       <c r="AA17">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AB17">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AC17">
-        <v>3.08</v>
+        <v>2.38</v>
       </c>
       <c r="AD17">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AE17">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AF17">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AG17">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AK17">
-        <v>1.47</v>
+        <v>1.15</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O18">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="P18">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="Q18">
-        <v>4.16</v>
+        <v>3.77</v>
       </c>
       <c r="R18">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="S18">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="U18">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="V18">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="Z18">
-        <v>4.56</v>
+        <v>5.05</v>
       </c>
       <c r="AA18">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AB18">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC18">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="AD18">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AE18">
         <v>1.2</v>
       </c>
       <c r="AF18">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AG18">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.19</v>
       </c>
       <c r="AK18">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,61 +3406,61 @@
         </is>
       </c>
       <c r="N19">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="O19">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Q19">
-        <v>3.77</v>
+        <v>3.26</v>
       </c>
       <c r="R19">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U19">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V19">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z19">
-        <v>5.05</v>
+        <v>4.45</v>
       </c>
       <c r="AA19">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB19">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC19">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="AD19">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AE19">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF19">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG19">
         <v>2.4</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK19">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.1</v>
+        <v>2.39</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P20">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="Q20">
-        <v>3.26</v>
+        <v>2.82</v>
       </c>
       <c r="R20">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="S20">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U20">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="V20">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="Z20">
-        <v>4.45</v>
+        <v>3.61</v>
       </c>
       <c r="AA20">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AB20">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AC20">
-        <v>2.38</v>
+        <v>3.08</v>
       </c>
       <c r="AD20">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AE20">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AF20">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AG20">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK20">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O26">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P26">
         <v>3.5</v>
       </c>
       <c r="Q26">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="R26">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S26">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="U26">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="V26">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W26">
         <v>1.11</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="Z26">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA26">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AB26">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AC26">
-        <v>2.33</v>
+        <v>3.1</v>
       </c>
       <c r="AD26">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AE26">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG26">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK26">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,28 +4710,28 @@
         </is>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>2.47</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P27">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q27">
-        <v>2.53</v>
+        <v>3.05</v>
       </c>
       <c r="R27">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="S27">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U27">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="V27">
         <v>1.44</v>
@@ -4740,34 +4740,34 @@
         <v>1.11</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z27">
-        <v>3.58</v>
+        <v>4.03</v>
       </c>
       <c r="AA27">
         <v>1.8</v>
       </c>
       <c r="AB27">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AC27">
         <v>2.92</v>
       </c>
       <c r="AD27">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE27">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF27">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG27">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.47</v>
+        <v>3.4</v>
       </c>
       <c r="O28">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P28">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="Q28">
-        <v>3.05</v>
+        <v>3.94</v>
       </c>
       <c r="R28">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T28">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="U28">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X28">
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z28">
-        <v>4.03</v>
+        <v>4.25</v>
       </c>
       <c r="AA28">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AB28">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC28">
-        <v>2.92</v>
+        <v>2.46</v>
       </c>
       <c r="AD28">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE28">
         <v>1.15</v>
       </c>
       <c r="AF28">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG28">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
+        <v>1.29</v>
+      </c>
+      <c r="AK28">
         <v>1.3</v>
-      </c>
-      <c r="AK28">
-        <v>1.47</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,65 +5036,65 @@
         </is>
       </c>
       <c r="N29">
+        <v>1.3</v>
+      </c>
+      <c r="O29">
+        <v>6.5</v>
+      </c>
+      <c r="P29">
+        <v>8.5</v>
+      </c>
+      <c r="Q29">
+        <v>1.67</v>
+      </c>
+      <c r="R29">
+        <v>2.78</v>
+      </c>
+      <c r="S29">
+        <v>1.18</v>
+      </c>
+      <c r="T29">
+        <v>3.98</v>
+      </c>
+      <c r="U29">
+        <v>1.91</v>
+      </c>
+      <c r="V29">
+        <v>1.83</v>
+      </c>
+      <c r="W29">
+        <v>1.22</v>
+      </c>
+      <c r="X29">
+        <v>1.01</v>
+      </c>
+      <c r="Y29">
+        <v>1.06</v>
+      </c>
+      <c r="Z29">
+        <v>6.25</v>
+      </c>
+      <c r="AA29">
+        <v>1.33</v>
+      </c>
+      <c r="AB29">
         <v>3.4</v>
       </c>
-      <c r="O29">
-        <v>3.75</v>
-      </c>
-      <c r="P29">
-        <v>2.05</v>
-      </c>
-      <c r="Q29">
-        <v>3.94</v>
-      </c>
-      <c r="R29">
+      <c r="AC29">
+        <v>1.81</v>
+      </c>
+      <c r="AD29">
+        <v>1.93</v>
+      </c>
+      <c r="AE29">
+        <v>1.37</v>
+      </c>
+      <c r="AF29">
+        <v>1.61</v>
+      </c>
+      <c r="AG29">
         <v>2.25</v>
       </c>
-      <c r="S29">
-        <v>1.28</v>
-      </c>
-      <c r="T29">
-        <v>3.24</v>
-      </c>
-      <c r="U29">
-        <v>2.38</v>
-      </c>
-      <c r="V29">
-        <v>1.5</v>
-      </c>
-      <c r="W29">
-        <v>1.12</v>
-      </c>
-      <c r="X29">
-        <v>1.02</v>
-      </c>
-      <c r="Y29">
-        <v>1.15</v>
-      </c>
-      <c r="Z29">
-        <v>4.25</v>
-      </c>
-      <c r="AA29">
-        <v>1.61</v>
-      </c>
-      <c r="AB29">
-        <v>2.21</v>
-      </c>
-      <c r="AC29">
-        <v>2.46</v>
-      </c>
-      <c r="AD29">
-        <v>1.43</v>
-      </c>
-      <c r="AE29">
-        <v>1.15</v>
-      </c>
-      <c r="AF29">
-        <v>1.57</v>
-      </c>
-      <c r="AG29">
-        <v>2.3</v>
-      </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="AK29">
-        <v>1.3</v>
+        <v>3.58</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="O30">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="P30">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q30">
-        <v>1.67</v>
+        <v>2.47</v>
       </c>
       <c r="R30">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="S30">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="T30">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="U30">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="V30">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="W30">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z30">
-        <v>5.95</v>
+        <v>4.5</v>
       </c>
       <c r="AA30">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB30">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AC30">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="AD30">
-        <v>1.87</v>
+        <v>1.48</v>
       </c>
       <c r="AE30">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AF30">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG30">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>3.58</v>
+        <v>1.79</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5860,25 +5860,25 @@
         <v>2.1</v>
       </c>
       <c r="Q34">
-        <v>3.69</v>
+        <v>3.72</v>
       </c>
       <c r="R34">
         <v>2.46</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T34">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U34">
         <v>2.26</v>
       </c>
       <c r="V34">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X34">
         <v>1.01</v>
@@ -5887,22 +5887,22 @@
         <v>1.18</v>
       </c>
       <c r="Z34">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="AA34">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AB34">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC34">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="AD34">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE34">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF34">
         <v>1.57</v>
@@ -6506,16 +6506,16 @@
         <v>1.55</v>
       </c>
       <c r="O38">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P38">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q38">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="R38">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
         <v>1.3</v>
@@ -6536,47 +6536,47 @@
         <v>1.02</v>
       </c>
       <c r="Y38">
+        <v>1.19</v>
+      </c>
+      <c r="Z38">
+        <v>4</v>
+      </c>
+      <c r="AA38">
+        <v>1.66</v>
+      </c>
+      <c r="AB38">
+        <v>2.1</v>
+      </c>
+      <c r="AC38">
+        <v>2.6</v>
+      </c>
+      <c r="AD38">
+        <v>1.45</v>
+      </c>
+      <c r="AE38">
+        <v>1.13</v>
+      </c>
+      <c r="AF38">
+        <v>1.67</v>
+      </c>
+      <c r="AG38">
+        <v>2.05</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
         <v>1.17</v>
       </c>
-      <c r="Z38">
-        <v>4.05</v>
-      </c>
-      <c r="AA38">
-        <v>1.68</v>
-      </c>
-      <c r="AB38">
-        <v>2.22</v>
-      </c>
-      <c r="AC38">
-        <v>2.62</v>
-      </c>
-      <c r="AD38">
-        <v>1.48</v>
-      </c>
-      <c r="AE38">
-        <v>1.11</v>
-      </c>
-      <c r="AF38">
-        <v>1.72</v>
-      </c>
-      <c r="AG38">
-        <v>1.95</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.2</v>
-      </c>
       <c r="AK38">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AL38">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -1166,7 +1166,7 @@
         <v>1.9</v>
       </c>
       <c r="AB5">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AC5">
         <v>2.94</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="N17">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="O17">
         <v>3.85</v>
@@ -3249,7 +3249,7 @@
         <v>3.75</v>
       </c>
       <c r="P18">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="Q18">
         <v>3.77</v>
@@ -3285,7 +3285,7 @@
         <v>1.5</v>
       </c>
       <c r="AB18">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AC18">
         <v>2.21</v>
@@ -3415,10 +3415,10 @@
         <v>2</v>
       </c>
       <c r="Q19">
-        <v>3.26</v>
+        <v>3.69</v>
       </c>
       <c r="R19">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="S19">
         <v>1.25</v>
@@ -3448,7 +3448,7 @@
         <v>1.6</v>
       </c>
       <c r="AB19">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AC19">
         <v>2.38</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.23</v>
+        <v>1.71</v>
       </c>
       <c r="AK19">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="O35">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
         <v>2.5</v>
@@ -6056,16 +6056,16 @@
         <v>1.9</v>
       </c>
       <c r="AB35">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC35">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD35">
         <v>1.34</v>
       </c>
       <c r="AE35">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF35">
         <v>1.75</v>
@@ -6183,7 +6183,7 @@
         <v>3.5</v>
       </c>
       <c r="P36">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Q36">
         <v>2.46</v>
@@ -6198,25 +6198,25 @@
         <v>2.9</v>
       </c>
       <c r="U36">
-        <v>2.93</v>
+        <v>2.66</v>
       </c>
       <c r="V36">
         <v>1.4</v>
       </c>
       <c r="W36">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X36">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
         <v>1.33</v>
       </c>
       <c r="Z36">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA36">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AB36">
         <v>1.85</v>
@@ -6250,7 +6250,7 @@
         <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6346,19 +6346,19 @@
         <v>5.65</v>
       </c>
       <c r="P37">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Q37">
         <v>1.65</v>
       </c>
       <c r="R37">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="S37">
         <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U37">
         <v>2.18</v>
@@ -6382,7 +6382,7 @@
         <v>1.52</v>
       </c>
       <c r="AB37">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC37">
         <v>2.27</v>
@@ -6394,7 +6394,7 @@
         <v>1.19</v>
       </c>
       <c r="AF37">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG37">
         <v>1.91</v>
@@ -6413,7 +6413,7 @@
         <v>1.05</v>
       </c>
       <c r="AK37">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -8785,25 +8785,25 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="O52">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P52">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="Q52">
         <v>3</v>
       </c>
       <c r="R52">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T52">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U52">
         <v>2.38</v>
@@ -8818,22 +8818,22 @@
         <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z52">
-        <v>4.18</v>
+        <v>4.13</v>
       </c>
       <c r="AA52">
         <v>1.65</v>
       </c>
       <c r="AB52">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AC52">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AD52">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE52">
         <v>1.13</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK52">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="N53">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="O53">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P53">
         <v>3.54</v>
@@ -8987,10 +8987,10 @@
         <v>3.53</v>
       </c>
       <c r="AA53">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB53">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC53">
         <v>3.1</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -2304,7 +2304,7 @@
         <v>4.2</v>
       </c>
       <c r="AA12">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB12">
         <v>2.15</v>
@@ -4553,7 +4553,7 @@
         <v>3.5</v>
       </c>
       <c r="P26">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q26">
         <v>2.53</v>
@@ -4589,7 +4589,7 @@
         <v>1.8</v>
       </c>
       <c r="AB26">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC26">
         <v>3.1</v>
@@ -4713,10 +4713,10 @@
         <v>2.47</v>
       </c>
       <c r="O27">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P27">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="Q27">
         <v>3.05</v>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="O28">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P28">
         <v>2.05</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="O29">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="P29">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="Q29">
         <v>1.67</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK29">
         <v>3.58</v>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="O30">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P30">
         <v>3.5</v>
@@ -5214,7 +5214,7 @@
         <v>2.3</v>
       </c>
       <c r="S30">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
         <v>3.6</v>
@@ -5223,10 +5223,10 @@
         <v>2.32</v>
       </c>
       <c r="V30">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X30">
         <v>1.01</v>
@@ -5241,7 +5241,7 @@
         <v>1.57</v>
       </c>
       <c r="AB30">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AC30">
         <v>2.33</v>
@@ -5857,7 +5857,7 @@
         <v>3.7</v>
       </c>
       <c r="P34">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="Q34">
         <v>3.72</v>
@@ -5878,7 +5878,7 @@
         <v>1.56</v>
       </c>
       <c r="W34">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
         <v>1.01</v>
@@ -5924,7 +5924,7 @@
         <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL34">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="O13">
-        <v>5.75</v>
+        <v>5.85</v>
       </c>
       <c r="P13">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Q13">
         <v>6</v>
@@ -2467,13 +2467,13 @@
         <v>8</v>
       </c>
       <c r="AA13">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AB13">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="AC13">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AD13">
         <v>1.9</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AK13">
         <v>1.06</v>
@@ -2917,25 +2917,25 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.37</v>
+        <v>2.47</v>
       </c>
       <c r="O16">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
       </c>
       <c r="R16">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
         <v>1.3</v>
       </c>
       <c r="T16">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U16">
         <v>2.45</v>
@@ -2956,7 +2956,7 @@
         <v>3.92</v>
       </c>
       <c r="AA16">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB16">
         <v>2.03</v>
@@ -2971,10 +2971,10 @@
         <v>1.14</v>
       </c>
       <c r="AF16">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG16">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.3</v>
       </c>
       <c r="AK16">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3934,7 +3934,7 @@
         <v>3.6</v>
       </c>
       <c r="AA22">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB22">
         <v>1.98</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="O23">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="P23">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="Q23">
         <v>2.7</v>
@@ -4073,19 +4073,19 @@
         <v>2.1</v>
       </c>
       <c r="S23">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="U23">
         <v>2.8</v>
       </c>
       <c r="V23">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W23">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
         <v>1.03</v>
@@ -4115,7 +4115,7 @@
         <v>1.75</v>
       </c>
       <c r="AG23">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="O24">
         <v>3.2</v>
@@ -4236,19 +4236,19 @@
         <v>2.13</v>
       </c>
       <c r="S24">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="U24">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="V24">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
         <v>1.03</v>
@@ -4275,10 +4275,10 @@
         <v>1.09</v>
       </c>
       <c r="AF24">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG24">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -5374,13 +5374,13 @@
         <v>5</v>
       </c>
       <c r="R31">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S31">
         <v>1.44</v>
       </c>
       <c r="T31">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="U31">
         <v>3.18</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="O32">
         <v>3.71</v>
       </c>
       <c r="P32">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q32">
         <v>4.72</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -6506,7 +6506,7 @@
         <v>1.55</v>
       </c>
       <c r="O38">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P38">
         <v>4.8</v>
@@ -6545,7 +6545,7 @@
         <v>1.66</v>
       </c>
       <c r="AB38">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AC38">
         <v>2.6</v>
@@ -6675,10 +6675,10 @@
         <v>4.9</v>
       </c>
       <c r="Q39">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R39">
-        <v>3.03</v>
+        <v>2.76</v>
       </c>
       <c r="S39">
         <v>1.15</v>
@@ -6717,13 +6717,13 @@
         <v>2.25</v>
       </c>
       <c r="AE39">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AF39">
         <v>1.3</v>
       </c>
       <c r="AG39">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6832,7 +6832,7 @@
         <v>1.95</v>
       </c>
       <c r="O40">
-        <v>4.21</v>
+        <v>3.9</v>
       </c>
       <c r="P40">
         <v>3.3</v>
@@ -6992,16 +6992,16 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="O41">
         <v>3.6</v>
       </c>
       <c r="P41">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q41">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="R41">
         <v>2.38</v>
@@ -7028,22 +7028,22 @@
         <v>1.16</v>
       </c>
       <c r="Z41">
-        <v>5.15</v>
+        <v>5.25</v>
       </c>
       <c r="AA41">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AB41">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="AC41">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="AD41">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE41">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF41">
         <v>1.44</v>
@@ -7155,19 +7155,19 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="O42">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P42">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q42">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="R42">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="S42">
         <v>1.25</v>
@@ -7188,25 +7188,25 @@
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z42">
-        <v>4.71</v>
+        <v>4.4</v>
       </c>
       <c r="AA42">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AB42">
         <v>2.45</v>
       </c>
       <c r="AC42">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AD42">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE42">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF42">
         <v>1.55</v>
@@ -7318,22 +7318,22 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="O43">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="P43">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="Q43">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="R43">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="S43">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T43">
         <v>4</v>
@@ -7345,7 +7345,7 @@
         <v>1.7</v>
       </c>
       <c r="W43">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X43">
         <v>0</v>
@@ -7357,19 +7357,19 @@
         <v>6</v>
       </c>
       <c r="AA43">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB43">
         <v>2.75</v>
       </c>
       <c r="AC43">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AD43">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE43">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF43">
         <v>1.53</v>
@@ -7391,7 +7391,7 @@
         <v>1.14</v>
       </c>
       <c r="AK43">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -9111,16 +9111,16 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.49</v>
+        <v>2.64</v>
       </c>
       <c r="O54">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P54">
         <v>2.58</v>
       </c>
       <c r="Q54">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="R54">
         <v>2.47</v>
@@ -9150,10 +9150,10 @@
         <v>4.87</v>
       </c>
       <c r="AA54">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AB54">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="AC54">
         <v>2.29</v>
@@ -9274,16 +9274,16 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="O55">
-        <v>4.58</v>
+        <v>4</v>
       </c>
       <c r="P55">
-        <v>3.95</v>
+        <v>4.35</v>
       </c>
       <c r="Q55">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="R55">
         <v>2.8</v>
@@ -9295,10 +9295,10 @@
         <v>4.6</v>
       </c>
       <c r="U55">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="V55">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="W55">
         <v>1.25</v>
@@ -9313,25 +9313,25 @@
         <v>8</v>
       </c>
       <c r="AA55">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AB55">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AC55">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AD55">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AE55">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AF55">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AG55">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>3.9</v>
       </c>
       <c r="P56">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="Q56">
         <v>2.4</v>
@@ -9476,7 +9476,7 @@
         <v>5.14</v>
       </c>
       <c r="AA56">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB56">
         <v>2.5</v>
@@ -9639,10 +9639,10 @@
         <v>5.1</v>
       </c>
       <c r="AA57">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB57">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="AC57">
         <v>2.26</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="O58">
         <v>3.8</v>
       </c>
       <c r="P58">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q58">
         <v>2.23</v>
@@ -9802,7 +9802,7 @@
         <v>6.24</v>
       </c>
       <c r="AA58">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AB58">
         <v>3.1</v>
@@ -9926,10 +9926,10 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="O59">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="P59">
         <v>6</v>
@@ -9965,10 +9965,10 @@
         <v>6.99</v>
       </c>
       <c r="AA59">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AB59">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="AC59">
         <v>1.89</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="O60">
         <v>4.5</v>
       </c>
       <c r="P60">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="Q60">
         <v>1.85</v>
@@ -10261,49 +10261,49 @@
         <v>3.6</v>
       </c>
       <c r="Q61">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="R61">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="S61">
         <v>1.29</v>
       </c>
       <c r="T61">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U61">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V61">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W61">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X61">
         <v>0</v>
       </c>
       <c r="Y61">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z61">
-        <v>4.52</v>
+        <v>4.44</v>
       </c>
       <c r="AA61">
         <v>1.64</v>
       </c>
       <c r="AB61">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AC61">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD61">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE61">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF61">
         <v>1.55</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -816,7 +816,7 @@
         <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="U3">
         <v>2.9</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.28</v>
+        <v>1.94</v>
       </c>
       <c r="O29">
-        <v>5.7</v>
+        <v>3.7</v>
       </c>
       <c r="P29">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="Q29">
-        <v>1.67</v>
+        <v>2.47</v>
       </c>
       <c r="R29">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="S29">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T29">
-        <v>3.98</v>
+        <v>3.6</v>
       </c>
       <c r="U29">
-        <v>1.91</v>
+        <v>2.32</v>
       </c>
       <c r="V29">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="W29">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Z29">
-        <v>6.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA29">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AB29">
-        <v>3.4</v>
+        <v>2.37</v>
       </c>
       <c r="AC29">
-        <v>1.81</v>
+        <v>2.33</v>
       </c>
       <c r="AD29">
-        <v>1.93</v>
+        <v>1.48</v>
       </c>
       <c r="AE29">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="AF29">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AG29">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>3.58</v>
+        <v>1.79</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.94</v>
+        <v>1.28</v>
       </c>
       <c r="O30">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="P30">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>2.47</v>
+        <v>1.67</v>
       </c>
       <c r="R30">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="S30">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T30">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="U30">
-        <v>2.32</v>
+        <v>1.91</v>
       </c>
       <c r="V30">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="W30">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Z30">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA30">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AB30">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="AC30">
-        <v>2.33</v>
+        <v>1.81</v>
       </c>
       <c r="AD30">
-        <v>1.48</v>
+        <v>1.93</v>
       </c>
       <c r="AE30">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AF30">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AG30">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK30">
-        <v>1.79</v>
+        <v>3.58</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,28 +6014,28 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.87</v>
+        <v>1.91</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P35">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="Q35">
-        <v>3.4</v>
+        <v>2.46</v>
       </c>
       <c r="R35">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S35">
         <v>1.36</v>
       </c>
       <c r="T35">
+        <v>2.9</v>
+      </c>
+      <c r="U35">
         <v>2.66</v>
-      </c>
-      <c r="U35">
-        <v>2.84</v>
       </c>
       <c r="V35">
         <v>1.4</v>
@@ -6047,31 +6047,31 @@
         <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z35">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="AA35">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB35">
         <v>1.85</v>
       </c>
       <c r="AC35">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="AD35">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AE35">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF35">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AG35">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,61 +6177,61 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.91</v>
+        <v>1.3</v>
       </c>
       <c r="O36">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="P36">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q36">
-        <v>2.46</v>
+        <v>1.65</v>
       </c>
       <c r="R36">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="S36">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T36">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="U36">
-        <v>2.66</v>
+        <v>2.18</v>
       </c>
       <c r="V36">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="W36">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="Z36">
-        <v>3.3</v>
+        <v>5.12</v>
       </c>
       <c r="AA36">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AB36">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="AC36">
-        <v>3.44</v>
+        <v>2.27</v>
       </c>
       <c r="AD36">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="AE36">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AF36">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG36">
         <v>1.91</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AK36">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.3</v>
+        <v>2.87</v>
       </c>
       <c r="O37">
-        <v>5.65</v>
+        <v>3.4</v>
       </c>
       <c r="P37">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Q37">
-        <v>1.65</v>
+        <v>3.4</v>
       </c>
       <c r="R37">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="S37">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T37">
-        <v>3.9</v>
+        <v>2.66</v>
       </c>
       <c r="U37">
-        <v>2.18</v>
+        <v>2.84</v>
       </c>
       <c r="V37">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="W37">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="X37">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="Z37">
-        <v>5.12</v>
+        <v>3.64</v>
       </c>
       <c r="AA37">
-        <v>1.52</v>
+        <v>1.9</v>
       </c>
       <c r="AB37">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="AC37">
-        <v>2.27</v>
+        <v>3.4</v>
       </c>
       <c r="AD37">
-        <v>1.59</v>
+        <v>1.34</v>
       </c>
       <c r="AE37">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AF37">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="AK37">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="O52">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P52">
-        <v>2.4</v>
+        <v>3.54</v>
       </c>
       <c r="Q52">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="R52">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="S52">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U52">
-        <v>2.38</v>
+        <v>2.69</v>
       </c>
       <c r="V52">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="W52">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z52">
-        <v>4.13</v>
+        <v>3.53</v>
       </c>
       <c r="AA52">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AB52">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AC52">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="AD52">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="AE52">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF52">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AG52">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="O53">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P53">
-        <v>3.54</v>
+        <v>2.4</v>
       </c>
       <c r="Q53">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="R53">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="S53">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T53">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U53">
-        <v>2.69</v>
+        <v>2.38</v>
       </c>
       <c r="V53">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="W53">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y53">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z53">
-        <v>3.53</v>
+        <v>4.13</v>
       </c>
       <c r="AA53">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AB53">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AC53">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="AD53">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AE53">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF53">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AG53">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>1.78</v>
+        <v>1.4</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="O56">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P56">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q56">
         <v>2.4</v>
@@ -9452,49 +9452,49 @@
         <v>2.4</v>
       </c>
       <c r="S56">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T56">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="U56">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="V56">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="W56">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y56">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="Z56">
-        <v>5.14</v>
+        <v>5.1</v>
       </c>
       <c r="AA56">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB56">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC56">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="AD56">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AE56">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AF56">
         <v>1.44</v>
       </c>
       <c r="AG56">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK56">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,80 +9600,80 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="O57">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P57">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q57">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="R57">
-        <v>2.4</v>
+        <v>2.71</v>
       </c>
       <c r="S57">
+        <v>1.2</v>
+      </c>
+      <c r="T57">
+        <v>4.2</v>
+      </c>
+      <c r="U57">
+        <v>2</v>
+      </c>
+      <c r="V57">
+        <v>1.73</v>
+      </c>
+      <c r="W57">
+        <v>1.2</v>
+      </c>
+      <c r="X57">
+        <v>0</v>
+      </c>
+      <c r="Y57">
+        <v>1.12</v>
+      </c>
+      <c r="Z57">
+        <v>6.24</v>
+      </c>
+      <c r="AA57">
+        <v>1.36</v>
+      </c>
+      <c r="AB57">
+        <v>3.1</v>
+      </c>
+      <c r="AC57">
+        <v>2.04</v>
+      </c>
+      <c r="AD57">
+        <v>1.79</v>
+      </c>
+      <c r="AE57">
+        <v>1.33</v>
+      </c>
+      <c r="AF57">
+        <v>1.4</v>
+      </c>
+      <c r="AG57">
+        <v>2.7</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
         <v>1.22</v>
       </c>
-      <c r="T57">
-        <v>3.64</v>
-      </c>
-      <c r="U57">
-        <v>2.1</v>
-      </c>
-      <c r="V57">
-        <v>1.67</v>
-      </c>
-      <c r="W57">
-        <v>1.18</v>
-      </c>
-      <c r="X57">
-        <v>0</v>
-      </c>
-      <c r="Y57">
-        <v>1.1</v>
-      </c>
-      <c r="Z57">
-        <v>5.1</v>
-      </c>
-      <c r="AA57">
-        <v>1.47</v>
-      </c>
-      <c r="AB57">
-        <v>2.63</v>
-      </c>
-      <c r="AC57">
-        <v>2.26</v>
-      </c>
-      <c r="AD57">
-        <v>1.66</v>
-      </c>
-      <c r="AE57">
-        <v>1.27</v>
-      </c>
-      <c r="AF57">
-        <v>1.44</v>
-      </c>
-      <c r="AG57">
-        <v>2.6</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ57">
-        <v>1.23</v>
-      </c>
       <c r="AK57">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="O58">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P58">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q58">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="R58">
-        <v>2.71</v>
+        <v>2.4</v>
       </c>
       <c r="S58">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T58">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="U58">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="V58">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="W58">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Z58">
-        <v>6.24</v>
+        <v>5.14</v>
       </c>
       <c r="AA58">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AB58">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AC58">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="AD58">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AE58">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AF58">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG58">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,80 +10089,80 @@
         </is>
       </c>
       <c r="N60">
+        <v>1.8</v>
+      </c>
+      <c r="O60">
+        <v>3.75</v>
+      </c>
+      <c r="P60">
+        <v>3.6</v>
+      </c>
+      <c r="Q60">
+        <v>2.39</v>
+      </c>
+      <c r="R60">
+        <v>2.46</v>
+      </c>
+      <c r="S60">
+        <v>1.29</v>
+      </c>
+      <c r="T60">
+        <v>3.4</v>
+      </c>
+      <c r="U60">
+        <v>2.38</v>
+      </c>
+      <c r="V60">
+        <v>1.53</v>
+      </c>
+      <c r="W60">
+        <v>1.12</v>
+      </c>
+      <c r="X60">
+        <v>0</v>
+      </c>
+      <c r="Y60">
+        <v>1.21</v>
+      </c>
+      <c r="Z60">
+        <v>4.44</v>
+      </c>
+      <c r="AA60">
+        <v>1.64</v>
+      </c>
+      <c r="AB60">
+        <v>2.17</v>
+      </c>
+      <c r="AC60">
+        <v>2.63</v>
+      </c>
+      <c r="AD60">
         <v>1.44</v>
       </c>
-      <c r="O60">
-        <v>4.5</v>
-      </c>
-      <c r="P60">
-        <v>5.25</v>
-      </c>
-      <c r="Q60">
+      <c r="AE60">
+        <v>1.14</v>
+      </c>
+      <c r="AF60">
+        <v>1.55</v>
+      </c>
+      <c r="AG60">
+        <v>2.25</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ60">
+        <v>1.25</v>
+      </c>
+      <c r="AK60">
         <v>1.85</v>
-      </c>
-      <c r="R60">
-        <v>2.75</v>
-      </c>
-      <c r="S60">
-        <v>1.18</v>
-      </c>
-      <c r="T60">
-        <v>4.5</v>
-      </c>
-      <c r="U60">
-        <v>1.85</v>
-      </c>
-      <c r="V60">
-        <v>1.85</v>
-      </c>
-      <c r="W60">
-        <v>1.25</v>
-      </c>
-      <c r="X60">
-        <v>0</v>
-      </c>
-      <c r="Y60">
-        <v>1.03</v>
-      </c>
-      <c r="Z60">
-        <v>8</v>
-      </c>
-      <c r="AA60">
-        <v>1.3</v>
-      </c>
-      <c r="AB60">
-        <v>3.3</v>
-      </c>
-      <c r="AC60">
-        <v>1.85</v>
-      </c>
-      <c r="AD60">
-        <v>1.99</v>
-      </c>
-      <c r="AE60">
-        <v>1.4</v>
-      </c>
-      <c r="AF60">
-        <v>1.44</v>
-      </c>
-      <c r="AG60">
-        <v>2.62</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ60">
-        <v>1.17</v>
-      </c>
-      <c r="AK60">
-        <v>2.62</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="O61">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P61">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q61">
-        <v>2.39</v>
+        <v>2.68</v>
       </c>
       <c r="R61">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="S61">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T61">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="U61">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="V61">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="W61">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X61">
         <v>0</v>
       </c>
       <c r="Y61">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z61">
-        <v>4.44</v>
+        <v>4.98</v>
       </c>
       <c r="AA61">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB61">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="AC61">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="AD61">
+        <v>1.58</v>
+      </c>
+      <c r="AE61">
+        <v>1.23</v>
+      </c>
+      <c r="AF61">
         <v>1.44</v>
       </c>
-      <c r="AE61">
-        <v>1.14</v>
-      </c>
-      <c r="AF61">
-        <v>1.55</v>
-      </c>
       <c r="AG61">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>1.25</v>
       </c>
       <c r="AK61">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="O62">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="P62">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="Q62">
-        <v>2.68</v>
+        <v>1.85</v>
       </c>
       <c r="R62">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="S62">
+        <v>1.18</v>
+      </c>
+      <c r="T62">
+        <v>4.5</v>
+      </c>
+      <c r="U62">
+        <v>1.85</v>
+      </c>
+      <c r="V62">
+        <v>1.85</v>
+      </c>
+      <c r="W62">
         <v>1.25</v>
       </c>
-      <c r="T62">
-        <v>3.7</v>
-      </c>
-      <c r="U62">
-        <v>2.2</v>
-      </c>
-      <c r="V62">
-        <v>1.62</v>
-      </c>
-      <c r="W62">
-        <v>1.17</v>
-      </c>
       <c r="X62">
         <v>0</v>
       </c>
       <c r="Y62">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="Z62">
-        <v>4.98</v>
+        <v>8</v>
       </c>
       <c r="AA62">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AB62">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="AC62">
-        <v>2.41</v>
+        <v>1.85</v>
       </c>
       <c r="AD62">
-        <v>1.58</v>
+        <v>1.99</v>
       </c>
       <c r="AE62">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AF62">
         <v>1.44</v>
       </c>
       <c r="AG62">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK62">
-        <v>1.67</v>
+        <v>2.62</v>
       </c>
       <c r="AL62">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="O13">
         <v>5.85</v>
       </c>
       <c r="P13">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Q13">
         <v>6</v>
@@ -2464,13 +2464,13 @@
         <v>1.07</v>
       </c>
       <c r="Z13">
-        <v>8</v>
+        <v>6.75</v>
       </c>
       <c r="AA13">
         <v>1.34</v>
       </c>
       <c r="AB13">
-        <v>2.91</v>
+        <v>3.06</v>
       </c>
       <c r="AC13">
         <v>1.81</v>
@@ -2479,10 +2479,10 @@
         <v>1.9</v>
       </c>
       <c r="AE13">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AF13">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AG13">
         <v>2.3</v>
@@ -2600,16 +2600,16 @@
         <v>2.5</v>
       </c>
       <c r="Q14">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="R14">
         <v>2</v>
       </c>
       <c r="S14">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T14">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="U14">
         <v>3.3</v>
@@ -2618,16 +2618,16 @@
         <v>1.29</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
         <v>1.39</v>
       </c>
       <c r="Z14">
-        <v>3.09</v>
+        <v>3.02</v>
       </c>
       <c r="AA14">
         <v>2.2</v>
@@ -2636,10 +2636,10 @@
         <v>1.67</v>
       </c>
       <c r="AC14">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AD14">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE14">
         <v>1.07</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AK14">
         <v>1.3</v>
@@ -2757,7 +2757,7 @@
         <v>1.51</v>
       </c>
       <c r="O15">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P15">
         <v>4.95</v>
@@ -2772,13 +2772,13 @@
         <v>1.3</v>
       </c>
       <c r="T15">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="U15">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="V15">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
         <v>1.07</v>
@@ -2790,28 +2790,28 @@
         <v>1.25</v>
       </c>
       <c r="Z15">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA15">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AB15">
         <v>1.9</v>
       </c>
       <c r="AC15">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="AD15">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE15">
         <v>1.1</v>
       </c>
       <c r="AF15">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG15">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK15">
         <v>2.2</v>
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="O16">
         <v>3.4</v>
       </c>
       <c r="P16">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="Q16">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R16">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T16">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="U16">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W16">
         <v>1.11</v>
@@ -2950,16 +2950,16 @@
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z16">
         <v>3.92</v>
       </c>
       <c r="AA16">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AB16">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AC16">
         <v>2.46</v>
@@ -2971,10 +2971,10 @@
         <v>1.14</v>
       </c>
       <c r="AF16">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG16">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK16">
         <v>1.46</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="O23">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P23">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q23">
         <v>2.7</v>
       </c>
       <c r="R23">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S23">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T23">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="U23">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="V23">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z23">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="AA23">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AB23">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC23">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="AD23">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE23">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF23">
         <v>1.75</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AK23">
         <v>1.57</v>
@@ -4221,10 +4221,10 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="O24">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P24">
         <v>2.2</v>
@@ -4236,22 +4236,22 @@
         <v>2.13</v>
       </c>
       <c r="S24">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T24">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="U24">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="V24">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
         <v>1.21</v>
@@ -4260,13 +4260,13 @@
         <v>3.6</v>
       </c>
       <c r="AA24">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AB24">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AC24">
-        <v>2.83</v>
+        <v>3.13</v>
       </c>
       <c r="AD24">
         <v>1.33</v>
@@ -4275,10 +4275,10 @@
         <v>1.09</v>
       </c>
       <c r="AF24">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG24">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
         <v>1.4</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.47</v>
+        <v>3.15</v>
       </c>
       <c r="O27">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="P27">
-        <v>2.58</v>
+        <v>2.05</v>
       </c>
       <c r="Q27">
-        <v>3.05</v>
+        <v>3.94</v>
       </c>
       <c r="R27">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T27">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="U27">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V27">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W27">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X27">
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z27">
-        <v>4.03</v>
+        <v>4.25</v>
       </c>
       <c r="AA27">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AB27">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC27">
-        <v>2.92</v>
+        <v>2.46</v>
       </c>
       <c r="AD27">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE27">
         <v>1.15</v>
       </c>
       <c r="AF27">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG27">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
+        <v>1.29</v>
+      </c>
+      <c r="AK27">
         <v>1.3</v>
-      </c>
-      <c r="AK27">
-        <v>1.47</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.15</v>
+        <v>1.94</v>
       </c>
       <c r="O28">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P28">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="Q28">
-        <v>3.94</v>
+        <v>2.47</v>
       </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T28">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="U28">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="V28">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="W28">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z28">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA28">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB28">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AC28">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="AD28">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AE28">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF28">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG28">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.3</v>
+        <v>1.79</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.94</v>
+        <v>1.28</v>
       </c>
       <c r="O29">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="P29">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>2.47</v>
+        <v>1.67</v>
       </c>
       <c r="R29">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="S29">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T29">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="U29">
-        <v>2.32</v>
+        <v>1.91</v>
       </c>
       <c r="V29">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="W29">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Z29">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA29">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AB29">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="AC29">
-        <v>2.33</v>
+        <v>1.81</v>
       </c>
       <c r="AD29">
-        <v>1.48</v>
+        <v>1.93</v>
       </c>
       <c r="AE29">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AF29">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AG29">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK29">
-        <v>1.79</v>
+        <v>3.58</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.28</v>
+        <v>2.47</v>
       </c>
       <c r="O30">
-        <v>5.7</v>
+        <v>3.45</v>
       </c>
       <c r="P30">
-        <v>8</v>
+        <v>2.58</v>
       </c>
       <c r="Q30">
-        <v>1.67</v>
+        <v>3.05</v>
       </c>
       <c r="R30">
-        <v>2.78</v>
+        <v>2.32</v>
       </c>
       <c r="S30">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
-        <v>3.98</v>
+        <v>3.25</v>
       </c>
       <c r="U30">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="V30">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="W30">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="Z30">
-        <v>6.25</v>
+        <v>4.03</v>
       </c>
       <c r="AA30">
+        <v>1.8</v>
+      </c>
+      <c r="AB30">
+        <v>2</v>
+      </c>
+      <c r="AC30">
+        <v>2.92</v>
+      </c>
+      <c r="AD30">
         <v>1.33</v>
       </c>
-      <c r="AB30">
-        <v>3.4</v>
-      </c>
-      <c r="AC30">
-        <v>1.81</v>
-      </c>
-      <c r="AD30">
-        <v>1.93</v>
-      </c>
       <c r="AE30">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="AF30">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG30">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AK30">
-        <v>3.58</v>
+        <v>1.47</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="N31">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O31">
-        <v>3.86</v>
+        <v>3.73</v>
       </c>
       <c r="P31">
         <v>1.66</v>
@@ -5374,16 +5374,16 @@
         <v>5</v>
       </c>
       <c r="R31">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="S31">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
         <v>2.58</v>
       </c>
       <c r="U31">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="V31">
         <v>1.36</v>
@@ -5395,10 +5395,10 @@
         <v>1.05</v>
       </c>
       <c r="Y31">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z31">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA31">
         <v>2.05</v>
@@ -5407,16 +5407,16 @@
         <v>1.75</v>
       </c>
       <c r="AC31">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="AD31">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE31">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF31">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG31">
         <v>1.83</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>2.11</v>
+        <v>2.29</v>
       </c>
       <c r="AK31">
         <v>1.14</v>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.82</v>
+        <v>4.33</v>
       </c>
       <c r="O32">
-        <v>3.71</v>
+        <v>3.63</v>
       </c>
       <c r="P32">
         <v>1.75</v>
@@ -5537,7 +5537,7 @@
         <v>4.72</v>
       </c>
       <c r="R32">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S32">
         <v>1.29</v>
@@ -5555,13 +5555,13 @@
         <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y32">
         <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>4.14</v>
+        <v>4.2</v>
       </c>
       <c r="AA32">
         <v>1.75</v>
@@ -5570,19 +5570,19 @@
         <v>2.05</v>
       </c>
       <c r="AC32">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="AD32">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE32">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF32">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AG32">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,58 +9763,58 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.92</v>
+        <v>1.4</v>
       </c>
       <c r="O58">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="P58">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="Q58">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="R58">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="S58">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T58">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="U58">
-        <v>2.27</v>
+        <v>1.91</v>
       </c>
       <c r="V58">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="W58">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y58">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="Z58">
-        <v>5.14</v>
+        <v>6.99</v>
       </c>
       <c r="AA58">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AB58">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="AC58">
-        <v>2.34</v>
+        <v>1.89</v>
       </c>
       <c r="AD58">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="AE58">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AF58">
         <v>1.44</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK58">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,58 +9926,58 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.4</v>
+        <v>1.92</v>
       </c>
       <c r="O59">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="P59">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="Q59">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="R59">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="S59">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T59">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="U59">
-        <v>1.91</v>
+        <v>2.27</v>
       </c>
       <c r="V59">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="W59">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Z59">
-        <v>6.99</v>
+        <v>5.14</v>
       </c>
       <c r="AA59">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AB59">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="AC59">
-        <v>1.89</v>
+        <v>2.34</v>
       </c>
       <c r="AD59">
-        <v>1.94</v>
+        <v>1.61</v>
       </c>
       <c r="AE59">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AF59">
         <v>1.44</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK59">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="AL59">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -1136,19 +1136,19 @@
         <v>2.05</v>
       </c>
       <c r="R5">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S5">
         <v>1.33</v>
       </c>
       <c r="T5">
-        <v>2.94</v>
+        <v>3.19</v>
       </c>
       <c r="U5">
         <v>2.67</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
         <v>1.07</v>
@@ -1163,7 +1163,7 @@
         <v>3.82</v>
       </c>
       <c r="AA5">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB5">
         <v>1.99</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1459,7 +1459,7 @@
         <v>2.6</v>
       </c>
       <c r="Q7">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R7">
         <v>2.19</v>
@@ -1468,13 +1468,13 @@
         <v>1.3</v>
       </c>
       <c r="T7">
-        <v>2.91</v>
+        <v>3.24</v>
       </c>
       <c r="U7">
         <v>2.45</v>
       </c>
       <c r="V7">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
         <v>1.1</v>
@@ -1483,28 +1483,28 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA7">
         <v>1.69</v>
       </c>
       <c r="AB7">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC7">
         <v>2.66</v>
       </c>
       <c r="AD7">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE7">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF7">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG7">
         <v>2.19</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1625,10 +1625,10 @@
         <v>2.88</v>
       </c>
       <c r="R8">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S8">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T8">
         <v>3.18</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="N17">
-        <v>4.25</v>
+        <v>4.64</v>
       </c>
       <c r="O17">
         <v>3.85</v>
@@ -3098,13 +3098,13 @@
         <v>1.25</v>
       </c>
       <c r="T17">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U17">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="V17">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W17">
         <v>1.11</v>
@@ -3113,16 +3113,16 @@
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z17">
-        <v>4.56</v>
+        <v>4.3</v>
       </c>
       <c r="AA17">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB17">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AC17">
         <v>2.38</v>
@@ -3131,7 +3131,7 @@
         <v>1.46</v>
       </c>
       <c r="AE17">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF17">
         <v>1.61</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
         <v>1.15</v>
@@ -3252,25 +3252,25 @@
         <v>1.77</v>
       </c>
       <c r="Q18">
-        <v>3.77</v>
+        <v>4.2</v>
       </c>
       <c r="R18">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T18">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U18">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="V18">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W18">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3282,13 +3282,13 @@
         <v>5.05</v>
       </c>
       <c r="AA18">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB18">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="AC18">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="AD18">
         <v>1.62</v>
@@ -3297,10 +3297,10 @@
         <v>1.2</v>
       </c>
       <c r="AF18">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG18">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK18">
         <v>1.18</v>
@@ -3406,19 +3406,19 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O19">
+        <v>3.6</v>
+      </c>
+      <c r="P19">
+        <v>2.05</v>
+      </c>
+      <c r="Q19">
         <v>3.4</v>
       </c>
-      <c r="P19">
-        <v>2</v>
-      </c>
-      <c r="Q19">
-        <v>3.69</v>
-      </c>
       <c r="R19">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="S19">
         <v>1.25</v>
@@ -3436,7 +3436,7 @@
         <v>1.1</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
         <v>1.14</v>
@@ -3445,10 +3445,10 @@
         <v>4.45</v>
       </c>
       <c r="AA19">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AB19">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AC19">
         <v>2.38</v>
@@ -3460,10 +3460,10 @@
         <v>1.16</v>
       </c>
       <c r="AF19">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG19">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.71</v>
       </c>
       <c r="AK19">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,13 +3578,13 @@
         <v>2.62</v>
       </c>
       <c r="Q20">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="R20">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T20">
         <v>3</v>
@@ -3599,7 +3599,7 @@
         <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
         <v>1.24</v>
@@ -3608,25 +3608,25 @@
         <v>3.61</v>
       </c>
       <c r="AA20">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AB20">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AC20">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AD20">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE20">
         <v>1.07</v>
       </c>
       <c r="AF20">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG20">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK20">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>2.6</v>
       </c>
       <c r="Q22">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="R22">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S22">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
         <v>3.2</v>
       </c>
       <c r="U22">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V22">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W22">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z22">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA22">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB22">
         <v>1.98</v>
       </c>
       <c r="AC22">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AD22">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE22">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG22">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4547,16 +4547,16 @@
         </is>
       </c>
       <c r="N26">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="O26">
         <v>3.5</v>
       </c>
       <c r="P26">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q26">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="R26">
         <v>2.15</v>
@@ -4589,7 +4589,7 @@
         <v>1.8</v>
       </c>
       <c r="AB26">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AC26">
         <v>3.1</v>
@@ -4598,13 +4598,13 @@
         <v>1.33</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF26">
         <v>1.65</v>
       </c>
       <c r="AG26">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O27">
         <v>3.65</v>
@@ -4722,10 +4722,10 @@
         <v>3.94</v>
       </c>
       <c r="R27">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S27">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T27">
         <v>3.24</v>
@@ -4743,7 +4743,7 @@
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z27">
         <v>4.25</v>
@@ -4752,22 +4752,22 @@
         <v>1.61</v>
       </c>
       <c r="AB27">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AC27">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="AD27">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE27">
         <v>1.15</v>
       </c>
       <c r="AF27">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG27">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="O28">
         <v>3.7</v>
       </c>
       <c r="P28">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="Q28">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="R28">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="S28">
         <v>1.25</v>
@@ -4897,10 +4897,10 @@
         <v>2.32</v>
       </c>
       <c r="V28">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W28">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X28">
         <v>1.01</v>
@@ -4915,7 +4915,7 @@
         <v>1.57</v>
       </c>
       <c r="AB28">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="AC28">
         <v>2.33</v>
@@ -4927,10 +4927,10 @@
         <v>1.22</v>
       </c>
       <c r="AF28">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG28">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK28">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5039,16 +5039,16 @@
         <v>1.28</v>
       </c>
       <c r="O29">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="P29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q29">
         <v>1.67</v>
       </c>
       <c r="R29">
-        <v>2.78</v>
+        <v>3.19</v>
       </c>
       <c r="S29">
         <v>1.18</v>
@@ -5063,7 +5063,7 @@
         <v>1.83</v>
       </c>
       <c r="W29">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X29">
         <v>1.01</v>
@@ -5075,16 +5075,16 @@
         <v>6.25</v>
       </c>
       <c r="AA29">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AB29">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="AC29">
         <v>1.81</v>
       </c>
       <c r="AD29">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AE29">
         <v>1.37</v>
@@ -5093,7 +5093,7 @@
         <v>1.61</v>
       </c>
       <c r="AG29">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>3.45</v>
       </c>
       <c r="P30">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="Q30">
         <v>3.05</v>
@@ -5214,7 +5214,7 @@
         <v>2.32</v>
       </c>
       <c r="S30">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T30">
         <v>3.25</v>
@@ -5232,31 +5232,31 @@
         <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>4.03</v>
+        <v>3.7</v>
       </c>
       <c r="AA30">
         <v>1.8</v>
       </c>
       <c r="AB30">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC30">
         <v>2.92</v>
       </c>
       <c r="AD30">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE30">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF30">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG30">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK30">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5857,19 +5857,19 @@
         <v>3.7</v>
       </c>
       <c r="P34">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="Q34">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="R34">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T34">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U34">
         <v>2.26</v>
@@ -5878,7 +5878,7 @@
         <v>1.56</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X34">
         <v>1.01</v>
@@ -5887,28 +5887,28 @@
         <v>1.18</v>
       </c>
       <c r="Z34">
-        <v>4.82</v>
+        <v>4.33</v>
       </c>
       <c r="AA34">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB34">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC34">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="AD34">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE34">
         <v>1.17</v>
       </c>
       <c r="AF34">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AG34">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AK34">
         <v>1.33</v>
@@ -6017,16 +6017,16 @@
         <v>1.91</v>
       </c>
       <c r="O35">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P35">
         <v>4</v>
       </c>
       <c r="Q35">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="R35">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S35">
         <v>1.36</v>
@@ -6035,7 +6035,7 @@
         <v>2.9</v>
       </c>
       <c r="U35">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="V35">
         <v>1.4</v>
@@ -6050,28 +6050,28 @@
         <v>1.33</v>
       </c>
       <c r="Z35">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA35">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB35">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC35">
         <v>3.44</v>
       </c>
       <c r="AD35">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE35">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
         <v>1.84</v>
       </c>
       <c r="AG35">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK35">
         <v>1.85</v>
@@ -6180,16 +6180,16 @@
         <v>1.3</v>
       </c>
       <c r="O36">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="P36">
         <v>10</v>
       </c>
       <c r="Q36">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="R36">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="S36">
         <v>1.22</v>
@@ -6204,37 +6204,37 @@
         <v>1.67</v>
       </c>
       <c r="W36">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X36">
         <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z36">
-        <v>5.12</v>
+        <v>5.67</v>
       </c>
       <c r="AA36">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AB36">
         <v>2.6</v>
       </c>
       <c r="AC36">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AD36">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="AE36">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AF36">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG36">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6340,34 +6340,34 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="O37">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="P37">
         <v>2.5</v>
       </c>
       <c r="Q37">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R37">
         <v>2.25</v>
       </c>
       <c r="S37">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T37">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="U37">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="V37">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W37">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
         <v>1.03</v>
@@ -6376,22 +6376,22 @@
         <v>1.28</v>
       </c>
       <c r="Z37">
-        <v>3.64</v>
+        <v>3.14</v>
       </c>
       <c r="AA37">
         <v>1.9</v>
       </c>
       <c r="AB37">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC37">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="AD37">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AE37">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF37">
         <v>1.75</v>
@@ -6413,7 +6413,7 @@
         <v>1.34</v>
       </c>
       <c r="AK37">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6524,7 +6524,7 @@
         <v>3.3</v>
       </c>
       <c r="U38">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="V38">
         <v>1.5</v>
@@ -6545,13 +6545,13 @@
         <v>1.66</v>
       </c>
       <c r="AB38">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AC38">
         <v>2.6</v>
       </c>
       <c r="AD38">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AE38">
         <v>1.13</v>
@@ -6576,7 +6576,7 @@
         <v>1.17</v>
       </c>
       <c r="AK38">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6669,28 +6669,28 @@
         <v>1.6</v>
       </c>
       <c r="O39">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="P39">
         <v>4.9</v>
       </c>
       <c r="Q39">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="R39">
-        <v>2.76</v>
+        <v>3.08</v>
       </c>
       <c r="S39">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="T39">
-        <v>5.4</v>
+        <v>5.05</v>
       </c>
       <c r="U39">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="V39">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="W39">
         <v>1.3</v>
@@ -6705,25 +6705,25 @@
         <v>9</v>
       </c>
       <c r="AA39">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AB39">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AC39">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AD39">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AE39">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AF39">
         <v>1.3</v>
       </c>
       <c r="AG39">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,28 +6829,28 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O40">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P40">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="Q40">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R40">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="S40">
         <v>1.2</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U40">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="V40">
         <v>1.7</v>
@@ -6886,7 +6886,7 @@
         <v>1.4</v>
       </c>
       <c r="AG40">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,34 +6992,34 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="O41">
         <v>3.6</v>
       </c>
       <c r="P41">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="Q41">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="R41">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S41">
         <v>1.25</v>
       </c>
       <c r="T41">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U41">
         <v>2.2</v>
       </c>
       <c r="V41">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W41">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X41">
         <v>1.01</v>
@@ -7031,13 +7031,13 @@
         <v>5.25</v>
       </c>
       <c r="AA41">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AB41">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AC41">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AD41">
         <v>1.62</v>
@@ -7161,10 +7161,10 @@
         <v>3.6</v>
       </c>
       <c r="P42">
-        <v>3.9</v>
+        <v>4.06</v>
       </c>
       <c r="Q42">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="R42">
         <v>2.38</v>
@@ -7179,10 +7179,10 @@
         <v>2.25</v>
       </c>
       <c r="V42">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W42">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X42">
         <v>1.01</v>
@@ -7197,7 +7197,7 @@
         <v>1.59</v>
       </c>
       <c r="AB42">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AC42">
         <v>2.5</v>
@@ -7206,13 +7206,13 @@
         <v>1.54</v>
       </c>
       <c r="AE42">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AF42">
         <v>1.55</v>
       </c>
       <c r="AG42">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK42">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,58 +7318,58 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="O43">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="P43">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q43">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="R43">
         <v>2.8</v>
       </c>
       <c r="S43">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T43">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U43">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="V43">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W43">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X43">
         <v>0</v>
       </c>
       <c r="Y43">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z43">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AA43">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB43">
         <v>2.75</v>
       </c>
       <c r="AC43">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AD43">
         <v>1.71</v>
       </c>
       <c r="AE43">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AF43">
         <v>1.53</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK43">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8788,7 +8788,7 @@
         <v>2.04</v>
       </c>
       <c r="O52">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
         <v>3.54</v>
@@ -8800,7 +8800,7 @@
         <v>2.33</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T52">
         <v>3.2</v>
@@ -8812,7 +8812,7 @@
         <v>1.45</v>
       </c>
       <c r="W52">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
         <v>1.03</v>
@@ -8830,10 +8830,10 @@
         <v>1.9</v>
       </c>
       <c r="AC52">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AD52">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE52">
         <v>1.11</v>
@@ -8842,7 +8842,7 @@
         <v>1.67</v>
       </c>
       <c r="AG52">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK52">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8954,7 +8954,7 @@
         <v>3.7</v>
       </c>
       <c r="P53">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -8963,7 +8963,7 @@
         <v>2.18</v>
       </c>
       <c r="S53">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T53">
         <v>3.25</v>
@@ -8972,10 +8972,10 @@
         <v>2.38</v>
       </c>
       <c r="V53">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W53">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X53">
         <v>1</v>
@@ -8993,19 +8993,19 @@
         <v>2.2</v>
       </c>
       <c r="AC53">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="AD53">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE53">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF53">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG53">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
         <v>1.4</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O54">
         <v>3.6</v>
@@ -9120,10 +9120,10 @@
         <v>2.58</v>
       </c>
       <c r="Q54">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="R54">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="S54">
         <v>1.25</v>
@@ -9132,7 +9132,7 @@
         <v>3.6</v>
       </c>
       <c r="U54">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="V54">
         <v>1.6</v>
@@ -9150,16 +9150,16 @@
         <v>4.87</v>
       </c>
       <c r="AA54">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AB54">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="AC54">
-        <v>2.29</v>
+        <v>2.46</v>
       </c>
       <c r="AD54">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE54">
         <v>1.23</v>
@@ -9168,7 +9168,7 @@
         <v>1.5</v>
       </c>
       <c r="AG54">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK54">
         <v>1.44</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="O55">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P55">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="Q55">
         <v>1.99</v>
@@ -9289,19 +9289,19 @@
         <v>2.8</v>
       </c>
       <c r="S55">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T55">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="U55">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="V55">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="W55">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X55">
         <v>0</v>
@@ -9331,7 +9331,7 @@
         <v>1.33</v>
       </c>
       <c r="AG55">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9443,28 +9443,28 @@
         <v>3.7</v>
       </c>
       <c r="P56">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q56">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R56">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S56">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T56">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="U56">
         <v>2.1</v>
       </c>
       <c r="V56">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W56">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X56">
         <v>0</v>
@@ -9479,13 +9479,13 @@
         <v>1.47</v>
       </c>
       <c r="AB56">
-        <v>2.63</v>
+        <v>2.46</v>
       </c>
       <c r="AC56">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="AD56">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AE56">
         <v>1.27</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK56">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="O57">
         <v>3.8</v>
@@ -9615,19 +9615,19 @@
         <v>2.71</v>
       </c>
       <c r="S57">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T57">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="U57">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="V57">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W57">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X57">
         <v>0</v>
@@ -9639,10 +9639,10 @@
         <v>6.24</v>
       </c>
       <c r="AA57">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AB57">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC57">
         <v>2.04</v>
@@ -9651,13 +9651,13 @@
         <v>1.79</v>
       </c>
       <c r="AE57">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF57">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AG57">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="O58">
         <v>5.3</v>
@@ -9772,22 +9772,22 @@
         <v>6</v>
       </c>
       <c r="Q58">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R58">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="S58">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T58">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="U58">
         <v>1.91</v>
       </c>
       <c r="V58">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="W58">
         <v>1.22</v>
@@ -9799,19 +9799,19 @@
         <v>1.1</v>
       </c>
       <c r="Z58">
-        <v>6.99</v>
+        <v>7.5</v>
       </c>
       <c r="AA58">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB58">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AC58">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AD58">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AE58">
         <v>1.39</v>
@@ -9929,25 +9929,25 @@
         <v>1.92</v>
       </c>
       <c r="O59">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P59">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="Q59">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="R59">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S59">
         <v>1.25</v>
       </c>
       <c r="T59">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U59">
-        <v>2.27</v>
+        <v>2.13</v>
       </c>
       <c r="V59">
         <v>1.61</v>
@@ -9965,10 +9965,10 @@
         <v>5.14</v>
       </c>
       <c r="AA59">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AB59">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AC59">
         <v>2.34</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK59">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10095,7 +10095,7 @@
         <v>3.75</v>
       </c>
       <c r="P60">
-        <v>3.6</v>
+        <v>3.86</v>
       </c>
       <c r="Q60">
         <v>2.39</v>
@@ -10104,28 +10104,28 @@
         <v>2.46</v>
       </c>
       <c r="S60">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T60">
         <v>3.4</v>
       </c>
       <c r="U60">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V60">
         <v>1.53</v>
       </c>
       <c r="W60">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X60">
         <v>0</v>
       </c>
       <c r="Y60">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z60">
-        <v>4.44</v>
+        <v>4.15</v>
       </c>
       <c r="AA60">
         <v>1.64</v>
@@ -10134,19 +10134,19 @@
         <v>2.17</v>
       </c>
       <c r="AC60">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="AD60">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE60">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF60">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG60">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK60">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10255,31 +10255,31 @@
         <v>2.1</v>
       </c>
       <c r="O61">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P61">
         <v>3.1</v>
       </c>
       <c r="Q61">
-        <v>2.68</v>
+        <v>2.49</v>
       </c>
       <c r="R61">
-        <v>2.49</v>
+        <v>2.28</v>
       </c>
       <c r="S61">
         <v>1.25</v>
       </c>
       <c r="T61">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U61">
         <v>2.2</v>
       </c>
       <c r="V61">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W61">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X61">
         <v>0</v>
@@ -10291,19 +10291,19 @@
         <v>4.98</v>
       </c>
       <c r="AA61">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AB61">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC61">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="AD61">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AE61">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AF61">
         <v>1.44</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK61">
         <v>1.67</v>
@@ -10421,28 +10421,28 @@
         <v>4.5</v>
       </c>
       <c r="P62">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="Q62">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="R62">
         <v>2.75</v>
       </c>
       <c r="S62">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T62">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="U62">
         <v>1.85</v>
       </c>
       <c r="V62">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="W62">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X62">
         <v>0</v>
@@ -10451,28 +10451,28 @@
         <v>1.03</v>
       </c>
       <c r="Z62">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA62">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AB62">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AC62">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AD62">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AE62">
+        <v>1.36</v>
+      </c>
+      <c r="AF62">
         <v>1.4</v>
       </c>
-      <c r="AF62">
-        <v>1.44</v>
-      </c>
       <c r="AG62">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK62">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AL62">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -804,19 +804,19 @@
         <v>3.1</v>
       </c>
       <c r="P3">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S3">
         <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="U3">
         <v>2.9</v>
@@ -828,50 +828,50 @@
         <v>1.04</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y3">
+        <v>1.36</v>
+      </c>
+      <c r="Z3">
+        <v>3.1</v>
+      </c>
+      <c r="AA3">
+        <v>2.1</v>
+      </c>
+      <c r="AB3">
+        <v>1.7</v>
+      </c>
+      <c r="AC3">
+        <v>4.1</v>
+      </c>
+      <c r="AD3">
+        <v>1.22</v>
+      </c>
+      <c r="AE3">
+        <v>1.07</v>
+      </c>
+      <c r="AF3">
+        <v>1.79</v>
+      </c>
+      <c r="AG3">
+        <v>1.9</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
         <v>1.33</v>
       </c>
-      <c r="Z3">
-        <v>2.97</v>
-      </c>
-      <c r="AA3">
-        <v>2.12</v>
-      </c>
-      <c r="AB3">
-        <v>1.67</v>
-      </c>
-      <c r="AC3">
-        <v>3.58</v>
-      </c>
-      <c r="AD3">
-        <v>1.21</v>
-      </c>
-      <c r="AE3">
-        <v>1.03</v>
-      </c>
-      <c r="AF3">
-        <v>1.8</v>
-      </c>
-      <c r="AG3">
-        <v>1.95</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
+      <c r="AK3">
         <v>1.4</v>
-      </c>
-      <c r="AK3">
-        <v>1.44</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1127,10 +1127,10 @@
         <v>1.57</v>
       </c>
       <c r="O5">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q5">
         <v>2.05</v>
@@ -1142,10 +1142,10 @@
         <v>1.33</v>
       </c>
       <c r="T5">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="U5">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="V5">
         <v>1.42</v>
@@ -1154,13 +1154,13 @@
         <v>1.07</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="AA5">
         <v>1.75</v>
@@ -1169,19 +1169,19 @@
         <v>1.99</v>
       </c>
       <c r="AC5">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="AD5">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE5">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG5">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>4.12</v>
+        <v>4.03</v>
       </c>
       <c r="O6">
         <v>3.7</v>
       </c>
       <c r="P6">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q6">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R6">
         <v>2.3</v>
       </c>
       <c r="S6">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T6">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U6">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="V6">
+        <v>1.51</v>
+      </c>
+      <c r="W6">
+        <v>1.12</v>
+      </c>
+      <c r="X6">
+        <v>1.01</v>
+      </c>
+      <c r="Y6">
+        <v>1.16</v>
+      </c>
+      <c r="Z6">
+        <v>4.54</v>
+      </c>
+      <c r="AA6">
+        <v>1.65</v>
+      </c>
+      <c r="AB6">
+        <v>1.86</v>
+      </c>
+      <c r="AC6">
+        <v>2.58</v>
+      </c>
+      <c r="AD6">
         <v>1.5</v>
       </c>
-      <c r="W6">
-        <v>1.08</v>
-      </c>
-      <c r="X6">
-        <v>1.04</v>
-      </c>
-      <c r="Y6">
-        <v>1.14</v>
-      </c>
-      <c r="Z6">
-        <v>4</v>
-      </c>
-      <c r="AA6">
-        <v>1.7</v>
-      </c>
-      <c r="AB6">
-        <v>2.05</v>
-      </c>
-      <c r="AC6">
-        <v>2.75</v>
-      </c>
-      <c r="AD6">
-        <v>1.47</v>
-      </c>
       <c r="AE6">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG6">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
         <v>1.22</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="O7">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q7">
         <v>2.88</v>
@@ -1477,22 +1477,22 @@
         <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z7">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA7">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB7">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AC7">
         <v>2.66</v>
@@ -1622,7 +1622,7 @@
         <v>2.49</v>
       </c>
       <c r="Q8">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="R8">
         <v>2.3</v>
@@ -1631,46 +1631,46 @@
         <v>1.25</v>
       </c>
       <c r="T8">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="U8">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="V8">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="W8">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z8">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="AA8">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AB8">
         <v>2.2</v>
       </c>
       <c r="AC8">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="AD8">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AE8">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF8">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AG8">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,13 +2111,13 @@
         <v>4.16</v>
       </c>
       <c r="Q11">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="R11">
         <v>2</v>
       </c>
       <c r="S11">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="T11">
         <v>2.5</v>
@@ -2129,37 +2129,37 @@
         <v>1.3</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y11">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z11">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AA11">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AB11">
         <v>1.53</v>
       </c>
       <c r="AC11">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AD11">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG11">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2274,55 +2274,55 @@
         <v>2.61</v>
       </c>
       <c r="Q12">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="R12">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="S12">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T12">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U12">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V12">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z12">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA12">
         <v>1.66</v>
       </c>
       <c r="AB12">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC12">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="AD12">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AE12">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AF12">
         <v>1.53</v>
       </c>
       <c r="AG12">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="N13">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="O13">
-        <v>5.85</v>
+        <v>5.75</v>
       </c>
       <c r="P13">
         <v>1.31</v>
       </c>
       <c r="Q13">
-        <v>6</v>
+        <v>5.32</v>
       </c>
       <c r="R13">
         <v>2.88</v>
@@ -2467,13 +2467,13 @@
         <v>6.75</v>
       </c>
       <c r="AA13">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AB13">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="AC13">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AD13">
         <v>1.9</v>
@@ -2501,7 +2501,7 @@
         <v>1.16</v>
       </c>
       <c r="AK13">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,22 +2591,22 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.95</v>
+        <v>2.67</v>
       </c>
       <c r="O14">
         <v>3.23</v>
       </c>
       <c r="P14">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q14">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="R14">
         <v>2</v>
       </c>
       <c r="S14">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T14">
         <v>2.73</v>
@@ -2630,25 +2630,25 @@
         <v>3.02</v>
       </c>
       <c r="AA14">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AB14">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AC14">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AD14">
         <v>1.26</v>
       </c>
       <c r="AE14">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF14">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AG14">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AK14">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2760,43 +2760,43 @@
         <v>4</v>
       </c>
       <c r="P15">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="Q15">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="R15">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="U15">
         <v>2.73</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W15">
         <v>1.07</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z15">
         <v>3.7</v>
       </c>
       <c r="AA15">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB15">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC15">
         <v>3.1</v>
@@ -2805,7 +2805,7 @@
         <v>1.36</v>
       </c>
       <c r="AE15">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF15">
         <v>1.83</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O16">
         <v>3.4</v>
       </c>
       <c r="P16">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -2932,19 +2932,19 @@
         <v>2.35</v>
       </c>
       <c r="S16">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
         <v>2.97</v>
       </c>
       <c r="U16">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="V16">
         <v>1.52</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
         <v>1</v>
@@ -2953,16 +2953,16 @@
         <v>1.2</v>
       </c>
       <c r="Z16">
-        <v>3.92</v>
+        <v>4.31</v>
       </c>
       <c r="AA16">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB16">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AC16">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="AD16">
         <v>1.43</v>
@@ -2971,10 +2971,10 @@
         <v>1.14</v>
       </c>
       <c r="AF16">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG16">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AK16">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>4.64</v>
+        <v>4.25</v>
       </c>
       <c r="O17">
-        <v>3.85</v>
+        <v>4.15</v>
       </c>
       <c r="P17">
         <v>1.66</v>
@@ -3101,37 +3101,37 @@
         <v>3.6</v>
       </c>
       <c r="U17">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V17">
         <v>1.55</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z17">
-        <v>4.3</v>
+        <v>4.56</v>
       </c>
       <c r="AA17">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AB17">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AC17">
         <v>2.38</v>
       </c>
       <c r="AD17">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AE17">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF17">
         <v>1.61</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK17">
         <v>1.15</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="O18">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P18">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="Q18">
-        <v>4.2</v>
+        <v>3.26</v>
       </c>
       <c r="R18">
+        <v>2.25</v>
+      </c>
+      <c r="S18">
+        <v>1.25</v>
+      </c>
+      <c r="T18">
+        <v>3.5</v>
+      </c>
+      <c r="U18">
+        <v>2.3</v>
+      </c>
+      <c r="V18">
+        <v>1.57</v>
+      </c>
+      <c r="W18">
+        <v>1.14</v>
+      </c>
+      <c r="X18">
+        <v>1.03</v>
+      </c>
+      <c r="Y18">
+        <v>1.14</v>
+      </c>
+      <c r="Z18">
+        <v>4.45</v>
+      </c>
+      <c r="AA18">
+        <v>1.6</v>
+      </c>
+      <c r="AB18">
+        <v>2.33</v>
+      </c>
+      <c r="AC18">
+        <v>2.38</v>
+      </c>
+      <c r="AD18">
+        <v>1.53</v>
+      </c>
+      <c r="AE18">
+        <v>1.17</v>
+      </c>
+      <c r="AF18">
+        <v>1.53</v>
+      </c>
+      <c r="AG18">
         <v>2.4</v>
       </c>
-      <c r="S18">
-        <v>1.19</v>
-      </c>
-      <c r="T18">
-        <v>3.6</v>
-      </c>
-      <c r="U18">
-        <v>2.13</v>
-      </c>
-      <c r="V18">
-        <v>1.6</v>
-      </c>
-      <c r="W18">
-        <v>1.15</v>
-      </c>
-      <c r="X18">
-        <v>1.01</v>
-      </c>
-      <c r="Y18">
-        <v>1.1</v>
-      </c>
-      <c r="Z18">
-        <v>5.05</v>
-      </c>
-      <c r="AA18">
-        <v>1.44</v>
-      </c>
-      <c r="AB18">
-        <v>2.34</v>
-      </c>
-      <c r="AC18">
-        <v>2.22</v>
-      </c>
-      <c r="AD18">
-        <v>1.62</v>
-      </c>
-      <c r="AE18">
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
         <v>1.2</v>
       </c>
-      <c r="AF18">
-        <v>1.49</v>
-      </c>
-      <c r="AG18">
-        <v>2.44</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.18</v>
-      </c>
       <c r="AK18">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.43</v>
       </c>
       <c r="P19">
-        <v>2.05</v>
+        <v>2.58</v>
       </c>
       <c r="Q19">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R19">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U19">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="V19">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="Z19">
-        <v>4.45</v>
+        <v>3.34</v>
       </c>
       <c r="AA19">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AB19">
-        <v>2.29</v>
+        <v>1.82</v>
       </c>
       <c r="AC19">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="AD19">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="AE19">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AF19">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AG19">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.71</v>
+        <v>1.27</v>
       </c>
       <c r="AK19">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.39</v>
+        <v>3.95</v>
       </c>
       <c r="O20">
-        <v>3.2</v>
+        <v>4.15</v>
       </c>
       <c r="P20">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="Q20">
-        <v>3</v>
+        <v>3.77</v>
       </c>
       <c r="R20">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="S20">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T20">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U20">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="Z20">
-        <v>3.61</v>
+        <v>6</v>
       </c>
       <c r="AA20">
-        <v>1.86</v>
+        <v>1.47</v>
       </c>
       <c r="AB20">
-        <v>1.81</v>
+        <v>2.34</v>
       </c>
       <c r="AC20">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD20">
-        <v>1.29</v>
+        <v>1.65</v>
       </c>
       <c r="AE20">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AF20">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AG20">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AK20">
-        <v>1.53</v>
+        <v>1.14</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.65</v>
+        <v>2.37</v>
       </c>
       <c r="O22">
         <v>3.25</v>
@@ -3928,13 +3928,13 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z22">
         <v>3.8</v>
       </c>
       <c r="AA22">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AB22">
         <v>1.98</v>
@@ -3943,16 +3943,16 @@
         <v>2.85</v>
       </c>
       <c r="AD22">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE22">
         <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG22">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>3.25</v>
       </c>
       <c r="P23">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q23">
         <v>2.7</v>
@@ -4076,13 +4076,13 @@
         <v>1.39</v>
       </c>
       <c r="T23">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="U23">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="V23">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W23">
         <v>1.05</v>
@@ -4094,13 +4094,13 @@
         <v>1.32</v>
       </c>
       <c r="Z23">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="AA23">
         <v>1.91</v>
       </c>
       <c r="AB23">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC23">
         <v>3.14</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AK23">
         <v>1.57</v>
@@ -4221,25 +4221,25 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="O24">
         <v>3.4</v>
       </c>
       <c r="P24">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q24">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="R24">
         <v>2.13</v>
       </c>
       <c r="S24">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="U24">
         <v>2.56</v>
@@ -4248,7 +4248,7 @@
         <v>1.43</v>
       </c>
       <c r="W24">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4257,13 +4257,13 @@
         <v>1.21</v>
       </c>
       <c r="Z24">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA24">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AB24">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AC24">
         <v>3.13</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK24">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4547,55 +4547,55 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="O26">
         <v>3.5</v>
       </c>
       <c r="P26">
-        <v>3.3</v>
+        <v>3.01</v>
       </c>
       <c r="Q26">
-        <v>2.51</v>
+        <v>2.58</v>
       </c>
       <c r="R26">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S26">
         <v>1.36</v>
       </c>
       <c r="T26">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U26">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V26">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="AA26">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AB26">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AC26">
         <v>3.1</v>
       </c>
       <c r="AD26">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE26">
         <v>1.08</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>2.05</v>
       </c>
       <c r="Q27">
-        <v>3.94</v>
+        <v>3.31</v>
       </c>
       <c r="R27">
         <v>2.3</v>
@@ -4731,7 +4731,7 @@
         <v>3.24</v>
       </c>
       <c r="U27">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="V27">
         <v>1.5</v>
@@ -4743,19 +4743,19 @@
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z27">
         <v>4.25</v>
       </c>
       <c r="AA27">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB27">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AC27">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD27">
         <v>1.45</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
+        <v>1.21</v>
+      </c>
+      <c r="AK27">
         <v>1.25</v>
-      </c>
-      <c r="AK27">
-        <v>1.28</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.95</v>
+        <v>1.3</v>
       </c>
       <c r="O28">
-        <v>3.7</v>
+        <v>5.75</v>
       </c>
       <c r="P28">
-        <v>3.35</v>
+        <v>8.5</v>
       </c>
       <c r="Q28">
-        <v>2.43</v>
+        <v>1.55</v>
       </c>
       <c r="R28">
-        <v>2.51</v>
+        <v>2.78</v>
       </c>
       <c r="S28">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T28">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="U28">
-        <v>2.32</v>
+        <v>1.9</v>
       </c>
       <c r="V28">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="W28">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z28">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA28">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AB28">
-        <v>2.31</v>
+        <v>3.4</v>
       </c>
       <c r="AC28">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="AD28">
-        <v>1.48</v>
+        <v>1.87</v>
       </c>
       <c r="AE28">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AF28">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AG28">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="AK28">
-        <v>1.8</v>
+        <v>3.41</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.28</v>
+        <v>2.31</v>
       </c>
       <c r="O29">
-        <v>6</v>
+        <v>3.45</v>
       </c>
       <c r="P29">
-        <v>9</v>
+        <v>2.7</v>
       </c>
       <c r="Q29">
-        <v>1.67</v>
+        <v>3.05</v>
       </c>
       <c r="R29">
-        <v>3.19</v>
+        <v>2.33</v>
       </c>
       <c r="S29">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="T29">
-        <v>3.98</v>
+        <v>3.2</v>
       </c>
       <c r="U29">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="V29">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>6.25</v>
+        <v>3.7</v>
       </c>
       <c r="AA29">
-        <v>1.29</v>
+        <v>1.79</v>
       </c>
       <c r="AB29">
-        <v>3.04</v>
+        <v>2.03</v>
       </c>
       <c r="AC29">
-        <v>1.81</v>
+        <v>3.1</v>
       </c>
       <c r="AD29">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="AE29">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="AF29">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG29">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="AK29">
-        <v>3.58</v>
+        <v>1.44</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.47</v>
+        <v>1.97</v>
       </c>
       <c r="O30">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="P30">
-        <v>2.57</v>
+        <v>3.05</v>
       </c>
       <c r="Q30">
-        <v>3.05</v>
+        <v>2.33</v>
       </c>
       <c r="R30">
+        <v>2.51</v>
+      </c>
+      <c r="S30">
+        <v>1.25</v>
+      </c>
+      <c r="T30">
+        <v>3.6</v>
+      </c>
+      <c r="U30">
         <v>2.32</v>
       </c>
-      <c r="S30">
-        <v>1.32</v>
-      </c>
-      <c r="T30">
-        <v>3.25</v>
-      </c>
-      <c r="U30">
-        <v>2.5</v>
-      </c>
       <c r="V30">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
         <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA30">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AB30">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="AC30">
-        <v>2.92</v>
+        <v>2.33</v>
       </c>
       <c r="AD30">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE30">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AF30">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AG30">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK30">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5368,19 +5368,19 @@
         <v>3.73</v>
       </c>
       <c r="P31">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="Q31">
         <v>5</v>
       </c>
       <c r="R31">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="S31">
         <v>1.36</v>
       </c>
       <c r="T31">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="U31">
         <v>2.88</v>
@@ -5395,13 +5395,13 @@
         <v>1.05</v>
       </c>
       <c r="Y31">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z31">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA31">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AB31">
         <v>1.75</v>
@@ -5413,7 +5413,7 @@
         <v>1.29</v>
       </c>
       <c r="AE31">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF31">
         <v>1.91</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="AK31">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,31 +5525,31 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="O32">
         <v>3.63</v>
       </c>
       <c r="P32">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Q32">
-        <v>4.72</v>
+        <v>4.82</v>
       </c>
       <c r="R32">
         <v>2.3</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U32">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V32">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
         <v>1.08</v>
@@ -5561,10 +5561,10 @@
         <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA32">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB32">
         <v>2.05</v>
@@ -5576,7 +5576,7 @@
         <v>1.4</v>
       </c>
       <c r="AE32">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF32">
         <v>1.66</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AK32">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="O34">
         <v>3.7</v>
       </c>
       <c r="P34">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="Q34">
         <v>3.6</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S34">
         <v>1.26</v>
@@ -5872,19 +5872,19 @@
         <v>3.4</v>
       </c>
       <c r="U34">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="V34">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W34">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z34">
         <v>4.33</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.7</v>
+        <v>1.21</v>
       </c>
       <c r="AK34">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="O35">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="P35">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="Q35">
         <v>2.45</v>
@@ -6180,25 +6180,25 @@
         <v>1.3</v>
       </c>
       <c r="O36">
-        <v>5.75</v>
+        <v>5.85</v>
       </c>
       <c r="P36">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Q36">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R36">
         <v>2.7</v>
       </c>
       <c r="S36">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T36">
         <v>3.9</v>
       </c>
       <c r="U36">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="V36">
         <v>1.67</v>
@@ -6216,13 +6216,13 @@
         <v>5.67</v>
       </c>
       <c r="AA36">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AB36">
         <v>2.6</v>
       </c>
       <c r="AC36">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AD36">
         <v>1.69</v>
@@ -6231,7 +6231,7 @@
         <v>1.27</v>
       </c>
       <c r="AF36">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
         <v>2</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK36">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,34 +6340,34 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="O37">
-        <v>3.28</v>
+        <v>3.43</v>
       </c>
       <c r="P37">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="Q37">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R37">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S37">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T37">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="U37">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="V37">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W37">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
         <v>1.03</v>
@@ -6376,28 +6376,28 @@
         <v>1.28</v>
       </c>
       <c r="Z37">
-        <v>3.14</v>
+        <v>3.38</v>
       </c>
       <c r="AA37">
         <v>1.9</v>
       </c>
       <c r="AB37">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC37">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="AD37">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE37">
         <v>1.12</v>
       </c>
       <c r="AF37">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG37">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK37">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6499,20 +6499,20 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N38">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O38">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P38">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q38">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="R38">
         <v>2.3</v>
@@ -6524,7 +6524,7 @@
         <v>3.3</v>
       </c>
       <c r="U38">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="V38">
         <v>1.5</v>
@@ -6536,19 +6536,19 @@
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z38">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AA38">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB38">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC38">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AD38">
         <v>1.43</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,80 +6666,80 @@
         </is>
       </c>
       <c r="N39">
+        <v>1.95</v>
+      </c>
+      <c r="O39">
+        <v>3.98</v>
+      </c>
+      <c r="P39">
+        <v>3.1</v>
+      </c>
+      <c r="Q39">
+        <v>2.38</v>
+      </c>
+      <c r="R39">
+        <v>2.56</v>
+      </c>
+      <c r="S39">
+        <v>1.25</v>
+      </c>
+      <c r="T39">
+        <v>3.7</v>
+      </c>
+      <c r="U39">
+        <v>2.2</v>
+      </c>
+      <c r="V39">
         <v>1.6</v>
       </c>
-      <c r="O39">
-        <v>4.6</v>
-      </c>
-      <c r="P39">
-        <v>4.9</v>
-      </c>
-      <c r="Q39">
+      <c r="W39">
+        <v>1.14</v>
+      </c>
+      <c r="X39">
+        <v>1.01</v>
+      </c>
+      <c r="Y39">
+        <v>1.14</v>
+      </c>
+      <c r="Z39">
+        <v>5.5</v>
+      </c>
+      <c r="AA39">
+        <v>1.51</v>
+      </c>
+      <c r="AB39">
+        <v>2.55</v>
+      </c>
+      <c r="AC39">
+        <v>2.27</v>
+      </c>
+      <c r="AD39">
+        <v>1.6</v>
+      </c>
+      <c r="AE39">
+        <v>1.25</v>
+      </c>
+      <c r="AF39">
+        <v>1.44</v>
+      </c>
+      <c r="AG39">
+        <v>2.5</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>1.25</v>
+      </c>
+      <c r="AK39">
         <v>1.87</v>
-      </c>
-      <c r="R39">
-        <v>3.08</v>
-      </c>
-      <c r="S39">
-        <v>1.11</v>
-      </c>
-      <c r="T39">
-        <v>5.05</v>
-      </c>
-      <c r="U39">
-        <v>1.65</v>
-      </c>
-      <c r="V39">
-        <v>2.07</v>
-      </c>
-      <c r="W39">
-        <v>1.3</v>
-      </c>
-      <c r="X39">
-        <v>0</v>
-      </c>
-      <c r="Y39">
-        <v>1.01</v>
-      </c>
-      <c r="Z39">
-        <v>9</v>
-      </c>
-      <c r="AA39">
-        <v>1.23</v>
-      </c>
-      <c r="AB39">
-        <v>4.1</v>
-      </c>
-      <c r="AC39">
-        <v>1.62</v>
-      </c>
-      <c r="AD39">
-        <v>2.32</v>
-      </c>
-      <c r="AE39">
-        <v>1.54</v>
-      </c>
-      <c r="AF39">
-        <v>1.3</v>
-      </c>
-      <c r="AG39">
-        <v>3.2</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.18</v>
-      </c>
-      <c r="AK39">
-        <v>2.38</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>2</v>
+        <v>1.49</v>
       </c>
       <c r="O40">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="P40">
-        <v>2.98</v>
+        <v>5</v>
       </c>
       <c r="Q40">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="R40">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="S40">
         <v>1.2</v>
@@ -6850,10 +6850,10 @@
         <v>4.1</v>
       </c>
       <c r="U40">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="V40">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W40">
         <v>1.18</v>
@@ -6862,47 +6862,47 @@
         <v>0</v>
       </c>
       <c r="Y40">
+        <v>1.1</v>
+      </c>
+      <c r="Z40">
+        <v>6.5</v>
+      </c>
+      <c r="AA40">
+        <v>1.38</v>
+      </c>
+      <c r="AB40">
+        <v>2.75</v>
+      </c>
+      <c r="AC40">
+        <v>2.1</v>
+      </c>
+      <c r="AD40">
+        <v>1.71</v>
+      </c>
+      <c r="AE40">
+        <v>1.31</v>
+      </c>
+      <c r="AF40">
+        <v>1.53</v>
+      </c>
+      <c r="AG40">
+        <v>2.45</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
         <v>1.13</v>
       </c>
-      <c r="Z40">
-        <v>6.09</v>
-      </c>
-      <c r="AA40">
-        <v>1.42</v>
-      </c>
-      <c r="AB40">
-        <v>2.84</v>
-      </c>
-      <c r="AC40">
-        <v>2.06</v>
-      </c>
-      <c r="AD40">
-        <v>1.78</v>
-      </c>
-      <c r="AE40">
-        <v>1.32</v>
-      </c>
-      <c r="AF40">
-        <v>1.4</v>
-      </c>
-      <c r="AG40">
-        <v>2.72</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.22</v>
-      </c>
       <c r="AK40">
-        <v>1.75</v>
+        <v>2.54</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="O41">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="P41">
-        <v>3.48</v>
+        <v>4.85</v>
       </c>
       <c r="Q41">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="R41">
-        <v>2.4</v>
+        <v>3.16</v>
       </c>
       <c r="S41">
+        <v>1.11</v>
+      </c>
+      <c r="T41">
+        <v>5.5</v>
+      </c>
+      <c r="U41">
+        <v>1.65</v>
+      </c>
+      <c r="V41">
+        <v>2.1</v>
+      </c>
+      <c r="W41">
+        <v>1.3</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>1</v>
+      </c>
+      <c r="Z41">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AA41">
         <v>1.25</v>
       </c>
-      <c r="T41">
-        <v>3.75</v>
-      </c>
-      <c r="U41">
-        <v>2.2</v>
-      </c>
-      <c r="V41">
+      <c r="AB41">
+        <v>4.21</v>
+      </c>
+      <c r="AC41">
         <v>1.6</v>
       </c>
-      <c r="W41">
-        <v>1.14</v>
-      </c>
-      <c r="X41">
-        <v>1.01</v>
-      </c>
-      <c r="Y41">
-        <v>1.16</v>
-      </c>
-      <c r="Z41">
-        <v>5.25</v>
-      </c>
-      <c r="AA41">
-        <v>1.51</v>
-      </c>
-      <c r="AB41">
-        <v>2.55</v>
-      </c>
-      <c r="AC41">
-        <v>2.27</v>
-      </c>
       <c r="AD41">
-        <v>1.62</v>
+        <v>2.37</v>
       </c>
       <c r="AE41">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AF41">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AG41">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK41">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
+        <v>1.98</v>
+      </c>
+      <c r="O42">
+        <v>4.21</v>
+      </c>
+      <c r="P42">
+        <v>3.15</v>
+      </c>
+      <c r="Q42">
+        <v>2.3</v>
+      </c>
+      <c r="R42">
+        <v>2.5</v>
+      </c>
+      <c r="S42">
+        <v>1.18</v>
+      </c>
+      <c r="T42">
+        <v>4.33</v>
+      </c>
+      <c r="U42">
+        <v>1.93</v>
+      </c>
+      <c r="V42">
         <v>1.75</v>
       </c>
-      <c r="O42">
-        <v>3.6</v>
-      </c>
-      <c r="P42">
-        <v>4.06</v>
-      </c>
-      <c r="Q42">
-        <v>2.31</v>
-      </c>
-      <c r="R42">
-        <v>2.38</v>
-      </c>
-      <c r="S42">
-        <v>1.25</v>
-      </c>
-      <c r="T42">
-        <v>3.5</v>
-      </c>
-      <c r="U42">
-        <v>2.25</v>
-      </c>
-      <c r="V42">
-        <v>1.56</v>
-      </c>
       <c r="W42">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y42">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z42">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="AA42">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="AB42">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="AC42">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="AD42">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="AE42">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AF42">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AG42">
-        <v>2.26</v>
+        <v>2.72</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.2</v>
       </c>
       <c r="AK42">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="O43">
+        <v>4</v>
+      </c>
+      <c r="P43">
+        <v>3.95</v>
+      </c>
+      <c r="Q43">
+        <v>2.23</v>
+      </c>
+      <c r="R43">
+        <v>2.38</v>
+      </c>
+      <c r="S43">
+        <v>1.25</v>
+      </c>
+      <c r="T43">
+        <v>3.5</v>
+      </c>
+      <c r="U43">
+        <v>2.25</v>
+      </c>
+      <c r="V43">
+        <v>1.56</v>
+      </c>
+      <c r="W43">
+        <v>1.11</v>
+      </c>
+      <c r="X43">
+        <v>1.01</v>
+      </c>
+      <c r="Y43">
+        <v>1.17</v>
+      </c>
+      <c r="Z43">
         <v>4.5</v>
       </c>
-      <c r="P43">
-        <v>5.4</v>
-      </c>
-      <c r="Q43">
-        <v>1.89</v>
-      </c>
-      <c r="R43">
-        <v>2.8</v>
-      </c>
-      <c r="S43">
-        <v>1.2</v>
-      </c>
-      <c r="T43">
-        <v>4.1</v>
-      </c>
-      <c r="U43">
-        <v>2.16</v>
-      </c>
-      <c r="V43">
-        <v>1.71</v>
-      </c>
-      <c r="W43">
-        <v>1.17</v>
-      </c>
-      <c r="X43">
-        <v>0</v>
-      </c>
-      <c r="Y43">
-        <v>1.09</v>
-      </c>
-      <c r="Z43">
-        <v>5.4</v>
-      </c>
       <c r="AA43">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AB43">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AC43">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="AD43">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AE43">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AF43">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG43">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>2.54</v>
+        <v>1.95</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P52">
-        <v>3.54</v>
+        <v>3.08</v>
       </c>
       <c r="Q52">
         <v>2.59</v>
@@ -8815,34 +8815,34 @@
         <v>1.07</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z52">
-        <v>3.53</v>
+        <v>3.8</v>
       </c>
       <c r="AA52">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AB52">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AC52">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AD52">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE52">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF52">
         <v>1.67</v>
       </c>
       <c r="AG52">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8951,13 +8951,13 @@
         <v>2.75</v>
       </c>
       <c r="O53">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="P53">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="Q53">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="R53">
         <v>2.18</v>
@@ -8978,34 +8978,34 @@
         <v>1.08</v>
       </c>
       <c r="X53">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z53">
-        <v>4.13</v>
+        <v>4.5</v>
       </c>
       <c r="AA53">
         <v>1.65</v>
       </c>
       <c r="AB53">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AC53">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AD53">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE53">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF53">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG53">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="O54">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P54">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="Q54">
         <v>3.13</v>
@@ -9141,34 +9141,34 @@
         <v>1.15</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z54">
-        <v>4.87</v>
+        <v>5</v>
       </c>
       <c r="AA54">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AB54">
         <v>2.37</v>
       </c>
       <c r="AC54">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="AD54">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE54">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF54">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG54">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>1.25</v>
       </c>
       <c r="AK54">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="O55">
         <v>4.2</v>
       </c>
       <c r="P55">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="Q55">
         <v>1.99</v>
@@ -9289,10 +9289,10 @@
         <v>2.8</v>
       </c>
       <c r="S55">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="T55">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="U55">
         <v>1.78</v>
@@ -9307,31 +9307,31 @@
         <v>0</v>
       </c>
       <c r="Y55">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z55">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AA55">
         <v>1.3</v>
       </c>
       <c r="AB55">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AC55">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AD55">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AE55">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AF55">
         <v>1.33</v>
       </c>
       <c r="AG55">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK55">
         <v>2.2</v>
@@ -9437,19 +9437,19 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="O56">
-        <v>3.7</v>
+        <v>3.98</v>
       </c>
       <c r="P56">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q56">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="R56">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S56">
         <v>1.21</v>
@@ -9467,13 +9467,13 @@
         <v>1.15</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z56">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AA56">
         <v>1.47</v>
@@ -9488,13 +9488,13 @@
         <v>1.61</v>
       </c>
       <c r="AE56">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF56">
         <v>1.44</v>
       </c>
       <c r="AG56">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9603,61 +9603,61 @@
         <v>1.79</v>
       </c>
       <c r="O57">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P57">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q57">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="R57">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="S57">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T57">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U57">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V57">
         <v>1.74</v>
       </c>
       <c r="W57">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X57">
         <v>0</v>
       </c>
       <c r="Y57">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z57">
-        <v>6.24</v>
+        <v>6.5</v>
       </c>
       <c r="AA57">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AB57">
         <v>2.9</v>
       </c>
       <c r="AC57">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="AD57">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AE57">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF57">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG57">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9763,10 +9763,10 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="O58">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="P58">
         <v>6</v>
@@ -9775,7 +9775,7 @@
         <v>1.75</v>
       </c>
       <c r="R58">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="S58">
         <v>1.17</v>
@@ -9796,10 +9796,10 @@
         <v>0</v>
       </c>
       <c r="Y58">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z58">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA58">
         <v>1.3</v>
@@ -9811,16 +9811,16 @@
         <v>1.84</v>
       </c>
       <c r="AD58">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AE58">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AF58">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG58">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AK58">
         <v>2.62</v>
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="O59">
         <v>3.75</v>
@@ -9944,7 +9944,7 @@
         <v>1.25</v>
       </c>
       <c r="T59">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U59">
         <v>2.13</v>
@@ -9959,31 +9959,31 @@
         <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z59">
-        <v>5.14</v>
+        <v>5.5</v>
       </c>
       <c r="AA59">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AB59">
         <v>2.48</v>
       </c>
       <c r="AC59">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AD59">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE59">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF59">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG59">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK59">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="O60">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="P60">
-        <v>3.86</v>
+        <v>3.16</v>
       </c>
       <c r="Q60">
-        <v>2.39</v>
+        <v>2.68</v>
       </c>
       <c r="R60">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="S60">
         <v>1.25</v>
       </c>
       <c r="T60">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="U60">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="V60">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W60">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z60">
-        <v>4.15</v>
+        <v>5.5</v>
       </c>
       <c r="AA60">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="AB60">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AC60">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AD60">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AE60">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AF60">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AG60">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AK60">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="O61">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="P61">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q61">
-        <v>2.49</v>
+        <v>1.87</v>
       </c>
       <c r="R61">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="S61">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="T61">
-        <v>3.6</v>
+        <v>5.05</v>
       </c>
       <c r="U61">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="V61">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="W61">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="X61">
         <v>0</v>
       </c>
       <c r="Y61">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Z61">
-        <v>4.98</v>
+        <v>8</v>
       </c>
       <c r="AA61">
-        <v>1.49</v>
+        <v>1.26</v>
       </c>
       <c r="AB61">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="AC61">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="AD61">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="AE61">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AF61">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG61">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AK61">
-        <v>1.67</v>
+        <v>2.64</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="O62">
+        <v>3.8</v>
+      </c>
+      <c r="P62">
+        <v>3.9</v>
+      </c>
+      <c r="Q62">
+        <v>2.28</v>
+      </c>
+      <c r="R62">
+        <v>2.3</v>
+      </c>
+      <c r="S62">
+        <v>1.25</v>
+      </c>
+      <c r="T62">
+        <v>3.5</v>
+      </c>
+      <c r="U62">
+        <v>2.4</v>
+      </c>
+      <c r="V62">
+        <v>1.57</v>
+      </c>
+      <c r="W62">
+        <v>1.15</v>
+      </c>
+      <c r="X62">
+        <v>1.01</v>
+      </c>
+      <c r="Y62">
+        <v>1.2</v>
+      </c>
+      <c r="Z62">
         <v>4.5</v>
       </c>
-      <c r="P62">
-        <v>6</v>
-      </c>
-      <c r="Q62">
-        <v>1.73</v>
-      </c>
-      <c r="R62">
-        <v>2.75</v>
-      </c>
-      <c r="S62">
+      <c r="AA62">
+        <v>1.62</v>
+      </c>
+      <c r="AB62">
+        <v>2.3</v>
+      </c>
+      <c r="AC62">
+        <v>2.63</v>
+      </c>
+      <c r="AD62">
+        <v>1.47</v>
+      </c>
+      <c r="AE62">
         <v>1.17</v>
       </c>
-      <c r="T62">
-        <v>5.05</v>
-      </c>
-      <c r="U62">
-        <v>1.85</v>
-      </c>
-      <c r="V62">
-        <v>1.9</v>
-      </c>
-      <c r="W62">
-        <v>1.22</v>
-      </c>
-      <c r="X62">
-        <v>0</v>
-      </c>
-      <c r="Y62">
-        <v>1.03</v>
-      </c>
-      <c r="Z62">
-        <v>7.5</v>
-      </c>
-      <c r="AA62">
-        <v>1.26</v>
-      </c>
-      <c r="AB62">
-        <v>3.2</v>
-      </c>
-      <c r="AC62">
-        <v>1.79</v>
-      </c>
-      <c r="AD62">
-        <v>1.95</v>
-      </c>
-      <c r="AE62">
-        <v>1.36</v>
-      </c>
       <c r="AF62">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AG62">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK62">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="AL62">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -1015,10 +1015,10 @@
         <v>1.08</v>
       </c>
       <c r="AF4">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG4">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O5">
         <v>3.8</v>
@@ -1290,7 +1290,7 @@
         <v>4.03</v>
       </c>
       <c r="O6">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="P6">
         <v>1.83</v>
@@ -1305,7 +1305,7 @@
         <v>1.22</v>
       </c>
       <c r="T6">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="U6">
         <v>2.46</v>
@@ -1314,7 +1314,7 @@
         <v>1.51</v>
       </c>
       <c r="W6">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
         <v>1.01</v>
@@ -1329,7 +1329,7 @@
         <v>1.65</v>
       </c>
       <c r="AB6">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AC6">
         <v>2.58</v>
@@ -1338,13 +1338,13 @@
         <v>1.5</v>
       </c>
       <c r="AE6">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG6">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AK6">
         <v>1.22</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="O7">
         <v>3.4</v>
@@ -1652,10 +1652,10 @@
         <v>5</v>
       </c>
       <c r="AA8">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB8">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AC8">
         <v>2.55</v>
@@ -2286,10 +2286,10 @@
         <v>3.4</v>
       </c>
       <c r="U12">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="V12">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W12">
         <v>1.12</v>
@@ -2307,7 +2307,7 @@
         <v>1.66</v>
       </c>
       <c r="AB12">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC12">
         <v>2.55</v>
@@ -2319,7 +2319,7 @@
         <v>1.2</v>
       </c>
       <c r="AF12">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG12">
         <v>2.38</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="O13">
-        <v>5.75</v>
+        <v>5.85</v>
       </c>
       <c r="P13">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="Q13">
         <v>5.32</v>
       </c>
       <c r="R13">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="S13">
         <v>1.14</v>
@@ -2501,7 +2501,7 @@
         <v>1.16</v>
       </c>
       <c r="AK13">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2636,7 +2636,7 @@
         <v>1.64</v>
       </c>
       <c r="AC14">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD14">
         <v>1.26</v>
@@ -2760,7 +2760,7 @@
         <v>4</v>
       </c>
       <c r="P15">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
         <v>2</v>
@@ -2793,10 +2793,10 @@
         <v>3.7</v>
       </c>
       <c r="AA15">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB15">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC15">
         <v>3.1</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="O16">
         <v>3.4</v>
       </c>
       <c r="P16">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q16">
         <v>3</v>
       </c>
       <c r="R16">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="S16">
         <v>1.3</v>
@@ -2953,16 +2953,16 @@
         <v>1.2</v>
       </c>
       <c r="Z16">
-        <v>4.31</v>
+        <v>4.35</v>
       </c>
       <c r="AA16">
         <v>1.67</v>
       </c>
       <c r="AB16">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AC16">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AD16">
         <v>1.43</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AK16">
         <v>1.51</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="O17">
-        <v>4.15</v>
+        <v>3.73</v>
       </c>
       <c r="P17">
         <v>1.66</v>
@@ -3110,13 +3110,13 @@
         <v>1.12</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
         <v>1.19</v>
       </c>
       <c r="Z17">
-        <v>4.56</v>
+        <v>4.6</v>
       </c>
       <c r="AA17">
         <v>1.57</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O18">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q18">
         <v>3.26</v>
@@ -3273,7 +3273,7 @@
         <v>1.14</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
         <v>1.14</v>
@@ -3285,13 +3285,13 @@
         <v>1.6</v>
       </c>
       <c r="AB18">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AC18">
         <v>2.38</v>
       </c>
       <c r="AD18">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE18">
         <v>1.17</v>
@@ -3316,7 +3316,7 @@
         <v>1.2</v>
       </c>
       <c r="AK18">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="O19">
         <v>3.43</v>
@@ -3415,7 +3415,7 @@
         <v>2.58</v>
       </c>
       <c r="Q19">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="R19">
         <v>2.1</v>
@@ -3445,7 +3445,7 @@
         <v>3.34</v>
       </c>
       <c r="AA19">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AB19">
         <v>1.82</v>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="O20">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="P20">
         <v>1.7</v>
@@ -3581,7 +3581,7 @@
         <v>3.77</v>
       </c>
       <c r="R20">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S20">
         <v>1.25</v>
@@ -3605,19 +3605,19 @@
         <v>1.13</v>
       </c>
       <c r="Z20">
-        <v>6</v>
+        <v>5.14</v>
       </c>
       <c r="AA20">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AB20">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="AC20">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AD20">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AE20">
         <v>1.2</v>
@@ -3934,7 +3934,7 @@
         <v>3.8</v>
       </c>
       <c r="AA22">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AB22">
         <v>1.98</v>
@@ -3943,13 +3943,13 @@
         <v>2.85</v>
       </c>
       <c r="AD22">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AE22">
         <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG22">
         <v>2.15</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
+        <v>2.8</v>
+      </c>
+      <c r="O23">
+        <v>3.4</v>
+      </c>
+      <c r="P23">
         <v>2.25</v>
       </c>
-      <c r="O23">
-        <v>3.25</v>
-      </c>
-      <c r="P23">
+      <c r="Q23">
+        <v>3.21</v>
+      </c>
+      <c r="R23">
+        <v>2.13</v>
+      </c>
+      <c r="S23">
+        <v>1.33</v>
+      </c>
+      <c r="T23">
         <v>3</v>
       </c>
-      <c r="Q23">
-        <v>2.7</v>
-      </c>
-      <c r="R23">
-        <v>2.07</v>
-      </c>
-      <c r="S23">
-        <v>1.39</v>
-      </c>
-      <c r="T23">
-        <v>2.88</v>
-      </c>
       <c r="U23">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="V23">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W23">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="Z23">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA23">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AB23">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AC23">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AD23">
+        <v>1.33</v>
+      </c>
+      <c r="AE23">
+        <v>1.09</v>
+      </c>
+      <c r="AF23">
+        <v>1.61</v>
+      </c>
+      <c r="AG23">
+        <v>2.18</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
         <v>1.27</v>
       </c>
-      <c r="AE23">
-        <v>1.1</v>
-      </c>
-      <c r="AF23">
-        <v>1.75</v>
-      </c>
-      <c r="AG23">
-        <v>1.95</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.28</v>
-      </c>
       <c r="AK23">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
+        <v>2.12</v>
+      </c>
+      <c r="O24">
+        <v>3.3</v>
+      </c>
+      <c r="P24">
+        <v>3</v>
+      </c>
+      <c r="Q24">
+        <v>2.7</v>
+      </c>
+      <c r="R24">
+        <v>2.07</v>
+      </c>
+      <c r="S24">
+        <v>1.4</v>
+      </c>
+      <c r="T24">
+        <v>2.88</v>
+      </c>
+      <c r="U24">
         <v>2.8</v>
       </c>
-      <c r="O24">
-        <v>3.4</v>
-      </c>
-      <c r="P24">
-        <v>2.25</v>
-      </c>
-      <c r="Q24">
-        <v>3.21</v>
-      </c>
-      <c r="R24">
-        <v>2.13</v>
-      </c>
-      <c r="S24">
-        <v>1.33</v>
-      </c>
-      <c r="T24">
-        <v>3</v>
-      </c>
-      <c r="U24">
-        <v>2.56</v>
-      </c>
       <c r="V24">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
+        <v>1.05</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
+        <v>1.32</v>
+      </c>
+      <c r="Z24">
+        <v>3.25</v>
+      </c>
+      <c r="AA24">
+        <v>1.91</v>
+      </c>
+      <c r="AB24">
+        <v>1.83</v>
+      </c>
+      <c r="AC24">
+        <v>3.14</v>
+      </c>
+      <c r="AD24">
+        <v>1.27</v>
+      </c>
+      <c r="AE24">
         <v>1.1</v>
       </c>
-      <c r="X24">
-        <v>1.01</v>
-      </c>
-      <c r="Y24">
-        <v>1.21</v>
-      </c>
-      <c r="Z24">
-        <v>3.5</v>
-      </c>
-      <c r="AA24">
-        <v>1.89</v>
-      </c>
-      <c r="AB24">
-        <v>1.93</v>
-      </c>
-      <c r="AC24">
-        <v>3.13</v>
-      </c>
-      <c r="AD24">
-        <v>1.33</v>
-      </c>
-      <c r="AE24">
-        <v>1.09</v>
-      </c>
       <c r="AF24">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AG24">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK24">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>2.05</v>
       </c>
       <c r="O26">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P26">
-        <v>3.01</v>
+        <v>3.45</v>
       </c>
       <c r="Q26">
         <v>2.58</v>
@@ -4562,16 +4562,16 @@
         <v>2.14</v>
       </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U26">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V26">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
         <v>1.06</v>
@@ -4583,7 +4583,7 @@
         <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA26">
         <v>1.84</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.25</v>
+        <v>2.33</v>
       </c>
       <c r="O27">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P27">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="Q27">
-        <v>3.31</v>
+        <v>3.05</v>
       </c>
       <c r="R27">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S27">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T27">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="U27">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="V27">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W27">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z27">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="AA27">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AB27">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AC27">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AD27">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AE27">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AG27">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AK27">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,80 +4873,80 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="O28">
-        <v>5.75</v>
+        <v>3.65</v>
       </c>
       <c r="P28">
-        <v>8.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q28">
-        <v>1.55</v>
+        <v>3.31</v>
       </c>
       <c r="R28">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>4.8</v>
+        <v>3.24</v>
       </c>
       <c r="U28">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="V28">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="W28">
+        <v>1.12</v>
+      </c>
+      <c r="X28">
+        <v>1.02</v>
+      </c>
+      <c r="Y28">
+        <v>1.19</v>
+      </c>
+      <c r="Z28">
+        <v>4.25</v>
+      </c>
+      <c r="AA28">
+        <v>1.62</v>
+      </c>
+      <c r="AB28">
+        <v>2.15</v>
+      </c>
+      <c r="AC28">
+        <v>2.6</v>
+      </c>
+      <c r="AD28">
+        <v>1.45</v>
+      </c>
+      <c r="AE28">
+        <v>1.15</v>
+      </c>
+      <c r="AF28">
+        <v>1.54</v>
+      </c>
+      <c r="AG28">
+        <v>2.32</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
         <v>1.21</v>
       </c>
-      <c r="X28">
-        <v>1.01</v>
-      </c>
-      <c r="Y28">
-        <v>1.08</v>
-      </c>
-      <c r="Z28">
-        <v>6.25</v>
-      </c>
-      <c r="AA28">
-        <v>1.33</v>
-      </c>
-      <c r="AB28">
-        <v>3.4</v>
-      </c>
-      <c r="AC28">
-        <v>1.9</v>
-      </c>
-      <c r="AD28">
-        <v>1.87</v>
-      </c>
-      <c r="AE28">
-        <v>1.36</v>
-      </c>
-      <c r="AF28">
-        <v>1.61</v>
-      </c>
-      <c r="AG28">
-        <v>2.15</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.06</v>
-      </c>
       <c r="AK28">
-        <v>3.41</v>
+        <v>1.25</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.31</v>
+        <v>1.99</v>
       </c>
       <c r="O29">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="P29">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="Q29">
-        <v>3.05</v>
+        <v>2.33</v>
       </c>
       <c r="R29">
-        <v>2.33</v>
+        <v>2.51</v>
       </c>
       <c r="S29">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T29">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U29">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V29">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="W29">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
         <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA29">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AB29">
-        <v>2.03</v>
+        <v>2.31</v>
       </c>
       <c r="AC29">
-        <v>3.1</v>
+        <v>2.33</v>
       </c>
       <c r="AD29">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE29">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AF29">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AG29">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK29">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.97</v>
+        <v>1.3</v>
       </c>
       <c r="O30">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="P30">
-        <v>3.05</v>
+        <v>8.5</v>
       </c>
       <c r="Q30">
-        <v>2.33</v>
+        <v>1.57</v>
       </c>
       <c r="R30">
-        <v>2.51</v>
+        <v>2.78</v>
       </c>
       <c r="S30">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T30">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="U30">
-        <v>2.32</v>
+        <v>1.85</v>
       </c>
       <c r="V30">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="W30">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z30">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA30">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AB30">
-        <v>2.31</v>
+        <v>3.2</v>
       </c>
       <c r="AC30">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="AD30">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AE30">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AF30">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AG30">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK30">
-        <v>1.85</v>
+        <v>3.41</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5395,16 +5395,16 @@
         <v>1.05</v>
       </c>
       <c r="Y31">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z31">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA31">
         <v>2.16</v>
       </c>
       <c r="AB31">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC31">
         <v>3.5</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="O32">
         <v>3.63</v>
@@ -5534,10 +5534,10 @@
         <v>1.72</v>
       </c>
       <c r="Q32">
-        <v>4.82</v>
+        <v>3.81</v>
       </c>
       <c r="R32">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S32">
         <v>1.3</v>
@@ -5564,7 +5564,7 @@
         <v>4.1</v>
       </c>
       <c r="AA32">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB32">
         <v>2.05</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="O34">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P34">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="Q34">
         <v>3.6</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.21</v>
+        <v>1.7</v>
       </c>
       <c r="AK34">
         <v>1.27</v>
@@ -6041,7 +6041,7 @@
         <v>1.4</v>
       </c>
       <c r="W35">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
         <v>1.03</v>
@@ -6087,7 +6087,7 @@
         <v>1.28</v>
       </c>
       <c r="AK35">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="O36">
         <v>5.85</v>
@@ -6346,22 +6346,22 @@
         <v>3.43</v>
       </c>
       <c r="P37">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
       </c>
       <c r="R37">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="S37">
         <v>1.38</v>
       </c>
       <c r="T37">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="U37">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="V37">
         <v>1.42</v>
@@ -6373,7 +6373,7 @@
         <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z37">
         <v>3.38</v>
@@ -6382,7 +6382,7 @@
         <v>1.9</v>
       </c>
       <c r="AB37">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AC37">
         <v>3.2</v>
@@ -6391,7 +6391,7 @@
         <v>1.33</v>
       </c>
       <c r="AE37">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
         <v>1.73</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O39">
         <v>3.98</v>
       </c>
       <c r="P39">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q39">
         <v>2.38</v>
@@ -6832,10 +6832,10 @@
         <v>1.49</v>
       </c>
       <c r="O40">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="P40">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q40">
         <v>1.89</v>
@@ -6871,7 +6871,7 @@
         <v>1.38</v>
       </c>
       <c r="AB40">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC40">
         <v>2.1</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="O41">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="P41">
-        <v>4.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q41">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="R41">
-        <v>3.16</v>
+        <v>2.38</v>
       </c>
       <c r="S41">
+        <v>1.25</v>
+      </c>
+      <c r="T41">
+        <v>3.5</v>
+      </c>
+      <c r="U41">
+        <v>2.25</v>
+      </c>
+      <c r="V41">
+        <v>1.56</v>
+      </c>
+      <c r="W41">
         <v>1.11</v>
       </c>
-      <c r="T41">
-        <v>5.5</v>
-      </c>
-      <c r="U41">
-        <v>1.65</v>
-      </c>
-      <c r="V41">
-        <v>2.1</v>
-      </c>
-      <c r="W41">
-        <v>1.3</v>
-      </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="Z41">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="AA41">
+        <v>1.57</v>
+      </c>
+      <c r="AB41">
+        <v>2.31</v>
+      </c>
+      <c r="AC41">
+        <v>2.45</v>
+      </c>
+      <c r="AD41">
+        <v>1.53</v>
+      </c>
+      <c r="AE41">
+        <v>1.16</v>
+      </c>
+      <c r="AF41">
+        <v>1.55</v>
+      </c>
+      <c r="AG41">
+        <v>2.3</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
         <v>1.25</v>
       </c>
-      <c r="AB41">
-        <v>4.21</v>
-      </c>
-      <c r="AC41">
-        <v>1.6</v>
-      </c>
-      <c r="AD41">
-        <v>2.37</v>
-      </c>
-      <c r="AE41">
-        <v>1.56</v>
-      </c>
-      <c r="AF41">
-        <v>1.3</v>
-      </c>
-      <c r="AG41">
-        <v>3.2</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.18</v>
-      </c>
       <c r="AK41">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,80 +7155,80 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.98</v>
+        <v>1.52</v>
       </c>
       <c r="O42">
+        <v>4.8</v>
+      </c>
+      <c r="P42">
+        <v>4.85</v>
+      </c>
+      <c r="Q42">
+        <v>1.8</v>
+      </c>
+      <c r="R42">
+        <v>3.16</v>
+      </c>
+      <c r="S42">
+        <v>1.11</v>
+      </c>
+      <c r="T42">
+        <v>5.5</v>
+      </c>
+      <c r="U42">
+        <v>1.65</v>
+      </c>
+      <c r="V42">
+        <v>2.1</v>
+      </c>
+      <c r="W42">
+        <v>1.3</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>1</v>
+      </c>
+      <c r="Z42">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AA42">
+        <v>1.2</v>
+      </c>
+      <c r="AB42">
         <v>4.21</v>
       </c>
-      <c r="P42">
-        <v>3.15</v>
-      </c>
-      <c r="Q42">
-        <v>2.3</v>
-      </c>
-      <c r="R42">
-        <v>2.5</v>
-      </c>
-      <c r="S42">
+      <c r="AC42">
+        <v>1.6</v>
+      </c>
+      <c r="AD42">
+        <v>2.45</v>
+      </c>
+      <c r="AE42">
+        <v>1.56</v>
+      </c>
+      <c r="AF42">
+        <v>1.3</v>
+      </c>
+      <c r="AG42">
+        <v>3.2</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
         <v>1.18</v>
       </c>
-      <c r="T42">
-        <v>4.33</v>
-      </c>
-      <c r="U42">
-        <v>1.93</v>
-      </c>
-      <c r="V42">
-        <v>1.75</v>
-      </c>
-      <c r="W42">
-        <v>1.2</v>
-      </c>
-      <c r="X42">
-        <v>0</v>
-      </c>
-      <c r="Y42">
-        <v>1.12</v>
-      </c>
-      <c r="Z42">
-        <v>6.5</v>
-      </c>
-      <c r="AA42">
-        <v>1.42</v>
-      </c>
-      <c r="AB42">
-        <v>2.8</v>
-      </c>
-      <c r="AC42">
-        <v>2.01</v>
-      </c>
-      <c r="AD42">
-        <v>1.75</v>
-      </c>
-      <c r="AE42">
-        <v>1.29</v>
-      </c>
-      <c r="AF42">
-        <v>1.4</v>
-      </c>
-      <c r="AG42">
-        <v>2.72</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.2</v>
-      </c>
       <c r="AK42">
-        <v>1.78</v>
+        <v>2.6</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="O43">
-        <v>4</v>
+        <v>4.21</v>
       </c>
       <c r="P43">
-        <v>3.95</v>
+        <v>2.93</v>
       </c>
       <c r="Q43">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="R43">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T43">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="U43">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="V43">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="W43">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y43">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z43">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA43">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AB43">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AC43">
-        <v>2.45</v>
+        <v>2.01</v>
       </c>
       <c r="AD43">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AE43">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AF43">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AG43">
-        <v>2.26</v>
+        <v>2.72</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK43">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8812,7 +8812,7 @@
         <v>1.45</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X52">
         <v>1.04</v>
@@ -8827,7 +8827,7 @@
         <v>1.84</v>
       </c>
       <c r="AB52">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AC52">
         <v>3.1</v>
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="O53">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
         <v>2.37</v>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK53">
         <v>1.4</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="O55">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="P55">
-        <v>4.45</v>
+        <v>3.3</v>
       </c>
       <c r="Q55">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="R55">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="S55">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="T55">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="U55">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="V55">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="W55">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Z55">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="AA55">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AB55">
-        <v>3.34</v>
+        <v>2.46</v>
       </c>
       <c r="AC55">
-        <v>1.67</v>
+        <v>2.13</v>
       </c>
       <c r="AD55">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="AE55">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AF55">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AG55">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK55">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.97</v>
+        <v>1.41</v>
       </c>
       <c r="O56">
-        <v>3.98</v>
+        <v>5</v>
       </c>
       <c r="P56">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="Q56">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="R56">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="S56">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="T56">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U56">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="V56">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="W56">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y56">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z56">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA56">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AB56">
-        <v>2.46</v>
+        <v>3.05</v>
       </c>
       <c r="AC56">
-        <v>2.13</v>
+        <v>1.84</v>
       </c>
       <c r="AD56">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="AE56">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AF56">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG56">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AK56">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="O57">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="P57">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q57">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="R57">
-        <v>2.72</v>
+        <v>2.38</v>
       </c>
       <c r="S57">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T57">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="U57">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="V57">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="W57">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z57">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA57">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AB57">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="AC57">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AD57">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AE57">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AF57">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AG57">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK57">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,80 +9763,80 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.41</v>
+        <v>1.76</v>
       </c>
       <c r="O58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P58">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="Q58">
+        <v>2.19</v>
+      </c>
+      <c r="R58">
+        <v>2.72</v>
+      </c>
+      <c r="S58">
+        <v>1.2</v>
+      </c>
+      <c r="T58">
+        <v>4.2</v>
+      </c>
+      <c r="U58">
+        <v>1.95</v>
+      </c>
+      <c r="V58">
         <v>1.75</v>
       </c>
-      <c r="R58">
-        <v>2.61</v>
-      </c>
-      <c r="S58">
-        <v>1.17</v>
-      </c>
-      <c r="T58">
-        <v>4.6</v>
-      </c>
-      <c r="U58">
-        <v>1.91</v>
-      </c>
-      <c r="V58">
-        <v>1.85</v>
-      </c>
       <c r="W58">
+        <v>1.2</v>
+      </c>
+      <c r="X58">
+        <v>0</v>
+      </c>
+      <c r="Y58">
+        <v>1.1</v>
+      </c>
+      <c r="Z58">
+        <v>6.5</v>
+      </c>
+      <c r="AA58">
+        <v>1.36</v>
+      </c>
+      <c r="AB58">
+        <v>2.9</v>
+      </c>
+      <c r="AC58">
+        <v>1.9</v>
+      </c>
+      <c r="AD58">
+        <v>1.87</v>
+      </c>
+      <c r="AE58">
+        <v>1.36</v>
+      </c>
+      <c r="AF58">
+        <v>1.4</v>
+      </c>
+      <c r="AG58">
+        <v>2.88</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
         <v>1.22</v>
       </c>
-      <c r="X58">
-        <v>0</v>
-      </c>
-      <c r="Y58">
-        <v>1.07</v>
-      </c>
-      <c r="Z58">
-        <v>8</v>
-      </c>
-      <c r="AA58">
-        <v>1.3</v>
-      </c>
-      <c r="AB58">
-        <v>3.05</v>
-      </c>
-      <c r="AC58">
-        <v>1.84</v>
-      </c>
-      <c r="AD58">
-        <v>1.98</v>
-      </c>
-      <c r="AE58">
-        <v>1.4</v>
-      </c>
-      <c r="AF58">
-        <v>1.5</v>
-      </c>
-      <c r="AG58">
-        <v>2.55</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>1.11</v>
-      </c>
       <c r="AK58">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="O59">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="P59">
-        <v>3.58</v>
+        <v>4.45</v>
       </c>
       <c r="Q59">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="R59">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="S59">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="T59">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="U59">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="V59">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="W59">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="X59">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y59">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="Z59">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA59">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="AB59">
-        <v>2.48</v>
+        <v>3.34</v>
       </c>
       <c r="AC59">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AD59">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AE59">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AF59">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AG59">
-        <v>2.46</v>
+        <v>2.9</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK59">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10092,7 +10092,7 @@
         <v>2.05</v>
       </c>
       <c r="O60">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="P60">
         <v>3.16</v>
@@ -10107,7 +10107,7 @@
         <v>1.25</v>
       </c>
       <c r="T60">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="U60">
         <v>2.25</v>
@@ -10252,16 +10252,16 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="O61">
-        <v>4.8</v>
+        <v>5.05</v>
       </c>
       <c r="P61">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Q61">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="R61">
         <v>2.75</v>
@@ -10270,7 +10270,7 @@
         <v>1.15</v>
       </c>
       <c r="T61">
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="U61">
         <v>1.92</v>
@@ -10294,7 +10294,7 @@
         <v>1.26</v>
       </c>
       <c r="AB61">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AC61">
         <v>1.8</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK61">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="O62">
         <v>3.8</v>
@@ -10424,7 +10424,7 @@
         <v>3.9</v>
       </c>
       <c r="Q62">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="R62">
         <v>2.3</v>
@@ -10436,7 +10436,7 @@
         <v>3.5</v>
       </c>
       <c r="U62">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V62">
         <v>1.57</v>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK62">
         <v>1.91</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -656,13 +656,13 @@
         <v>2.5</v>
       </c>
       <c r="U2">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="V2">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
         <v>1.06</v>
@@ -689,10 +689,10 @@
         <v>1.01</v>
       </c>
       <c r="AF2">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AG2">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK2">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>3.1</v>
       </c>
       <c r="P3">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -816,7 +816,7 @@
         <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="U3">
         <v>2.9</v>
@@ -852,7 +852,7 @@
         <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
         <v>1.9</v>
@@ -1127,10 +1127,10 @@
         <v>1.55</v>
       </c>
       <c r="O5">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P5">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q5">
         <v>2.05</v>
@@ -1160,7 +1160,7 @@
         <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA5">
         <v>1.75</v>
@@ -1175,7 +1175,7 @@
         <v>1.4</v>
       </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF5">
         <v>1.8</v>
@@ -1197,7 +1197,7 @@
         <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1791,7 +1791,7 @@
         <v>1.96</v>
       </c>
       <c r="S9">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T9">
         <v>2.58</v>
@@ -1800,10 +1800,10 @@
         <v>2.81</v>
       </c>
       <c r="V9">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
         <v>1.02</v>
@@ -1833,7 +1833,7 @@
         <v>1.84</v>
       </c>
       <c r="AG9">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2147,10 +2147,10 @@
         <v>1.53</v>
       </c>
       <c r="AC11">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AD11">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE11">
         <v>1.05</v>
@@ -2431,19 +2431,19 @@
         <v>6.7</v>
       </c>
       <c r="O13">
-        <v>5.85</v>
+        <v>5.75</v>
       </c>
       <c r="P13">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Q13">
         <v>5.32</v>
       </c>
       <c r="R13">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="S13">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T13">
         <v>4.8</v>
@@ -2501,7 +2501,7 @@
         <v>1.16</v>
       </c>
       <c r="AK13">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2612,7 +2612,7 @@
         <v>2.73</v>
       </c>
       <c r="U14">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="V14">
         <v>1.29</v>
@@ -2769,28 +2769,28 @@
         <v>2.3</v>
       </c>
       <c r="S15">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="U15">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="V15">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
         <v>1.07</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z15">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="AA15">
         <v>1.78</v>
@@ -2805,7 +2805,7 @@
         <v>1.36</v>
       </c>
       <c r="AE15">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF15">
         <v>1.83</v>
@@ -2827,7 +2827,7 @@
         <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
+        <v>1.99</v>
+      </c>
+      <c r="O28">
+        <v>3.8</v>
+      </c>
+      <c r="P28">
         <v>3.4</v>
       </c>
-      <c r="O28">
-        <v>3.65</v>
-      </c>
-      <c r="P28">
-        <v>2.05</v>
-      </c>
       <c r="Q28">
-        <v>3.31</v>
+        <v>2.33</v>
       </c>
       <c r="R28">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T28">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="U28">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="V28">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W28">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA28">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB28">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="AC28">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AD28">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE28">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF28">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AG28">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK28">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.99</v>
+        <v>3.4</v>
       </c>
       <c r="O29">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P29">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="Q29">
-        <v>2.33</v>
+        <v>3.31</v>
       </c>
       <c r="R29">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="S29">
+        <v>1.29</v>
+      </c>
+      <c r="T29">
+        <v>3.24</v>
+      </c>
+      <c r="U29">
+        <v>2.55</v>
+      </c>
+      <c r="V29">
+        <v>1.53</v>
+      </c>
+      <c r="W29">
+        <v>1.12</v>
+      </c>
+      <c r="X29">
+        <v>1.02</v>
+      </c>
+      <c r="Y29">
+        <v>1.19</v>
+      </c>
+      <c r="Z29">
+        <v>4.25</v>
+      </c>
+      <c r="AA29">
+        <v>1.62</v>
+      </c>
+      <c r="AB29">
+        <v>2.15</v>
+      </c>
+      <c r="AC29">
+        <v>2.6</v>
+      </c>
+      <c r="AD29">
+        <v>1.45</v>
+      </c>
+      <c r="AE29">
+        <v>1.15</v>
+      </c>
+      <c r="AF29">
+        <v>1.54</v>
+      </c>
+      <c r="AG29">
+        <v>2.32</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>1.21</v>
+      </c>
+      <c r="AK29">
         <v>1.25</v>
-      </c>
-      <c r="T29">
-        <v>3.6</v>
-      </c>
-      <c r="U29">
-        <v>2.32</v>
-      </c>
-      <c r="V29">
-        <v>1.6</v>
-      </c>
-      <c r="W29">
-        <v>1.1</v>
-      </c>
-      <c r="X29">
-        <v>1.01</v>
-      </c>
-      <c r="Y29">
-        <v>1.2</v>
-      </c>
-      <c r="Z29">
-        <v>4.5</v>
-      </c>
-      <c r="AA29">
-        <v>1.6</v>
-      </c>
-      <c r="AB29">
-        <v>2.31</v>
-      </c>
-      <c r="AC29">
-        <v>2.33</v>
-      </c>
-      <c r="AD29">
-        <v>1.5</v>
-      </c>
-      <c r="AE29">
-        <v>1.22</v>
-      </c>
-      <c r="AF29">
-        <v>1.5</v>
-      </c>
-      <c r="AG29">
-        <v>2.42</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.2</v>
-      </c>
-      <c r="AK29">
-        <v>1.85</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5404,7 +5404,7 @@
         <v>2.16</v>
       </c>
       <c r="AB31">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC31">
         <v>3.5</v>
@@ -5413,7 +5413,7 @@
         <v>1.29</v>
       </c>
       <c r="AE31">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF31">
         <v>1.91</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O32">
         <v>3.63</v>
@@ -5552,7 +5552,7 @@
         <v>1.44</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
         <v>1</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL33">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="P4">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -976,43 +976,43 @@
         <v>2.15</v>
       </c>
       <c r="S4">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U4">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="V4">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z4">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="AA4">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AB4">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC4">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="AD4">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF4">
         <v>1.7</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK4">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>1.83</v>
       </c>
       <c r="Q6">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="R6">
         <v>2.3</v>
@@ -1305,7 +1305,7 @@
         <v>1.22</v>
       </c>
       <c r="T6">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="U6">
         <v>2.46</v>
@@ -1314,7 +1314,7 @@
         <v>1.51</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X6">
         <v>1.01</v>
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
         <v>2.7</v>
@@ -1631,13 +1631,13 @@
         <v>1.25</v>
       </c>
       <c r="T8">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U8">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V8">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W8">
         <v>1.15</v>
@@ -1652,16 +1652,16 @@
         <v>5</v>
       </c>
       <c r="AA8">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AB8">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC8">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AD8">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AE8">
         <v>1.2</v>
@@ -1670,7 +1670,7 @@
         <v>1.44</v>
       </c>
       <c r="AG8">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>1.57</v>
       </c>
       <c r="AG12">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O16">
         <v>3.4</v>
       </c>
       <c r="P16">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q16">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R16">
         <v>2.15</v>
@@ -2938,13 +2938,13 @@
         <v>2.97</v>
       </c>
       <c r="U16">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="V16">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
         <v>1</v>
@@ -2965,10 +2965,10 @@
         <v>2.82</v>
       </c>
       <c r="AD16">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE16">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF16">
         <v>1.62</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AK16">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3083,7 +3083,7 @@
         <v>4.15</v>
       </c>
       <c r="O17">
-        <v>3.73</v>
+        <v>3.78</v>
       </c>
       <c r="P17">
         <v>1.66</v>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.76</v>
       </c>
       <c r="P18">
         <v>1.98</v>
@@ -3267,10 +3267,10 @@
         <v>2.3</v>
       </c>
       <c r="V18">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W18">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="O19">
-        <v>3.43</v>
+        <v>3.53</v>
       </c>
       <c r="P19">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="Q19">
         <v>2.82</v>
@@ -3421,10 +3421,10 @@
         <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T19">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U19">
         <v>2.62</v>
@@ -3433,7 +3433,7 @@
         <v>1.4</v>
       </c>
       <c r="W19">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
         <v>1.03</v>
@@ -3448,7 +3448,7 @@
         <v>1.89</v>
       </c>
       <c r="AB19">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC19">
         <v>3.3</v>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="O20">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P20">
         <v>1.7</v>
@@ -3581,7 +3581,7 @@
         <v>3.77</v>
       </c>
       <c r="R20">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="S20">
         <v>1.25</v>
@@ -3620,7 +3620,7 @@
         <v>1.61</v>
       </c>
       <c r="AE20">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF20">
         <v>1.5</v>
@@ -3898,7 +3898,7 @@
         <v>2.37</v>
       </c>
       <c r="O22">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P22">
         <v>2.6</v>
@@ -3934,10 +3934,10 @@
         <v>3.8</v>
       </c>
       <c r="AA22">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AB22">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC22">
         <v>2.85</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
         <v>1.5</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O23">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="P23">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="Q23">
         <v>3.21</v>
       </c>
       <c r="R23">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="S23">
         <v>1.33</v>
@@ -4094,7 +4094,7 @@
         <v>1.21</v>
       </c>
       <c r="Z23">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA23">
         <v>1.89</v>
@@ -4109,13 +4109,13 @@
         <v>1.33</v>
       </c>
       <c r="AE23">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG23">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK23">
         <v>1.34</v>
@@ -4221,10 +4221,10 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P24">
         <v>3</v>
@@ -4553,7 +4553,7 @@
         <v>3.48</v>
       </c>
       <c r="P26">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Q26">
         <v>2.58</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,34 +4710,34 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.33</v>
+        <v>3.4</v>
       </c>
       <c r="O27">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="P27">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="Q27">
-        <v>3.05</v>
+        <v>3.31</v>
       </c>
       <c r="R27">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="S27">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T27">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="U27">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V27">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W27">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X27">
         <v>1.02</v>
@@ -4746,28 +4746,28 @@
         <v>1.2</v>
       </c>
       <c r="Z27">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="AA27">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AB27">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC27">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="AD27">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AE27">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF27">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AG27">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AK27">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.99</v>
+        <v>2.32</v>
       </c>
       <c r="O28">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P28">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q28">
-        <v>2.33</v>
+        <v>3.05</v>
       </c>
       <c r="R28">
-        <v>2.51</v>
+        <v>2.31</v>
       </c>
       <c r="S28">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T28">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U28">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V28">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
         <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA28">
+        <v>1.83</v>
+      </c>
+      <c r="AB28">
+        <v>2.04</v>
+      </c>
+      <c r="AC28">
+        <v>3.1</v>
+      </c>
+      <c r="AD28">
+        <v>1.33</v>
+      </c>
+      <c r="AE28">
+        <v>1.08</v>
+      </c>
+      <c r="AF28">
         <v>1.6</v>
       </c>
-      <c r="AB28">
-        <v>2.31</v>
-      </c>
-      <c r="AC28">
-        <v>2.33</v>
-      </c>
-      <c r="AD28">
-        <v>1.5</v>
-      </c>
-      <c r="AE28">
-        <v>1.22</v>
-      </c>
-      <c r="AF28">
-        <v>1.5</v>
-      </c>
       <c r="AG28">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK28">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.4</v>
+        <v>1.99</v>
       </c>
       <c r="O29">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="P29">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="Q29">
-        <v>3.31</v>
+        <v>2.33</v>
       </c>
       <c r="R29">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="S29">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T29">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="U29">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="V29">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W29">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA29">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB29">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="AC29">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AD29">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE29">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF29">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AG29">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK29">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5211,13 +5211,13 @@
         <v>1.57</v>
       </c>
       <c r="R30">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="S30">
         <v>1.18</v>
       </c>
       <c r="T30">
-        <v>4.8</v>
+        <v>3.84</v>
       </c>
       <c r="U30">
         <v>1.85</v>
@@ -5226,7 +5226,7 @@
         <v>1.85</v>
       </c>
       <c r="W30">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="X30">
         <v>1.01</v>
@@ -5235,13 +5235,13 @@
         <v>1.08</v>
       </c>
       <c r="Z30">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="AA30">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AB30">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AC30">
         <v>1.9</v>
@@ -5253,10 +5253,10 @@
         <v>1.36</v>
       </c>
       <c r="AF30">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG30">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="O34">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="Q34">
         <v>3.6</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="O35">
         <v>3.33</v>
@@ -6059,7 +6059,7 @@
         <v>1.75</v>
       </c>
       <c r="AC35">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="AD35">
         <v>1.29</v>
@@ -6087,7 +6087,7 @@
         <v>1.28</v>
       </c>
       <c r="AK35">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.29</v>
+        <v>3</v>
       </c>
       <c r="O36">
-        <v>5.85</v>
+        <v>3.4</v>
       </c>
       <c r="P36">
-        <v>8.5</v>
+        <v>2.26</v>
       </c>
       <c r="Q36">
-        <v>1.67</v>
+        <v>3.6</v>
       </c>
       <c r="R36">
-        <v>2.7</v>
+        <v>2.09</v>
       </c>
       <c r="S36">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="T36">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="U36">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="V36">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="W36">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="Z36">
-        <v>5.67</v>
+        <v>3.42</v>
       </c>
       <c r="AA36">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="AB36">
-        <v>2.6</v>
+        <v>1.94</v>
       </c>
       <c r="AC36">
-        <v>2.18</v>
+        <v>3.09</v>
       </c>
       <c r="AD36">
-        <v>1.69</v>
+        <v>1.35</v>
       </c>
       <c r="AE36">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG36">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>3.24</v>
+        <v>1.36</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.68</v>
+        <v>1.3</v>
       </c>
       <c r="O37">
-        <v>3.43</v>
+        <v>5.75</v>
       </c>
       <c r="P37">
-        <v>2.35</v>
+        <v>8.5</v>
       </c>
       <c r="Q37">
-        <v>3.5</v>
+        <v>1.67</v>
       </c>
       <c r="R37">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="S37">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="T37">
-        <v>2.73</v>
+        <v>3.9</v>
       </c>
       <c r="U37">
-        <v>2.75</v>
+        <v>2.17</v>
       </c>
       <c r="V37">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y37">
+        <v>1.14</v>
+      </c>
+      <c r="Z37">
+        <v>5.75</v>
+      </c>
+      <c r="AA37">
+        <v>1.45</v>
+      </c>
+      <c r="AB37">
+        <v>2.6</v>
+      </c>
+      <c r="AC37">
+        <v>2.18</v>
+      </c>
+      <c r="AD37">
+        <v>1.69</v>
+      </c>
+      <c r="AE37">
         <v>1.27</v>
       </c>
-      <c r="Z37">
-        <v>3.38</v>
-      </c>
-      <c r="AA37">
-        <v>1.9</v>
-      </c>
-      <c r="AB37">
-        <v>1.94</v>
-      </c>
-      <c r="AC37">
-        <v>3.2</v>
-      </c>
-      <c r="AD37">
-        <v>1.33</v>
-      </c>
-      <c r="AE37">
-        <v>1.13</v>
-      </c>
       <c r="AF37">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AK37">
-        <v>1.4</v>
+        <v>3.24</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>3.8</v>
       </c>
       <c r="P38">
-        <v>4.6</v>
+        <v>5.25</v>
       </c>
       <c r="Q38">
         <v>2.01</v>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O39">
         <v>3.98</v>
       </c>
       <c r="P39">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="Q39">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="R39">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="S39">
         <v>1.25</v>
@@ -6711,13 +6711,13 @@
         <v>2.55</v>
       </c>
       <c r="AC39">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AD39">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE39">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF39">
         <v>1.44</v>
@@ -6832,10 +6832,10 @@
         <v>1.49</v>
       </c>
       <c r="O40">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="P40">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q40">
         <v>1.89</v>
@@ -6995,10 +6995,10 @@
         <v>1.7</v>
       </c>
       <c r="O41">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="P41">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q41">
         <v>2.23</v>
@@ -7007,7 +7007,7 @@
         <v>2.38</v>
       </c>
       <c r="S41">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T41">
         <v>3.5</v>
@@ -7049,7 +7049,7 @@
         <v>1.55</v>
       </c>
       <c r="AG41">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="O42">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="P42">
-        <v>4.85</v>
+        <v>5.5</v>
       </c>
       <c r="Q42">
         <v>1.8</v>
@@ -7182,7 +7182,7 @@
         <v>2.1</v>
       </c>
       <c r="W42">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X42">
         <v>0</v>
@@ -7194,7 +7194,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AA42">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AB42">
         <v>4.21</v>
@@ -7372,7 +7372,7 @@
         <v>1.29</v>
       </c>
       <c r="AF43">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG43">
         <v>2.72</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G44">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G45">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N45">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N46">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N48">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G51">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N51">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="O53">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="P53">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="Q53">
         <v>2.99</v>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
         <v>1.4</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="O54">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P54">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="Q54">
         <v>3.13</v>
@@ -9150,7 +9150,7 @@
         <v>5</v>
       </c>
       <c r="AA54">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AB54">
         <v>2.37</v>
@@ -9280,7 +9280,7 @@
         <v>3.98</v>
       </c>
       <c r="P55">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Q55">
         <v>2.4</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="O56">
-        <v>5</v>
+        <v>5.42</v>
       </c>
       <c r="P56">
-        <v>5.7</v>
+        <v>6.35</v>
       </c>
       <c r="Q56">
         <v>1.75</v>
@@ -9600,19 +9600,19 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O57">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P57">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q57">
         <v>2.25</v>
       </c>
       <c r="R57">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S57">
         <v>1.25</v>
@@ -9639,10 +9639,10 @@
         <v>5.5</v>
       </c>
       <c r="AA57">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB57">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="AC57">
         <v>2.3</v>
@@ -9654,7 +9654,7 @@
         <v>1.22</v>
       </c>
       <c r="AF57">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AG57">
         <v>2.46</v>
@@ -9763,10 +9763,10 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="O58">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="P58">
         <v>3.85</v>
@@ -9929,10 +9929,10 @@
         <v>1.61</v>
       </c>
       <c r="O59">
-        <v>4.2</v>
+        <v>4.79</v>
       </c>
       <c r="P59">
-        <v>4.45</v>
+        <v>4.64</v>
       </c>
       <c r="Q59">
         <v>1.99</v>
@@ -9965,7 +9965,7 @@
         <v>8.5</v>
       </c>
       <c r="AA59">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AB59">
         <v>3.34</v>
@@ -10092,13 +10092,13 @@
         <v>2.05</v>
       </c>
       <c r="O60">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="P60">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="Q60">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="R60">
         <v>2.48</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="O61">
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="P61">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="Q61">
         <v>1.73</v>
@@ -10294,7 +10294,7 @@
         <v>1.26</v>
       </c>
       <c r="AB61">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AC61">
         <v>1.8</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="O4">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="P4">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -1000,7 +1000,7 @@
         <v>3.5</v>
       </c>
       <c r="AA4">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB4">
         <v>2</v>
@@ -1127,61 +1127,61 @@
         <v>1.55</v>
       </c>
       <c r="O5">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q5">
         <v>2.05</v>
       </c>
       <c r="R5">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T5">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="U5">
-        <v>2.68</v>
+        <v>2.47</v>
       </c>
       <c r="V5">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W5">
         <v>1.07</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
         <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AA5">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB5">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AC5">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD5">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE5">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK5">
         <v>2.3</v>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="N6">
-        <v>4.03</v>
+        <v>3.35</v>
       </c>
       <c r="O6">
-        <v>3.84</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
         <v>1.83</v>
@@ -1344,7 +1344,7 @@
         <v>1.62</v>
       </c>
       <c r="AG6">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         <v>2.25</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P7">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q7">
         <v>2.88</v>
@@ -1474,7 +1474,7 @@
         <v>2.45</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W7">
         <v>1.11</v>
@@ -1830,7 +1830,7 @@
         <v>1.05</v>
       </c>
       <c r="AF9">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
         <v>1.8</v>
@@ -1948,55 +1948,55 @@
         <v>4.33</v>
       </c>
       <c r="Q10">
+        <v>2</v>
+      </c>
+      <c r="R10">
         <v>2.38</v>
       </c>
-      <c r="R10">
-        <v>2.25</v>
-      </c>
       <c r="S10">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U10">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="V10">
+        <v>1.59</v>
+      </c>
+      <c r="W10">
+        <v>1.14</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>1.11</v>
+      </c>
+      <c r="Z10">
+        <v>4.8</v>
+      </c>
+      <c r="AA10">
         <v>1.47</v>
       </c>
-      <c r="W10">
-        <v>1.07</v>
-      </c>
-      <c r="X10">
-        <v>1.02</v>
-      </c>
-      <c r="Y10">
-        <v>1.22</v>
-      </c>
-      <c r="Z10">
-        <v>4</v>
-      </c>
-      <c r="AA10">
-        <v>1.7</v>
-      </c>
       <c r="AB10">
-        <v>1.99</v>
+        <v>2.35</v>
       </c>
       <c r="AC10">
-        <v>2.88</v>
+        <v>2.24</v>
       </c>
       <c r="AD10">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AE10">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AF10">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG10">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK10">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>5.75</v>
+        <v>5.85</v>
       </c>
       <c r="P13">
         <v>1.35</v>
@@ -2482,7 +2482,7 @@
         <v>1.41</v>
       </c>
       <c r="AF13">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AG13">
         <v>2.3</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK13">
         <v>1.08</v>
@@ -2591,22 +2591,22 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="O14">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="Q14">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R14">
         <v>2</v>
       </c>
       <c r="S14">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="T14">
         <v>2.73</v>
@@ -2615,19 +2615,19 @@
         <v>2.9</v>
       </c>
       <c r="V14">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W14">
         <v>1.03</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y14">
         <v>1.39</v>
       </c>
       <c r="Z14">
-        <v>3.02</v>
+        <v>2.89</v>
       </c>
       <c r="AA14">
         <v>2.28</v>
@@ -2639,16 +2639,16 @@
         <v>4.33</v>
       </c>
       <c r="AD14">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE14">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF14">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="AK14">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="O15">
         <v>4</v>
       </c>
       <c r="P15">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="Q15">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S15">
         <v>1.3</v>
       </c>
       <c r="T15">
-        <v>3.19</v>
+        <v>3.27</v>
       </c>
       <c r="U15">
-        <v>2.77</v>
+        <v>2.47</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W15">
         <v>1.07</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z15">
-        <v>3.66</v>
+        <v>4.1</v>
       </c>
       <c r="AA15">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AB15">
         <v>1.9</v>
       </c>
       <c r="AC15">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD15">
         <v>1.36</v>
       </c>
       <c r="AE15">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF15">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG15">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK15">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2920,10 +2920,10 @@
         <v>2.3</v>
       </c>
       <c r="O16">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P16">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
         <v>2.8</v>
@@ -2944,7 +2944,7 @@
         <v>1.44</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
         <v>1</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
         <v>1.57</v>
@@ -3083,7 +3083,7 @@
         <v>4.15</v>
       </c>
       <c r="O17">
-        <v>3.78</v>
+        <v>3.85</v>
       </c>
       <c r="P17">
         <v>1.66</v>
@@ -3131,13 +3131,13 @@
         <v>1.49</v>
       </c>
       <c r="AE17">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF17">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG17">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O18">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q18">
         <v>3.26</v>
@@ -3285,7 +3285,7 @@
         <v>1.6</v>
       </c>
       <c r="AB18">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AC18">
         <v>2.38</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.23</v>
+        <v>2.42</v>
       </c>
       <c r="O19">
-        <v>3.53</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>2.53</v>
+        <v>2.79</v>
       </c>
       <c r="Q19">
         <v>2.82</v>
@@ -3421,10 +3421,10 @@
         <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T19">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U19">
         <v>2.62</v>
@@ -3448,7 +3448,7 @@
         <v>1.89</v>
       </c>
       <c r="AB19">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC19">
         <v>3.3</v>
@@ -3572,7 +3572,7 @@
         <v>4.1</v>
       </c>
       <c r="O20">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="P20">
         <v>1.7</v>
@@ -3581,7 +3581,7 @@
         <v>3.77</v>
       </c>
       <c r="R20">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="S20">
         <v>1.25</v>
@@ -3741,40 +3741,40 @@
         <v>5.25</v>
       </c>
       <c r="Q21">
+        <v>2</v>
+      </c>
+      <c r="R21">
         <v>2.15</v>
       </c>
-      <c r="R21">
-        <v>2.02</v>
-      </c>
       <c r="S21">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T21">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="U21">
-        <v>2.86</v>
+        <v>3.07</v>
       </c>
       <c r="V21">
         <v>1.33</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
         <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z21">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AA21">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AB21">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC21">
         <v>3.58</v>
@@ -3786,10 +3786,10 @@
         <v>1.04</v>
       </c>
       <c r="AF21">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AG21">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
+        <v>2.31</v>
+      </c>
+      <c r="O23">
+        <v>3.32</v>
+      </c>
+      <c r="P23">
+        <v>3</v>
+      </c>
+      <c r="Q23">
         <v>2.7</v>
       </c>
-      <c r="O23">
-        <v>3.34</v>
-      </c>
-      <c r="P23">
-        <v>2.37</v>
-      </c>
-      <c r="Q23">
-        <v>3.21</v>
-      </c>
       <c r="R23">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="S23">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T23">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U23">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="V23">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="Z23">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="AA23">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AB23">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AC23">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AD23">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE23">
         <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG23">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK23">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="O24">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P24">
+        <v>2.37</v>
+      </c>
+      <c r="Q24">
+        <v>3.21</v>
+      </c>
+      <c r="R24">
+        <v>2.08</v>
+      </c>
+      <c r="S24">
+        <v>1.33</v>
+      </c>
+      <c r="T24">
         <v>3</v>
       </c>
-      <c r="Q24">
-        <v>2.7</v>
-      </c>
-      <c r="R24">
-        <v>2.07</v>
-      </c>
-      <c r="S24">
-        <v>1.4</v>
-      </c>
-      <c r="T24">
-        <v>2.88</v>
-      </c>
       <c r="U24">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="V24">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
+        <v>1.22</v>
+      </c>
+      <c r="Z24">
+        <v>3.8</v>
+      </c>
+      <c r="AA24">
+        <v>1.89</v>
+      </c>
+      <c r="AB24">
+        <v>1.93</v>
+      </c>
+      <c r="AC24">
+        <v>3.1</v>
+      </c>
+      <c r="AD24">
         <v>1.32</v>
-      </c>
-      <c r="Z24">
-        <v>3.25</v>
-      </c>
-      <c r="AA24">
-        <v>1.91</v>
-      </c>
-      <c r="AB24">
-        <v>1.83</v>
-      </c>
-      <c r="AC24">
-        <v>3.14</v>
-      </c>
-      <c r="AD24">
-        <v>1.27</v>
       </c>
       <c r="AE24">
         <v>1.1</v>
       </c>
       <c r="AF24">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4550,7 +4550,7 @@
         <v>2.05</v>
       </c>
       <c r="O26">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="P26">
         <v>3.4</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="O27">
-        <v>3.65</v>
+        <v>3.57</v>
       </c>
       <c r="P27">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q27">
         <v>3.31</v>
@@ -4752,7 +4752,7 @@
         <v>1.62</v>
       </c>
       <c r="AB27">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC27">
         <v>2.62</v>
@@ -4879,7 +4879,7 @@
         <v>3.45</v>
       </c>
       <c r="P28">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q28">
         <v>3.05</v>
@@ -4915,7 +4915,7 @@
         <v>1.83</v>
       </c>
       <c r="AB28">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC28">
         <v>3.1</v>
@@ -5039,10 +5039,10 @@
         <v>1.99</v>
       </c>
       <c r="O29">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P29">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q29">
         <v>2.33</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="O30">
         <v>5.7</v>
       </c>
       <c r="P30">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q30">
         <v>1.57</v>
@@ -5220,10 +5220,10 @@
         <v>3.84</v>
       </c>
       <c r="U30">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V30">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="W30">
         <v>1.19</v>
@@ -5232,7 +5232,7 @@
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z30">
         <v>7.5</v>
@@ -5247,7 +5247,7 @@
         <v>1.9</v>
       </c>
       <c r="AD30">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AE30">
         <v>1.36</v>
@@ -5377,7 +5377,7 @@
         <v>2.13</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T31">
         <v>2.56</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="O32">
         <v>3.63</v>
       </c>
       <c r="P32">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="Q32">
         <v>3.81</v>
@@ -5546,43 +5546,43 @@
         <v>3.25</v>
       </c>
       <c r="U32">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W32">
         <v>1.11</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
         <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA32">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB32">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC32">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD32">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE32">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF32">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AG32">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>2</v>
       </c>
       <c r="AK32">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5691,46 +5691,46 @@
         <v>1.5</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P33">
         <v>5.75</v>
       </c>
       <c r="Q33">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="R33">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="S33">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="T33">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="U33">
-        <v>2.81</v>
+        <v>2.93</v>
       </c>
       <c r="V33">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W33">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z33">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AA33">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AB33">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC33">
         <v>3.5</v>
@@ -5742,7 +5742,7 @@
         <v>1.04</v>
       </c>
       <c r="AF33">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG33">
         <v>1.67</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O36">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="P36">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q36">
         <v>3.6</v>
@@ -6192,10 +6192,10 @@
         <v>2.09</v>
       </c>
       <c r="S36">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T36">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="U36">
         <v>2.75</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="O37">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="P37">
-        <v>8.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q37">
         <v>1.67</v>
@@ -6672,7 +6672,7 @@
         <v>3.98</v>
       </c>
       <c r="P39">
-        <v>3.03</v>
+        <v>3.48</v>
       </c>
       <c r="Q39">
         <v>2.45</v>
@@ -6711,13 +6711,13 @@
         <v>2.55</v>
       </c>
       <c r="AC39">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AD39">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE39">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF39">
         <v>1.44</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,34 +6829,34 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.49</v>
+        <v>1.92</v>
       </c>
       <c r="O40">
-        <v>4.33</v>
+        <v>4.21</v>
       </c>
       <c r="P40">
-        <v>5</v>
+        <v>3.53</v>
       </c>
       <c r="Q40">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="R40">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="S40">
         <v>1.2</v>
       </c>
       <c r="T40">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="U40">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="V40">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="W40">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X40">
         <v>0</v>
@@ -6868,25 +6868,25 @@
         <v>6.5</v>
       </c>
       <c r="AA40">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB40">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AC40">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AD40">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AE40">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AF40">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AG40">
-        <v>2.45</v>
+        <v>2.72</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK40">
-        <v>2.54</v>
+        <v>1.78</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,65 +6992,65 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="O41">
-        <v>3.77</v>
+        <v>5</v>
       </c>
       <c r="P41">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="Q41">
-        <v>2.23</v>
+        <v>1.89</v>
       </c>
       <c r="R41">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="S41">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T41">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="U41">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="V41">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="W41">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y41">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z41">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA41">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AB41">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="AC41">
+        <v>2.1</v>
+      </c>
+      <c r="AD41">
+        <v>1.71</v>
+      </c>
+      <c r="AE41">
+        <v>1.31</v>
+      </c>
+      <c r="AF41">
+        <v>1.53</v>
+      </c>
+      <c r="AG41">
         <v>2.45</v>
       </c>
-      <c r="AD41">
-        <v>1.53</v>
-      </c>
-      <c r="AE41">
-        <v>1.16</v>
-      </c>
-      <c r="AF41">
-        <v>1.55</v>
-      </c>
-      <c r="AG41">
-        <v>2.26</v>
-      </c>
       <c r="AH41" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK41">
-        <v>1.95</v>
+        <v>2.54</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="O42">
-        <v>5.1</v>
+        <v>3.77</v>
       </c>
       <c r="P42">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q42">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="R42">
-        <v>3.16</v>
+        <v>2.38</v>
       </c>
       <c r="S42">
+        <v>1.25</v>
+      </c>
+      <c r="T42">
+        <v>3.5</v>
+      </c>
+      <c r="U42">
+        <v>2.25</v>
+      </c>
+      <c r="V42">
+        <v>1.56</v>
+      </c>
+      <c r="W42">
         <v>1.11</v>
       </c>
-      <c r="T42">
-        <v>5.5</v>
-      </c>
-      <c r="U42">
-        <v>1.65</v>
-      </c>
-      <c r="V42">
-        <v>2.1</v>
-      </c>
-      <c r="W42">
-        <v>1.33</v>
-      </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="Z42">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="AA42">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AB42">
-        <v>4.21</v>
+        <v>2.31</v>
       </c>
       <c r="AC42">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="AD42">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="AE42">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AF42">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AG42">
-        <v>3.2</v>
+        <v>2.26</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,80 +7318,80 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.95</v>
+        <v>1.38</v>
       </c>
       <c r="O43">
-        <v>4.21</v>
+        <v>5.2</v>
       </c>
       <c r="P43">
-        <v>2.93</v>
+        <v>4.85</v>
       </c>
       <c r="Q43">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="R43">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="S43">
+        <v>1.11</v>
+      </c>
+      <c r="T43">
+        <v>5.5</v>
+      </c>
+      <c r="U43">
+        <v>1.65</v>
+      </c>
+      <c r="V43">
+        <v>2.12</v>
+      </c>
+      <c r="W43">
+        <v>1.33</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>1</v>
+      </c>
+      <c r="Z43">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AA43">
+        <v>1.22</v>
+      </c>
+      <c r="AB43">
+        <v>4.33</v>
+      </c>
+      <c r="AC43">
+        <v>1.58</v>
+      </c>
+      <c r="AD43">
+        <v>2.45</v>
+      </c>
+      <c r="AE43">
+        <v>1.57</v>
+      </c>
+      <c r="AF43">
+        <v>1.3</v>
+      </c>
+      <c r="AG43">
+        <v>3.2</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
         <v>1.18</v>
       </c>
-      <c r="T43">
-        <v>4.33</v>
-      </c>
-      <c r="U43">
-        <v>1.93</v>
-      </c>
-      <c r="V43">
-        <v>1.75</v>
-      </c>
-      <c r="W43">
-        <v>1.22</v>
-      </c>
-      <c r="X43">
-        <v>0</v>
-      </c>
-      <c r="Y43">
-        <v>1.12</v>
-      </c>
-      <c r="Z43">
-        <v>6.5</v>
-      </c>
-      <c r="AA43">
-        <v>1.42</v>
-      </c>
-      <c r="AB43">
-        <v>2.8</v>
-      </c>
-      <c r="AC43">
-        <v>2.01</v>
-      </c>
-      <c r="AD43">
-        <v>1.75</v>
-      </c>
-      <c r="AE43">
-        <v>1.29</v>
-      </c>
-      <c r="AF43">
-        <v>1.36</v>
-      </c>
-      <c r="AG43">
-        <v>2.72</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>1.2</v>
-      </c>
       <c r="AK43">
-        <v>1.78</v>
+        <v>2.6</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8806,7 +8806,7 @@
         <v>3.2</v>
       </c>
       <c r="U52">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="V52">
         <v>1.45</v>
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="O53">
-        <v>3.53</v>
+        <v>3.6</v>
       </c>
       <c r="P53">
         <v>2.39</v>
@@ -8960,10 +8960,10 @@
         <v>2.99</v>
       </c>
       <c r="R53">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S53">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T53">
         <v>3.25</v>
@@ -8972,7 +8972,7 @@
         <v>2.38</v>
       </c>
       <c r="V53">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W53">
         <v>1.08</v>
@@ -8984,28 +8984,28 @@
         <v>1.2</v>
       </c>
       <c r="Z53">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA53">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB53">
         <v>2.14</v>
       </c>
       <c r="AC53">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD53">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE53">
         <v>1.17</v>
       </c>
       <c r="AF53">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG53">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK53">
         <v>1.4</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="O54">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P54">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="Q54">
         <v>3.13</v>
@@ -9150,10 +9150,10 @@
         <v>5</v>
       </c>
       <c r="AA54">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB54">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AC54">
         <v>2.45</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="O55">
         <v>3.98</v>
       </c>
       <c r="P55">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="Q55">
         <v>2.4</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="O56">
-        <v>5.42</v>
+        <v>5</v>
       </c>
       <c r="P56">
-        <v>6.35</v>
+        <v>5.7</v>
       </c>
       <c r="Q56">
         <v>1.75</v>
@@ -9639,10 +9639,10 @@
         <v>5.5</v>
       </c>
       <c r="AA57">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AB57">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AC57">
         <v>2.3</v>
@@ -9673,7 +9673,7 @@
         <v>1.19</v>
       </c>
       <c r="AK57">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,19 +9763,19 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="O58">
-        <v>4.22</v>
+        <v>3.98</v>
       </c>
       <c r="P58">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="Q58">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="R58">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="S58">
         <v>1.2</v>
@@ -9805,16 +9805,16 @@
         <v>1.36</v>
       </c>
       <c r="AB58">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="AC58">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AD58">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AE58">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AF58">
         <v>1.4</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="O59">
-        <v>4.79</v>
+        <v>4.75</v>
       </c>
       <c r="P59">
-        <v>4.64</v>
+        <v>4.2</v>
       </c>
       <c r="Q59">
         <v>1.99</v>
@@ -10092,16 +10092,16 @@
         <v>2.05</v>
       </c>
       <c r="O60">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="P60">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q60">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="R60">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="S60">
         <v>1.25</v>
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="O61">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="P61">
         <v>6</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="O62">
         <v>3.8</v>
@@ -10427,7 +10427,7 @@
         <v>2.25</v>
       </c>
       <c r="R62">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S62">
         <v>1.25</v>
@@ -10488,7 +10488,7 @@
         <v>1.19</v>
       </c>
       <c r="AK62">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL62">
         <v>0</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O4">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="P4">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -1012,7 +1012,7 @@
         <v>1.25</v>
       </c>
       <c r="AE4">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
         <v>1.7</v>
@@ -1127,10 +1127,10 @@
         <v>1.55</v>
       </c>
       <c r="O5">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P5">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="Q5">
         <v>2.05</v>
@@ -1142,7 +1142,7 @@
         <v>1.35</v>
       </c>
       <c r="T5">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="U5">
         <v>2.47</v>
@@ -1163,10 +1163,10 @@
         <v>3.7</v>
       </c>
       <c r="AA5">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB5">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC5">
         <v>2.9</v>
@@ -1290,10 +1290,10 @@
         <v>3.35</v>
       </c>
       <c r="O6">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="P6">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -1329,7 +1329,7 @@
         <v>1.65</v>
       </c>
       <c r="AB6">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC6">
         <v>2.58</v>
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="O7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
         <v>2.62</v>
@@ -1489,10 +1489,10 @@
         <v>4.5</v>
       </c>
       <c r="AA7">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB7">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC7">
         <v>2.66</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="O8">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>2.49</v>
+        <v>2.67</v>
       </c>
       <c r="Q8">
         <v>2.6</v>
@@ -1655,7 +1655,7 @@
         <v>1.54</v>
       </c>
       <c r="AB8">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AC8">
         <v>2.45</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="O9">
         <v>3.1</v>
       </c>
       <c r="P9">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="Q9">
         <v>2.56</v>
@@ -1791,7 +1791,7 @@
         <v>1.96</v>
       </c>
       <c r="S9">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T9">
         <v>2.58</v>
@@ -1800,10 +1800,10 @@
         <v>2.81</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
         <v>1.02</v>
@@ -1830,10 +1830,10 @@
         <v>1.05</v>
       </c>
       <c r="AF9">
+        <v>1.83</v>
+      </c>
+      <c r="AG9">
         <v>1.85</v>
-      </c>
-      <c r="AG9">
-        <v>1.8</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>4.33</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R10">
         <v>2.38</v>
@@ -1960,10 +1960,10 @@
         <v>3.6</v>
       </c>
       <c r="U10">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="V10">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W10">
         <v>1.14</v>
@@ -1981,7 +1981,7 @@
         <v>1.47</v>
       </c>
       <c r="AB10">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AC10">
         <v>2.24</v>
@@ -1996,7 +1996,7 @@
         <v>1.53</v>
       </c>
       <c r="AG10">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="O12">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="P12">
-        <v>2.61</v>
+        <v>2.95</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -2322,7 +2322,7 @@
         <v>1.57</v>
       </c>
       <c r="AG12">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>5.85</v>
       </c>
       <c r="P13">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Q13">
         <v>5.32</v>
@@ -2482,7 +2482,7 @@
         <v>1.41</v>
       </c>
       <c r="AF13">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AG13">
         <v>2.3</v>
@@ -2591,25 +2591,25 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="O14">
         <v>3.2</v>
       </c>
       <c r="P14">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="Q14">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R14">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S14">
         <v>1.49</v>
       </c>
       <c r="T14">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="U14">
         <v>2.9</v>
@@ -2624,7 +2624,7 @@
         <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z14">
         <v>2.89</v>
@@ -2636,7 +2636,7 @@
         <v>1.64</v>
       </c>
       <c r="AC14">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AD14">
         <v>1.22</v>
@@ -2664,7 +2664,7 @@
         <v>1.33</v>
       </c>
       <c r="AK14">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="O15">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P15">
-        <v>4.95</v>
+        <v>5.3</v>
       </c>
       <c r="Q15">
         <v>2.18</v>
@@ -2775,7 +2775,7 @@
         <v>3.27</v>
       </c>
       <c r="U15">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V15">
         <v>1.46</v>
@@ -2799,7 +2799,7 @@
         <v>1.9</v>
       </c>
       <c r="AC15">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="AD15">
         <v>1.36</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK15">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O16">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="Q16">
         <v>2.8</v>
@@ -2935,13 +2935,13 @@
         <v>1.3</v>
       </c>
       <c r="T16">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="U16">
         <v>2.3</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W16">
         <v>1.08</v>
@@ -2953,16 +2953,16 @@
         <v>1.2</v>
       </c>
       <c r="Z16">
-        <v>4.35</v>
+        <v>4.41</v>
       </c>
       <c r="AA16">
         <v>1.67</v>
       </c>
       <c r="AB16">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AC16">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AD16">
         <v>1.44</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="O17">
         <v>3.85</v>
       </c>
       <c r="P17">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q17">
         <v>4.16</v>
@@ -3113,10 +3113,10 @@
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>4.6</v>
+        <v>4.63</v>
       </c>
       <c r="AA17">
         <v>1.57</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P18">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q18">
         <v>3.26</v>
@@ -3270,7 +3270,7 @@
         <v>1.53</v>
       </c>
       <c r="W18">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3282,7 +3282,7 @@
         <v>4.45</v>
       </c>
       <c r="AA18">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB18">
         <v>2.3</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="O19">
         <v>3.2</v>
       </c>
       <c r="P19">
-        <v>2.79</v>
+        <v>2.53</v>
       </c>
       <c r="Q19">
         <v>2.82</v>
@@ -3445,10 +3445,10 @@
         <v>3.34</v>
       </c>
       <c r="AA19">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB19">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC19">
         <v>3.3</v>
@@ -3572,7 +3572,7 @@
         <v>4.1</v>
       </c>
       <c r="O20">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P20">
         <v>1.7</v>
@@ -3581,7 +3581,7 @@
         <v>3.77</v>
       </c>
       <c r="R20">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="S20">
         <v>1.25</v>
@@ -3605,16 +3605,16 @@
         <v>1.13</v>
       </c>
       <c r="Z20">
-        <v>5.14</v>
+        <v>5.27</v>
       </c>
       <c r="AA20">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AB20">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="AC20">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AD20">
         <v>1.61</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P21">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q21">
         <v>2</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="O22">
         <v>3.3</v>
@@ -3943,7 +3943,7 @@
         <v>2.85</v>
       </c>
       <c r="AD22">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE22">
         <v>1.1</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="O23">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="P23">
+        <v>2.38</v>
+      </c>
+      <c r="Q23">
+        <v>3.21</v>
+      </c>
+      <c r="R23">
+        <v>2.08</v>
+      </c>
+      <c r="S23">
+        <v>1.33</v>
+      </c>
+      <c r="T23">
         <v>3</v>
       </c>
-      <c r="Q23">
-        <v>2.7</v>
-      </c>
-      <c r="R23">
-        <v>2.07</v>
-      </c>
-      <c r="S23">
-        <v>1.4</v>
-      </c>
-      <c r="T23">
-        <v>2.88</v>
-      </c>
       <c r="U23">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="V23">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W23">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
+        <v>1.22</v>
+      </c>
+      <c r="Z23">
+        <v>3.8</v>
+      </c>
+      <c r="AA23">
+        <v>1.89</v>
+      </c>
+      <c r="AB23">
+        <v>1.9</v>
+      </c>
+      <c r="AC23">
+        <v>3.1</v>
+      </c>
+      <c r="AD23">
         <v>1.32</v>
-      </c>
-      <c r="Z23">
-        <v>3.25</v>
-      </c>
-      <c r="AA23">
-        <v>1.91</v>
-      </c>
-      <c r="AB23">
-        <v>1.83</v>
-      </c>
-      <c r="AC23">
-        <v>3.14</v>
-      </c>
-      <c r="AD23">
-        <v>1.27</v>
       </c>
       <c r="AE23">
         <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="O24">
         <v>3.2</v>
       </c>
       <c r="P24">
-        <v>2.37</v>
+        <v>2.9</v>
       </c>
       <c r="Q24">
-        <v>3.21</v>
+        <v>2.7</v>
       </c>
       <c r="R24">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="S24">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T24">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U24">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="V24">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="Z24">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="AA24">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AB24">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AC24">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AD24">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE24">
         <v>1.1</v>
       </c>
       <c r="AF24">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG24">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK24">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>2.05</v>
       </c>
       <c r="O26">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="P26">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="Q26">
         <v>2.58</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.83</v>
+        <v>1.98</v>
       </c>
       <c r="O27">
-        <v>3.57</v>
+        <v>3.8</v>
       </c>
       <c r="P27">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q27">
-        <v>3.31</v>
+        <v>2.33</v>
       </c>
       <c r="R27">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="S27">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T27">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="U27">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="V27">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W27">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
         <v>1.2</v>
       </c>
       <c r="Z27">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA27">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB27">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AC27">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="AD27">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE27">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF27">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AG27">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK27">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
+        <v>2.83</v>
+      </c>
+      <c r="O29">
+        <v>3.57</v>
+      </c>
+      <c r="P29">
         <v>1.99</v>
       </c>
-      <c r="O29">
-        <v>3.75</v>
-      </c>
-      <c r="P29">
-        <v>3.3</v>
-      </c>
       <c r="Q29">
-        <v>2.33</v>
+        <v>3.31</v>
       </c>
       <c r="R29">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="S29">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T29">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="U29">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="V29">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W29">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
         <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA29">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB29">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AC29">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="AD29">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AE29">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AF29">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AG29">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK29">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5202,10 +5202,10 @@
         <v>1.16</v>
       </c>
       <c r="O30">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="P30">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q30">
         <v>1.57</v>
@@ -5220,10 +5220,10 @@
         <v>3.84</v>
       </c>
       <c r="U30">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="V30">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="W30">
         <v>1.19</v>
@@ -5232,25 +5232,25 @@
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z30">
-        <v>7.5</v>
+        <v>6.77</v>
       </c>
       <c r="AA30">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AB30">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AC30">
+        <v>1.87</v>
+      </c>
+      <c r="AD30">
         <v>1.9</v>
       </c>
-      <c r="AD30">
-        <v>1.87</v>
-      </c>
       <c r="AE30">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF30">
         <v>1.67</v>
@@ -5416,10 +5416,10 @@
         <v>1.08</v>
       </c>
       <c r="AF31">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG31">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="O32">
-        <v>3.63</v>
+        <v>4.1</v>
       </c>
       <c r="P32">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Q32">
         <v>3.81</v>
@@ -5555,13 +5555,13 @@
         <v>1.11</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
         <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA32">
         <v>1.65</v>
@@ -5598,7 +5598,7 @@
         <v>2</v>
       </c>
       <c r="AK32">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5691,10 +5691,10 @@
         <v>1.5</v>
       </c>
       <c r="O33">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P33">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Q33">
         <v>2</v>
@@ -5727,10 +5727,10 @@
         <v>3.04</v>
       </c>
       <c r="AA33">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AB33">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC33">
         <v>3.5</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P34">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="Q34">
         <v>3.6</v>
@@ -5905,7 +5905,7 @@
         <v>1.17</v>
       </c>
       <c r="AF34">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AG34">
         <v>2.39</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="O35">
-        <v>3.33</v>
+        <v>3.45</v>
       </c>
       <c r="P35">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="Q35">
         <v>2.45</v>
@@ -6087,7 +6087,7 @@
         <v>1.28</v>
       </c>
       <c r="AK35">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6180,10 +6180,10 @@
         <v>3.1</v>
       </c>
       <c r="O36">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="P36">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q36">
         <v>3.6</v>
@@ -6506,7 +6506,7 @@
         <v>1.6</v>
       </c>
       <c r="O38">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P38">
         <v>5.25</v>
@@ -6542,7 +6542,7 @@
         <v>4.33</v>
       </c>
       <c r="AA38">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB38">
         <v>2.2</v>
@@ -6672,7 +6672,7 @@
         <v>3.98</v>
       </c>
       <c r="P39">
-        <v>3.48</v>
+        <v>3.03</v>
       </c>
       <c r="Q39">
         <v>2.45</v>
@@ -6708,7 +6708,7 @@
         <v>1.51</v>
       </c>
       <c r="AB39">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AC39">
         <v>2.34</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.92</v>
+        <v>1.44</v>
       </c>
       <c r="O40">
-        <v>4.21</v>
+        <v>4.6</v>
       </c>
       <c r="P40">
-        <v>3.53</v>
+        <v>5</v>
       </c>
       <c r="Q40">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="R40">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="S40">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="T40">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="U40">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="V40">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="W40">
+        <v>1.33</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>1</v>
+      </c>
+      <c r="Z40">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AA40">
         <v>1.22</v>
       </c>
-      <c r="X40">
-        <v>0</v>
-      </c>
-      <c r="Y40">
-        <v>1.1</v>
-      </c>
-      <c r="Z40">
-        <v>6.5</v>
-      </c>
-      <c r="AA40">
-        <v>1.4</v>
-      </c>
       <c r="AB40">
-        <v>2.8</v>
+        <v>4.33</v>
       </c>
       <c r="AC40">
-        <v>2.01</v>
+        <v>1.58</v>
       </c>
       <c r="AD40">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AE40">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AF40">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AG40">
-        <v>2.72</v>
+        <v>3.2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK40">
-        <v>1.78</v>
+        <v>2.6</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,34 +6992,34 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="O41">
-        <v>5</v>
+        <v>4.21</v>
       </c>
       <c r="P41">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="Q41">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="R41">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="S41">
         <v>1.2</v>
       </c>
       <c r="T41">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="U41">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="V41">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W41">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X41">
         <v>0</v>
@@ -7031,25 +7031,25 @@
         <v>6.5</v>
       </c>
       <c r="AA41">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB41">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AC41">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AD41">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AE41">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AF41">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AG41">
-        <v>2.45</v>
+        <v>2.72</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK41">
-        <v>2.54</v>
+        <v>1.78</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,65 +7155,65 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="O42">
-        <v>3.77</v>
+        <v>4.33</v>
       </c>
       <c r="P42">
+        <v>5</v>
+      </c>
+      <c r="Q42">
+        <v>1.89</v>
+      </c>
+      <c r="R42">
+        <v>2.8</v>
+      </c>
+      <c r="S42">
+        <v>1.2</v>
+      </c>
+      <c r="T42">
         <v>4.1</v>
       </c>
-      <c r="Q42">
-        <v>2.23</v>
-      </c>
-      <c r="R42">
-        <v>2.38</v>
-      </c>
-      <c r="S42">
-        <v>1.25</v>
-      </c>
-      <c r="T42">
-        <v>3.5</v>
-      </c>
       <c r="U42">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="V42">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="W42">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y42">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z42">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA42">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB42">
-        <v>2.31</v>
+        <v>2.7</v>
       </c>
       <c r="AC42">
+        <v>2.1</v>
+      </c>
+      <c r="AD42">
+        <v>1.71</v>
+      </c>
+      <c r="AE42">
+        <v>1.31</v>
+      </c>
+      <c r="AF42">
+        <v>1.53</v>
+      </c>
+      <c r="AG42">
         <v>2.45</v>
       </c>
-      <c r="AD42">
-        <v>1.53</v>
-      </c>
-      <c r="AE42">
-        <v>1.16</v>
-      </c>
-      <c r="AF42">
-        <v>1.55</v>
-      </c>
-      <c r="AG42">
-        <v>2.26</v>
-      </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK42">
-        <v>1.95</v>
+        <v>2.54</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="O43">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="P43">
-        <v>4.85</v>
+        <v>4.1</v>
       </c>
       <c r="Q43">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="R43">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="S43">
+        <v>1.25</v>
+      </c>
+      <c r="T43">
+        <v>3.5</v>
+      </c>
+      <c r="U43">
+        <v>2.25</v>
+      </c>
+      <c r="V43">
+        <v>1.56</v>
+      </c>
+      <c r="W43">
         <v>1.11</v>
       </c>
-      <c r="T43">
-        <v>5.5</v>
-      </c>
-      <c r="U43">
-        <v>1.65</v>
-      </c>
-      <c r="V43">
-        <v>2.12</v>
-      </c>
-      <c r="W43">
-        <v>1.33</v>
-      </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="Z43">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="AA43">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AB43">
-        <v>4.33</v>
+        <v>2.31</v>
       </c>
       <c r="AC43">
-        <v>1.58</v>
+        <v>2.45</v>
       </c>
       <c r="AD43">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="AE43">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="AF43">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AG43">
-        <v>3.2</v>
+        <v>2.26</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8791,7 +8791,7 @@
         <v>3.6</v>
       </c>
       <c r="P52">
-        <v>3.08</v>
+        <v>3.54</v>
       </c>
       <c r="Q52">
         <v>2.59</v>
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O53">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="P53">
         <v>2.39</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="O54">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="Q54">
         <v>3.13</v>
@@ -9150,7 +9150,7 @@
         <v>5</v>
       </c>
       <c r="AA54">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AB54">
         <v>2.38</v>
@@ -9277,31 +9277,31 @@
         <v>1.99</v>
       </c>
       <c r="O55">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="P55">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="Q55">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R55">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S55">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T55">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="U55">
         <v>2.1</v>
       </c>
       <c r="V55">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W55">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X55">
         <v>1.01</v>
@@ -9313,13 +9313,13 @@
         <v>6</v>
       </c>
       <c r="AA55">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB55">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AC55">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AD55">
         <v>1.61</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,80 +9437,80 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.32</v>
+        <v>1.86</v>
       </c>
       <c r="O56">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="P56">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q56">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="R56">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="S56">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T56">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="U56">
+        <v>2.13</v>
+      </c>
+      <c r="V56">
+        <v>1.61</v>
+      </c>
+      <c r="W56">
+        <v>1.14</v>
+      </c>
+      <c r="X56">
+        <v>1.01</v>
+      </c>
+      <c r="Y56">
+        <v>1.14</v>
+      </c>
+      <c r="Z56">
+        <v>5.5</v>
+      </c>
+      <c r="AA56">
+        <v>1.51</v>
+      </c>
+      <c r="AB56">
+        <v>2.38</v>
+      </c>
+      <c r="AC56">
+        <v>2.3</v>
+      </c>
+      <c r="AD56">
+        <v>1.6</v>
+      </c>
+      <c r="AE56">
+        <v>1.22</v>
+      </c>
+      <c r="AF56">
+        <v>1.47</v>
+      </c>
+      <c r="AG56">
+        <v>2.46</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
+        <v>1.19</v>
+      </c>
+      <c r="AK56">
         <v>1.91</v>
-      </c>
-      <c r="V56">
-        <v>1.85</v>
-      </c>
-      <c r="W56">
-        <v>1.22</v>
-      </c>
-      <c r="X56">
-        <v>0</v>
-      </c>
-      <c r="Y56">
-        <v>1.07</v>
-      </c>
-      <c r="Z56">
-        <v>8</v>
-      </c>
-      <c r="AA56">
-        <v>1.3</v>
-      </c>
-      <c r="AB56">
-        <v>3.05</v>
-      </c>
-      <c r="AC56">
-        <v>1.84</v>
-      </c>
-      <c r="AD56">
-        <v>1.98</v>
-      </c>
-      <c r="AE56">
-        <v>1.4</v>
-      </c>
-      <c r="AF56">
-        <v>1.5</v>
-      </c>
-      <c r="AG56">
-        <v>2.55</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56">
-        <v>1.11</v>
-      </c>
-      <c r="AK56">
-        <v>2.62</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,80 +9600,80 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="O57">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P57">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="Q57">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="R57">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="S57">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T57">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="U57">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="V57">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="W57">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y57">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z57">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA57">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AB57">
-        <v>2.38</v>
+        <v>2.87</v>
       </c>
       <c r="AC57">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="AD57">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AE57">
+        <v>1.3</v>
+      </c>
+      <c r="AF57">
+        <v>1.4</v>
+      </c>
+      <c r="AG57">
+        <v>2.88</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
         <v>1.22</v>
       </c>
-      <c r="AF57">
-        <v>1.47</v>
-      </c>
-      <c r="AG57">
-        <v>2.46</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ57">
-        <v>1.19</v>
-      </c>
       <c r="AK57">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,80 +9763,80 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="O58">
-        <v>3.98</v>
+        <v>4.4</v>
       </c>
       <c r="P58">
-        <v>3.58</v>
+        <v>4.64</v>
       </c>
       <c r="Q58">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="R58">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="S58">
+        <v>1.12</v>
+      </c>
+      <c r="T58">
+        <v>4.75</v>
+      </c>
+      <c r="U58">
+        <v>1.75</v>
+      </c>
+      <c r="V58">
+        <v>1.95</v>
+      </c>
+      <c r="W58">
+        <v>1.29</v>
+      </c>
+      <c r="X58">
+        <v>0</v>
+      </c>
+      <c r="Y58">
+        <v>1.06</v>
+      </c>
+      <c r="Z58">
+        <v>8.5</v>
+      </c>
+      <c r="AA58">
+        <v>1.28</v>
+      </c>
+      <c r="AB58">
+        <v>3.34</v>
+      </c>
+      <c r="AC58">
+        <v>1.67</v>
+      </c>
+      <c r="AD58">
+        <v>2.15</v>
+      </c>
+      <c r="AE58">
+        <v>1.47</v>
+      </c>
+      <c r="AF58">
+        <v>1.33</v>
+      </c>
+      <c r="AG58">
+        <v>2.9</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
         <v>1.2</v>
       </c>
-      <c r="T58">
-        <v>4.2</v>
-      </c>
-      <c r="U58">
-        <v>1.95</v>
-      </c>
-      <c r="V58">
-        <v>1.75</v>
-      </c>
-      <c r="W58">
-        <v>1.2</v>
-      </c>
-      <c r="X58">
-        <v>0</v>
-      </c>
-      <c r="Y58">
-        <v>1.1</v>
-      </c>
-      <c r="Z58">
-        <v>6.5</v>
-      </c>
-      <c r="AA58">
-        <v>1.36</v>
-      </c>
-      <c r="AB58">
-        <v>2.87</v>
-      </c>
-      <c r="AC58">
-        <v>2.04</v>
-      </c>
-      <c r="AD58">
-        <v>1.81</v>
-      </c>
-      <c r="AE58">
-        <v>1.3</v>
-      </c>
-      <c r="AF58">
-        <v>1.4</v>
-      </c>
-      <c r="AG58">
-        <v>2.88</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>1.22</v>
-      </c>
       <c r="AK58">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="O59">
-        <v>4.75</v>
+        <v>5.3</v>
       </c>
       <c r="P59">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="Q59">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="R59">
-        <v>2.8</v>
+        <v>2.61</v>
       </c>
       <c r="S59">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="T59">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="U59">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="V59">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="W59">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="X59">
         <v>0</v>
       </c>
       <c r="Y59">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z59">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA59">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB59">
-        <v>3.34</v>
+        <v>3.05</v>
       </c>
       <c r="AC59">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AD59">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AE59">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AF59">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AG59">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK59">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O60">
         <v>3.75</v>
       </c>
       <c r="P60">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="Q60">
         <v>2.63</v>
@@ -10122,10 +10122,10 @@
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z60">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA60">
         <v>1.49</v>
@@ -10134,13 +10134,13 @@
         <v>2.3</v>
       </c>
       <c r="AC60">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AD60">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE60">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF60">
         <v>1.47</v>
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="O61">
         <v>5.2</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="O62">
         <v>3.8</v>
@@ -10457,7 +10457,7 @@
         <v>1.62</v>
       </c>
       <c r="AB62">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC62">
         <v>2.63</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -798,25 +798,25 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O3">
         <v>3.1</v>
       </c>
       <c r="P3">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
       </c>
       <c r="R3">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="S3">
         <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="U3">
         <v>2.9</v>
@@ -852,7 +852,7 @@
         <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG3">
         <v>1.9</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK3">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -957,14 +957,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N4">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="O4">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="P4">
         <v>2.75</v>
@@ -1003,7 +1003,7 @@
         <v>1.85</v>
       </c>
       <c r="AB4">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC4">
         <v>2.5</v>
@@ -1012,7 +1012,7 @@
         <v>1.25</v>
       </c>
       <c r="AE4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF4">
         <v>1.7</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="O5">
         <v>4</v>
       </c>
       <c r="P5">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q5">
         <v>2.05</v>
@@ -1163,10 +1163,10 @@
         <v>3.7</v>
       </c>
       <c r="AA5">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB5">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AC5">
         <v>2.9</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N6">
@@ -1329,7 +1329,7 @@
         <v>1.65</v>
       </c>
       <c r="AB6">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC6">
         <v>2.58</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="O7">
         <v>3.4</v>
       </c>
       <c r="P7">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="Q7">
         <v>2.88</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="O8">
         <v>3.4</v>
       </c>
       <c r="P8">
-        <v>2.67</v>
+        <v>2.78</v>
       </c>
       <c r="Q8">
         <v>2.6</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1948,7 +1948,7 @@
         <v>4.33</v>
       </c>
       <c r="Q10">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="R10">
         <v>2.38</v>
@@ -1960,10 +1960,10 @@
         <v>3.6</v>
       </c>
       <c r="U10">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="V10">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W10">
         <v>1.14</v>
@@ -1972,25 +1972,25 @@
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z10">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA10">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB10">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AC10">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="AD10">
         <v>1.55</v>
       </c>
       <c r="AE10">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF10">
         <v>1.53</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK10">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2123,7 +2123,7 @@
         <v>2.5</v>
       </c>
       <c r="U11">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="V11">
         <v>1.3</v>
@@ -2141,10 +2141,10 @@
         <v>2.7</v>
       </c>
       <c r="AA11">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AB11">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC11">
         <v>4.5</v>
@@ -2265,16 +2265,16 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="O12">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="Q12">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="R12">
         <v>2.36</v>
@@ -2304,10 +2304,10 @@
         <v>4.5</v>
       </c>
       <c r="AA12">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB12">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AC12">
         <v>2.55</v>
@@ -2319,10 +2319,10 @@
         <v>1.2</v>
       </c>
       <c r="AF12">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG12">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>7</v>
+        <v>8.25</v>
       </c>
       <c r="O13">
-        <v>5.85</v>
+        <v>5.25</v>
       </c>
       <c r="P13">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Q13">
         <v>5.32</v>
@@ -2443,13 +2443,13 @@
         <v>2.88</v>
       </c>
       <c r="S13">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T13">
         <v>4.8</v>
       </c>
       <c r="U13">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="V13">
         <v>1.85</v>
@@ -2473,7 +2473,7 @@
         <v>3.2</v>
       </c>
       <c r="AC13">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AD13">
         <v>1.9</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="O14">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="P14">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -2648,7 +2648,7 @@
         <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.33</v>
       </c>
       <c r="AK14">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="O15">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P15">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="Q15">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R15">
         <v>2.25</v>
@@ -2772,28 +2772,28 @@
         <v>1.3</v>
       </c>
       <c r="T15">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="U15">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="V15">
         <v>1.46</v>
       </c>
       <c r="W15">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z15">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="AA15">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB15">
         <v>1.9</v>
@@ -2808,10 +2808,10 @@
         <v>1.09</v>
       </c>
       <c r="AF15">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK15">
         <v>2.22</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="O16">
         <v>3.4</v>
       </c>
       <c r="P16">
-        <v>3.03</v>
+        <v>2.88</v>
       </c>
       <c r="Q16">
         <v>2.8</v>
@@ -2953,7 +2953,7 @@
         <v>1.2</v>
       </c>
       <c r="Z16">
-        <v>4.41</v>
+        <v>4.4</v>
       </c>
       <c r="AA16">
         <v>1.67</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK16">
         <v>1.57</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O17">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P17">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q17">
         <v>4.16</v>
@@ -3119,16 +3119,16 @@
         <v>4.63</v>
       </c>
       <c r="AA17">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB17">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AC17">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AD17">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AE17">
         <v>1.15</v>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O18">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="P18">
         <v>2.04</v>
@@ -3409,10 +3409,10 @@
         <v>2.37</v>
       </c>
       <c r="O19">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="P19">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="Q19">
         <v>2.82</v>
@@ -3421,10 +3421,10 @@
         <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T19">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U19">
         <v>2.62</v>
@@ -3445,16 +3445,16 @@
         <v>3.34</v>
       </c>
       <c r="AA19">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB19">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC19">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD19">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE19">
         <v>1.07</v>
@@ -3572,22 +3572,22 @@
         <v>4.1</v>
       </c>
       <c r="O20">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P20">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Q20">
         <v>3.77</v>
       </c>
       <c r="R20">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="S20">
         <v>1.25</v>
       </c>
       <c r="T20">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U20">
         <v>2.2</v>
@@ -3608,10 +3608,10 @@
         <v>5.27</v>
       </c>
       <c r="AA20">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AB20">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="AC20">
         <v>2.31</v>
@@ -3623,10 +3623,10 @@
         <v>1.22</v>
       </c>
       <c r="AF20">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG20">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="O21">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>4.6</v>
+        <v>5.25</v>
       </c>
       <c r="Q21">
         <v>2</v>
@@ -3771,7 +3771,7 @@
         <v>2.9</v>
       </c>
       <c r="AA21">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AB21">
         <v>1.66</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O22">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P22">
         <v>2.6</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.9</v>
+        <v>2.33</v>
       </c>
       <c r="O23">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="P23">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="Q23">
-        <v>3.21</v>
+        <v>2.7</v>
       </c>
       <c r="R23">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="S23">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U23">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="V23">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y23">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="Z23">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="AA23">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AB23">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC23">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AD23">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE23">
         <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG23">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK23">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="O24">
         <v>3.2</v>
       </c>
       <c r="P24">
-        <v>2.9</v>
+        <v>2.37</v>
       </c>
       <c r="Q24">
-        <v>2.7</v>
+        <v>3.21</v>
       </c>
       <c r="R24">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="S24">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U24">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="V24">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
+        <v>1.22</v>
+      </c>
+      <c r="Z24">
+        <v>3.8</v>
+      </c>
+      <c r="AA24">
+        <v>1.89</v>
+      </c>
+      <c r="AB24">
+        <v>1.93</v>
+      </c>
+      <c r="AC24">
+        <v>3.1</v>
+      </c>
+      <c r="AD24">
         <v>1.32</v>
-      </c>
-      <c r="Z24">
-        <v>3.25</v>
-      </c>
-      <c r="AA24">
-        <v>2.05</v>
-      </c>
-      <c r="AB24">
-        <v>1.83</v>
-      </c>
-      <c r="AC24">
-        <v>3.14</v>
-      </c>
-      <c r="AD24">
-        <v>1.27</v>
       </c>
       <c r="AE24">
         <v>1.1</v>
       </c>
       <c r="AF24">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>2.05</v>
       </c>
       <c r="O26">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="P26">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="Q26">
         <v>2.58</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.98</v>
+        <v>2.33</v>
       </c>
       <c r="O27">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P27">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q27">
-        <v>2.33</v>
+        <v>3.05</v>
       </c>
       <c r="R27">
-        <v>2.51</v>
+        <v>2.34</v>
       </c>
       <c r="S27">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T27">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U27">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="V27">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W27">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
         <v>1.2</v>
       </c>
       <c r="Z27">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA27">
+        <v>1.83</v>
+      </c>
+      <c r="AB27">
+        <v>2</v>
+      </c>
+      <c r="AC27">
+        <v>3.1</v>
+      </c>
+      <c r="AD27">
+        <v>1.33</v>
+      </c>
+      <c r="AE27">
+        <v>1.08</v>
+      </c>
+      <c r="AF27">
         <v>1.6</v>
       </c>
-      <c r="AB27">
-        <v>2.31</v>
-      </c>
-      <c r="AC27">
-        <v>2.33</v>
-      </c>
-      <c r="AD27">
-        <v>1.5</v>
-      </c>
-      <c r="AE27">
-        <v>1.22</v>
-      </c>
-      <c r="AF27">
-        <v>1.5</v>
-      </c>
       <c r="AG27">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK27">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.32</v>
+        <v>1.27</v>
       </c>
       <c r="O28">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="P28">
+        <v>9</v>
+      </c>
+      <c r="Q28">
+        <v>1.57</v>
+      </c>
+      <c r="R28">
         <v>2.75</v>
       </c>
-      <c r="Q28">
-        <v>3.05</v>
-      </c>
-      <c r="R28">
-        <v>2.31</v>
-      </c>
       <c r="S28">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="T28">
-        <v>3.2</v>
+        <v>3.84</v>
       </c>
       <c r="U28">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="Z28">
-        <v>3.7</v>
+        <v>6.77</v>
       </c>
       <c r="AA28">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AB28">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="AC28">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="AD28">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="AE28">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AF28">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG28">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="AK28">
-        <v>1.44</v>
+        <v>3.41</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="O29">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="Q29">
         <v>3.31</v>
@@ -5075,13 +5075,13 @@
         <v>4.25</v>
       </c>
       <c r="AA29">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AB29">
         <v>2.2</v>
       </c>
       <c r="AC29">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD29">
         <v>1.45</v>
@@ -5090,10 +5090,10 @@
         <v>1.15</v>
       </c>
       <c r="AF29">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AG29">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.16</v>
+        <v>1.98</v>
       </c>
       <c r="O30">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="P30">
-        <v>9.199999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="Q30">
-        <v>1.57</v>
+        <v>2.33</v>
       </c>
       <c r="R30">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="S30">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="U30">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="V30">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="W30">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>6.77</v>
+        <v>4.5</v>
       </c>
       <c r="AA30">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AB30">
-        <v>3.2</v>
+        <v>2.31</v>
       </c>
       <c r="AC30">
-        <v>1.87</v>
+        <v>2.33</v>
       </c>
       <c r="AD30">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AE30">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AF30">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AG30">
-        <v>2.05</v>
+        <v>2.42</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AK30">
-        <v>3.41</v>
+        <v>1.85</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>4.1</v>
       </c>
       <c r="P32">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q32">
         <v>3.81</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="O33">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P33">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Q33">
         <v>2</v>
@@ -5718,7 +5718,7 @@
         <v>1.07</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
         <v>1.34</v>
@@ -5727,25 +5727,25 @@
         <v>3.04</v>
       </c>
       <c r="AA33">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AB33">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC33">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AD33">
         <v>1.22</v>
       </c>
       <c r="AE33">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF33">
         <v>2</v>
       </c>
       <c r="AG33">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK33">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="O34">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P34">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="Q34">
         <v>3.6</v>
@@ -5875,13 +5875,13 @@
         <v>2.4</v>
       </c>
       <c r="V34">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
         <v>1.2</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="O35">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="P35">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="Q35">
         <v>2.45</v>
@@ -6035,7 +6035,7 @@
         <v>2.9</v>
       </c>
       <c r="U35">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="V35">
         <v>1.4</v>
@@ -6047,31 +6047,31 @@
         <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z35">
         <v>3.4</v>
       </c>
       <c r="AA35">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="AB35">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC35">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="AD35">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE35">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF35">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG35">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="O36">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="P36">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="Q36">
         <v>3.6</v>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O37">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="P37">
         <v>9.699999999999999</v>
@@ -6364,7 +6364,7 @@
         <v>2.17</v>
       </c>
       <c r="V37">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W37">
         <v>1.18</v>
@@ -6373,22 +6373,22 @@
         <v>1</v>
       </c>
       <c r="Y37">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z37">
-        <v>5.75</v>
+        <v>5.82</v>
       </c>
       <c r="AA37">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AB37">
         <v>2.6</v>
       </c>
       <c r="AC37">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AD37">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE37">
         <v>1.27</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AK37">
         <v>3.24</v>
@@ -6506,10 +6506,10 @@
         <v>1.6</v>
       </c>
       <c r="O38">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="P38">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q38">
         <v>2.01</v>
@@ -6530,25 +6530,25 @@
         <v>1.5</v>
       </c>
       <c r="W38">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z38">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA38">
         <v>1.66</v>
       </c>
       <c r="AB38">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC38">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AD38">
         <v>1.43</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.95</v>
+        <v>1.38</v>
       </c>
       <c r="O39">
-        <v>3.98</v>
+        <v>5</v>
       </c>
       <c r="P39">
-        <v>3.03</v>
+        <v>5.63</v>
       </c>
       <c r="Q39">
+        <v>1.8</v>
+      </c>
+      <c r="R39">
+        <v>3.2</v>
+      </c>
+      <c r="S39">
+        <v>1.11</v>
+      </c>
+      <c r="T39">
+        <v>5.5</v>
+      </c>
+      <c r="U39">
+        <v>1.65</v>
+      </c>
+      <c r="V39">
+        <v>2.13</v>
+      </c>
+      <c r="W39">
+        <v>1.33</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>1</v>
+      </c>
+      <c r="Z39">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AA39">
+        <v>1.22</v>
+      </c>
+      <c r="AB39">
+        <v>4.38</v>
+      </c>
+      <c r="AC39">
+        <v>1.59</v>
+      </c>
+      <c r="AD39">
         <v>2.45</v>
       </c>
-      <c r="R39">
-        <v>2.53</v>
-      </c>
-      <c r="S39">
-        <v>1.25</v>
-      </c>
-      <c r="T39">
-        <v>3.7</v>
-      </c>
-      <c r="U39">
-        <v>2.2</v>
-      </c>
-      <c r="V39">
-        <v>1.6</v>
-      </c>
-      <c r="W39">
-        <v>1.14</v>
-      </c>
-      <c r="X39">
-        <v>1.01</v>
-      </c>
-      <c r="Y39">
-        <v>1.14</v>
-      </c>
-      <c r="Z39">
-        <v>5.5</v>
-      </c>
-      <c r="AA39">
-        <v>1.51</v>
-      </c>
-      <c r="AB39">
-        <v>2.4</v>
-      </c>
-      <c r="AC39">
-        <v>2.34</v>
-      </c>
-      <c r="AD39">
-        <v>1.62</v>
-      </c>
       <c r="AE39">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AF39">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AG39">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>1.87</v>
+        <v>2.6</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
+        <v>1.91</v>
+      </c>
+      <c r="O40">
+        <v>3.98</v>
+      </c>
+      <c r="P40">
+        <v>3.48</v>
+      </c>
+      <c r="Q40">
+        <v>2.38</v>
+      </c>
+      <c r="R40">
+        <v>2.5</v>
+      </c>
+      <c r="S40">
+        <v>1.25</v>
+      </c>
+      <c r="T40">
+        <v>3.75</v>
+      </c>
+      <c r="U40">
+        <v>2.2</v>
+      </c>
+      <c r="V40">
+        <v>1.6</v>
+      </c>
+      <c r="W40">
+        <v>1.13</v>
+      </c>
+      <c r="X40">
+        <v>1.01</v>
+      </c>
+      <c r="Y40">
+        <v>1.14</v>
+      </c>
+      <c r="Z40">
+        <v>5.5</v>
+      </c>
+      <c r="AA40">
+        <v>1.49</v>
+      </c>
+      <c r="AB40">
+        <v>2.5</v>
+      </c>
+      <c r="AC40">
+        <v>2.29</v>
+      </c>
+      <c r="AD40">
+        <v>1.66</v>
+      </c>
+      <c r="AE40">
+        <v>1.27</v>
+      </c>
+      <c r="AF40">
         <v>1.44</v>
       </c>
-      <c r="O40">
-        <v>4.6</v>
-      </c>
-      <c r="P40">
-        <v>5</v>
-      </c>
-      <c r="Q40">
-        <v>1.8</v>
-      </c>
-      <c r="R40">
-        <v>2.88</v>
-      </c>
-      <c r="S40">
-        <v>1.11</v>
-      </c>
-      <c r="T40">
-        <v>5.5</v>
-      </c>
-      <c r="U40">
-        <v>1.65</v>
-      </c>
-      <c r="V40">
-        <v>2.12</v>
-      </c>
-      <c r="W40">
-        <v>1.33</v>
-      </c>
-      <c r="X40">
-        <v>0</v>
-      </c>
-      <c r="Y40">
-        <v>1</v>
-      </c>
-      <c r="Z40">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AA40">
-        <v>1.22</v>
-      </c>
-      <c r="AB40">
-        <v>4.33</v>
-      </c>
-      <c r="AC40">
-        <v>1.58</v>
-      </c>
-      <c r="AD40">
-        <v>2.45</v>
-      </c>
-      <c r="AE40">
-        <v>1.57</v>
-      </c>
-      <c r="AF40">
-        <v>1.3</v>
-      </c>
       <c r="AG40">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>2.6</v>
+        <v>1.87</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,34 +6992,34 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="O41">
-        <v>4.21</v>
+        <v>4.33</v>
       </c>
       <c r="P41">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="Q41">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="R41">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="S41">
         <v>1.2</v>
       </c>
       <c r="T41">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="U41">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="V41">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W41">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X41">
         <v>0</v>
@@ -7031,25 +7031,25 @@
         <v>6.5</v>
       </c>
       <c r="AA41">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB41">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AC41">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AD41">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AE41">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AF41">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AG41">
-        <v>2.72</v>
+        <v>2.45</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK41">
-        <v>1.78</v>
+        <v>2.54</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="O42">
-        <v>4.33</v>
+        <v>3.83</v>
       </c>
       <c r="P42">
-        <v>5</v>
+        <v>4.37</v>
       </c>
       <c r="Q42">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="R42">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="S42">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T42">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="U42">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V42">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="W42">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z42">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA42">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AB42">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="AC42">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AD42">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AE42">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AF42">
         <v>1.53</v>
       </c>
       <c r="AG42">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>2.54</v>
+        <v>2.05</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
+        <v>1.97</v>
+      </c>
+      <c r="O43">
+        <v>4.21</v>
+      </c>
+      <c r="P43">
+        <v>3.53</v>
+      </c>
+      <c r="Q43">
+        <v>2.3</v>
+      </c>
+      <c r="R43">
+        <v>2.5</v>
+      </c>
+      <c r="S43">
+        <v>1.2</v>
+      </c>
+      <c r="T43">
+        <v>4.5</v>
+      </c>
+      <c r="U43">
+        <v>1.91</v>
+      </c>
+      <c r="V43">
         <v>1.75</v>
       </c>
-      <c r="O43">
-        <v>3.75</v>
-      </c>
-      <c r="P43">
-        <v>4.1</v>
-      </c>
-      <c r="Q43">
-        <v>2.23</v>
-      </c>
-      <c r="R43">
-        <v>2.38</v>
-      </c>
-      <c r="S43">
-        <v>1.25</v>
-      </c>
-      <c r="T43">
-        <v>3.5</v>
-      </c>
-      <c r="U43">
-        <v>2.25</v>
-      </c>
-      <c r="V43">
-        <v>1.56</v>
-      </c>
       <c r="W43">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y43">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z43">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA43">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AB43">
-        <v>2.31</v>
+        <v>2.8</v>
       </c>
       <c r="AC43">
-        <v>2.45</v>
+        <v>2.01</v>
       </c>
       <c r="AD43">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AE43">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AF43">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AG43">
-        <v>2.26</v>
+        <v>2.72</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK43">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8788,10 +8788,10 @@
         <v>2</v>
       </c>
       <c r="O52">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P52">
-        <v>3.54</v>
+        <v>3.08</v>
       </c>
       <c r="Q52">
         <v>2.59</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="O53">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="Q53">
         <v>2.99</v>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
         <v>1.4</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="O54">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P54">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="Q54">
         <v>3.13</v>
@@ -9129,13 +9129,13 @@
         <v>1.25</v>
       </c>
       <c r="T54">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U54">
         <v>2.19</v>
       </c>
       <c r="V54">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W54">
         <v>1.15</v>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="O55">
         <v>3.9</v>
@@ -9283,7 +9283,7 @@
         <v>3.1</v>
       </c>
       <c r="Q55">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R55">
         <v>2.38</v>
@@ -9295,7 +9295,7 @@
         <v>3.64</v>
       </c>
       <c r="U55">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="V55">
         <v>1.64</v>
@@ -9322,16 +9322,16 @@
         <v>2.14</v>
       </c>
       <c r="AD55">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE55">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF55">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG55">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9437,25 +9437,25 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="O56">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P56">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q56">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R56">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S56">
         <v>1.25</v>
       </c>
       <c r="T56">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U56">
         <v>2.13</v>
@@ -9470,28 +9470,28 @@
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z56">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA56">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AB56">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AC56">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AD56">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AE56">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AF56">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG56">
         <v>2.46</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="O57">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="P57">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="Q57">
         <v>2.18</v>
@@ -9615,16 +9615,16 @@
         <v>2.73</v>
       </c>
       <c r="S57">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T57">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="U57">
         <v>1.95</v>
       </c>
       <c r="V57">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W57">
         <v>1.2</v>
@@ -9763,25 +9763,25 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="O58">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="P58">
-        <v>4.64</v>
+        <v>4.45</v>
       </c>
       <c r="Q58">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="R58">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="S58">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="T58">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="U58">
         <v>1.75</v>
@@ -9802,10 +9802,10 @@
         <v>8.5</v>
       </c>
       <c r="AA58">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AB58">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AC58">
         <v>1.67</v>
@@ -9817,7 +9817,7 @@
         <v>1.47</v>
       </c>
       <c r="AF58">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG58">
         <v>2.9</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK58">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="O59">
-        <v>5.3</v>
+        <v>5.42</v>
       </c>
       <c r="P59">
-        <v>5.5</v>
+        <v>6.35</v>
       </c>
       <c r="Q59">
         <v>1.75</v>
@@ -10101,19 +10101,19 @@
         <v>2.63</v>
       </c>
       <c r="R60">
+        <v>2.38</v>
+      </c>
+      <c r="S60">
+        <v>1.22</v>
+      </c>
+      <c r="T60">
+        <v>3.48</v>
+      </c>
+      <c r="U60">
         <v>2.3</v>
       </c>
-      <c r="S60">
-        <v>1.25</v>
-      </c>
-      <c r="T60">
-        <v>3.6</v>
-      </c>
-      <c r="U60">
-        <v>2.25</v>
-      </c>
       <c r="V60">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W60">
         <v>1.15</v>
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="O61">
         <v>5.2</v>
@@ -10261,13 +10261,13 @@
         <v>6</v>
       </c>
       <c r="Q61">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="R61">
         <v>2.75</v>
       </c>
       <c r="S61">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T61">
         <v>4.5</v>
@@ -10285,25 +10285,25 @@
         <v>0</v>
       </c>
       <c r="Y61">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z61">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA61">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AB61">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AC61">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AD61">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AE61">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF61">
         <v>1.47</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK61">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,19 +10415,19 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="O62">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P62">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q62">
         <v>2.25</v>
       </c>
       <c r="R62">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S62">
         <v>1.25</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK4">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="O7">
         <v>3.4</v>
       </c>
       <c r="P7">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="Q7">
         <v>2.88</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="O8">
         <v>3.4</v>
       </c>
       <c r="P8">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
       <c r="Q8">
         <v>2.6</v>
@@ -1652,10 +1652,10 @@
         <v>5</v>
       </c>
       <c r="AA8">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AB8">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC8">
         <v>2.45</v>
@@ -1815,7 +1815,7 @@
         <v>2.88</v>
       </c>
       <c r="AA9">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB9">
         <v>1.67</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="O12">
         <v>3.5</v>
       </c>
       <c r="P12">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
       </c>
       <c r="R12">
-        <v>2.36</v>
+        <v>2.21</v>
       </c>
       <c r="S12">
         <v>1.29</v>
@@ -2304,10 +2304,10 @@
         <v>4.5</v>
       </c>
       <c r="AA12">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB12">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC12">
         <v>2.55</v>
@@ -2319,7 +2319,7 @@
         <v>1.2</v>
       </c>
       <c r="AF12">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG12">
         <v>2.38</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK12">
         <v>1.62</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>8.25</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>5.25</v>
+        <v>5.7</v>
       </c>
       <c r="P13">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Q13">
         <v>5.32</v>
@@ -2473,7 +2473,7 @@
         <v>3.2</v>
       </c>
       <c r="AC13">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AD13">
         <v>1.9</v>
@@ -2597,19 +2597,19 @@
         <v>3.23</v>
       </c>
       <c r="P14">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
       </c>
       <c r="R14">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S14">
         <v>1.49</v>
       </c>
       <c r="T14">
-        <v>2.72</v>
+        <v>2.4</v>
       </c>
       <c r="U14">
         <v>2.9</v>
@@ -2624,7 +2624,7 @@
         <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z14">
         <v>2.89</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="O15">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P15">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
         <v>2.22</v>
@@ -2778,7 +2778,7 @@
         <v>2.7</v>
       </c>
       <c r="V15">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W15">
         <v>1.08</v>
@@ -3119,10 +3119,10 @@
         <v>4.63</v>
       </c>
       <c r="AA17">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB17">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC17">
         <v>2.63</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O18">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P18">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="Q18">
         <v>3.26</v>
@@ -3267,7 +3267,7 @@
         <v>2.3</v>
       </c>
       <c r="V18">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W18">
         <v>1.14</v>
@@ -3409,7 +3409,7 @@
         <v>2.37</v>
       </c>
       <c r="O19">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
         <v>2.55</v>
@@ -3623,10 +3623,10 @@
         <v>1.22</v>
       </c>
       <c r="AF20">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG20">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>2</v>
@@ -3786,7 +3786,7 @@
         <v>1.04</v>
       </c>
       <c r="AF21">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG21">
         <v>1.62</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK21">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="O23">
         <v>3.2</v>
       </c>
       <c r="P23">
+        <v>2.37</v>
+      </c>
+      <c r="Q23">
+        <v>3.21</v>
+      </c>
+      <c r="R23">
+        <v>2.08</v>
+      </c>
+      <c r="S23">
+        <v>1.33</v>
+      </c>
+      <c r="T23">
+        <v>3</v>
+      </c>
+      <c r="U23">
+        <v>2.59</v>
+      </c>
+      <c r="V23">
+        <v>1.42</v>
+      </c>
+      <c r="W23">
+        <v>1.08</v>
+      </c>
+      <c r="X23">
+        <v>1.01</v>
+      </c>
+      <c r="Y23">
+        <v>1.22</v>
+      </c>
+      <c r="Z23">
+        <v>3.8</v>
+      </c>
+      <c r="AA23">
+        <v>1.89</v>
+      </c>
+      <c r="AB23">
+        <v>1.93</v>
+      </c>
+      <c r="AC23">
         <v>3.1</v>
       </c>
-      <c r="Q23">
-        <v>2.7</v>
-      </c>
-      <c r="R23">
-        <v>2.03</v>
-      </c>
-      <c r="S23">
-        <v>1.36</v>
-      </c>
-      <c r="T23">
-        <v>2.88</v>
-      </c>
-      <c r="U23">
-        <v>2.8</v>
-      </c>
-      <c r="V23">
-        <v>1.4</v>
-      </c>
-      <c r="W23">
-        <v>1.05</v>
-      </c>
-      <c r="X23">
-        <v>1.05</v>
-      </c>
-      <c r="Y23">
+      <c r="AD23">
         <v>1.32</v>
-      </c>
-      <c r="Z23">
-        <v>3.25</v>
-      </c>
-      <c r="AA23">
-        <v>2</v>
-      </c>
-      <c r="AB23">
-        <v>1.75</v>
-      </c>
-      <c r="AC23">
-        <v>3.14</v>
-      </c>
-      <c r="AD23">
-        <v>1.27</v>
       </c>
       <c r="AE23">
         <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>1.62</v>
+        <v>1.34</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="O24">
         <v>3.2</v>
       </c>
       <c r="P24">
-        <v>2.37</v>
+        <v>3.1</v>
       </c>
       <c r="Q24">
-        <v>3.21</v>
+        <v>2.7</v>
       </c>
       <c r="R24">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="S24">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T24">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U24">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="V24">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y24">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="Z24">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="AA24">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AB24">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AC24">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AD24">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE24">
         <v>1.1</v>
       </c>
       <c r="AF24">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG24">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK24">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5401,7 +5401,7 @@
         <v>3.25</v>
       </c>
       <c r="AA31">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AB31">
         <v>1.75</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O32">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="P32">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="Q32">
         <v>3.81</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="O35">
         <v>3.33</v>
@@ -6056,10 +6056,10 @@
         <v>1.92</v>
       </c>
       <c r="AB35">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC35">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="AD35">
         <v>1.32</v>
@@ -6071,7 +6071,7 @@
         <v>1.8</v>
       </c>
       <c r="AG35">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.28</v>
       </c>
       <c r="AK35">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6180,10 +6180,10 @@
         <v>2.73</v>
       </c>
       <c r="O36">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="P36">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="Q36">
         <v>3.6</v>
@@ -6192,10 +6192,10 @@
         <v>2.09</v>
       </c>
       <c r="S36">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="U36">
         <v>2.75</v>
@@ -6231,10 +6231,10 @@
         <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG36">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK36">
         <v>1.36</v>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="O37">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="P37">
         <v>9.699999999999999</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.38</v>
+        <v>1.91</v>
       </c>
       <c r="O39">
-        <v>5</v>
+        <v>3.98</v>
       </c>
       <c r="P39">
-        <v>5.63</v>
+        <v>3.48</v>
       </c>
       <c r="Q39">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="R39">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="S39">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
+        <v>3.75</v>
+      </c>
+      <c r="U39">
+        <v>2.2</v>
+      </c>
+      <c r="V39">
+        <v>1.6</v>
+      </c>
+      <c r="W39">
+        <v>1.13</v>
+      </c>
+      <c r="X39">
+        <v>1.01</v>
+      </c>
+      <c r="Y39">
+        <v>1.14</v>
+      </c>
+      <c r="Z39">
         <v>5.5</v>
       </c>
-      <c r="U39">
-        <v>1.65</v>
-      </c>
-      <c r="V39">
-        <v>2.13</v>
-      </c>
-      <c r="W39">
-        <v>1.33</v>
-      </c>
-      <c r="X39">
-        <v>0</v>
-      </c>
-      <c r="Y39">
-        <v>1</v>
-      </c>
-      <c r="Z39">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AA39">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="AB39">
-        <v>4.38</v>
+        <v>2.5</v>
       </c>
       <c r="AC39">
-        <v>1.59</v>
+        <v>2.29</v>
       </c>
       <c r="AD39">
-        <v>2.45</v>
+        <v>1.66</v>
       </c>
       <c r="AE39">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AF39">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AG39">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>2.6</v>
+        <v>1.87</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,80 +6829,80 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.91</v>
+        <v>1.48</v>
       </c>
       <c r="O40">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="P40">
-        <v>3.48</v>
+        <v>5</v>
       </c>
       <c r="Q40">
-        <v>2.38</v>
+        <v>1.89</v>
       </c>
       <c r="R40">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="S40">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T40">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="U40">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V40">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="W40">
+        <v>1.18</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>1.1</v>
+      </c>
+      <c r="Z40">
+        <v>6.5</v>
+      </c>
+      <c r="AA40">
+        <v>1.38</v>
+      </c>
+      <c r="AB40">
+        <v>2.7</v>
+      </c>
+      <c r="AC40">
+        <v>2.1</v>
+      </c>
+      <c r="AD40">
+        <v>1.71</v>
+      </c>
+      <c r="AE40">
+        <v>1.32</v>
+      </c>
+      <c r="AF40">
+        <v>1.53</v>
+      </c>
+      <c r="AG40">
+        <v>2.45</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
         <v>1.13</v>
       </c>
-      <c r="X40">
-        <v>1.01</v>
-      </c>
-      <c r="Y40">
-        <v>1.14</v>
-      </c>
-      <c r="Z40">
-        <v>5.5</v>
-      </c>
-      <c r="AA40">
-        <v>1.49</v>
-      </c>
-      <c r="AB40">
-        <v>2.5</v>
-      </c>
-      <c r="AC40">
-        <v>2.29</v>
-      </c>
-      <c r="AD40">
-        <v>1.66</v>
-      </c>
-      <c r="AE40">
-        <v>1.27</v>
-      </c>
-      <c r="AF40">
-        <v>1.44</v>
-      </c>
-      <c r="AG40">
-        <v>2.5</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.25</v>
-      </c>
       <c r="AK40">
-        <v>1.87</v>
+        <v>2.54</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="O41">
-        <v>4.33</v>
+        <v>3.83</v>
       </c>
       <c r="P41">
-        <v>5</v>
+        <v>4.37</v>
       </c>
       <c r="Q41">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="R41">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="S41">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="U41">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V41">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="W41">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z41">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA41">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AB41">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="AC41">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AD41">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AE41">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AF41">
         <v>1.53</v>
       </c>
       <c r="AG41">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>2.54</v>
+        <v>2.05</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="O42">
-        <v>3.83</v>
+        <v>5</v>
       </c>
       <c r="P42">
-        <v>4.37</v>
+        <v>5.63</v>
       </c>
       <c r="Q42">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="R42">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="S42">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="T42">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="U42">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="V42">
-        <v>1.6</v>
+        <v>2.13</v>
       </c>
       <c r="W42">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y42">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="Z42">
-        <v>4.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA42">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AB42">
-        <v>2.54</v>
+        <v>4.38</v>
       </c>
       <c r="AC42">
-        <v>2.38</v>
+        <v>1.59</v>
       </c>
       <c r="AD42">
+        <v>2.45</v>
+      </c>
+      <c r="AE42">
         <v>1.57</v>
       </c>
-      <c r="AE42">
-        <v>1.25</v>
-      </c>
       <c r="AF42">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AG42">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK42">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -8794,10 +8794,10 @@
         <v>3.08</v>
       </c>
       <c r="Q52">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="R52">
-        <v>2.33</v>
+        <v>2.16</v>
       </c>
       <c r="S52">
         <v>1.36</v>
@@ -8806,10 +8806,10 @@
         <v>3.2</v>
       </c>
       <c r="U52">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="V52">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W52">
         <v>1.11</v>
@@ -8827,7 +8827,7 @@
         <v>1.84</v>
       </c>
       <c r="AB52">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC52">
         <v>3.1</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK52">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8951,7 +8951,7 @@
         <v>2.52</v>
       </c>
       <c r="O53">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="P53">
         <v>2.37</v>
@@ -8966,7 +8966,7 @@
         <v>1.29</v>
       </c>
       <c r="T53">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U53">
         <v>2.38</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O2">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="P2">
         <v>2.15</v>
       </c>
       <c r="Q2">
-        <v>4.24</v>
+        <v>4</v>
       </c>
       <c r="R2">
         <v>1.87</v>
@@ -653,13 +653,13 @@
         <v>1.44</v>
       </c>
       <c r="T2">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U2">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W2">
         <v>1.05</v>
@@ -668,10 +668,10 @@
         <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="Z2">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="AA2">
         <v>2.31</v>
@@ -1000,10 +1000,10 @@
         <v>3.5</v>
       </c>
       <c r="AA4">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB4">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC4">
         <v>2.5</v>
@@ -1127,7 +1127,7 @@
         <v>1.5</v>
       </c>
       <c r="O5">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
         <v>4.6</v>
@@ -1148,7 +1148,7 @@
         <v>2.47</v>
       </c>
       <c r="V5">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
         <v>1.07</v>
@@ -1160,19 +1160,19 @@
         <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AA5">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AB5">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC5">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD5">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE5">
         <v>1.1</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK5">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1329,7 +1329,7 @@
         <v>1.65</v>
       </c>
       <c r="AB6">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC6">
         <v>2.58</v>
@@ -1489,10 +1489,10 @@
         <v>4.5</v>
       </c>
       <c r="AA7">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB7">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC7">
         <v>2.66</v>
@@ -1815,7 +1815,7 @@
         <v>2.88</v>
       </c>
       <c r="AA9">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AB9">
         <v>1.67</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P10">
         <v>4.33</v>
@@ -1987,7 +1987,7 @@
         <v>2.23</v>
       </c>
       <c r="AD10">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AE10">
         <v>1.22</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="O13">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="P13">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Q13">
         <v>5.32</v>
@@ -2449,7 +2449,7 @@
         <v>4.8</v>
       </c>
       <c r="U13">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="V13">
         <v>1.85</v>
@@ -2461,31 +2461,31 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z13">
-        <v>6.75</v>
+        <v>6.38</v>
       </c>
       <c r="AA13">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AB13">
         <v>3.2</v>
       </c>
       <c r="AC13">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AD13">
         <v>1.9</v>
       </c>
       <c r="AE13">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AF13">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AG13">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.13</v>
+        <v>3.3</v>
       </c>
       <c r="AK13">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2594,10 +2594,10 @@
         <v>2.85</v>
       </c>
       <c r="O14">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="P14">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -2606,16 +2606,16 @@
         <v>2</v>
       </c>
       <c r="S14">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="T14">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="U14">
         <v>2.9</v>
       </c>
       <c r="V14">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W14">
         <v>1.03</v>
@@ -2624,10 +2624,10 @@
         <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="Z14">
-        <v>2.89</v>
+        <v>3.31</v>
       </c>
       <c r="AA14">
         <v>2.28</v>
@@ -2636,10 +2636,10 @@
         <v>1.64</v>
       </c>
       <c r="AC14">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AD14">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE14">
         <v>1.07</v>
@@ -2648,7 +2648,7 @@
         <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.33</v>
       </c>
       <c r="AK14">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,65 +2754,65 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="O15">
-        <v>3.7</v>
+        <v>3.77</v>
       </c>
       <c r="P15">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Q15">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="R15">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T15">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="U15">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="V15">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z15">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="AA15">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="AB15">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AC15">
-        <v>2.94</v>
+        <v>3.54</v>
       </c>
       <c r="AD15">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE15">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF15">
+        <v>1.95</v>
+      </c>
+      <c r="AG15">
         <v>1.8</v>
       </c>
-      <c r="AG15">
-        <v>1.95</v>
-      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK15">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="O16">
         <v>3.4</v>
       </c>
       <c r="P16">
+        <v>2.75</v>
+      </c>
+      <c r="Q16">
         <v>2.88</v>
-      </c>
-      <c r="Q16">
-        <v>2.8</v>
       </c>
       <c r="R16">
         <v>2.15</v>
@@ -2953,13 +2953,13 @@
         <v>1.2</v>
       </c>
       <c r="Z16">
-        <v>4.4</v>
+        <v>4.42</v>
       </c>
       <c r="AA16">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB16">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC16">
         <v>2.83</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3738,7 +3738,7 @@
         <v>3.6</v>
       </c>
       <c r="P21">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="Q21">
         <v>2</v>
@@ -3968,7 +3968,7 @@
         <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4100,7 +4100,7 @@
         <v>1.89</v>
       </c>
       <c r="AB23">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC23">
         <v>3.1</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.27</v>
+        <v>3</v>
       </c>
       <c r="O28">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>9</v>
+        <v>2.2</v>
       </c>
       <c r="Q28">
+        <v>3.31</v>
+      </c>
+      <c r="R28">
+        <v>2.3</v>
+      </c>
+      <c r="S28">
+        <v>1.29</v>
+      </c>
+      <c r="T28">
+        <v>3.22</v>
+      </c>
+      <c r="U28">
+        <v>2.55</v>
+      </c>
+      <c r="V28">
+        <v>1.53</v>
+      </c>
+      <c r="W28">
+        <v>1.12</v>
+      </c>
+      <c r="X28">
+        <v>1.02</v>
+      </c>
+      <c r="Y28">
+        <v>1.2</v>
+      </c>
+      <c r="Z28">
+        <v>4.2</v>
+      </c>
+      <c r="AA28">
+        <v>1.66</v>
+      </c>
+      <c r="AB28">
+        <v>2.2</v>
+      </c>
+      <c r="AC28">
+        <v>2.88</v>
+      </c>
+      <c r="AD28">
+        <v>1.44</v>
+      </c>
+      <c r="AE28">
+        <v>1.14</v>
+      </c>
+      <c r="AF28">
         <v>1.57</v>
       </c>
-      <c r="R28">
-        <v>2.75</v>
-      </c>
-      <c r="S28">
-        <v>1.18</v>
-      </c>
-      <c r="T28">
-        <v>3.84</v>
-      </c>
-      <c r="U28">
-        <v>1.85</v>
-      </c>
-      <c r="V28">
-        <v>1.85</v>
-      </c>
-      <c r="W28">
-        <v>1.19</v>
-      </c>
-      <c r="X28">
-        <v>1.01</v>
-      </c>
-      <c r="Y28">
-        <v>1.1</v>
-      </c>
-      <c r="Z28">
-        <v>6.77</v>
-      </c>
-      <c r="AA28">
-        <v>1.36</v>
-      </c>
-      <c r="AB28">
-        <v>2.88</v>
-      </c>
-      <c r="AC28">
-        <v>1.9</v>
-      </c>
-      <c r="AD28">
-        <v>1.9</v>
-      </c>
-      <c r="AE28">
-        <v>1.36</v>
-      </c>
-      <c r="AF28">
-        <v>1.67</v>
-      </c>
       <c r="AG28">
-        <v>2.05</v>
+        <v>2.31</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="AK28">
-        <v>3.41</v>
+        <v>1.25</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.1</v>
+        <v>1.97</v>
       </c>
       <c r="O29">
+        <v>3.8</v>
+      </c>
+      <c r="P29">
+        <v>3.3</v>
+      </c>
+      <c r="Q29">
+        <v>2.33</v>
+      </c>
+      <c r="R29">
+        <v>2.53</v>
+      </c>
+      <c r="S29">
+        <v>1.25</v>
+      </c>
+      <c r="T29">
         <v>3.6</v>
       </c>
-      <c r="P29">
-        <v>2.1</v>
-      </c>
-      <c r="Q29">
-        <v>3.31</v>
-      </c>
-      <c r="R29">
-        <v>2.3</v>
-      </c>
-      <c r="S29">
-        <v>1.29</v>
-      </c>
-      <c r="T29">
-        <v>3.24</v>
-      </c>
       <c r="U29">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="V29">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W29">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
         <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA29">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB29">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC29">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="AD29">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE29">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF29">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG29">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK29">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.98</v>
+        <v>1.25</v>
       </c>
       <c r="O30">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="P30">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>2.33</v>
+        <v>1.57</v>
       </c>
       <c r="R30">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="S30">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T30">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="U30">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="V30">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="W30">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="Z30">
-        <v>4.5</v>
+        <v>6.77</v>
       </c>
       <c r="AA30">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AB30">
-        <v>2.31</v>
+        <v>2.88</v>
       </c>
       <c r="AC30">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="AD30">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AE30">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AF30">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AG30">
-        <v>2.42</v>
+        <v>2.05</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AK30">
-        <v>1.85</v>
+        <v>3.41</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5691,7 +5691,7 @@
         <v>1.48</v>
       </c>
       <c r="O33">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P33">
         <v>5.5</v>
@@ -5742,7 +5742,7 @@
         <v>1.05</v>
       </c>
       <c r="AF33">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG33">
         <v>1.65</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="O34">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="Q34">
         <v>3.6</v>
@@ -5875,7 +5875,7 @@
         <v>2.4</v>
       </c>
       <c r="V34">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W34">
         <v>1.13</v>
@@ -6717,7 +6717,7 @@
         <v>1.66</v>
       </c>
       <c r="AE39">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF39">
         <v>1.44</v>
@@ -6850,10 +6850,10 @@
         <v>4.1</v>
       </c>
       <c r="U40">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="V40">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W40">
         <v>1.18</v>
@@ -6871,7 +6871,7 @@
         <v>1.38</v>
       </c>
       <c r="AB40">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC40">
         <v>2.1</v>
@@ -7158,7 +7158,7 @@
         <v>1.38</v>
       </c>
       <c r="O42">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="P42">
         <v>5.63</v>
@@ -7197,7 +7197,7 @@
         <v>1.22</v>
       </c>
       <c r="AB42">
-        <v>4.38</v>
+        <v>4.2</v>
       </c>
       <c r="AC42">
         <v>1.59</v>
@@ -7206,7 +7206,7 @@
         <v>2.45</v>
       </c>
       <c r="AE42">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AF42">
         <v>1.3</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="O43">
         <v>4.21</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="O54">
         <v>3.8</v>
       </c>
       <c r="P54">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="Q54">
         <v>3.13</v>
@@ -9153,7 +9153,7 @@
         <v>1.6</v>
       </c>
       <c r="AB54">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC54">
         <v>2.45</v>
@@ -9184,7 +9184,7 @@
         <v>1.25</v>
       </c>
       <c r="AK54">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="O55">
         <v>3.9</v>
       </c>
       <c r="P55">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -9319,7 +9319,7 @@
         <v>2.43</v>
       </c>
       <c r="AC55">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AD55">
         <v>1.6</v>
@@ -9449,7 +9449,7 @@
         <v>2.15</v>
       </c>
       <c r="R56">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S56">
         <v>1.25</v>
@@ -9470,16 +9470,16 @@
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z56">
-        <v>5.25</v>
+        <v>5.32</v>
       </c>
       <c r="AA56">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB56">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AC56">
         <v>2.15</v>
@@ -9491,10 +9491,10 @@
         <v>1.29</v>
       </c>
       <c r="AF56">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG56">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.19</v>
       </c>
       <c r="AK56">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9603,31 +9603,31 @@
         <v>1.7</v>
       </c>
       <c r="O57">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="P57">
         <v>3.7</v>
       </c>
       <c r="Q57">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R57">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="S57">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T57">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="U57">
         <v>1.95</v>
       </c>
       <c r="V57">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="W57">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X57">
         <v>0</v>
@@ -9645,10 +9645,10 @@
         <v>2.87</v>
       </c>
       <c r="AC57">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AD57">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AE57">
         <v>1.3</v>
@@ -9769,7 +9769,7 @@
         <v>4.65</v>
       </c>
       <c r="P58">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="Q58">
         <v>1.93</v>
@@ -9784,7 +9784,7 @@
         <v>5</v>
       </c>
       <c r="U58">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V58">
         <v>1.95</v>
@@ -9932,7 +9932,7 @@
         <v>5.42</v>
       </c>
       <c r="P59">
-        <v>6.35</v>
+        <v>6.2</v>
       </c>
       <c r="Q59">
         <v>1.75</v>
@@ -9965,10 +9965,10 @@
         <v>8</v>
       </c>
       <c r="AA59">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB59">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AC59">
         <v>1.84</v>
@@ -10092,16 +10092,16 @@
         <v>2.1</v>
       </c>
       <c r="O60">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="P60">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="Q60">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="R60">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S60">
         <v>1.22</v>
@@ -10267,7 +10267,7 @@
         <v>2.75</v>
       </c>
       <c r="S61">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T61">
         <v>4.5</v>
@@ -10427,7 +10427,7 @@
         <v>2.25</v>
       </c>
       <c r="R62">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S62">
         <v>1.25</v>
@@ -10454,7 +10454,7 @@
         <v>4.5</v>
       </c>
       <c r="AA62">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AB62">
         <v>2.25</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="O5">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="P5">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="Q5">
         <v>2.05</v>
@@ -1139,16 +1139,16 @@
         <v>2.2</v>
       </c>
       <c r="S5">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T5">
         <v>3.1</v>
       </c>
       <c r="U5">
-        <v>2.47</v>
+        <v>2.57</v>
       </c>
       <c r="V5">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
         <v>1.07</v>
@@ -1160,28 +1160,28 @@
         <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AA5">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB5">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AC5">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AD5">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE5">
         <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG5">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK5">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1625,19 +1625,19 @@
         <v>2.6</v>
       </c>
       <c r="R8">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="S8">
         <v>1.25</v>
       </c>
       <c r="T8">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U8">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V8">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W8">
         <v>1.15</v>
@@ -1652,16 +1652,16 @@
         <v>5</v>
       </c>
       <c r="AA8">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AB8">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC8">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AD8">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AE8">
         <v>1.2</v>
@@ -1670,7 +1670,7 @@
         <v>1.44</v>
       </c>
       <c r="AG8">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2265,16 +2265,16 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="O12">
         <v>3.5</v>
       </c>
       <c r="P12">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q12">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="R12">
         <v>2.21</v>
@@ -2286,7 +2286,7 @@
         <v>3.4</v>
       </c>
       <c r="U12">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V12">
         <v>1.53</v>
@@ -2304,10 +2304,10 @@
         <v>4.5</v>
       </c>
       <c r="AA12">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AB12">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AC12">
         <v>2.55</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AK12">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="O13">
         <v>5.5</v>
       </c>
       <c r="P13">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Q13">
-        <v>5.32</v>
+        <v>6.38</v>
       </c>
       <c r="R13">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="S13">
         <v>1.2</v>
@@ -2461,19 +2461,19 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z13">
         <v>6.38</v>
       </c>
       <c r="AA13">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AB13">
         <v>3.2</v>
       </c>
       <c r="AC13">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AD13">
         <v>1.9</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>3.3</v>
+        <v>1.13</v>
       </c>
       <c r="AK13">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,25 +2591,25 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="O14">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="P14">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q14">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R14">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S14">
         <v>1.47</v>
       </c>
       <c r="T14">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="U14">
         <v>2.9</v>
@@ -2624,16 +2624,16 @@
         <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z14">
-        <v>3.31</v>
+        <v>3.52</v>
       </c>
       <c r="AA14">
-        <v>2.28</v>
+        <v>2.09</v>
       </c>
       <c r="AB14">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AC14">
         <v>3.8</v>
@@ -2760,13 +2760,13 @@
         <v>3.77</v>
       </c>
       <c r="P15">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="Q15">
         <v>2.25</v>
       </c>
       <c r="R15">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S15">
         <v>1.36</v>
@@ -2778,7 +2778,7 @@
         <v>3.08</v>
       </c>
       <c r="V15">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W15">
         <v>1.05</v>
@@ -2787,16 +2787,16 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z15">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="AA15">
         <v>2.12</v>
       </c>
       <c r="AB15">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC15">
         <v>3.54</v>
@@ -2808,10 +2808,10 @@
         <v>1.04</v>
       </c>
       <c r="AF15">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG15">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.19</v>
       </c>
       <c r="AK15">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2926,7 +2926,7 @@
         <v>2.75</v>
       </c>
       <c r="Q16">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R16">
         <v>2.15</v>
@@ -2953,16 +2953,16 @@
         <v>1.2</v>
       </c>
       <c r="Z16">
-        <v>4.42</v>
+        <v>4.46</v>
       </c>
       <c r="AA16">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB16">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AC16">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AD16">
         <v>1.44</v>
@@ -3083,10 +3083,10 @@
         <v>4.4</v>
       </c>
       <c r="O17">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P17">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Q17">
         <v>4.16</v>
@@ -3095,49 +3095,49 @@
         <v>2.32</v>
       </c>
       <c r="S17">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T17">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U17">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V17">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
+        <v>1.13</v>
+      </c>
+      <c r="Z17">
+        <v>5.32</v>
+      </c>
+      <c r="AA17">
+        <v>1.53</v>
+      </c>
+      <c r="AB17">
+        <v>2.55</v>
+      </c>
+      <c r="AC17">
+        <v>2.38</v>
+      </c>
+      <c r="AD17">
+        <v>1.57</v>
+      </c>
+      <c r="AE17">
         <v>1.2</v>
       </c>
-      <c r="Z17">
-        <v>4.63</v>
-      </c>
-      <c r="AA17">
-        <v>1.6</v>
-      </c>
-      <c r="AB17">
-        <v>2.3</v>
-      </c>
-      <c r="AC17">
-        <v>2.63</v>
-      </c>
-      <c r="AD17">
-        <v>1.47</v>
-      </c>
-      <c r="AE17">
-        <v>1.15</v>
-      </c>
       <c r="AF17">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AG17">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>4.45</v>
       </c>
       <c r="AA18">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AB18">
         <v>2.3</v>
@@ -3291,7 +3291,7 @@
         <v>2.38</v>
       </c>
       <c r="AD18">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AE18">
         <v>1.17</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="O19">
         <v>3.2</v>
       </c>
       <c r="P19">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="Q19">
         <v>2.82</v>
@@ -3421,10 +3421,10 @@
         <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T19">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U19">
         <v>2.62</v>
@@ -3442,10 +3442,10 @@
         <v>1.24</v>
       </c>
       <c r="Z19">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AA19">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AB19">
         <v>1.94</v>
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="N20">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="O20">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P20">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Q20">
         <v>3.77</v>
       </c>
       <c r="R20">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="S20">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T20">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="U20">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V20">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="W20">
         <v>1.15</v>
@@ -3602,25 +3602,25 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z20">
-        <v>5.27</v>
+        <v>5.91</v>
       </c>
       <c r="AA20">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AB20">
-        <v>2.53</v>
+        <v>2.74</v>
       </c>
       <c r="AC20">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="AD20">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AE20">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF20">
         <v>1.5</v>
@@ -3931,13 +3931,13 @@
         <v>1.22</v>
       </c>
       <c r="Z22">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA22">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB22">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC22">
         <v>2.85</v>
@@ -3949,7 +3949,7 @@
         <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG22">
         <v>2.15</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="O23">
         <v>3.2</v>
       </c>
       <c r="P23">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="Q23">
-        <v>3.21</v>
+        <v>2.7</v>
       </c>
       <c r="R23">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="S23">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="T23">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U23">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="V23">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="Z23">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="AA23">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="AB23">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC23">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD23">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE23">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF23">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG23">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK23">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="O24">
         <v>3.2</v>
       </c>
       <c r="P24">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q24">
-        <v>2.7</v>
+        <v>3.21</v>
       </c>
       <c r="R24">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="S24">
         <v>1.36</v>
       </c>
       <c r="T24">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U24">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="V24">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
+        <v>1.22</v>
+      </c>
+      <c r="Z24">
+        <v>3.5</v>
+      </c>
+      <c r="AA24">
+        <v>1.89</v>
+      </c>
+      <c r="AB24">
+        <v>1.93</v>
+      </c>
+      <c r="AC24">
+        <v>3.25</v>
+      </c>
+      <c r="AD24">
         <v>1.32</v>
-      </c>
-      <c r="Z24">
-        <v>3.25</v>
-      </c>
-      <c r="AA24">
-        <v>2</v>
-      </c>
-      <c r="AB24">
-        <v>1.75</v>
-      </c>
-      <c r="AC24">
-        <v>3.14</v>
-      </c>
-      <c r="AD24">
-        <v>1.27</v>
       </c>
       <c r="AE24">
         <v>1.1</v>
       </c>
       <c r="AF24">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>1.62</v>
+        <v>1.34</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O26">
         <v>3.48</v>
       </c>
       <c r="P26">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q26">
         <v>2.58</v>
@@ -4601,7 +4601,7 @@
         <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG26">
         <v>2.15</v>
@@ -4719,55 +4719,55 @@
         <v>2.75</v>
       </c>
       <c r="Q27">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="R27">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="S27">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T27">
         <v>3.2</v>
       </c>
       <c r="U27">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V27">
         <v>1.44</v>
       </c>
       <c r="W27">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z27">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="AA27">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AB27">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC27">
         <v>3.1</v>
       </c>
       <c r="AD27">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG27">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>3</v>
+        <v>1.97</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P28">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q28">
-        <v>3.31</v>
+        <v>2.33</v>
       </c>
       <c r="R28">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="S28">
         <v>1.29</v>
       </c>
       <c r="T28">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="U28">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="V28">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W28">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
         <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA28">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB28">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AC28">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="AD28">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE28">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF28">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG28">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK28">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.97</v>
+        <v>1.25</v>
       </c>
       <c r="O29">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="P29">
-        <v>3.3</v>
+        <v>10.5</v>
       </c>
       <c r="Q29">
-        <v>2.33</v>
+        <v>1.53</v>
       </c>
       <c r="R29">
-        <v>2.53</v>
+        <v>3.28</v>
       </c>
       <c r="S29">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T29">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="U29">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="V29">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="W29">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="Z29">
-        <v>4.5</v>
+        <v>6.88</v>
       </c>
       <c r="AA29">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AB29">
-        <v>2.3</v>
+        <v>3.26</v>
       </c>
       <c r="AC29">
-        <v>2.33</v>
+        <v>1.88</v>
       </c>
       <c r="AD29">
-        <v>1.5</v>
+        <v>1.97</v>
       </c>
       <c r="AE29">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AF29">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AG29">
-        <v>2.42</v>
+        <v>2.03</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AK29">
-        <v>1.85</v>
+        <v>3.84</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
+        <v>3</v>
+      </c>
+      <c r="O30">
+        <v>3.55</v>
+      </c>
+      <c r="P30">
+        <v>2.2</v>
+      </c>
+      <c r="Q30">
+        <v>3.31</v>
+      </c>
+      <c r="R30">
+        <v>2.3</v>
+      </c>
+      <c r="S30">
+        <v>1.3</v>
+      </c>
+      <c r="T30">
+        <v>3.22</v>
+      </c>
+      <c r="U30">
+        <v>2.58</v>
+      </c>
+      <c r="V30">
+        <v>1.5</v>
+      </c>
+      <c r="W30">
+        <v>1.12</v>
+      </c>
+      <c r="X30">
+        <v>1.02</v>
+      </c>
+      <c r="Y30">
+        <v>1.23</v>
+      </c>
+      <c r="Z30">
+        <v>4.33</v>
+      </c>
+      <c r="AA30">
+        <v>1.72</v>
+      </c>
+      <c r="AB30">
+        <v>2.1</v>
+      </c>
+      <c r="AC30">
+        <v>2.88</v>
+      </c>
+      <c r="AD30">
+        <v>1.4</v>
+      </c>
+      <c r="AE30">
+        <v>1.13</v>
+      </c>
+      <c r="AF30">
+        <v>1.57</v>
+      </c>
+      <c r="AG30">
+        <v>2.3</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>1.21</v>
+      </c>
+      <c r="AK30">
         <v>1.25</v>
-      </c>
-      <c r="O30">
-        <v>6</v>
-      </c>
-      <c r="P30">
-        <v>9</v>
-      </c>
-      <c r="Q30">
-        <v>1.57</v>
-      </c>
-      <c r="R30">
-        <v>2.75</v>
-      </c>
-      <c r="S30">
-        <v>1.18</v>
-      </c>
-      <c r="T30">
-        <v>3.84</v>
-      </c>
-      <c r="U30">
-        <v>1.85</v>
-      </c>
-      <c r="V30">
-        <v>1.85</v>
-      </c>
-      <c r="W30">
-        <v>1.19</v>
-      </c>
-      <c r="X30">
-        <v>1.01</v>
-      </c>
-      <c r="Y30">
-        <v>1.1</v>
-      </c>
-      <c r="Z30">
-        <v>6.77</v>
-      </c>
-      <c r="AA30">
-        <v>1.32</v>
-      </c>
-      <c r="AB30">
-        <v>2.88</v>
-      </c>
-      <c r="AC30">
-        <v>1.9</v>
-      </c>
-      <c r="AD30">
-        <v>1.9</v>
-      </c>
-      <c r="AE30">
-        <v>1.36</v>
-      </c>
-      <c r="AF30">
-        <v>1.67</v>
-      </c>
-      <c r="AG30">
-        <v>2.05</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.05</v>
-      </c>
-      <c r="AK30">
-        <v>3.41</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O31">
-        <v>3.73</v>
+        <v>3.51</v>
       </c>
       <c r="P31">
+        <v>1.6</v>
+      </c>
+      <c r="Q31">
+        <v>5.5</v>
+      </c>
+      <c r="R31">
+        <v>2.04</v>
+      </c>
+      <c r="S31">
+        <v>1.5</v>
+      </c>
+      <c r="T31">
+        <v>2.37</v>
+      </c>
+      <c r="U31">
+        <v>3.31</v>
+      </c>
+      <c r="V31">
+        <v>1.33</v>
+      </c>
+      <c r="W31">
+        <v>1.03</v>
+      </c>
+      <c r="X31">
+        <v>1.07</v>
+      </c>
+      <c r="Y31">
+        <v>1.44</v>
+      </c>
+      <c r="Z31">
+        <v>2.76</v>
+      </c>
+      <c r="AA31">
+        <v>2.44</v>
+      </c>
+      <c r="AB31">
         <v>1.53</v>
       </c>
-      <c r="Q31">
+      <c r="AC31">
         <v>5</v>
       </c>
-      <c r="R31">
-        <v>2.13</v>
-      </c>
-      <c r="S31">
-        <v>1.43</v>
-      </c>
-      <c r="T31">
-        <v>2.56</v>
-      </c>
-      <c r="U31">
-        <v>2.88</v>
-      </c>
-      <c r="V31">
-        <v>1.36</v>
-      </c>
-      <c r="W31">
-        <v>1.05</v>
-      </c>
-      <c r="X31">
-        <v>1.05</v>
-      </c>
-      <c r="Y31">
-        <v>1.33</v>
-      </c>
-      <c r="Z31">
-        <v>3.25</v>
-      </c>
-      <c r="AA31">
+      <c r="AD31">
+        <v>1.17</v>
+      </c>
+      <c r="AE31">
+        <v>1.03</v>
+      </c>
+      <c r="AF31">
         <v>2.15</v>
       </c>
-      <c r="AB31">
-        <v>1.75</v>
-      </c>
-      <c r="AC31">
-        <v>3.5</v>
-      </c>
-      <c r="AD31">
-        <v>1.29</v>
-      </c>
-      <c r="AE31">
-        <v>1.08</v>
-      </c>
-      <c r="AF31">
-        <v>1.95</v>
-      </c>
       <c r="AG31">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="AK31">
         <v>1.13</v>
@@ -5531,10 +5531,10 @@
         <v>4.05</v>
       </c>
       <c r="P32">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="Q32">
-        <v>3.81</v>
+        <v>4.85</v>
       </c>
       <c r="R32">
         <v>2.15</v>
@@ -5543,7 +5543,7 @@
         <v>1.3</v>
       </c>
       <c r="T32">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U32">
         <v>2.4</v>
@@ -5552,16 +5552,16 @@
         <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z32">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA32">
         <v>1.65</v>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O33">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
         <v>5.5</v>
@@ -5703,19 +5703,19 @@
         <v>2.15</v>
       </c>
       <c r="S33">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T33">
         <v>2.72</v>
       </c>
       <c r="U33">
-        <v>2.93</v>
+        <v>2.77</v>
       </c>
       <c r="V33">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
         <v>1.04</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="N34">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O34">
         <v>3.6</v>
@@ -5860,55 +5860,55 @@
         <v>2.09</v>
       </c>
       <c r="Q34">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R34">
         <v>2.18</v>
       </c>
       <c r="S34">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T34">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="U34">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V34">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W34">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
+        <v>1.17</v>
+      </c>
+      <c r="Z34">
+        <v>4.2</v>
+      </c>
+      <c r="AA34">
+        <v>1.64</v>
+      </c>
+      <c r="AB34">
+        <v>2.17</v>
+      </c>
+      <c r="AC34">
+        <v>2.55</v>
+      </c>
+      <c r="AD34">
+        <v>1.43</v>
+      </c>
+      <c r="AE34">
         <v>1.2</v>
       </c>
-      <c r="Z34">
-        <v>4.33</v>
-      </c>
-      <c r="AA34">
-        <v>1.6</v>
-      </c>
-      <c r="AB34">
-        <v>2.25</v>
-      </c>
-      <c r="AC34">
-        <v>2.42</v>
-      </c>
-      <c r="AD34">
-        <v>1.44</v>
-      </c>
-      <c r="AE34">
-        <v>1.17</v>
-      </c>
       <c r="AF34">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG34">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AK34">
         <v>1.27</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="O35">
         <v>3.33</v>
@@ -6023,7 +6023,7 @@
         <v>3.58</v>
       </c>
       <c r="Q35">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R35">
         <v>2.11</v>
@@ -6035,7 +6035,7 @@
         <v>2.9</v>
       </c>
       <c r="U35">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="V35">
         <v>1.4</v>
@@ -6071,7 +6071,7 @@
         <v>1.8</v>
       </c>
       <c r="AG35">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.73</v>
+        <v>2.96</v>
       </c>
       <c r="O36">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="P36">
         <v>2.21</v>
@@ -6195,7 +6195,7 @@
         <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="U36">
         <v>2.75</v>
@@ -6234,7 +6234,7 @@
         <v>1.67</v>
       </c>
       <c r="AG36">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6340,28 +6340,28 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O37">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="P37">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="Q37">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="R37">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="S37">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U37">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="V37">
         <v>1.68</v>
@@ -6373,25 +6373,25 @@
         <v>1</v>
       </c>
       <c r="Y37">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z37">
-        <v>5.82</v>
+        <v>6.14</v>
       </c>
       <c r="AA37">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AB37">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC37">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AD37">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AE37">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF37">
         <v>1.75</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O38">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="P38">
         <v>4.6</v>
@@ -6515,13 +6515,13 @@
         <v>2.01</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S38">
         <v>1.3</v>
       </c>
       <c r="T38">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="U38">
         <v>2.4</v>
@@ -6530,7 +6530,7 @@
         <v>1.5</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X38">
         <v>1.02</v>
@@ -6539,10 +6539,10 @@
         <v>1.19</v>
       </c>
       <c r="Z38">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA38">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AB38">
         <v>2.1</v>
@@ -6554,13 +6554,13 @@
         <v>1.43</v>
       </c>
       <c r="AE38">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF38">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6684,31 +6684,31 @@
         <v>1.25</v>
       </c>
       <c r="T39">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U39">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V39">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W39">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z39">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA39">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB39">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC39">
         <v>2.29</v>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="O40">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P40">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q40">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="R40">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="S40">
         <v>1.2</v>
@@ -6850,10 +6850,10 @@
         <v>4.1</v>
       </c>
       <c r="U40">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="V40">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="W40">
         <v>1.18</v>
@@ -6868,16 +6868,16 @@
         <v>6.5</v>
       </c>
       <c r="AA40">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB40">
         <v>2.75</v>
       </c>
       <c r="AC40">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD40">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE40">
         <v>1.32</v>
@@ -6886,7 +6886,7 @@
         <v>1.53</v>
       </c>
       <c r="AG40">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.13</v>
       </c>
       <c r="AK40">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6995,7 +6995,7 @@
         <v>1.75</v>
       </c>
       <c r="O41">
-        <v>3.83</v>
+        <v>3.77</v>
       </c>
       <c r="P41">
         <v>4.37</v>
@@ -7004,7 +7004,7 @@
         <v>2.2</v>
       </c>
       <c r="R41">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S41">
         <v>1.25</v>
@@ -7034,7 +7034,7 @@
         <v>1.53</v>
       </c>
       <c r="AB41">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="AC41">
         <v>2.38</v>
@@ -7043,13 +7043,13 @@
         <v>1.57</v>
       </c>
       <c r="AE41">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF41">
         <v>1.53</v>
       </c>
       <c r="AG41">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7155,31 +7155,31 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="O42">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="P42">
-        <v>5.63</v>
+        <v>5.5</v>
       </c>
       <c r="Q42">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R42">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="S42">
         <v>1.11</v>
       </c>
       <c r="T42">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="U42">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="V42">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="W42">
         <v>1.33</v>
@@ -7194,19 +7194,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AA42">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AB42">
         <v>4.2</v>
       </c>
       <c r="AC42">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AD42">
         <v>2.45</v>
       </c>
       <c r="AE42">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AF42">
         <v>1.3</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK42">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7321,25 +7321,25 @@
         <v>1.98</v>
       </c>
       <c r="O43">
-        <v>4.21</v>
+        <v>4.17</v>
       </c>
       <c r="P43">
-        <v>3.53</v>
+        <v>3.48</v>
       </c>
       <c r="Q43">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="R43">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="S43">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T43">
         <v>4.5</v>
       </c>
       <c r="U43">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V43">
         <v>1.75</v>
@@ -7354,28 +7354,28 @@
         <v>1.1</v>
       </c>
       <c r="Z43">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA43">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AB43">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AC43">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="AD43">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AE43">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF43">
         <v>1.4</v>
       </c>
       <c r="AG43">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -8788,19 +8788,19 @@
         <v>2</v>
       </c>
       <c r="O52">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P52">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="Q52">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="R52">
         <v>2.16</v>
       </c>
       <c r="S52">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T52">
         <v>3.2</v>
@@ -8815,13 +8815,13 @@
         <v>1.11</v>
       </c>
       <c r="X52">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA52">
         <v>1.84</v>
@@ -8830,10 +8830,10 @@
         <v>2</v>
       </c>
       <c r="AC52">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD52">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE52">
         <v>1.13</v>
@@ -8842,7 +8842,7 @@
         <v>1.67</v>
       </c>
       <c r="AG52">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8951,10 +8951,10 @@
         <v>2.52</v>
       </c>
       <c r="O53">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="P53">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Q53">
         <v>2.99</v>
@@ -9002,10 +9002,10 @@
         <v>1.17</v>
       </c>
       <c r="AF53">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG53">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK53">
         <v>1.4</v>
@@ -9111,16 +9111,16 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="O54">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P54">
-        <v>2.43</v>
+        <v>2.14</v>
       </c>
       <c r="Q54">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="R54">
         <v>2.3</v>
@@ -9153,7 +9153,7 @@
         <v>1.6</v>
       </c>
       <c r="AB54">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AC54">
         <v>2.45</v>
@@ -9184,7 +9184,7 @@
         <v>1.25</v>
       </c>
       <c r="AK54">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,10 +9274,10 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="O55">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="P55">
         <v>2.95</v>
@@ -9289,10 +9289,10 @@
         <v>2.38</v>
       </c>
       <c r="S55">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T55">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="U55">
         <v>2.15</v>
@@ -9313,10 +9313,10 @@
         <v>6</v>
       </c>
       <c r="AA55">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AB55">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="AC55">
         <v>2.15</v>
@@ -9328,10 +9328,10 @@
         <v>1.29</v>
       </c>
       <c r="AF55">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG55">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9440,16 +9440,16 @@
         <v>1.73</v>
       </c>
       <c r="O56">
+        <v>4.11</v>
+      </c>
+      <c r="P56">
         <v>3.75</v>
       </c>
-      <c r="P56">
-        <v>3.7</v>
-      </c>
       <c r="Q56">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="R56">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S56">
         <v>1.25</v>
@@ -9458,43 +9458,43 @@
         <v>3.6</v>
       </c>
       <c r="U56">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="V56">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W56">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X56">
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z56">
-        <v>5.32</v>
+        <v>4.91</v>
       </c>
       <c r="AA56">
+        <v>1.55</v>
+      </c>
+      <c r="AB56">
+        <v>2.35</v>
+      </c>
+      <c r="AC56">
+        <v>2.38</v>
+      </c>
+      <c r="AD56">
+        <v>1.57</v>
+      </c>
+      <c r="AE56">
+        <v>1.22</v>
+      </c>
+      <c r="AF56">
         <v>1.5</v>
       </c>
-      <c r="AB56">
-        <v>2.38</v>
-      </c>
-      <c r="AC56">
-        <v>2.15</v>
-      </c>
-      <c r="AD56">
-        <v>1.67</v>
-      </c>
-      <c r="AE56">
-        <v>1.29</v>
-      </c>
-      <c r="AF56">
-        <v>1.47</v>
-      </c>
       <c r="AG56">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9600,34 +9600,34 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="O57">
-        <v>3.9</v>
+        <v>4.22</v>
       </c>
       <c r="P57">
-        <v>3.7</v>
+        <v>3.83</v>
       </c>
       <c r="Q57">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="R57">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="S57">
         <v>1.2</v>
       </c>
       <c r="T57">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U57">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="V57">
         <v>1.73</v>
       </c>
       <c r="W57">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X57">
         <v>0</v>
@@ -9642,22 +9642,22 @@
         <v>1.36</v>
       </c>
       <c r="AB57">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AC57">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AD57">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AE57">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF57">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AG57">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,28 +9763,28 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="O58">
-        <v>4.65</v>
+        <v>5.05</v>
       </c>
       <c r="P58">
         <v>4.5</v>
       </c>
       <c r="Q58">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R58">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="S58">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T58">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="U58">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V58">
         <v>1.95</v>
@@ -9799,28 +9799,28 @@
         <v>1.06</v>
       </c>
       <c r="Z58">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AA58">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AB58">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AC58">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AD58">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AE58">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AF58">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG58">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK58">
         <v>2.3</v>
@@ -9932,10 +9932,10 @@
         <v>5.42</v>
       </c>
       <c r="P59">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="Q59">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R59">
         <v>2.61</v>
@@ -9965,10 +9965,10 @@
         <v>8</v>
       </c>
       <c r="AA59">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB59">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AC59">
         <v>1.84</v>
@@ -9999,7 +9999,7 @@
         <v>1.11</v>
       </c>
       <c r="AK59">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,34 +10089,34 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O60">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="P60">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="Q60">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="R60">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="S60">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T60">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="U60">
         <v>2.3</v>
       </c>
       <c r="V60">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W60">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X60">
         <v>1.01</v>
@@ -10128,25 +10128,25 @@
         <v>5</v>
       </c>
       <c r="AA60">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AB60">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC60">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AD60">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE60">
         <v>1.2</v>
       </c>
       <c r="AF60">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG60">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10252,31 +10252,31 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="O61">
         <v>5.2</v>
       </c>
       <c r="P61">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="Q61">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="R61">
         <v>2.75</v>
       </c>
       <c r="S61">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T61">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="U61">
         <v>1.92</v>
       </c>
       <c r="V61">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="W61">
         <v>1.22</v>
@@ -10285,10 +10285,10 @@
         <v>0</v>
       </c>
       <c r="Y61">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z61">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA61">
         <v>1.33</v>
@@ -10303,7 +10303,7 @@
         <v>1.9</v>
       </c>
       <c r="AE61">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF61">
         <v>1.47</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK61">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10418,7 +10418,7 @@
         <v>1.84</v>
       </c>
       <c r="O62">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P62">
         <v>4</v>
@@ -10427,22 +10427,22 @@
         <v>2.25</v>
       </c>
       <c r="R62">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="S62">
         <v>1.25</v>
       </c>
       <c r="T62">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U62">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V62">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W62">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X62">
         <v>1.01</v>
@@ -10454,10 +10454,10 @@
         <v>4.5</v>
       </c>
       <c r="AA62">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AB62">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC62">
         <v>2.63</v>
@@ -10466,7 +10466,7 @@
         <v>1.47</v>
       </c>
       <c r="AE62">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF62">
         <v>1.6</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
         </is>
       </c>
       <c r="N3">
+        <v>2.5</v>
+      </c>
+      <c r="O3">
+        <v>3</v>
+      </c>
+      <c r="P3">
         <v>2.6</v>
       </c>
-      <c r="O3">
-        <v>3.1</v>
-      </c>
-      <c r="P3">
-        <v>2.5</v>
-      </c>
       <c r="Q3">
-        <v>3.25</v>
+        <v>3.07</v>
       </c>
       <c r="R3">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="S3">
         <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U3">
         <v>2.9</v>
@@ -825,16 +825,16 @@
         <v>1.36</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y3">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z3">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA3">
         <v>2.1</v>
@@ -843,19 +843,19 @@
         <v>1.7</v>
       </c>
       <c r="AC3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD3">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE3">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG3">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK3">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,22 +961,22 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="O4">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="P4">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="Q4">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R4">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T4">
         <v>3.1</v>
@@ -997,13 +997,13 @@
         <v>1.18</v>
       </c>
       <c r="Z4">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA4">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AB4">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC4">
         <v>2.5</v>
@@ -1012,10 +1012,10 @@
         <v>1.25</v>
       </c>
       <c r="AE4">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AG4">
         <v>2.05</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK4">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="O5">
-        <v>3.77</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="Q5">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="R5">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="S5">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T5">
         <v>3.1</v>
       </c>
       <c r="U5">
-        <v>2.57</v>
+        <v>2.68</v>
       </c>
       <c r="V5">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
         <v>1.07</v>
@@ -1157,31 +1157,31 @@
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z5">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AA5">
         <v>1.75</v>
       </c>
       <c r="AB5">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC5">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD5">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE5">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK5">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="O6">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="Q6">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="R6">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S6">
         <v>1.22</v>
@@ -1326,7 +1326,7 @@
         <v>4.54</v>
       </c>
       <c r="AA6">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB6">
         <v>2.1</v>
@@ -1338,10 +1338,10 @@
         <v>1.5</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF6">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG6">
         <v>2.3</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AK6">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O7">
         <v>3.4</v>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="O8">
         <v>3.4</v>
@@ -1622,55 +1622,55 @@
         <v>2.69</v>
       </c>
       <c r="Q8">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R8">
-        <v>2.39</v>
+        <v>2.22</v>
       </c>
       <c r="S8">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="U8">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V8">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
+        <v>1.2</v>
+      </c>
+      <c r="Z8">
+        <v>4.5</v>
+      </c>
+      <c r="AA8">
+        <v>1.72</v>
+      </c>
+      <c r="AB8">
+        <v>2.07</v>
+      </c>
+      <c r="AC8">
+        <v>2.52</v>
+      </c>
+      <c r="AD8">
+        <v>1.4</v>
+      </c>
+      <c r="AE8">
         <v>1.17</v>
       </c>
-      <c r="Z8">
-        <v>5</v>
-      </c>
-      <c r="AA8">
-        <v>1.58</v>
-      </c>
-      <c r="AB8">
-        <v>2.25</v>
-      </c>
-      <c r="AC8">
-        <v>2.55</v>
-      </c>
-      <c r="AD8">
-        <v>1.52</v>
-      </c>
-      <c r="AE8">
-        <v>1.2</v>
-      </c>
       <c r="AF8">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG8">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>4.33</v>
       </c>
       <c r="Q10">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="R10">
         <v>2.38</v>
@@ -1978,7 +1978,7 @@
         <v>5.5</v>
       </c>
       <c r="AA10">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AB10">
         <v>2.33</v>
@@ -1993,10 +1993,10 @@
         <v>1.22</v>
       </c>
       <c r="AF10">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG10">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="O11">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="P11">
-        <v>4.16</v>
+        <v>3.75</v>
       </c>
       <c r="Q11">
+        <v>2.67</v>
+      </c>
+      <c r="R11">
+        <v>1.85</v>
+      </c>
+      <c r="S11">
+        <v>1.58</v>
+      </c>
+      <c r="T11">
+        <v>2.4</v>
+      </c>
+      <c r="U11">
+        <v>3.4</v>
+      </c>
+      <c r="V11">
+        <v>1.22</v>
+      </c>
+      <c r="W11">
+        <v>1.02</v>
+      </c>
+      <c r="X11">
+        <v>1.12</v>
+      </c>
+      <c r="Y11">
+        <v>1.5</v>
+      </c>
+      <c r="Z11">
         <v>2.55</v>
       </c>
-      <c r="R11">
-        <v>2</v>
-      </c>
-      <c r="S11">
-        <v>1.53</v>
-      </c>
-      <c r="T11">
+      <c r="AA11">
         <v>2.5</v>
       </c>
-      <c r="U11">
-        <v>3.25</v>
-      </c>
-      <c r="V11">
-        <v>1.3</v>
-      </c>
-      <c r="W11">
-        <v>1.01</v>
-      </c>
-      <c r="X11">
-        <v>1.07</v>
-      </c>
-      <c r="Y11">
-        <v>1.44</v>
-      </c>
-      <c r="Z11">
-        <v>2.7</v>
-      </c>
-      <c r="AA11">
-        <v>2.35</v>
-      </c>
       <c r="AB11">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AC11">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AD11">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AG11">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P12">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="Q12">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R12">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T12">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="U12">
-        <v>2.42</v>
+        <v>2.02</v>
       </c>
       <c r="V12">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z12">
         <v>4.5</v>
       </c>
       <c r="AA12">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="AB12">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AC12">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AD12">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AE12">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG12">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AK12">
         <v>1.57</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="O16">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="Q16">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="R16">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S16">
         <v>1.3</v>
@@ -2956,10 +2956,10 @@
         <v>4.46</v>
       </c>
       <c r="AA16">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB16">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AC16">
         <v>2.85</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK16">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3083,22 +3083,22 @@
         <v>4.4</v>
       </c>
       <c r="O17">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P17">
         <v>1.63</v>
       </c>
       <c r="Q17">
-        <v>4.16</v>
+        <v>4.12</v>
       </c>
       <c r="R17">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="S17">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U17">
         <v>2.2</v>
@@ -3116,28 +3116,28 @@
         <v>1.13</v>
       </c>
       <c r="Z17">
-        <v>5.32</v>
+        <v>5</v>
       </c>
       <c r="AA17">
         <v>1.53</v>
       </c>
       <c r="AB17">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AC17">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="AD17">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE17">
         <v>1.2</v>
       </c>
       <c r="AF17">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG17">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK17">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="O18">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
       <c r="P18">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="Q18">
-        <v>3.26</v>
+        <v>3.58</v>
       </c>
       <c r="R18">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S18">
         <v>1.25</v>
@@ -3270,7 +3270,7 @@
         <v>1.57</v>
       </c>
       <c r="W18">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3282,25 +3282,25 @@
         <v>4.45</v>
       </c>
       <c r="AA18">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB18">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC18">
         <v>2.38</v>
       </c>
       <c r="AD18">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AE18">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF18">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG18">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK18">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,25 +3406,25 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O19">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q19">
-        <v>2.82</v>
+        <v>3.14</v>
       </c>
       <c r="R19">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S19">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T19">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U19">
         <v>2.62</v>
@@ -3445,10 +3445,10 @@
         <v>3.6</v>
       </c>
       <c r="AA19">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AB19">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC19">
         <v>3.2</v>
@@ -3463,7 +3463,7 @@
         <v>1.67</v>
       </c>
       <c r="AG19">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK19">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="P20">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Q20">
-        <v>3.77</v>
+        <v>4.29</v>
       </c>
       <c r="R20">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="S20">
         <v>1.22</v>
@@ -3590,10 +3590,10 @@
         <v>3.8</v>
       </c>
       <c r="U20">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="V20">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W20">
         <v>1.15</v>
@@ -3602,31 +3602,31 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z20">
-        <v>5.91</v>
+        <v>6.02</v>
       </c>
       <c r="AA20">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AB20">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AC20">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AD20">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AE20">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF20">
         <v>1.5</v>
       </c>
       <c r="AG20">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK20">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3738,40 +3738,40 @@
         <v>3.6</v>
       </c>
       <c r="P21">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q21">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="R21">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="S21">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T21">
-        <v>2.61</v>
+        <v>2.51</v>
       </c>
       <c r="U21">
-        <v>3.07</v>
+        <v>2.87</v>
       </c>
       <c r="V21">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W21">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
         <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z21">
         <v>2.9</v>
       </c>
       <c r="AA21">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AB21">
         <v>1.66</v>
@@ -3780,7 +3780,7 @@
         <v>3.58</v>
       </c>
       <c r="AD21">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE21">
         <v>1.04</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>3.7</v>
       </c>
       <c r="AA22">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB22">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC22">
         <v>2.85</v>
@@ -3949,7 +3949,7 @@
         <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG22">
         <v>2.15</v>
@@ -4058,22 +4058,22 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O23">
         <v>3.2</v>
       </c>
       <c r="P23">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q23">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="R23">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="S23">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T23">
         <v>2.88</v>
@@ -4085,19 +4085,19 @@
         <v>1.37</v>
       </c>
       <c r="W23">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
         <v>1.35</v>
       </c>
       <c r="Z23">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA23">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AB23">
         <v>1.75</v>
@@ -4109,7 +4109,7 @@
         <v>1.26</v>
       </c>
       <c r="AE23">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF23">
         <v>1.75</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4227,10 +4227,10 @@
         <v>3.2</v>
       </c>
       <c r="P24">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="Q24">
-        <v>3.21</v>
+        <v>3.32</v>
       </c>
       <c r="R24">
         <v>2.07</v>
@@ -4242,10 +4242,10 @@
         <v>2.9</v>
       </c>
       <c r="U24">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="V24">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
         <v>1.08</v>
@@ -4254,19 +4254,19 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z24">
         <v>3.5</v>
       </c>
       <c r="AA24">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AB24">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AC24">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AD24">
         <v>1.32</v>
@@ -4278,7 +4278,7 @@
         <v>1.67</v>
       </c>
       <c r="AG24">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O26">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="P26">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="Q26">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="R26">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="S26">
         <v>1.33</v>
@@ -4577,7 +4577,7 @@
         <v>1.06</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
         <v>1.2</v>
@@ -4586,7 +4586,7 @@
         <v>3.5</v>
       </c>
       <c r="AA26">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AB26">
         <v>1.98</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK26">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4722,16 +4722,16 @@
         <v>3.14</v>
       </c>
       <c r="R27">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="S27">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T27">
         <v>3.2</v>
       </c>
       <c r="U27">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="V27">
         <v>1.44</v>
@@ -4749,7 +4749,7 @@
         <v>3.42</v>
       </c>
       <c r="AA27">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB27">
         <v>1.9</v>
@@ -4764,10 +4764,10 @@
         <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG27">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK27">
         <v>1.44</v>
@@ -4876,16 +4876,16 @@
         <v>1.97</v>
       </c>
       <c r="O28">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P28">
-        <v>3.3</v>
+        <v>3.07</v>
       </c>
       <c r="Q28">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="R28">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="S28">
         <v>1.29</v>
@@ -4894,7 +4894,7 @@
         <v>3.5</v>
       </c>
       <c r="U28">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="V28">
         <v>1.57</v>
@@ -4912,10 +4912,10 @@
         <v>4.5</v>
       </c>
       <c r="AA28">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AB28">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AC28">
         <v>2.33</v>
@@ -4924,7 +4924,7 @@
         <v>1.5</v>
       </c>
       <c r="AE28">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF28">
         <v>1.5</v>
@@ -4946,7 +4946,7 @@
         <v>1.2</v>
       </c>
       <c r="AK28">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="O29">
         <v>6.5</v>
       </c>
       <c r="P29">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Q29">
         <v>1.53</v>
       </c>
       <c r="R29">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="S29">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T29">
-        <v>3.92</v>
+        <v>4.8</v>
       </c>
       <c r="U29">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V29">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="W29">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z29">
         <v>6.88</v>
       </c>
       <c r="AA29">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB29">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="AC29">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AD29">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="AE29">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AF29">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AG29">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AK29">
-        <v>3.84</v>
+        <v>3.94</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5202,16 +5202,16 @@
         <v>3</v>
       </c>
       <c r="O30">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
         <v>2.2</v>
       </c>
       <c r="Q30">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="R30">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S30">
         <v>1.3</v>
@@ -5235,7 +5235,7 @@
         <v>1.23</v>
       </c>
       <c r="Z30">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA30">
         <v>1.72</v>
@@ -5250,7 +5250,7 @@
         <v>1.4</v>
       </c>
       <c r="AE30">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF30">
         <v>1.57</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5371,7 +5371,7 @@
         <v>1.6</v>
       </c>
       <c r="Q31">
-        <v>5.5</v>
+        <v>5.32</v>
       </c>
       <c r="R31">
         <v>2.04</v>
@@ -5380,7 +5380,7 @@
         <v>1.5</v>
       </c>
       <c r="T31">
-        <v>2.37</v>
+        <v>2.53</v>
       </c>
       <c r="U31">
         <v>3.31</v>
@@ -5395,25 +5395,25 @@
         <v>1.07</v>
       </c>
       <c r="Y31">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z31">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="AA31">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AB31">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC31">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AD31">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE31">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF31">
         <v>2.15</v>
@@ -5528,28 +5528,28 @@
         <v>4.3</v>
       </c>
       <c r="O32">
-        <v>4.05</v>
+        <v>3.96</v>
       </c>
       <c r="P32">
         <v>1.63</v>
       </c>
       <c r="Q32">
-        <v>4.85</v>
+        <v>4.88</v>
       </c>
       <c r="R32">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="S32">
         <v>1.3</v>
       </c>
       <c r="T32">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="U32">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="V32">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W32">
         <v>1.12</v>
@@ -5558,16 +5558,16 @@
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
         <v>4.33</v>
       </c>
       <c r="AA32">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB32">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AC32">
         <v>2.7</v>
@@ -5579,10 +5579,10 @@
         <v>1.17</v>
       </c>
       <c r="AF32">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG32">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5691,16 +5691,16 @@
         <v>1.5</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P33">
         <v>5.5</v>
       </c>
       <c r="Q33">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R33">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S33">
         <v>1.42</v>
@@ -5721,19 +5721,19 @@
         <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z33">
         <v>3.04</v>
       </c>
       <c r="AA33">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB33">
         <v>1.75</v>
       </c>
       <c r="AC33">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AD33">
         <v>1.22</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK33">
-        <v>2.45</v>
+        <v>2.24</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,25 +5851,25 @@
         </is>
       </c>
       <c r="N34">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P34">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="Q34">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="R34">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="S34">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T34">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="U34">
         <v>2.25</v>
@@ -5878,7 +5878,7 @@
         <v>1.55</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X34">
         <v>1.01</v>
@@ -5887,19 +5887,19 @@
         <v>1.17</v>
       </c>
       <c r="Z34">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="AA34">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB34">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AC34">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AD34">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AE34">
         <v>1.2</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AK34">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O35">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="P35">
-        <v>3.58</v>
+        <v>4.18</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -6056,10 +6056,10 @@
         <v>1.92</v>
       </c>
       <c r="AB35">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC35">
-        <v>3.47</v>
+        <v>3.49</v>
       </c>
       <c r="AD35">
         <v>1.32</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK35">
         <v>1.9</v>
@@ -6186,7 +6186,7 @@
         <v>2.21</v>
       </c>
       <c r="Q36">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R36">
         <v>2.09</v>
@@ -6195,13 +6195,13 @@
         <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="U36">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V36">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W36">
         <v>1.08</v>
@@ -6250,7 +6250,7 @@
         <v>1.29</v>
       </c>
       <c r="AK36">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6343,10 +6343,10 @@
         <v>1.3</v>
       </c>
       <c r="O37">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="P37">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Q37">
         <v>1.63</v>
@@ -6361,7 +6361,7 @@
         <v>4</v>
       </c>
       <c r="U37">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V37">
         <v>1.68</v>
@@ -6373,28 +6373,28 @@
         <v>1</v>
       </c>
       <c r="Y37">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z37">
-        <v>6.14</v>
+        <v>6.47</v>
       </c>
       <c r="AA37">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB37">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AC37">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AD37">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AE37">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AF37">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG37">
         <v>2</v>
@@ -6413,7 +6413,7 @@
         <v>1.13</v>
       </c>
       <c r="AK37">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6512,7 +6512,7 @@
         <v>4.6</v>
       </c>
       <c r="Q38">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="R38">
         <v>2.22</v>
@@ -6521,7 +6521,7 @@
         <v>1.3</v>
       </c>
       <c r="T38">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="U38">
         <v>2.4</v>
@@ -6530,7 +6530,7 @@
         <v>1.5</v>
       </c>
       <c r="W38">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
         <v>1.02</v>
@@ -6542,10 +6542,10 @@
         <v>3.9</v>
       </c>
       <c r="AA38">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AB38">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AC38">
         <v>2.6</v>
@@ -6554,7 +6554,7 @@
         <v>1.43</v>
       </c>
       <c r="AE38">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF38">
         <v>1.75</v>
@@ -6576,7 +6576,7 @@
         <v>1.17</v>
       </c>
       <c r="AK38">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O39">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="P39">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="Q39">
         <v>2.38</v>
@@ -6684,13 +6684,13 @@
         <v>1.25</v>
       </c>
       <c r="T39">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U39">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V39">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W39">
         <v>1.17</v>
@@ -6705,19 +6705,19 @@
         <v>6</v>
       </c>
       <c r="AA39">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AB39">
         <v>2.63</v>
       </c>
       <c r="AC39">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="AD39">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AE39">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF39">
         <v>1.44</v>
@@ -6739,7 +6739,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,22 +6829,22 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O40">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P40">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="Q40">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="R40">
-        <v>2.8</v>
+        <v>2.51</v>
       </c>
       <c r="S40">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T40">
         <v>4.1</v>
@@ -6871,19 +6871,19 @@
         <v>1.4</v>
       </c>
       <c r="AB40">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="AC40">
         <v>2</v>
       </c>
       <c r="AD40">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE40">
         <v>1.32</v>
       </c>
       <c r="AF40">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG40">
         <v>2.55</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O41">
-        <v>3.77</v>
+        <v>3.85</v>
       </c>
       <c r="P41">
-        <v>4.37</v>
+        <v>4.28</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -7013,10 +7013,10 @@
         <v>3.5</v>
       </c>
       <c r="U41">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="V41">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W41">
         <v>1.15</v>
@@ -7034,7 +7034,7 @@
         <v>1.53</v>
       </c>
       <c r="AB41">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="AC41">
         <v>2.38</v>
@@ -7046,7 +7046,7 @@
         <v>1.24</v>
       </c>
       <c r="AF41">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG41">
         <v>2.3</v>
@@ -7155,19 +7155,19 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="O42">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P42">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q42">
         <v>1.83</v>
       </c>
       <c r="R42">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="S42">
         <v>1.11</v>
@@ -7176,13 +7176,13 @@
         <v>5.4</v>
       </c>
       <c r="U42">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V42">
         <v>2.09</v>
       </c>
       <c r="W42">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X42">
         <v>0</v>
@@ -7194,10 +7194,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AA42">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AB42">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AC42">
         <v>1.63</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="O43">
         <v>4.17</v>
       </c>
       <c r="P43">
-        <v>3.48</v>
+        <v>3.35</v>
       </c>
       <c r="Q43">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="R43">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="S43">
         <v>1.18</v>
@@ -7339,7 +7339,7 @@
         <v>4.5</v>
       </c>
       <c r="U43">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V43">
         <v>1.75</v>
@@ -7372,7 +7372,7 @@
         <v>1.33</v>
       </c>
       <c r="AF43">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG43">
         <v>2.84</v>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N47">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N49">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N50">
@@ -8785,34 +8785,34 @@
         </is>
       </c>
       <c r="N52">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O52">
         <v>3.4</v>
       </c>
       <c r="P52">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="Q52">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="R52">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="S52">
         <v>1.35</v>
       </c>
       <c r="T52">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U52">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="V52">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W52">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
         <v>1.02</v>
@@ -8824,16 +8824,16 @@
         <v>4.1</v>
       </c>
       <c r="AA52">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB52">
         <v>2</v>
       </c>
       <c r="AC52">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AD52">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE52">
         <v>1.13</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK52">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,16 +8948,16 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="O53">
         <v>3.6</v>
       </c>
       <c r="P53">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="Q53">
-        <v>2.99</v>
+        <v>3.09</v>
       </c>
       <c r="R53">
         <v>2.3</v>
@@ -8972,7 +8972,7 @@
         <v>2.38</v>
       </c>
       <c r="V53">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W53">
         <v>1.08</v>
@@ -8999,13 +8999,13 @@
         <v>1.44</v>
       </c>
       <c r="AE53">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF53">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG53">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9111,16 +9111,16 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="O54">
-        <v>3.4</v>
+        <v>3.83</v>
       </c>
       <c r="P54">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="Q54">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R54">
         <v>2.3</v>
@@ -9129,7 +9129,7 @@
         <v>1.25</v>
       </c>
       <c r="T54">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U54">
         <v>2.19</v>
@@ -9150,7 +9150,7 @@
         <v>5</v>
       </c>
       <c r="AA54">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB54">
         <v>2.39</v>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="O55">
         <v>3.86</v>
@@ -9283,7 +9283,7 @@
         <v>2.95</v>
       </c>
       <c r="Q55">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R55">
         <v>2.38</v>
@@ -9301,7 +9301,7 @@
         <v>1.64</v>
       </c>
       <c r="W55">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X55">
         <v>1.01</v>
@@ -9319,19 +9319,19 @@
         <v>2.39</v>
       </c>
       <c r="AC55">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AD55">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AE55">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF55">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG55">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK55">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9440,7 +9440,7 @@
         <v>1.73</v>
       </c>
       <c r="O56">
-        <v>4.11</v>
+        <v>3.73</v>
       </c>
       <c r="P56">
         <v>3.75</v>
@@ -9461,7 +9461,7 @@
         <v>2.19</v>
       </c>
       <c r="V56">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W56">
         <v>1.13</v>
@@ -9473,22 +9473,22 @@
         <v>1.19</v>
       </c>
       <c r="Z56">
-        <v>4.91</v>
+        <v>4.93</v>
       </c>
       <c r="AA56">
         <v>1.55</v>
       </c>
       <c r="AB56">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AC56">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AD56">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE56">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF56">
         <v>1.5</v>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK56">
         <v>2</v>
@@ -9603,10 +9603,10 @@
         <v>1.88</v>
       </c>
       <c r="O57">
-        <v>4.22</v>
+        <v>3.95</v>
       </c>
       <c r="P57">
-        <v>3.83</v>
+        <v>3.3</v>
       </c>
       <c r="Q57">
         <v>2.38</v>
@@ -9615,13 +9615,13 @@
         <v>2.66</v>
       </c>
       <c r="S57">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T57">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U57">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V57">
         <v>1.73</v>
@@ -9654,10 +9654,10 @@
         <v>1.27</v>
       </c>
       <c r="AF57">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AG57">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK57">
         <v>1.83</v>
@@ -9769,13 +9769,13 @@
         <v>5.05</v>
       </c>
       <c r="P58">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q58">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R58">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="S58">
         <v>1.13</v>
@@ -9802,7 +9802,7 @@
         <v>9</v>
       </c>
       <c r="AA58">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AB58">
         <v>4</v>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK58">
         <v>2.3</v>
@@ -9926,28 +9926,28 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="O59">
-        <v>5.42</v>
+        <v>5.1</v>
       </c>
       <c r="P59">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="Q59">
         <v>1.8</v>
       </c>
       <c r="R59">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="S59">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T59">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U59">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="V59">
         <v>1.85</v>
@@ -9971,13 +9971,13 @@
         <v>3.25</v>
       </c>
       <c r="AC59">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AD59">
         <v>1.98</v>
       </c>
       <c r="AE59">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF59">
         <v>1.5</v>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK59">
         <v>2.8</v>
@@ -10089,16 +10089,16 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O60">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="P60">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="Q60">
-        <v>2.79</v>
+        <v>2.61</v>
       </c>
       <c r="R60">
         <v>2.27</v>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AK60">
         <v>1.67</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="O61">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="P61">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="Q61">
         <v>1.73</v>
@@ -10273,7 +10273,7 @@
         <v>4.33</v>
       </c>
       <c r="U61">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="V61">
         <v>1.83</v>
@@ -10294,7 +10294,7 @@
         <v>1.33</v>
       </c>
       <c r="AB61">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AC61">
         <v>1.87</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK61">
         <v>2.88</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="O62">
         <v>3.8</v>
@@ -10424,7 +10424,7 @@
         <v>4</v>
       </c>
       <c r="Q62">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="R62">
         <v>2.5</v>
@@ -10457,7 +10457,7 @@
         <v>1.67</v>
       </c>
       <c r="AB62">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AC62">
         <v>2.63</v>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK62">
         <v>1.85</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -775,26 +775,26 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,12 +859,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42"]</t>
         </is>
       </c>
       <c r="AJ3">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,26 +938,26 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "26"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,10 +1101,10 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1113,14 +1113,14 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+5"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,26 +1264,26 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47", "74"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30", "38", "67"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1605,11 +1605,11 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["83"]</t>
         </is>
       </c>
       <c r="AJ8">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,13 +1753,13 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1939,16 +1939,16 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O10">
         <v>4</v>
       </c>
       <c r="P10">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="Q10">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R10">
         <v>2.38</v>
@@ -1960,10 +1960,10 @@
         <v>3.6</v>
       </c>
       <c r="U10">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V10">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W10">
         <v>1.14</v>
@@ -1981,16 +1981,16 @@
         <v>1.53</v>
       </c>
       <c r="AB10">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AC10">
         <v>2.23</v>
       </c>
       <c r="AD10">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE10">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF10">
         <v>1.55</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="O12">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
         <v>2.87</v>
@@ -2280,19 +2280,19 @@
         <v>2.1</v>
       </c>
       <c r="S12">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T12">
         <v>2.63</v>
       </c>
       <c r="U12">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="V12">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X12">
         <v>1.01</v>
@@ -2301,7 +2301,7 @@
         <v>1.14</v>
       </c>
       <c r="Z12">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA12">
         <v>1.51</v>
@@ -2319,10 +2319,10 @@
         <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AG12">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="N13">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="P13">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Q13">
-        <v>6.38</v>
+        <v>5.9</v>
       </c>
       <c r="R13">
         <v>2.8</v>
@@ -2446,37 +2446,37 @@
         <v>1.2</v>
       </c>
       <c r="T13">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="U13">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="V13">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="W13">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X13">
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z13">
         <v>6.38</v>
       </c>
       <c r="AA13">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AB13">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AC13">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AD13">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AE13">
         <v>1.38</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.13</v>
+        <v>3</v>
       </c>
       <c r="AK13">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,58 +2591,58 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="O14">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="P14">
+        <v>2.7</v>
+      </c>
+      <c r="Q14">
+        <v>3.2</v>
+      </c>
+      <c r="R14">
+        <v>1.99</v>
+      </c>
+      <c r="S14">
+        <v>1.43</v>
+      </c>
+      <c r="T14">
         <v>2.62</v>
-      </c>
-      <c r="Q14">
-        <v>3.25</v>
-      </c>
-      <c r="R14">
-        <v>2.01</v>
-      </c>
-      <c r="S14">
-        <v>1.47</v>
-      </c>
-      <c r="T14">
-        <v>2.47</v>
       </c>
       <c r="U14">
         <v>2.9</v>
       </c>
       <c r="V14">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W14">
+        <v>1.04</v>
+      </c>
+      <c r="X14">
         <v>1.03</v>
       </c>
-      <c r="X14">
+      <c r="Y14">
+        <v>1.32</v>
+      </c>
+      <c r="Z14">
+        <v>3.6</v>
+      </c>
+      <c r="AA14">
+        <v>2.14</v>
+      </c>
+      <c r="AB14">
+        <v>1.77</v>
+      </c>
+      <c r="AC14">
+        <v>3.61</v>
+      </c>
+      <c r="AD14">
+        <v>1.32</v>
+      </c>
+      <c r="AE14">
         <v>1.06</v>
-      </c>
-      <c r="Y14">
-        <v>1.33</v>
-      </c>
-      <c r="Z14">
-        <v>3.52</v>
-      </c>
-      <c r="AA14">
-        <v>2.09</v>
-      </c>
-      <c r="AB14">
-        <v>1.79</v>
-      </c>
-      <c r="AC14">
-        <v>3.8</v>
-      </c>
-      <c r="AD14">
-        <v>1.25</v>
-      </c>
-      <c r="AE14">
-        <v>1.07</v>
       </c>
       <c r="AF14">
         <v>1.75</v>
@@ -2757,13 +2757,13 @@
         <v>1.7</v>
       </c>
       <c r="O15">
-        <v>3.77</v>
+        <v>3.67</v>
       </c>
       <c r="P15">
-        <v>4.75</v>
+        <v>5.1</v>
       </c>
       <c r="Q15">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="R15">
         <v>2.15</v>
@@ -2778,7 +2778,7 @@
         <v>3.08</v>
       </c>
       <c r="V15">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W15">
         <v>1.05</v>
@@ -2793,7 +2793,7 @@
         <v>2.91</v>
       </c>
       <c r="AA15">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB15">
         <v>1.72</v>
@@ -2808,10 +2808,10 @@
         <v>1.04</v>
       </c>
       <c r="AF15">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AG15">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.19</v>
       </c>
       <c r="AK15">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="O16">
         <v>3.3</v>
@@ -2938,10 +2938,10 @@
         <v>3.25</v>
       </c>
       <c r="U16">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="V16">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W16">
         <v>1.08</v>
@@ -2953,22 +2953,22 @@
         <v>1.2</v>
       </c>
       <c r="Z16">
-        <v>4.46</v>
+        <v>4.88</v>
       </c>
       <c r="AA16">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AB16">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC16">
-        <v>2.85</v>
+        <v>2.67</v>
       </c>
       <c r="AD16">
         <v>1.44</v>
       </c>
       <c r="AE16">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF16">
         <v>1.62</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK16">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3083,10 +3083,10 @@
         <v>4.4</v>
       </c>
       <c r="O17">
-        <v>3.95</v>
+        <v>3.81</v>
       </c>
       <c r="P17">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="Q17">
         <v>4.12</v>
@@ -3119,10 +3119,10 @@
         <v>5</v>
       </c>
       <c r="AA17">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB17">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AC17">
         <v>2.23</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O18">
-        <v>3.76</v>
+        <v>3.9</v>
       </c>
       <c r="P18">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="Q18">
         <v>3.58</v>
@@ -3270,37 +3270,37 @@
         <v>1.57</v>
       </c>
       <c r="W18">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z18">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="AA18">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AB18">
         <v>2.25</v>
       </c>
       <c r="AC18">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AD18">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AE18">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF18">
         <v>1.5</v>
       </c>
       <c r="AG18">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK18">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,7 +3409,7 @@
         <v>2.62</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
         <v>2.3</v>
@@ -3421,10 +3421,10 @@
         <v>2.14</v>
       </c>
       <c r="S19">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U19">
         <v>2.62</v>
@@ -3433,7 +3433,7 @@
         <v>1.4</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
         <v>1.03</v>
@@ -3442,19 +3442,19 @@
         <v>1.24</v>
       </c>
       <c r="Z19">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA19">
         <v>2</v>
       </c>
       <c r="AB19">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AC19">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD19">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE19">
         <v>1.07</v>
@@ -3569,25 +3569,25 @@
         </is>
       </c>
       <c r="N20">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="O20">
         <v>4.7</v>
       </c>
       <c r="P20">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="Q20">
-        <v>4.29</v>
+        <v>4.32</v>
       </c>
       <c r="R20">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="S20">
         <v>1.22</v>
       </c>
       <c r="T20">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U20">
         <v>2.19</v>
@@ -3605,19 +3605,19 @@
         <v>1.08</v>
       </c>
       <c r="Z20">
-        <v>6.02</v>
+        <v>6</v>
       </c>
       <c r="AA20">
         <v>1.39</v>
       </c>
       <c r="AB20">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AC20">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AD20">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE20">
         <v>1.24</v>
@@ -3642,7 +3642,7 @@
         <v>1.15</v>
       </c>
       <c r="AK20">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="R21">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="S21">
         <v>1.45</v>
@@ -3771,10 +3771,10 @@
         <v>2.9</v>
       </c>
       <c r="AA21">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AB21">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC21">
         <v>3.58</v>
@@ -3789,7 +3789,7 @@
         <v>2.15</v>
       </c>
       <c r="AG21">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK21">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>3.1</v>
       </c>
       <c r="R22">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S22">
         <v>1.3</v>
@@ -3925,28 +3925,28 @@
         <v>1.08</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
         <v>1.22</v>
       </c>
       <c r="Z22">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA22">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB22">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC22">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="AD22">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE22">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF22">
         <v>1.62</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="O23">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P23">
-        <v>3.2</v>
+        <v>2.43</v>
       </c>
       <c r="Q23">
-        <v>2.64</v>
+        <v>3.32</v>
       </c>
       <c r="R23">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="S23">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U23">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V23">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W23">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="Z23">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA23">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB23">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AC23">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AD23">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AE23">
         <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK23">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,80 +4221,80 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="O24">
         <v>3.2</v>
       </c>
       <c r="P24">
-        <v>2.41</v>
+        <v>3.25</v>
       </c>
       <c r="Q24">
-        <v>3.32</v>
+        <v>2.7</v>
       </c>
       <c r="R24">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="S24">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T24">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U24">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V24">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
+        <v>1.3</v>
+      </c>
+      <c r="Z24">
+        <v>3.4</v>
+      </c>
+      <c r="AA24">
+        <v>1.88</v>
+      </c>
+      <c r="AB24">
+        <v>1.89</v>
+      </c>
+      <c r="AC24">
+        <v>2.97</v>
+      </c>
+      <c r="AD24">
+        <v>1.3</v>
+      </c>
+      <c r="AE24">
+        <v>1.08</v>
+      </c>
+      <c r="AF24">
+        <v>1.75</v>
+      </c>
+      <c r="AG24">
+        <v>2</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
         <v>1.25</v>
       </c>
-      <c r="Z24">
-        <v>3.5</v>
-      </c>
-      <c r="AA24">
-        <v>1.93</v>
-      </c>
-      <c r="AB24">
-        <v>1.91</v>
-      </c>
-      <c r="AC24">
-        <v>2.88</v>
-      </c>
-      <c r="AD24">
-        <v>1.32</v>
-      </c>
-      <c r="AE24">
-        <v>1.1</v>
-      </c>
-      <c r="AF24">
-        <v>1.67</v>
-      </c>
-      <c r="AG24">
-        <v>2.15</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.3</v>
-      </c>
       <c r="AK24">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O26">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P26">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="Q26">
         <v>2.52</v>
@@ -4565,13 +4565,13 @@
         <v>1.33</v>
       </c>
       <c r="T26">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="U26">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W26">
         <v>1.06</v>
@@ -4580,7 +4580,7 @@
         <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
         <v>3.5</v>
@@ -4595,16 +4595,16 @@
         <v>3.1</v>
       </c>
       <c r="AD26">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE26">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF26">
         <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,31 +4710,31 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.33</v>
+        <v>1.97</v>
       </c>
       <c r="O27">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="P27">
-        <v>2.75</v>
+        <v>3.17</v>
       </c>
       <c r="Q27">
-        <v>3.14</v>
+        <v>2.29</v>
       </c>
       <c r="R27">
-        <v>2.13</v>
+        <v>2.51</v>
       </c>
       <c r="S27">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="T27">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U27">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="V27">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W27">
         <v>1.1</v>
@@ -4743,31 +4743,31 @@
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z27">
-        <v>3.42</v>
+        <v>4.4</v>
       </c>
       <c r="AA27">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AB27">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AC27">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AD27">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="AF27">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG27">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK27">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O28">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P28">
-        <v>3.07</v>
+        <v>2.7</v>
       </c>
       <c r="Q28">
-        <v>2.29</v>
+        <v>3.14</v>
       </c>
       <c r="R28">
-        <v>2.51</v>
+        <v>2.13</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="T28">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U28">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="V28">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
         <v>1.1</v>
@@ -4906,47 +4906,47 @@
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z28">
-        <v>4.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA28">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AB28">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC28">
-        <v>2.33</v>
+        <v>3.1</v>
       </c>
       <c r="AD28">
+        <v>1.3</v>
+      </c>
+      <c r="AE28">
+        <v>1.06</v>
+      </c>
+      <c r="AF28">
+        <v>1.57</v>
+      </c>
+      <c r="AG28">
+        <v>2.38</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>1.28</v>
+      </c>
+      <c r="AK28">
         <v>1.5</v>
-      </c>
-      <c r="AE28">
-        <v>1.21</v>
-      </c>
-      <c r="AF28">
-        <v>1.5</v>
-      </c>
-      <c r="AG28">
-        <v>2.42</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.2</v>
-      </c>
-      <c r="AK28">
-        <v>1.87</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
+        <v>3.13</v>
+      </c>
+      <c r="O29">
+        <v>3.47</v>
+      </c>
+      <c r="P29">
+        <v>2.2</v>
+      </c>
+      <c r="Q29">
+        <v>3.35</v>
+      </c>
+      <c r="R29">
+        <v>2.27</v>
+      </c>
+      <c r="S29">
+        <v>1.36</v>
+      </c>
+      <c r="T29">
+        <v>3.17</v>
+      </c>
+      <c r="U29">
+        <v>2.78</v>
+      </c>
+      <c r="V29">
+        <v>1.5</v>
+      </c>
+      <c r="W29">
+        <v>1.12</v>
+      </c>
+      <c r="X29">
+        <v>1.02</v>
+      </c>
+      <c r="Y29">
+        <v>1.27</v>
+      </c>
+      <c r="Z29">
+        <v>3.5</v>
+      </c>
+      <c r="AA29">
+        <v>1.8</v>
+      </c>
+      <c r="AB29">
+        <v>2</v>
+      </c>
+      <c r="AC29">
+        <v>3.17</v>
+      </c>
+      <c r="AD29">
+        <v>1.4</v>
+      </c>
+      <c r="AE29">
         <v>1.14</v>
       </c>
-      <c r="O29">
-        <v>6.5</v>
-      </c>
-      <c r="P29">
-        <v>10</v>
-      </c>
-      <c r="Q29">
-        <v>1.53</v>
-      </c>
-      <c r="R29">
-        <v>3.42</v>
-      </c>
-      <c r="S29">
-        <v>1.17</v>
-      </c>
-      <c r="T29">
-        <v>4.8</v>
-      </c>
-      <c r="U29">
-        <v>1.91</v>
-      </c>
-      <c r="V29">
-        <v>1.8</v>
-      </c>
-      <c r="W29">
+      <c r="AF29">
+        <v>1.57</v>
+      </c>
+      <c r="AG29">
+        <v>2.3</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
         <v>1.22</v>
       </c>
-      <c r="X29">
-        <v>1.01</v>
-      </c>
-      <c r="Y29">
-        <v>1.08</v>
-      </c>
-      <c r="Z29">
-        <v>6.88</v>
-      </c>
-      <c r="AA29">
+      <c r="AK29">
         <v>1.3</v>
-      </c>
-      <c r="AB29">
-        <v>3.5</v>
-      </c>
-      <c r="AC29">
-        <v>1.9</v>
-      </c>
-      <c r="AD29">
-        <v>2.09</v>
-      </c>
-      <c r="AE29">
-        <v>1.45</v>
-      </c>
-      <c r="AF29">
-        <v>1.66</v>
-      </c>
-      <c r="AG29">
-        <v>2.06</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.02</v>
-      </c>
-      <c r="AK29">
-        <v>3.94</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>3</v>
+        <v>1.15</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="P30">
-        <v>2.2</v>
+        <v>9.5</v>
       </c>
       <c r="Q30">
-        <v>3.35</v>
+        <v>1.5</v>
       </c>
       <c r="R30">
-        <v>2.27</v>
+        <v>3.41</v>
       </c>
       <c r="S30">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T30">
-        <v>3.22</v>
+        <v>4.8</v>
       </c>
       <c r="U30">
-        <v>2.58</v>
+        <v>1.75</v>
       </c>
       <c r="V30">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="W30">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="X30">
+        <v>1.01</v>
+      </c>
+      <c r="Y30">
+        <v>1.06</v>
+      </c>
+      <c r="Z30">
+        <v>6.88</v>
+      </c>
+      <c r="AA30">
+        <v>1.24</v>
+      </c>
+      <c r="AB30">
+        <v>3.14</v>
+      </c>
+      <c r="AC30">
+        <v>1.73</v>
+      </c>
+      <c r="AD30">
+        <v>2.18</v>
+      </c>
+      <c r="AE30">
+        <v>1.48</v>
+      </c>
+      <c r="AF30">
+        <v>1.66</v>
+      </c>
+      <c r="AG30">
+        <v>2.18</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
         <v>1.02</v>
       </c>
-      <c r="Y30">
-        <v>1.23</v>
-      </c>
-      <c r="Z30">
-        <v>4.2</v>
-      </c>
-      <c r="AA30">
-        <v>1.72</v>
-      </c>
-      <c r="AB30">
-        <v>2.1</v>
-      </c>
-      <c r="AC30">
-        <v>2.88</v>
-      </c>
-      <c r="AD30">
-        <v>1.4</v>
-      </c>
-      <c r="AE30">
-        <v>1.14</v>
-      </c>
-      <c r="AF30">
-        <v>1.57</v>
-      </c>
-      <c r="AG30">
-        <v>2.3</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.22</v>
-      </c>
       <c r="AK30">
-        <v>1.3</v>
+        <v>3.94</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,25 +5362,25 @@
         </is>
       </c>
       <c r="N31">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="O31">
-        <v>3.51</v>
+        <v>3.18</v>
       </c>
       <c r="P31">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Q31">
         <v>5.32</v>
       </c>
       <c r="R31">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S31">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T31">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="U31">
         <v>3.31</v>
@@ -5392,16 +5392,16 @@
         <v>1.03</v>
       </c>
       <c r="X31">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z31">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AA31">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AB31">
         <v>1.57</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>2.14</v>
+        <v>1.3</v>
       </c>
       <c r="AK31">
         <v>1.13</v>
@@ -5528,19 +5528,19 @@
         <v>4.3</v>
       </c>
       <c r="O32">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="P32">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Q32">
-        <v>4.88</v>
+        <v>4.99</v>
       </c>
       <c r="R32">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
         <v>3.26</v>
@@ -5552,7 +5552,7 @@
         <v>1.52</v>
       </c>
       <c r="W32">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
         <v>1.02</v>
@@ -5576,10 +5576,10 @@
         <v>1.44</v>
       </c>
       <c r="AE32">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF32">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG32">
         <v>2.16</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
         <v>1.2</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="O33">
         <v>3.9</v>
@@ -5697,10 +5697,10 @@
         <v>5.5</v>
       </c>
       <c r="Q33">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R33">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S33">
         <v>1.42</v>
@@ -5718,7 +5718,7 @@
         <v>1.05</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
         <v>1.3</v>
@@ -5733,19 +5733,19 @@
         <v>1.75</v>
       </c>
       <c r="AC33">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD33">
         <v>1.22</v>
       </c>
       <c r="AE33">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF33">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG33">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK33">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
+        <v>3.4</v>
+      </c>
+      <c r="O34">
+        <v>3.5</v>
+      </c>
+      <c r="P34">
+        <v>2.09</v>
+      </c>
+      <c r="Q34">
         <v>3.75</v>
       </c>
-      <c r="O34">
-        <v>3.65</v>
-      </c>
-      <c r="P34">
-        <v>1.91</v>
-      </c>
-      <c r="Q34">
-        <v>4</v>
-      </c>
       <c r="R34">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S34">
         <v>1.26</v>
@@ -5890,7 +5890,7 @@
         <v>4.45</v>
       </c>
       <c r="AA34">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB34">
         <v>2.29</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="O35">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="P35">
         <v>4.18</v>
@@ -6044,7 +6044,7 @@
         <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
         <v>1.31</v>
@@ -6059,7 +6059,7 @@
         <v>1.83</v>
       </c>
       <c r="AC35">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="AD35">
         <v>1.32</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK35">
         <v>1.9</v>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="O36">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="Q36">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R36">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="S36">
         <v>1.36</v>
@@ -6201,7 +6201,7 @@
         <v>2.6</v>
       </c>
       <c r="V36">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W36">
         <v>1.08</v>
@@ -6213,7 +6213,7 @@
         <v>1.27</v>
       </c>
       <c r="Z36">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA36">
         <v>1.9</v>
@@ -6228,10 +6228,10 @@
         <v>1.35</v>
       </c>
       <c r="AE36">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF36">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG36">
         <v>2.1</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK36">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="O37">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="P37">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q37">
         <v>1.63</v>
@@ -6361,10 +6361,10 @@
         <v>4</v>
       </c>
       <c r="U37">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="V37">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W37">
         <v>1.18</v>
@@ -6373,28 +6373,28 @@
         <v>1</v>
       </c>
       <c r="Y37">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z37">
-        <v>6.47</v>
+        <v>7.17</v>
       </c>
       <c r="AA37">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB37">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="AC37">
-        <v>2.07</v>
+        <v>1.82</v>
       </c>
       <c r="AD37">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AE37">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AF37">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG37">
         <v>2</v>
@@ -6413,7 +6413,7 @@
         <v>1.13</v>
       </c>
       <c r="AK37">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>3.8</v>
       </c>
       <c r="P38">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="Q38">
         <v>2.06</v>
@@ -6542,10 +6542,10 @@
         <v>3.9</v>
       </c>
       <c r="AA38">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB38">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC38">
         <v>2.6</v>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="O39">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="P39">
         <v>3.25</v>
@@ -6690,7 +6690,7 @@
         <v>2.22</v>
       </c>
       <c r="V39">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W39">
         <v>1.17</v>
@@ -6699,10 +6699,10 @@
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z39">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA39">
         <v>1.49</v>
@@ -6714,10 +6714,10 @@
         <v>2.26</v>
       </c>
       <c r="AD39">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE39">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF39">
         <v>1.44</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O40">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P40">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="Q40">
         <v>2.01</v>
@@ -6874,19 +6874,19 @@
         <v>2.87</v>
       </c>
       <c r="AC40">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD40">
         <v>1.73</v>
       </c>
       <c r="AE40">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AF40">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG40">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O41">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="P41">
-        <v>4.28</v>
+        <v>4.37</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -7016,10 +7016,10 @@
         <v>2.35</v>
       </c>
       <c r="V41">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="W41">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X41">
         <v>1.01</v>
@@ -7028,7 +7028,7 @@
         <v>1.14</v>
       </c>
       <c r="Z41">
-        <v>4.75</v>
+        <v>5.1</v>
       </c>
       <c r="AA41">
         <v>1.53</v>
@@ -7043,13 +7043,13 @@
         <v>1.57</v>
       </c>
       <c r="AE41">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF41">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AG41">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="O42">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="P42">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="Q42">
         <v>1.83</v>
@@ -7176,13 +7176,13 @@
         <v>5.4</v>
       </c>
       <c r="U42">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V42">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="W42">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X42">
         <v>0</v>
@@ -7194,19 +7194,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AA42">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AB42">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AC42">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AD42">
         <v>2.45</v>
       </c>
       <c r="AE42">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AF42">
         <v>1.3</v>
@@ -7318,25 +7318,25 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="O43">
-        <v>4.17</v>
+        <v>4.04</v>
       </c>
       <c r="P43">
-        <v>3.35</v>
+        <v>2.63</v>
       </c>
       <c r="Q43">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="R43">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="S43">
         <v>1.18</v>
       </c>
       <c r="T43">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U43">
         <v>1.92</v>
@@ -7357,10 +7357,10 @@
         <v>7</v>
       </c>
       <c r="AA43">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AB43">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AC43">
         <v>1.92</v>
@@ -7372,10 +7372,10 @@
         <v>1.33</v>
       </c>
       <c r="AF43">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AG43">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.2</v>
       </c>
       <c r="AK43">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8788,13 +8788,13 @@
         <v>1.95</v>
       </c>
       <c r="O52">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P52">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q52">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="R52">
         <v>2.4</v>
@@ -8827,7 +8827,7 @@
         <v>1.83</v>
       </c>
       <c r="AB52">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC52">
         <v>3.1</v>
@@ -8842,7 +8842,7 @@
         <v>1.67</v>
       </c>
       <c r="AG52">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8948,16 +8948,16 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="O53">
         <v>3.6</v>
       </c>
       <c r="P53">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="Q53">
-        <v>3.09</v>
+        <v>3.02</v>
       </c>
       <c r="R53">
         <v>2.3</v>
@@ -9021,7 +9021,7 @@
         <v>1.3</v>
       </c>
       <c r="AK53">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9114,10 +9114,10 @@
         <v>2.61</v>
       </c>
       <c r="O54">
-        <v>3.83</v>
+        <v>3.6</v>
       </c>
       <c r="P54">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="Q54">
         <v>3.3</v>
@@ -9153,7 +9153,7 @@
         <v>1.53</v>
       </c>
       <c r="AB54">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="AC54">
         <v>2.45</v>
@@ -9274,10 +9274,10 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="O55">
-        <v>3.86</v>
+        <v>3.76</v>
       </c>
       <c r="P55">
         <v>2.95</v>
@@ -9298,10 +9298,10 @@
         <v>2.15</v>
       </c>
       <c r="V55">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W55">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X55">
         <v>1.01</v>
@@ -9316,13 +9316,13 @@
         <v>1.49</v>
       </c>
       <c r="AB55">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AC55">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="AD55">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AE55">
         <v>1.25</v>
@@ -9437,19 +9437,19 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="O56">
-        <v>3.73</v>
+        <v>4.02</v>
       </c>
       <c r="P56">
-        <v>3.75</v>
+        <v>4.12</v>
       </c>
       <c r="Q56">
         <v>2.25</v>
       </c>
       <c r="R56">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="S56">
         <v>1.25</v>
@@ -9461,7 +9461,7 @@
         <v>2.19</v>
       </c>
       <c r="V56">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W56">
         <v>1.13</v>
@@ -9470,28 +9470,28 @@
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z56">
-        <v>4.93</v>
+        <v>4.83</v>
       </c>
       <c r="AA56">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AB56">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AC56">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AD56">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE56">
         <v>1.2</v>
       </c>
       <c r="AF56">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AG56">
         <v>2.31</v>
@@ -9603,13 +9603,13 @@
         <v>1.88</v>
       </c>
       <c r="O57">
-        <v>3.95</v>
+        <v>4.06</v>
       </c>
       <c r="P57">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="Q57">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R57">
         <v>2.66</v>
@@ -9624,7 +9624,7 @@
         <v>2</v>
       </c>
       <c r="V57">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W57">
         <v>1.17</v>
@@ -9639,25 +9639,25 @@
         <v>6.5</v>
       </c>
       <c r="AA57">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AB57">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AC57">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="AD57">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AE57">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AF57">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG57">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,25 +9763,25 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="O58">
-        <v>5.05</v>
+        <v>4.8</v>
       </c>
       <c r="P58">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q58">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R58">
         <v>3.12</v>
       </c>
       <c r="S58">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="T58">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="U58">
         <v>1.75</v>
@@ -9796,28 +9796,28 @@
         <v>0</v>
       </c>
       <c r="Y58">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z58">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA58">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB58">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AC58">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AD58">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AE58">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF58">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AG58">
         <v>3.1</v>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK58">
         <v>2.3</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="O59">
         <v>5.1</v>
       </c>
       <c r="P59">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Q59">
         <v>1.8</v>
@@ -9980,10 +9980,10 @@
         <v>1.36</v>
       </c>
       <c r="AF59">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG59">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10092,28 +10092,28 @@
         <v>2.2</v>
       </c>
       <c r="O60">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="P60">
-        <v>2.53</v>
+        <v>2.94</v>
       </c>
       <c r="Q60">
-        <v>2.61</v>
+        <v>2.82</v>
       </c>
       <c r="R60">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="S60">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T60">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="U60">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V60">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W60">
         <v>1.14</v>
@@ -10122,22 +10122,22 @@
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z60">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA60">
         <v>1.57</v>
       </c>
       <c r="AB60">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AC60">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AD60">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE60">
         <v>1.2</v>
@@ -10146,7 +10146,7 @@
         <v>1.5</v>
       </c>
       <c r="AG60">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>1.35</v>
       </c>
       <c r="AK60">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="O61">
         <v>4.8</v>
       </c>
       <c r="P61">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="Q61">
         <v>1.73</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="O62">
         <v>3.8</v>
@@ -10424,10 +10424,10 @@
         <v>4</v>
       </c>
       <c r="Q62">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="R62">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S62">
         <v>1.25</v>
@@ -10436,7 +10436,7 @@
         <v>3.4</v>
       </c>
       <c r="U62">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="V62">
         <v>1.53</v>
@@ -10457,13 +10457,13 @@
         <v>1.67</v>
       </c>
       <c r="AB62">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AC62">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD62">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AE62">
         <v>1.2</v>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK62">
         <v>1.85</v>

--- a/jogos_2026-10-28.xlsx
+++ b/jogos_2026-10-28.xlsx
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1928,14 +1928,14 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57", "72"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+5"]</t>
         </is>
       </c>
       <c r="AJ10">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2091,33 +2091,33 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="O11">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P11">
         <v>3.75</v>
       </c>
       <c r="Q11">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="R11">
         <v>1.85</v>
       </c>
       <c r="S11">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="T11">
         <v>2.4</v>
@@ -2132,77 +2132,77 @@
         <v>1.02</v>
       </c>
       <c r="X11">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Y11">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="Z11">
         <v>2.55</v>
       </c>
       <c r="AA11">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB11">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AC11">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AD11">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF11">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AG11">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["46", "88"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57"]</t>
         </is>
       </c>
       <c r="AJ11">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK11">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2245,23 +2245,23 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "78"]</t>
         </is>
       </c>
       <c r="AJ12">
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2420,11 +2420,11 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["79", "82"]</t>
         </is>
       </c>
       <c r="AJ13">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
@@ -2670,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2731,26 +2731,26 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "27"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "60", "62", "86"]</t>
         </is>
       </c>
       <c r="AJ15">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,26 +2894,26 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2978,12 +2978,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26", "40", "80"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53", "57", "69"]</t>
         </is>
       </c>
       <c r="AJ16">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3048,22 +3048,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3072,115 +3072,115 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="O17">
-        <v>3.81</v>
+        <v>3.9</v>
       </c>
       <c r="P17">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="Q17">
-        <v>4.12</v>
+        <v>3.58</v>
       </c>
       <c r="R17">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S17">
         <v>1.25</v>
       </c>
       <c r="T17">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U17">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V17">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W17">
+        <v>1.1</v>
+      </c>
+      <c r="X17">
+        <v>1.02</v>
+      </c>
+      <c r="Y17">
         <v>1.15</v>
       </c>
-      <c r="X17">
-        <v>1.01</v>
-      </c>
-      <c r="Y17">
-        <v>1.13</v>
-      </c>
       <c r="Z17">
+        <v>4.8</v>
+      </c>
+      <c r="AA17">
+        <v>1.59</v>
+      </c>
+      <c r="AB17">
+        <v>2.25</v>
+      </c>
+      <c r="AC17">
+        <v>2.43</v>
+      </c>
+      <c r="AD17">
+        <v>1.44</v>
+      </c>
+      <c r="AE17">
+        <v>1.14</v>
+      </c>
+      <c r="AF17">
+        <v>1.5</v>
+      </c>
+      <c r="AG17">
+        <v>2.4</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>["39"]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>["59"]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>1.2</v>
+      </c>
+      <c r="AK17">
+        <v>1.22</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
         <v>5</v>
       </c>
-      <c r="AA17">
-        <v>1.57</v>
-      </c>
-      <c r="AB17">
-        <v>2.31</v>
-      </c>
-      <c r="AC17">
-        <v>2.23</v>
-      </c>
-      <c r="AD17">
-        <v>1.56</v>
-      </c>
-      <c r="AE17">
-        <v>1.2</v>
-      </c>
-      <c r="AF17">
-        <v>1.53</v>
-      </c>
-      <c r="AG17">
-        <v>2.3</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.17</v>
-      </c>
-      <c r="AK17">
-        <v>1.14</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>-1</v>
-      </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3211,139 +3211,139 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="O18">
-        <v>3.9</v>
+        <v>3.81</v>
       </c>
       <c r="P18">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="Q18">
-        <v>3.58</v>
+        <v>4.12</v>
       </c>
       <c r="R18">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S18">
         <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U18">
+        <v>2.2</v>
+      </c>
+      <c r="V18">
+        <v>1.62</v>
+      </c>
+      <c r="W18">
+        <v>1.15</v>
+      </c>
+      <c r="X18">
+        <v>1.01</v>
+      </c>
+      <c r="Y18">
+        <v>1.13</v>
+      </c>
+      <c r="Z18">
+        <v>5</v>
+      </c>
+      <c r="AA18">
+        <v>1.57</v>
+      </c>
+      <c r="AB18">
+        <v>2.31</v>
+      </c>
+      <c r="AC18">
+        <v>2.23</v>
+      </c>
+      <c r="AD18">
+        <v>1.56</v>
+      </c>
+      <c r="AE18">
+        <v>1.2</v>
+      </c>
+      <c r="AF18">
+        <v>1.53</v>
+      </c>
+      <c r="AG18">
         <v>2.3</v>
       </c>
-      <c r="V18">
-        <v>1.57</v>
-      </c>
-      <c r="W18">
-        <v>1.1</v>
-      </c>
-      <c r="X18">
-        <v>1.02</v>
-      </c>
-      <c r="Y18">
-        <v>1.15</v>
-      </c>
-      <c r="Z18">
-        <v>4.8</v>
-      </c>
-      <c r="AA18">
-        <v>1.59</v>
-      </c>
-      <c r="AB18">
-        <v>2.25</v>
-      </c>
-      <c r="AC18">
-        <v>2.43</v>
-      </c>
-      <c r="AD18">
-        <v>1.44</v>
-      </c>
-      <c r="AE18">
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>["4", "12", "67"]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.17</v>
+      </c>
+      <c r="AK18">
         <v>1.14</v>
       </c>
-      <c r="AF18">
-        <v>1.5</v>
-      </c>
-      <c r="AG18">
-        <v>2.4</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.2</v>
-      </c>
-      <c r="AK18">
-        <v>1.22</v>
-      </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3386,23 +3386,23 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "56", "90+7"]</t>
         </is>
       </c>
       <c r="AJ19">
@@ -3485,28 +3485,28 @@
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
@@ -3648,28 +3648,28 @@
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -3721,14 +3721,14 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67"]</t>
         </is>
       </c>
       <c r="AJ21">
@@ -3811,28 +3811,28 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3872,16 +3872,16 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38"]</t>
         </is>
       </c>
       <c r="AJ22">
@@ -3974,28 +3974,28 @@
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -4050,11 +4050,11 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87"]</t>
         </is>
       </c>
       <c r="AJ23">
@@ -4137,28 +4137,28 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -4210,14 +4210,14 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["83", "90"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+5"]</t>
         </is>
       </c>
       <c r="AJ24">
@@ -4300,28 +4300,28 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,43 +4873,43 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.35</v>
+        <v>3.13</v>
       </c>
       <c r="O28">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="P28">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="Q28">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="R28">
-        <v>2.13</v>
+        <v>2.27</v>
       </c>
       <c r="S28">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T28">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="U28">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W28">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z28">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA28">
         <v>1.8</v>
@@ -4918,19 +4918,19 @@
         <v>2</v>
       </c>
       <c r="AC28">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="AD28">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE28">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF28">
         <v>1.57</v>
       </c>
       <c r="AG28">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.13</v>
+        <v>1.15</v>
       </c>
       <c r="O29">
-        <v>3.47</v>
+        <v>6.5</v>
       </c>
       <c r="P29">
-        <v>2.2</v>
+        <v>9.5</v>
       </c>
       <c r="Q29">
-        <v>3.35</v>
+        <v>1.5</v>
       </c>
       <c r="R29">
-        <v>2.27</v>
+        <v>3.41</v>
       </c>
       <c r="S29">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="T29">
-        <v>3.17</v>
+        <v>4.8</v>
       </c>
       <c r="U29">
-        <v>2.78</v>
+        <v>1.75</v>
       </c>
       <c r="V29">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="W29">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="X29">
+        <v>1.01</v>
+      </c>
+      <c r="Y29">
+        <v>1.06</v>
+      </c>
+      <c r="Z29">
+        <v>6.88</v>
+      </c>
+      <c r="AA29">
+        <v>1.24</v>
+      </c>
+      <c r="AB29">
+        <v>3.14</v>
+      </c>
+      <c r="AC29">
+        <v>1.73</v>
+      </c>
+      <c r="AD29">
+        <v>2.18</v>
+      </c>
+      <c r="AE29">
+        <v>1.48</v>
+      </c>
+      <c r="AF29">
+        <v>1.66</v>
+      </c>
+      <c r="AG29">
+        <v>2.18</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
         <v>1.02</v>
       </c>
-      <c r="Y29">
-        <v>1.27</v>
-      </c>
-      <c r="Z29">
-        <v>3.5</v>
-      </c>
-      <c r="AA29">
-        <v>1.8</v>
-      </c>
-      <c r="AB29">
-        <v>2</v>
-      </c>
-      <c r="AC29">
-        <v>3.17</v>
-      </c>
-      <c r="AD29">
-        <v>1.4</v>
-      </c>
-      <c r="AE29">
-        <v>1.14</v>
-      </c>
-      <c r="AF29">
-        <v>1.57</v>
-      </c>
-      <c r="AG29">
-        <v>2.3</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.22</v>
-      </c>
       <c r="AK29">
-        <v>1.3</v>
+        <v>3.94</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.15</v>
+        <v>2.35</v>
       </c>
       <c r="O30">
-        <v>6.5</v>
+        <v>3.45</v>
       </c>
       <c r="P30">
-        <v>9.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q30">
-        <v>1.5</v>
+        <v>3.14</v>
       </c>
       <c r="R30">
-        <v>3.41</v>
+        <v>2.13</v>
       </c>
       <c r="S30">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="T30">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="U30">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="V30">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="W30">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
+        <v>1.21</v>
+      </c>
+      <c r="Z30">
+        <v>3.42</v>
+      </c>
+      <c r="AA30">
+        <v>1.8</v>
+      </c>
+      <c r="AB30">
+        <v>2</v>
+      </c>
+      <c r="AC30">
+        <v>3.1</v>
+      </c>
+      <c r="AD30">
+        <v>1.3</v>
+      </c>
+      <c r="AE30">
         <v>1.06</v>
       </c>
-      <c r="Z30">
-        <v>6.88</v>
-      </c>
-      <c r="AA30">
-        <v>1.24</v>
-      </c>
-      <c r="AB30">
-        <v>3.14</v>
-      </c>
-      <c r="AC30">
-        <v>1.73</v>
-      </c>
-      <c r="AD30">
-        <v>2.18</v>
-      </c>
-      <c r="AE30">
-        <v>1.48</v>
-      </c>
       <c r="AF30">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AG30">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="AK30">
-        <v>3.94</v>
+        <v>1.5</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5339,13 +5339,13 @@
         </is>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31">
         <v>0</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "28"]</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
@@ -5441,28 +5441,28 @@
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP31">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -5502,26 +5502,26 @@
         </is>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43"]</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "48", "62", "67"]</t>
         </is>
       </c>
       <c r="AJ32">
@@ -5604,28 +5604,28 @@
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -6017,13 +6017,13 @@
         <v>1.85</v>
       </c>
       <c r="O35">
-        <v>3.54</v>
+        <v>3.45</v>
       </c>
       <c r="P35">
         <v>4.18</v>
       </c>
       <c r="Q35">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="R35">
         <v>2.11</v>
@@ -6032,19 +6032,19 @@
         <v>1.36</v>
       </c>
       <c r="T35">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="U35">
         <v>2.63</v>
       </c>
       <c r="V35">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W35">
         <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
         <v>1.31</v>
@@ -6059,7 +6059,7 @@
         <v>1.83</v>
       </c>
       <c r="AC35">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="AD35">
         <v>1.32</v>
@@ -6177,16 +6177,16 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O36">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P36">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q36">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="R36">
         <v>2.13</v>
@@ -6201,37 +6201,37 @@
         <v>2.6</v>
       </c>
       <c r="V36">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W36">
         <v>1.08</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
         <v>3.58</v>
       </c>
       <c r="AA36">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AB36">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AC36">
-        <v>3.09</v>
+        <v>2.94</v>
       </c>
       <c r="AD36">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE36">
         <v>1.09</v>
       </c>
       <c r="AF36">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG36">
         <v>2.1</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK36">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="O37">
         <v>6.25</v>
       </c>
       <c r="P37">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="Q37">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="R37">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="S37">
+        <v>1.18</v>
+      </c>
+      <c r="T37">
+        <v>4.4</v>
+      </c>
+      <c r="U37">
+        <v>1.94</v>
+      </c>
+      <c r="V37">
+        <v>1.81</v>
+      </c>
+      <c r="W37">
         <v>1.22</v>
-      </c>
-      <c r="T37">
-        <v>4</v>
-      </c>
-      <c r="U37">
-        <v>1.93</v>
-      </c>
-      <c r="V37">
-        <v>1.69</v>
-      </c>
-      <c r="W37">
-        <v>1.18</v>
       </c>
       <c r="X37">
         <v>1</v>
       </c>
       <c r="Y37">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z37">
         <v>7.17</v>
       </c>
       <c r="AA37">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AB37">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AC37">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AD37">
-        <v>1.76</v>
+        <v>2.01</v>
       </c>
       <c r="AE37">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AF37">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG37">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.13</v>
       </c>
       <c r="AK37">
-        <v>3.29</v>
+        <v>3.39</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O38">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P38">
         <v>5.1</v>
@@ -6515,19 +6515,19 @@
         <v>2.06</v>
       </c>
       <c r="R38">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
         <v>2.85</v>
       </c>
       <c r="U38">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V38">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W38">
         <v>1.11</v>
@@ -6539,13 +6539,13 @@
         <v>1.19</v>
       </c>
       <c r="Z38">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AA38">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AB38">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC38">
         <v>2.6</v>
@@ -6554,7 +6554,7 @@
         <v>1.43</v>
       </c>
       <c r="AE38">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF38">
         <v>1.75</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O39">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="P39">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="Q39">
         <v>2.38</v>
@@ -6681,16 +6681,16 @@
         <v>2.5</v>
       </c>
       <c r="S39">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T39">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="U39">
         <v>2.22</v>
       </c>
       <c r="V39">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W39">
         <v>1.17</v>
@@ -6699,25 +6699,25 @@
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z39">
-        <v>5.5</v>
+        <v>5.78</v>
       </c>
       <c r="AA39">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AB39">
         <v>2.63</v>
       </c>
       <c r="AC39">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AD39">
         <v>1.69</v>
       </c>
       <c r="AE39">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF39">
         <v>1.44</v>
@@ -6739,7 +6739,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O40">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P40">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="Q40">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="R40">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="S40">
         <v>1.22</v>
@@ -6856,7 +6856,7 @@
         <v>1.7</v>
       </c>
       <c r="W40">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X40">
         <v>0</v>
@@ -6871,19 +6871,19 @@
         <v>1.4</v>
       </c>
       <c r="AB40">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="AC40">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AD40">
         <v>1.73</v>
       </c>
       <c r="AE40">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AF40">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AG40">
         <v>2.63</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK40">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,16 +6992,16 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O41">
-        <v>3.83</v>
+        <v>3.72</v>
       </c>
       <c r="P41">
-        <v>4.37</v>
+        <v>4.1</v>
       </c>
       <c r="Q41">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R41">
         <v>2.38</v>
@@ -7010,46 +7010,46 @@
         <v>1.25</v>
       </c>
       <c r="T41">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U41">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="V41">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="W41">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z41">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA41">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AB41">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AC41">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AD41">
+        <v>1.47</v>
+      </c>
+      <c r="AE41">
+        <v>1.16</v>
+      </c>
+      <c r="AF41">
         <v>1.57</v>
       </c>
-      <c r="AE41">
-        <v>1.22</v>
-      </c>
-      <c r="AF41">
-        <v>1.48</v>
-      </c>
       <c r="AG41">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="O42">
         <v>5</v>
@@ -7164,10 +7164,10 @@
         <v>5.1</v>
       </c>
       <c r="Q42">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="R42">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="S42">
         <v>1.11</v>
@@ -7176,13 +7176,13 @@
         <v>5.4</v>
       </c>
       <c r="U42">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V42">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="W42">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X42">
         <v>0</v>
@@ -7191,19 +7191,19 @@
         <v>1</v>
       </c>
       <c r="Z42">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="AA42">
         <v>1.22</v>
       </c>
       <c r="AB42">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
       <c r="AC42">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AD42">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="AE42">
         <v>1.57</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK42">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7324,7 +7324,7 @@
         <v>4.04</v>
       </c>
       <c r="P43">
-        <v>2.63</v>
+        <v>3.12</v>
       </c>
       <c r="Q43">
         <v>2.46</v>
@@ -7357,7 +7357,7 @@
         <v>7</v>
       </c>
       <c r="AA43">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AB43">
         <v>2.78</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK43">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8785,34 +8785,34 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="O52">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P52">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q52">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R52">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="S52">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
         <v>3.25</v>
       </c>
       <c r="U52">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="V52">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
         <v>1.02</v>
@@ -8821,28 +8821,28 @@
         <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA52">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AB52">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC52">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD52">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE52">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF52">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG52">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.22</v>
       </c>
       <c r="AK52">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8951,16 +8951,16 @@
         <v>2.38</v>
       </c>
       <c r="O53">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="P53">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q53">
         <v>3.02</v>
       </c>
       <c r="R53">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S53">
         <v>1.29</v>
@@ -9002,10 +9002,10 @@
         <v>1.14</v>
       </c>
       <c r="AF53">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG53">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK53">
         <v>1.44</v>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="O54">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P54">
         <v>2.2</v>
@@ -9129,7 +9129,7 @@
         <v>1.25</v>
       </c>
       <c r="T54">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U54">
         <v>2.19</v>
@@ -9165,10 +9165,10 @@
         <v>1.2</v>
       </c>
       <c r="AF54">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG54">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>1.25</v>
       </c>
       <c r="AK54">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9277,31 +9277,31 @@
         <v>2.13</v>
       </c>
       <c r="O55">
-        <v>3.76</v>
+        <v>3.82</v>
       </c>
       <c r="P55">
         <v>2.95</v>
       </c>
       <c r="Q55">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R55">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S55">
         <v>1.22</v>
       </c>
       <c r="T55">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U55">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="V55">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="W55">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X55">
         <v>1.01</v>
@@ -9313,19 +9313,19 @@
         <v>6</v>
       </c>
       <c r="AA55">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AB55">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="AC55">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="AD55">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE55">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF55">
         <v>1.4</v>
@@ -9347,7 +9347,7 @@
         <v>1.2</v>
       </c>
       <c r="AK55">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9449,7 +9449,7 @@
         <v>2.25</v>
       </c>
       <c r="R56">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="S56">
         <v>1.25</v>
@@ -9458,10 +9458,10 @@
         <v>3.6</v>
       </c>
       <c r="U56">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="V56">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W56">
         <v>1.13</v>
@@ -9473,7 +9473,7 @@
         <v>1.2</v>
       </c>
       <c r="Z56">
-        <v>4.83</v>
+        <v>4.89</v>
       </c>
       <c r="AA56">
         <v>1.61</v>
@@ -9491,7 +9491,7 @@
         <v>1.2</v>
       </c>
       <c r="AF56">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG56">
         <v>2.31</v>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK56">
         <v>2</v>
@@ -9600,28 +9600,28 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="O57">
-        <v>4.06</v>
+        <v>3.8</v>
       </c>
       <c r="P57">
         <v>3.67</v>
       </c>
       <c r="Q57">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R57">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="S57">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T57">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U57">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V57">
         <v>1.7</v>
@@ -9630,13 +9630,13 @@
         <v>1.17</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z57">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA57">
         <v>1.38</v>
@@ -9645,13 +9645,13 @@
         <v>2.62</v>
       </c>
       <c r="AC57">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="AD57">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AE57">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF57">
         <v>1.4</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK57">
         <v>1.8</v>
@@ -9778,10 +9778,10 @@
         <v>3.12</v>
       </c>
       <c r="S58">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="T58">
-        <v>5.35</v>
+        <v>5.4</v>
       </c>
       <c r="U58">
         <v>1.75</v>
@@ -9802,7 +9802,7 @@
         <v>10</v>
       </c>
       <c r="AA58">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AB58">
         <v>4.2</v>
@@ -9817,7 +9817,7 @@
         <v>1.57</v>
       </c>
       <c r="AF58">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AG58">
         <v>3.1</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK58">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,19 +9926,19 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="O59">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="P59">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="Q59">
         <v>1.8</v>
       </c>
       <c r="R59">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="S59">
         <v>1.14</v>
@@ -9950,7 +9950,7 @@
         <v>1.96</v>
       </c>
       <c r="V59">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="W59">
         <v>1.22</v>
@@ -9965,7 +9965,7 @@
         <v>8</v>
       </c>
       <c r="AA59">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AB59">
         <v>3.25</v>
@@ -10089,19 +10089,19 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O60">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P60">
         <v>2.94</v>
       </c>
       <c r="Q60">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="R60">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S60">
         <v>1.28</v>
@@ -10116,7 +10116,7 @@
         <v>1.52</v>
       </c>
       <c r="W60">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X60">
         <v>1.01</v>
@@ -10128,10 +10128,10 @@
         <v>4.5</v>
       </c>
       <c r="AA60">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB60">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AC60">
         <v>2.63</v>
@@ -10146,7 +10146,7 @@
         <v>1.5</v>
       </c>
       <c r="AG60">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK60">
         <v>1.53</v>
@@ -10261,7 +10261,7 @@
         <v>5.25</v>
       </c>
       <c r="Q61">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="R61">
         <v>2.75</v>
@@ -10273,7 +10273,7 @@
         <v>4.33</v>
       </c>
       <c r="U61">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="V61">
         <v>1.83</v>
@@ -10291,16 +10291,16 @@
         <v>8</v>
       </c>
       <c r="AA61">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB61">
         <v>3.4</v>
       </c>
       <c r="AC61">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AD61">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AE61">
         <v>1.4</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK61">
         <v>2.88</v>
@@ -10415,19 +10415,19 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="O62">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P62">
         <v>4</v>
       </c>
       <c r="Q62">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="R62">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="S62">
         <v>1.25</v>
@@ -10439,10 +10439,10 @@
         <v>2.47</v>
       </c>
       <c r="V62">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W62">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X62">
         <v>1.01</v>
@@ -10466,13 +10466,13 @@
         <v>1.5</v>
       </c>
       <c r="AE62">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF62">
         <v>1.6</v>
       </c>
       <c r="AG62">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.19</v>
       </c>
       <c r="AK62">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AL62">
         <v>0</v>
